--- a/skibi-data.xlsx
+++ b/skibi-data.xlsx
@@ -30,24 +30,24 @@
     <sheet name="waves" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'arcane'!$A$1:$AT$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'arcane'!$A$1:$AU$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'armour_matrix'!$A$1:$F$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'bosses'!$A$1:$O$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'caster_dps'!$A$1:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'caster_dps'!$A$1:$L$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'game_modes'!$A$1:$I$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'hero_ranking'!$A$1:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'heroes'!$A$1:$H$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'military'!$A$1:$AW$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'military'!$A$1:$AX$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'minigame_items'!$A$1:$D$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'minigame_readings'!$A$1:$G$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'minigames'!$A$1:$I$80</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'other_towers'!$A$1:$AU$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'ranger'!$A$1:$AT$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'royal_family'!$A$1:$AZ$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'scarlet_knight'!$A$1:$AT$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'specialist'!$A$1:$AX$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'tempest'!$A$1:$AZ$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'tower_traits'!$A$1:$I$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'other_towers'!$A$1:$AV$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'ranger'!$A$1:$AU$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'royal_family'!$A$1:$BA$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'scarlet_knight'!$A$1:$AU$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'specialist'!$A$1:$AY$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'tempest'!$A$1:$BA$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'tower_traits'!$A$1:$I$113</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'wave_modifiers'!$A$1:$D$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'wave_traits'!$A$1:$K$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'waves'!$A$1:$R$93</definedName>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT18"/>
+  <dimension ref="A1:AU18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -508,6 +508,7 @@
     <col width="9" customWidth="1" min="44" max="44"/>
     <col width="15" customWidth="1" min="45" max="45"/>
     <col width="22" customWidth="1" min="46" max="46"/>
+    <col width="48" customWidth="1" min="47" max="47"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -741,6 +742,11 @@
           <t>dps_per_gold_x_range</t>
         </is>
       </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dps_source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -810,6 +816,11 @@
         <f>IF(D2=0,"",AN2*(N2/725))</f>
         <v/>
       </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -838,7 +849,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Activate / Deactivate Mana Detection (ANcl); Arctic Blast; Cold Snap (AIm2)</t>
+          <t>Activate / Deactivate Mana Detection (ANcl); Arctic Blast (A07S); Cold Snap (AIm2)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -852,6 +863,9 @@
       <c r="AA3" t="n">
         <v>1250</v>
       </c>
+      <c r="AK3" t="n">
+        <v>39.8</v>
+      </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
@@ -879,6 +893,11 @@
         <f>IF(D3=0,"",AN3*(N3/725))</f>
         <v/>
       </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>caster: Arctic Blast (sustained, mana-limited)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -907,7 +926,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Activate / Deactivate Mana Detection (ANcl); Kiss of Flame (AHfa); Combustion</t>
+          <t>Activate / Deactivate Mana Detection (ANcl); Kiss of Flame (AHfa); Combustion (A014)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -948,6 +967,11 @@
         <f>IF(D4=0,"",AN4*(N4/725))</f>
         <v/>
       </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -976,7 +1000,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Activate / Deactivate Mana Detection (ANcl); Combustion; Scald (ANbf)</t>
+          <t>Activate / Deactivate Mana Detection (ANcl); Combustion (A014); Scald (ANbf)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -990,6 +1014,9 @@
       <c r="AA5" t="n">
         <v>1250</v>
       </c>
+      <c r="AK5" t="n">
+        <v>47.3</v>
+      </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
@@ -1017,6 +1044,11 @@
         <f>IF(D5=0,"",AN5*(N5/725))</f>
         <v/>
       </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>caster: Scald (sustained, mana-limited)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1045,7 +1077,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Activate / Deactivate Mana Detection (ANcl); Ball Lightning; Electrify (AIhb)</t>
+          <t>Activate / Deactivate Mana Detection (ANcl); Ball Lightning (A07R); Electrify (AIhb)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1059,6 +1091,9 @@
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
+      <c r="AK6" t="n">
+        <v>48.6</v>
+      </c>
       <c r="AL6" t="n">
         <v>1</v>
       </c>
@@ -1086,6 +1121,11 @@
         <f>IF(D6=0,"",AN6*(N6/725))</f>
         <v/>
       </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>caster: Ball Lightning (sustained, mana-limited)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1155,6 +1195,11 @@
         <f>IF(D7=0,"",AN7*(N7/725))</f>
         <v/>
       </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1178,7 +1223,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Activate / Deactivate Mana Detection (ANcl); Soothe Foundation</t>
+          <t>Activate / Deactivate Mana Detection (ANcl); Soothe Foundation (A080)</t>
         </is>
       </c>
       <c r="Z8" t="n">
@@ -1214,6 +1259,11 @@
         <f>IF(D8=0,"",AN8*(N8/725))</f>
         <v/>
       </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1256,6 +1306,9 @@
       <c r="AA9" t="n">
         <v>1500</v>
       </c>
+      <c r="AK9" t="n">
+        <v>58</v>
+      </c>
       <c r="AL9" t="n">
         <v>1</v>
       </c>
@@ -1283,6 +1336,11 @@
         <f>IF(D9=0,"",AN9*(N9/725))</f>
         <v/>
       </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>caster: Chilly Bits Grade Peorth (sustained, mana-limited)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1352,6 +1410,11 @@
         <f>IF(D10=0,"",AN10*(N10/725))</f>
         <v/>
       </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1380,7 +1443,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Activate / Deactivate Mana Detection (ANcl); Combustion; Fire Volley (Aroc)</t>
+          <t>Activate / Deactivate Mana Detection (ANcl); Combustion (A014); Fire Volley (Aroc)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1484,6 +1547,11 @@
         <f>IF(D11=0,"",AN11*(N11/725))</f>
         <v/>
       </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1512,7 +1580,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Activate / Deactivate Mana Detection (ANcl); Combustion; Burnify (ANic); Ground Critical Strike I</t>
+          <t>Activate / Deactivate Mana Detection (ANcl); Combustion (A014); Burnify (ANic); Ground Critical Strike I (A003)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1616,6 +1684,11 @@
         <f>IF(D12=0,"",AN12*(N12/725))</f>
         <v/>
       </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1658,6 +1731,9 @@
       <c r="AA13" t="n">
         <v>1500</v>
       </c>
+      <c r="AK13" t="n">
+        <v>857.1</v>
+      </c>
       <c r="AL13" t="n">
         <v>1</v>
       </c>
@@ -1685,6 +1761,11 @@
         <f>IF(D13=0,"",AN13*(N13/725))</f>
         <v/>
       </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>caster: Super Shock (sustained, mana-limited)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1713,7 +1794,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Activate / Deactivate Mana Detection (ANcl); Electrify (AIhb); Tsukikaze</t>
+          <t>Activate / Deactivate Mana Detection (ANcl); Electrify (AIhb); Tsukikaze (A07T)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1727,6 +1808,9 @@
       <c r="AA14" t="n">
         <v>1750</v>
       </c>
+      <c r="AK14" t="n">
+        <v>1356.7</v>
+      </c>
       <c r="AL14" t="n">
         <v>1</v>
       </c>
@@ -1754,6 +1838,11 @@
         <f>IF(D14=0,"",AN14*(N14/725))</f>
         <v/>
       </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>caster: Tsukikaze (sustained, mana-limited)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1808,6 +1897,11 @@
         <f>IF(D15=0,"",AN15*(N15/725))</f>
         <v/>
       </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1831,7 +1925,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Arpm; Sacrifice; Upon Death - Mana Well (Asth)</t>
+          <t>Arpm (Arpm); Sacrifice (A07P); Upon Death - Mana Well (Asth)</t>
         </is>
       </c>
       <c r="Z16" t="n">
@@ -1864,6 +1958,11 @@
         <f>IF(D16=0,"",AN16*(N16/725))</f>
         <v/>
       </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1887,7 +1986,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sacrifice; Upon Death - Phoenix (Atru); Phoenix Income (Amgl)</t>
+          <t>Sacrifice (A07P); Upon Death - Phoenix (Atru); Phoenix Income (Amgl)</t>
         </is>
       </c>
       <c r="Z17" t="n">
@@ -1920,6 +2019,11 @@
         <f>IF(D17=0,"",AN17*(N17/725))</f>
         <v/>
       </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1943,7 +2047,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sacrifice; Electromagnetic Aura (AOr2); Upon Death - Unstable Flux (ANca)</t>
+          <t>Sacrifice (A07P); Electromagnetic Aura (AOr2); Upon Death - Unstable Flux (ANca)</t>
         </is>
       </c>
       <c r="Z18" t="n">
@@ -1976,9 +2080,14 @@
         <f>IF(D18=0,"",AN18*(N18/725))</f>
         <v/>
       </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AT18"/>
+  <autoFilter ref="A1:AU18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5392,7 +5501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU15"/>
+  <dimension ref="A1:AV15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5442,6 +5551,7 @@
     <col width="22" customWidth="1" min="45" max="45"/>
     <col width="17" customWidth="1" min="46" max="46"/>
     <col width="27" customWidth="1" min="47" max="47"/>
+    <col width="14" customWidth="1" min="48" max="48"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5680,6 +5790,11 @@
           <t>dps_per_gold_coverage_adj</t>
         </is>
       </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dps_source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5763,7 +5878,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Machine Critical Strike (A03Y); A070; AChv; A028</t>
+          <t>Machine Critical Strike (A03Y); Super Regeneration (A070); Empathic Fix (AChv); Sell Tower (A028)</t>
         </is>
       </c>
       <c r="AL2" t="n">
@@ -5796,6 +5911,11 @@
         <f>IF(C2=0,"",AR2*AT2)</f>
         <v/>
       </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5869,7 +5989,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Vindicator II (A03C); A028</t>
+          <t>Vindicator II (A03C); Sell Tower (A028)</t>
         </is>
       </c>
       <c r="AL3" t="n">
@@ -5902,6 +6022,11 @@
         <f>IF(C3=0,"",AR3*AT3)</f>
         <v/>
       </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5975,7 +6100,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Vindicator II (A03C); Versatile Critical Strike I (A004); A028</t>
+          <t>Vindicator II (A03C); Versatile Critical Strike I (A004); Sell Tower (A028)</t>
         </is>
       </c>
       <c r="AL4" t="n">
@@ -6008,6 +6133,11 @@
         <f>IF(C4=0,"",AR4*AT4)</f>
         <v/>
       </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6081,7 +6211,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Vindicator II (A03C); Versatile Critical Strike II (A01E); A028</t>
+          <t>Vindicator II (A03C); Versatile Critical Strike II (A01E); Sell Tower (A028)</t>
         </is>
       </c>
       <c r="AL5" t="n">
@@ -6114,6 +6244,11 @@
         <f>IF(C5=0,"",AR5*AT5)</f>
         <v/>
       </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6187,7 +6322,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Vindicator III (A02Z); Versatile Critical Strike II (A01E); A028</t>
+          <t>Vindicator III (A02Z); Versatile Critical Strike II (A01E); Sell Tower (A028)</t>
         </is>
       </c>
       <c r="AL6" t="n">
@@ -6220,6 +6355,11 @@
         <f>IF(C6=0,"",AR6*AT6)</f>
         <v/>
       </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6293,7 +6433,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Bash I (ANbh); Vindicator III (A02Z); Versatile Critical Strike II (A01E); A028</t>
+          <t>Bash I (ANbh); Vindicator III (A02Z); Versatile Critical Strike II (A01E); Sell Tower (A028)</t>
         </is>
       </c>
       <c r="AL7" t="n">
@@ -6329,6 +6469,11 @@
         <f>IF(C7=0,"",AR7*AT7)</f>
         <v/>
       </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6412,7 +6557,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Regeneration (A03W); A028; Frost I (Afra)</t>
+          <t>Regeneration (A03W); Sell Tower (A028); Frost I (Afra)</t>
         </is>
       </c>
       <c r="AL8" t="n">
@@ -6445,6 +6590,11 @@
         <f>IF(C8=0,"",AR8*AT8)</f>
         <v/>
       </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6543,7 +6693,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Boss Assassin I (A03D); A028; Air Critical Strike II (A006); Slow Poison II (A008)</t>
+          <t>Boss Assassin I (A03D); Sell Tower (A028); Air Critical Strike II (A006); Slow Poison II (A008)</t>
         </is>
       </c>
       <c r="AL9" t="n">
@@ -6579,6 +6729,11 @@
         <f>IF(C9=0,"",AR9*AT9)</f>
         <v/>
       </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6657,7 +6812,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Bash I (ANbh); A028</t>
+          <t>Bash I (ANbh); Sell Tower (A028)</t>
         </is>
       </c>
       <c r="AL10" t="n">
@@ -6693,6 +6848,11 @@
         <f>IF(C10=0,"",AR10*AT10)</f>
         <v/>
       </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6776,7 +6936,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Afbb; (Dummy Ability - Life Steal) (Aabr); AIva; Versatile Critical Strike II (A01E); A028</t>
+          <t>Sunder Armor (Afbb); (Dummy Ability - Life Steal) (Aabr); AIva (AIva); Versatile Critical Strike II (A01E); Sell Tower (A028)</t>
         </is>
       </c>
       <c r="AL11" t="n">
@@ -6809,6 +6969,11 @@
         <f>IF(C11=0,"",AR11*AT11)</f>
         <v/>
       </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6892,7 +7057,7 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Activate / Deactivate Mana Detection (ANcl); Versatile Critical Strike I (A004); A02X; Combustion (A014); A028</t>
+          <t>Activate / Deactivate Mana Detection (ANcl); Versatile Critical Strike I (A004); Gooify (A02X); Combustion (A014); Sell Tower (A028)</t>
         </is>
       </c>
       <c r="AL12" t="n">
@@ -6925,6 +7090,11 @@
         <f>IF(C12=0,"",AR12*AT12)</f>
         <v/>
       </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7023,7 +7193,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Air Critical Strike II (A006); A028; ACvp</t>
+          <t>Air Critical Strike II (A006); Sell Tower (A028); Vampiric Aura (ACvp)</t>
         </is>
       </c>
       <c r="AL13" t="n">
@@ -7056,6 +7226,11 @@
         <f>IF(C13=0,"",AR13*AT13)</f>
         <v/>
       </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7154,7 +7329,7 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Machine Critical Strike (A03Y); Splash (A021); A028; Frost I (Afra)</t>
+          <t>Machine Critical Strike (A03Y); Splash (A021); Sell Tower (A028); Frost I (Afra)</t>
         </is>
       </c>
       <c r="AL14" t="n">
@@ -7187,6 +7362,11 @@
         <f>IF(C14=0,"",AR14*AT14)</f>
         <v/>
       </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7270,7 +7450,7 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Activate / Deactivate Mana Detection (ANcl); Afrz; Aap1; Cold Snap (AIm2); A028</t>
+          <t>Activate / Deactivate Mana Detection (ANcl); Stone Cold (Afrz); Grounding Curse (Aap1); Cold Snap (AIm2); Sell Tower (A028)</t>
         </is>
       </c>
       <c r="AL15" t="n">
@@ -7283,6 +7463,9 @@
         <f>AL15*AM15</f>
         <v/>
       </c>
+      <c r="AP15" t="n">
+        <v>1000</v>
+      </c>
       <c r="AQ15">
         <f>AN15+N(AO15)+N(AP15)</f>
         <v/>
@@ -7303,9 +7486,14 @@
         <f>IF(C15=0,"",AR15*AT15)</f>
         <v/>
       </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AU15"/>
+  <autoFilter ref="A1:AV15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7316,7 +7504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT20"/>
+  <dimension ref="A1:AU20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7365,6 +7553,7 @@
     <col width="9" customWidth="1" min="44" max="44"/>
     <col width="15" customWidth="1" min="45" max="45"/>
     <col width="22" customWidth="1" min="46" max="46"/>
+    <col width="14" customWidth="1" min="47" max="47"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7598,6 +7787,11 @@
           <t>dps_per_gold_x_range</t>
         </is>
       </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dps_source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7626,7 +7820,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Regeneration; Versatile Critical Strike I</t>
+          <t>Regeneration (A03W); Versatile Critical Strike I (A004)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -7730,6 +7924,11 @@
         <f>IF(D2=0,"",AN2*(N2/725))</f>
         <v/>
       </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7758,7 +7957,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Regeneration; Versatile Critical Strike II</t>
+          <t>Regeneration (A03W); Versatile Critical Strike II (A01E)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -7862,6 +8061,11 @@
         <f>IF(D3=0,"",AN3*(N3/725))</f>
         <v/>
       </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7890,7 +8094,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Cure I; Air Critical Strike II; Splash; Frost I (Afra)</t>
+          <t>Cure I (A03U); Air Critical Strike II (A006); Splash (A021); Frost I (Afra)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -7999,6 +8203,11 @@
         <f>IF(D4=0,"",AN4*(N4/725))</f>
         <v/>
       </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8027,7 +8236,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Cure I; Air Critical Strike I; Slow Poison I (Aspo)</t>
+          <t>Cure I (A03U); Air Critical Strike I (A005); Slow Poison I (Aspo)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -8134,6 +8343,11 @@
         <f>IF(D5=0,"",AN5*(N5/725))</f>
         <v/>
       </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8162,7 +8376,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Boss Assassin I; Slow Poison I (Aspo)</t>
+          <t>Boss Assassin I (A03D); Slow Poison I (Aspo)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -8269,6 +8483,11 @@
         <f>IF(D6=0,"",AN6*(N6/725))</f>
         <v/>
       </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8297,7 +8516,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Slow Poison II; Boss Assassin I</t>
+          <t>Slow Poison II (A008); Boss Assassin I (A03D)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8404,6 +8623,11 @@
         <f>IF(D7=0,"",AN7*(N7/725))</f>
         <v/>
       </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8427,7 +8651,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Vindicator I; Boss Assassin I; Splash</t>
+          <t>Vindicator I (A02Y); Boss Assassin I (A03D); Splash (A021)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -8536,6 +8760,11 @@
         <f>IF(D8=0,"",AN8*(N8/725))</f>
         <v/>
       </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8559,7 +8788,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dummy Ability - Life Steal) (Aabr); AIva; Ground Critical Strike I</t>
+          <t>(Dummy Ability - Life Steal) (Aabr); AIva (AIva); Ground Critical Strike I (A003)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8663,6 +8892,11 @@
         <f>IF(D9=0,"",AN9*(N9/725))</f>
         <v/>
       </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8691,7 +8925,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Vindicator II; Uber Splash</t>
+          <t>Vindicator II (A03C); Uber Splash (A022)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -8800,6 +9034,11 @@
         <f>IF(D10=0,"",AN10*(N10/725))</f>
         <v/>
       </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8828,7 +9067,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Vindicator III; Uber Ground Splash; Air Deficiency</t>
+          <t>Vindicator III (A02Z); Uber Ground Splash (A01X); Air Deficiency (A009)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -8937,6 +9176,11 @@
         <f>IF(D11=0,"",AN11*(N11/725))</f>
         <v/>
       </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8965,7 +9209,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Slow Poison II</t>
+          <t>Slow Poison II (A008)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -9072,6 +9316,11 @@
         <f>IF(D12=0,"",AN12*(N12/725))</f>
         <v/>
       </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9100,7 +9349,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Air Critical Strike I; Splash</t>
+          <t>Air Critical Strike I (A005); Splash (A021)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -9209,6 +9458,11 @@
         <f>IF(D13=0,"",AN13*(N13/725))</f>
         <v/>
       </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9232,7 +9486,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Supreme Ground Splash; Air Deficiency</t>
+          <t>Supreme Ground Splash (A01Y); Air Deficiency (A009)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9341,6 +9595,11 @@
         <f>IF(D14=0,"",AN14*(N14/725))</f>
         <v/>
       </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9369,7 +9628,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Cure II; Versatile Critical Strike I</t>
+          <t>Cure II (A03V); Versatile Critical Strike I (A004)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -9473,6 +9732,11 @@
         <f>IF(D15=0,"",AN15*(N15/725))</f>
         <v/>
       </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9501,7 +9765,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Fortitude; Cure II; Slow Poison I (Aspo)</t>
+          <t>Fortitude (A047); Cure II (A03V); Slow Poison I (Aspo)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -9608,6 +9872,11 @@
         <f>IF(D16=0,"",AN16*(N16/725))</f>
         <v/>
       </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9636,7 +9905,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Slow Poison I (Aspo); Air Critical Strike II</t>
+          <t>Slow Poison I (Aspo); Air Critical Strike II (A006)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -9743,6 +10012,11 @@
         <f>IF(D17=0,"",AN17*(N17/725))</f>
         <v/>
       </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9771,7 +10045,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Slow Poison II; Air Critical Strike III</t>
+          <t>Slow Poison II (A008); Air Critical Strike III (A00U)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -9878,6 +10152,11 @@
         <f>IF(D18=0,"",AN18*(N18/725))</f>
         <v/>
       </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10010,6 +10289,11 @@
         <f>IF(D19=0,"",AN19*(N19/725))</f>
         <v/>
       </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -10038,7 +10322,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Splash</t>
+          <t>Splash (A021)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -10147,9 +10431,14 @@
         <f>IF(D20=0,"",AN20*(N20/725))</f>
         <v/>
       </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AT20"/>
+  <autoFilter ref="A1:AU20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10160,7 +10449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ28"/>
+  <dimension ref="A1:BA28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10215,6 +10504,7 @@
     <col width="9" customWidth="1" min="50" max="50"/>
     <col width="15" customWidth="1" min="51" max="51"/>
     <col width="22" customWidth="1" min="52" max="52"/>
+    <col width="48" customWidth="1" min="53" max="53"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10478,6 +10768,11 @@
           <t>dps_per_gold_x_range</t>
         </is>
       </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dps_source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10501,7 +10796,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fortitude; Ground Splash</t>
+          <t>Fortitude (A047); Ground Splash (A01W)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -10610,6 +10905,11 @@
         <f>IF(D2=0,"",AT2*(N2/725))</f>
         <v/>
       </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10638,7 +10938,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Ground Critical Strike I</t>
+          <t>Ground Critical Strike I (A003)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -10752,6 +11052,11 @@
         <f>IF(D3=0,"",AT3*(N3/725))</f>
         <v/>
       </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10777,7 +11082,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Ground Critical Strike I; Slow Poison I (Aspo)</t>
+          <t>Ground Critical Strike I (A003); Slow Poison I (Aspo)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -10857,6 +11162,11 @@
         <f>IF(D4=0,"",AT4*(N4/725))</f>
         <v/>
       </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10995,6 +11305,11 @@
         <f>IF(D5=0,"",AT5*(N5/725))</f>
         <v/>
       </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11023,7 +11338,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Boss Assassin I; Splash</t>
+          <t>Boss Assassin I (A03D); Splash (A021)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -11142,6 +11457,11 @@
         <f>IF(D6=0,"",AT6*(N6/725))</f>
         <v/>
       </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11170,7 +11490,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Slow Poison III</t>
+          <t>Slow Poison III (A00T)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -11274,6 +11594,11 @@
         <f>IF(D7=0,"",AT7*(N7/725))</f>
         <v/>
       </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11302,7 +11627,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Splash; Air Critical Strike II</t>
+          <t>Splash (A021); Air Critical Strike II (A006)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -11448,6 +11773,11 @@
         <f>IF(D8=0,"",AT8*(N8/725))</f>
         <v/>
       </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11476,7 +11806,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Air Slow Poison; Boss Assassin II</t>
+          <t>Air Slow Poison (A03X); Boss Assassin II (A00R)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -11590,6 +11920,11 @@
         <f>IF(D9=0,"",AT9*(N9/725))</f>
         <v/>
       </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11618,7 +11953,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Splash; Air Critical Strike I</t>
+          <t>Splash (A021); Air Critical Strike I (A005)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -11737,6 +12072,11 @@
         <f>IF(D10=0,"",AT10*(N10/725))</f>
         <v/>
       </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11765,7 +12105,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Vindicator II; Cure II; Judgement</t>
+          <t>Vindicator II (A03C); Cure II (A03V); Judgement (A00N)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -11882,6 +12222,11 @@
         <f>IF(D11=0,"",AT11*(N11/725))</f>
         <v/>
       </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11910,7 +12255,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Cure II; Vindicator III; Judgement; Air Critical Strike II</t>
+          <t>Cure II (A03V); Vindicator III (A02Z); Judgement (A00N); Air Critical Strike II (A006)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -12027,6 +12372,11 @@
         <f>IF(D12=0,"",AT12*(N12/725))</f>
         <v/>
       </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12055,7 +12405,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Fortitude; Splash; Frost I (Afra)</t>
+          <t>Fortitude (A047); Splash (A021); Frost I (Afra)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -12164,6 +12514,11 @@
         <f>IF(D13=0,"",AT13*(N13/725))</f>
         <v/>
       </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12192,7 +12547,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Fortitude; Splash; Frost II; Versatile Critical Strike II</t>
+          <t>Fortitude (A047); Splash (A021); Frost II (A002); Versatile Critical Strike II (A01E)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -12306,6 +12661,11 @@
         <f>IF(D14=0,"",AT14*(N14/725))</f>
         <v/>
       </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12334,7 +12694,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Healing Wave (ANhw); Weak Ground Splash; Air Deficiency</t>
+          <t>Healing Wave (ANhw); Weak Ground Splash (A01V); Air Deficiency (A009)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -12453,6 +12813,11 @@
         <f>IF(D15=0,"",AT15*(N15/725))</f>
         <v/>
       </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -12481,7 +12846,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Healing Wave (ANhw); Machine Critical Strike; Ground Splash</t>
+          <t>Healing Wave (ANhw); Machine Critical Strike (A03Y); Ground Splash (A01W)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -12600,6 +12965,11 @@
         <f>IF(D16=0,"",AT16*(N16/725))</f>
         <v/>
       </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -12628,7 +12998,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Bash II (ACbh); Versatile Critical Strike I</t>
+          <t>Bash II (ACbh); Versatile Critical Strike I (A004)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -12740,6 +13110,11 @@
         <f>IF(D17=0,"",AT17*(N17/725))</f>
         <v/>
       </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12768,7 +13143,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Moon Stone Cannon (ACsh); Rail Driver; Vacuum Torpedo; Versatile Critical Strike I</t>
+          <t>Moon Stone Cannon (ACsh); Rail Driver (A00O); Vacuum Torpedo (A00P); Versatile Critical Strike I (A004)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -12877,6 +13252,11 @@
         <f>IF(D18=0,"",AT18*(N18/725))</f>
         <v/>
       </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -12905,7 +13285,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Vindicator I; Air Critical Strike II</t>
+          <t>Vindicator I (A02Y); Air Critical Strike II (A006)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -13011,6 +13391,11 @@
         <f>IF(D19=0,"",AT19*(N19/725))</f>
         <v/>
       </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -13039,7 +13424,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Aviary Degeneration; Air Critical Strike III</t>
+          <t>Aviary Degeneration (A024); Air Critical Strike III (A00U)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -13148,6 +13533,11 @@
         <f>IF(D20=0,"",AT20*(N20/725))</f>
         <v/>
       </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -13176,7 +13566,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Divine Shield (AHds); Gravity Well</t>
+          <t>Divine Shield (AHds); Gravity Well (A00V)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -13280,6 +13670,11 @@
         <f>IF(D21=0,"",AT21*(N21/725))</f>
         <v/>
       </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -13308,7 +13703,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Divine Shield (AHds); Gravity Well; Absolution; Boss Assassin II</t>
+          <t>Divine Shield (AHds); Gravity Well (A00V); Absolution (A00S); Boss Assassin II (A00R)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -13449,6 +13844,11 @@
         <f>IF(D22=0,"",AT22*(N22/725))</f>
         <v/>
       </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -13498,6 +13898,11 @@
         <f>IF(D23=0,"",AT23*(N23/725))</f>
         <v/>
       </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -13542,6 +13947,11 @@
         <f>IF(D24=0,"",AT24*(N24/725))</f>
         <v/>
       </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -13586,6 +13996,11 @@
         <f>IF(D25=0,"",AT25*(N25/725))</f>
         <v/>
       </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -13630,6 +14045,11 @@
         <f>IF(D26=0,"",AT26*(N26/725))</f>
         <v/>
       </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -13674,6 +14094,11 @@
         <f>IF(D27=0,"",AT27*(N27/725))</f>
         <v/>
       </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -13718,9 +14143,14 @@
         <f>IF(D28=0,"",AT28*(N28/725))</f>
         <v/>
       </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AZ28"/>
+  <autoFilter ref="A1:BA28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13731,7 +14161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT21"/>
+  <dimension ref="A1:AU21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -13780,6 +14210,7 @@
     <col width="9" customWidth="1" min="44" max="44"/>
     <col width="15" customWidth="1" min="45" max="45"/>
     <col width="22" customWidth="1" min="46" max="46"/>
+    <col width="48" customWidth="1" min="47" max="47"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14013,6 +14444,11 @@
           <t>dps_per_gold_x_range</t>
         </is>
       </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dps_source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14041,7 +14477,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Repel Aura; Vindicator III</t>
+          <t>Repel Aura (A03Q); Vindicator III (A02Z)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -14140,6 +14576,11 @@
         <f>IF(D2=0,"",AN2*(N2/725))</f>
         <v/>
       </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14168,7 +14609,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Fortitude; Slow Poison I (Aspo)</t>
+          <t>Fortitude (A047); Slow Poison I (Aspo)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -14270,6 +14711,11 @@
         <f>IF(D3=0,"",AN3*(N3/725))</f>
         <v/>
       </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14298,7 +14744,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Air Critical Strike I</t>
+          <t>Air Critical Strike I (A005)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -14407,6 +14853,11 @@
         <f>IF(D4=0,"",AN4*(N4/725))</f>
         <v/>
       </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14454,6 +14905,9 @@
       <c r="AA5" t="n">
         <v>1250</v>
       </c>
+      <c r="AK5" t="n">
+        <v>217.5</v>
+      </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
@@ -14481,6 +14935,11 @@
         <f>IF(D5=0,"",AN5*(N5/725))</f>
         <v/>
       </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>caster: Foxfire Laser (sustained, mana-limited)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14509,7 +14968,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Improved Ward; Slow Aura I; Supine Hex I</t>
+          <t>Improved Ward (S001); Slow Aura I (A03M); Supine Hex I (A01B)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -14618,6 +15077,11 @@
         <f>IF(D6=0,"",AN6*(N6/725))</f>
         <v/>
       </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14646,7 +15110,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Improved Ward; Slow Aura II; Supine Hex II</t>
+          <t>Improved Ward (S001); Slow Aura II (A03N); Supine Hex II (A01C)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -14755,6 +15219,11 @@
         <f>IF(D7=0,"",AN7*(N7/725))</f>
         <v/>
       </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14783,7 +15252,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sloth I</t>
+          <t>Sloth I (A01I)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -14882,6 +15351,11 @@
         <f>IF(D8=0,"",AN8*(N8/725))</f>
         <v/>
       </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14910,7 +15384,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Supreme Splash; Sloth II</t>
+          <t>Supreme Splash (A01Z); Sloth II (A01A)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -15014,6 +15488,11 @@
         <f>IF(D9=0,"",AN9*(N9/725))</f>
         <v/>
       </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15042,7 +15521,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Missile Salvo I</t>
+          <t>Missile Salvo I (A03R)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -15151,6 +15630,11 @@
         <f>IF(D10=0,"",AN10*(N10/725))</f>
         <v/>
       </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15179,7 +15663,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Missile Salvo II</t>
+          <t>Missile Salvo II (A03S)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -15288,6 +15772,11 @@
         <f>IF(D11=0,"",AN11*(N11/725))</f>
         <v/>
       </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15335,6 +15824,9 @@
       <c r="AA12" t="n">
         <v>2250</v>
       </c>
+      <c r="AK12" t="n">
+        <v>29</v>
+      </c>
       <c r="AL12" t="n">
         <v>1</v>
       </c>
@@ -15362,6 +15854,11 @@
         <f>IF(D12=0,"",AN12*(N12/725))</f>
         <v/>
       </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>caster: Fury of the Gods (sustained, mana-limited)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15494,6 +15991,11 @@
         <f>IF(D13=0,"",AN13*(N13/725))</f>
         <v/>
       </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -15522,7 +16024,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Toughness Aura I (AHad); Cure All</t>
+          <t>Toughness Aura I (AHad); Cure All (A00X)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -15628,6 +16130,11 @@
         <f>IF(D14=0,"",AN14*(N14/725))</f>
         <v/>
       </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -15656,7 +16163,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Toughness Aura II; Cure All</t>
+          <t>Toughness Aura II (A03P); Cure All (A00X)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -15762,6 +16269,11 @@
         <f>IF(D15=0,"",AN15*(N15/725))</f>
         <v/>
       </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -15790,7 +16302,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Improved Ward; Boss Assassin I; Curse Boss I</t>
+          <t>Improved Ward (S001); Boss Assassin I (A03D); Curse Boss I (A01H)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -15899,6 +16411,11 @@
         <f>IF(D16=0,"",AN16*(N16/725))</f>
         <v/>
       </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -15927,7 +16444,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Improved Ward; Boss Assassin I; Uber Splash; Curse Boss II</t>
+          <t>Improved Ward (S001); Boss Assassin I (A03D); Uber Splash (A022); Curse Boss II (A01G)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -16036,6 +16553,11 @@
         <f>IF(D17=0,"",AN17*(N17/725))</f>
         <v/>
       </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -16059,7 +16581,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Multiple Shot</t>
+          <t>Multiple Shot (A01M)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -16168,6 +16690,11 @@
         <f>IF(D18=0,"",AN18*(N18/725))</f>
         <v/>
       </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -16191,7 +16718,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Vindicator I; Air Deficiency; Uber Ground Splash</t>
+          <t>Vindicator I (A02Y); Air Deficiency (A009); Uber Ground Splash (A01X)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -16297,6 +16824,11 @@
         <f>IF(D19=0,"",AN19*(N19/725))</f>
         <v/>
       </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -16325,7 +16857,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Bash III; Versatile Critical Strike I</t>
+          <t>Bash III (A02E); Versatile Critical Strike I (A004)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -16432,6 +16964,11 @@
         <f>IF(D20=0,"",AN20*(N20/725))</f>
         <v/>
       </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -16460,7 +16997,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Improved Glacial Spike; Boss Assassin I; Collapse</t>
+          <t>Improved Glacial Spike (S000); Boss Assassin I (A03D); Collapse (A019)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -16564,9 +17101,14 @@
         <f>IF(D21=0,"",AN21*(N21/725))</f>
         <v/>
       </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AT21"/>
+  <autoFilter ref="A1:AU21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16577,7 +17119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX24"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -16630,6 +17172,7 @@
     <col width="9" customWidth="1" min="48" max="48"/>
     <col width="15" customWidth="1" min="49" max="49"/>
     <col width="22" customWidth="1" min="50" max="50"/>
+    <col width="48" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16883,6 +17426,11 @@
           <t>dps_per_gold_x_range</t>
         </is>
       </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dps_source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16911,7 +17459,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fortitude; Vindicator I; Weak Ground Splash</t>
+          <t>Fortitude (A047); Vindicator I (A02Y); Weak Ground Splash (A01V)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -17030,6 +17578,11 @@
         <f>IF(D2=0,"",AR2*(N2/725))</f>
         <v/>
       </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17058,7 +17611,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Fortitude; Ground Splash</t>
+          <t>Fortitude (A047); Ground Splash (A01W)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -17177,6 +17730,11 @@
         <f>IF(D3=0,"",AR3*(N3/725))</f>
         <v/>
       </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17205,7 +17763,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Boss Assassin I; Ground Splash</t>
+          <t>Boss Assassin I (A03D); Ground Splash (A01W)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -17321,6 +17879,11 @@
         <f>IF(D4=0,"",AR4*(N4/725))</f>
         <v/>
       </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -17349,7 +17912,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Boss Assassin I; Uber Ground Splash</t>
+          <t>Boss Assassin I (A03D); Uber Ground Splash (A01X)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -17455,6 +18018,11 @@
         <f>IF(D5=0,"",AR5*(N5/725))</f>
         <v/>
       </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17483,7 +18051,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Ground Critical Strike I; Slow Poison I (Aspo)</t>
+          <t>Ground Critical Strike I (A003); Slow Poison I (Aspo)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -17597,6 +18165,11 @@
         <f>IF(D6=0,"",AR6*(N6/725))</f>
         <v/>
       </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17625,7 +18198,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Versatile Critical Strike I; Slow Poison I (Aspo)</t>
+          <t>Versatile Critical Strike I (A004); Slow Poison I (Aspo)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -17739,6 +18312,11 @@
         <f>IF(D7=0,"",AR7*(N7/725))</f>
         <v/>
       </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17762,7 +18340,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Ground Splash; Ground Critical Strike I</t>
+          <t>Ground Splash (A01W); Ground Critical Strike I (A003)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -17873,6 +18451,11 @@
         <f>IF(D8=0,"",AR8*(N8/725))</f>
         <v/>
       </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17896,7 +18479,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Machine Critical Strike</t>
+          <t>Machine Critical Strike (A03Y)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -18010,6 +18593,11 @@
         <f>IF(D9=0,"",AR9*(N9/725))</f>
         <v/>
       </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18038,7 +18626,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Splash; Air Critical Strike I</t>
+          <t>Splash (A021); Air Critical Strike I (A005)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -18157,6 +18745,11 @@
         <f>IF(D10=0,"",AR10*(N10/725))</f>
         <v/>
       </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -18185,7 +18778,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Fortitude; Vindicator II; Uber Splash; Air Critical Strike I</t>
+          <t>Fortitude (A047); Vindicator II (A03C); Uber Splash (A022); Air Critical Strike I (A005)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -18304,6 +18897,11 @@
         <f>IF(D11=0,"",AR11*(N11/725))</f>
         <v/>
       </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -18332,7 +18930,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tornado Shot; Ground Critical Strike I</t>
+          <t>Tornado Shot (A00Q); Ground Critical Strike I (A003)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -18446,6 +19044,11 @@
         <f>IF(D12=0,"",AR12*(N12/725))</f>
         <v/>
       </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -18474,7 +19077,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tornado Shot; Fortitude; Bash II (ACbh); Slow Poison II</t>
+          <t>Tornado Shot (A00Q); Fortitude (A047); Bash II (ACbh); Slow Poison II (A008)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -18594,6 +19197,11 @@
         <f>IF(D13=0,"",AR13*(N13/725))</f>
         <v/>
       </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -18617,7 +19225,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Fortitude; Splash; Versatile Critical Strike I</t>
+          <t>Fortitude (A047); Splash (A021); Versatile Critical Strike I (A004)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -18750,6 +19358,11 @@
         <f>IF(D14=0,"",AR14*(N14/725))</f>
         <v/>
       </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18778,7 +19391,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Ground Splash; Ground Critical Strike I</t>
+          <t>Ground Splash (A01W); Ground Critical Strike I (A003)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -18897,6 +19510,11 @@
         <f>IF(D15=0,"",AR15*(N15/725))</f>
         <v/>
       </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -18925,7 +19543,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Machine Critical Strike; Regeneration; Ground Splash</t>
+          <t>Machine Critical Strike (A03Y); Regeneration (A03W); Ground Splash (A01W)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -19044,6 +19662,11 @@
         <f>IF(D16=0,"",AR16*(N16/725))</f>
         <v/>
       </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -19072,7 +19695,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Fortitude; Boss Assassin I; Ground Splash; Air Deficiency</t>
+          <t>Fortitude (A047); Boss Assassin I (A03D); Ground Splash (A01W); Air Deficiency (A009)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -19191,6 +19814,11 @@
         <f>IF(D17=0,"",AR17*(N17/725))</f>
         <v/>
       </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -19219,7 +19847,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Fortitude; Uber Ground Splash; Air Deficiency</t>
+          <t>Fortitude (A047); Uber Ground Splash (A01X); Air Deficiency (A009)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -19333,6 +19961,11 @@
         <f>IF(D18=0,"",AR18*(N18/725))</f>
         <v/>
       </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -19361,7 +19994,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Splash; Air Critical Strike I</t>
+          <t>Splash (A021); Air Critical Strike I (A005)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -19480,6 +20113,11 @@
         <f>IF(D19=0,"",AR19*(N19/725))</f>
         <v/>
       </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -19508,7 +20146,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Splash; Versatile Critical Strike I; Frost II; Calamity</t>
+          <t>Splash (A021); Versatile Critical Strike I (A004); Frost II (A002); Calamity (A00B)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -19617,6 +20255,11 @@
         <f>IF(D20=0,"",AR20*(N20/725))</f>
         <v/>
       </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -19666,6 +20309,11 @@
         <f>IF(D21=0,"",AR21*(N21/725))</f>
         <v/>
       </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -19715,6 +20363,11 @@
         <f>IF(D22=0,"",AR22*(N22/725))</f>
         <v/>
       </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -19764,6 +20417,11 @@
         <f>IF(D23=0,"",AR23*(N23/725))</f>
         <v/>
       </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -19808,9 +20466,14 @@
         <f>IF(D24=0,"",AR24*(N24/725))</f>
         <v/>
       </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AX24"/>
+  <autoFilter ref="A1:AY24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19821,7 +20484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ22"/>
+  <dimension ref="A1:BA22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -19876,6 +20539,7 @@
     <col width="9" customWidth="1" min="50" max="50"/>
     <col width="15" customWidth="1" min="51" max="51"/>
     <col width="22" customWidth="1" min="52" max="52"/>
+    <col width="48" customWidth="1" min="53" max="53"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20139,6 +20803,11 @@
           <t>dps_per_gold_x_range</t>
         </is>
       </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dps_source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20167,7 +20836,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Weak Splash; Air Critical Strike II</t>
+          <t>Weak Splash (A020); Air Critical Strike II (A006)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -20286,6 +20955,11 @@
         <f>IF(D2=0,"",AT2*(N2/725))</f>
         <v/>
       </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20314,7 +20988,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Air Critical Strike II; Slow Poison I (Aspo)</t>
+          <t>Air Critical Strike II (A006); Slow Poison I (Aspo)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -20431,6 +21105,11 @@
         <f>IF(D3=0,"",AT3*(N3/725))</f>
         <v/>
       </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20459,7 +21138,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Cure I; Air Critical Strike I; Splash</t>
+          <t>Cure I (A03U); Air Critical Strike I (A005); Splash (A021)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -20578,6 +21257,11 @@
         <f>IF(D4=0,"",AT4*(N4/725))</f>
         <v/>
       </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20606,7 +21290,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Cure I; Area Cure (AIha); Uber Splash; Air Critical Strike II</t>
+          <t>Cure I (A03U); Area Cure (AIha); Uber Splash (A022); Air Critical Strike II (A006)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -20725,6 +21409,11 @@
         <f>IF(D5=0,"",AT5*(N5/725))</f>
         <v/>
       </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20870,6 +21559,11 @@
         <f>IF(D6=0,"",AT6*(N6/725))</f>
         <v/>
       </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20898,7 +21592,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Boss Assassin II; Air Critical Strike II; Prison of Ice</t>
+          <t>Boss Assassin II (A00R); Air Critical Strike II (A006); Prison of Ice (A02U)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -21012,6 +21706,11 @@
         <f>IF(D7=0,"",AT7*(N7/725))</f>
         <v/>
       </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21035,7 +21734,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Uber Splash; Air Critical Strike I; Apxf; Phoenix Fire (Amgr)</t>
+          <t>Uber Splash (A022); Air Critical Strike I (A005); Apxf (Apxf); Phoenix Fire (Amgr)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -21154,6 +21853,11 @@
         <f>IF(D8=0,"",AT8*(N8/725))</f>
         <v/>
       </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21177,7 +21881,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Weak Splash; Air Critical Strike II</t>
+          <t>Weak Splash (A020); Air Critical Strike II (A006)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -21296,6 +22000,11 @@
         <f>IF(D9=0,"",AT9*(N9/725))</f>
         <v/>
       </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21324,7 +22033,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Splash; Frost I (Afra)</t>
+          <t>Splash (A021); Frost I (Afra)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -21443,6 +22152,11 @@
         <f>IF(D10=0,"",AT10*(N10/725))</f>
         <v/>
       </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -21471,7 +22185,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Fortitude; Vindicator I; Slow Poison II</t>
+          <t>Fortitude (A047); Vindicator I (A02Y); Slow Poison II (A008)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -21617,6 +22331,11 @@
         <f>IF(D11=0,"",AT11*(N11/725))</f>
         <v/>
       </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -21645,7 +22364,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Air Critical Strike II; Slow Poison II</t>
+          <t>Air Critical Strike II (A006); Slow Poison II (A008)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -21762,6 +22481,11 @@
         <f>IF(D12=0,"",AT12*(N12/725))</f>
         <v/>
       </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -21790,7 +22514,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dummy Ability - Life Steal) (Aabr); Slow Poison II</t>
+          <t>(Dummy Ability - Life Steal) (Aabr); Slow Poison II (A008)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -21907,6 +22631,11 @@
         <f>IF(D13=0,"",AT13*(N13/725))</f>
         <v/>
       </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -21930,7 +22659,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Splash; Versatile Critical Strike I; Frost II</t>
+          <t>Splash (A021); Versatile Critical Strike I (A004); Frost II (A002)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -22049,6 +22778,11 @@
         <f>IF(D14=0,"",AT14*(N14/725))</f>
         <v/>
       </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -22077,7 +22811,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Bash I (ANbh); Air Critical Strike I; Slow Poison I (Aspo)</t>
+          <t>Bash I (ANbh); Air Critical Strike I (A005); Slow Poison I (Aspo)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -22197,6 +22931,11 @@
         <f>IF(D15=0,"",AT15*(N15/725))</f>
         <v/>
       </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -22249,6 +22988,9 @@
           <t>Slot inferred, not observed. The kit rule is "each tower has at most ONE upgrade, and that upgrade unlocks a new tower type" - Havoc Wing is a REQUIREMENT of Death Shrine (T10) and sits between T9 and T10, so it is most likely Teenage Roc's upgrade. VERIFY.</t>
         </is>
       </c>
+      <c r="AQ16" t="n">
+        <v>316.7</v>
+      </c>
       <c r="AR16" t="n">
         <v>1</v>
       </c>
@@ -22276,6 +23018,11 @@
         <f>IF(D16=0,"",AT16*(N16/725))</f>
         <v/>
       </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>caster: Thresh Arrow (sustained, mana-limited)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -22304,7 +23051,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Air Critical Strike II</t>
+          <t>Air Critical Strike II (A006)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -22418,6 +23165,11 @@
         <f>IF(D17=0,"",AT17*(N17/725))</f>
         <v/>
       </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -22446,7 +23198,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Air Barrage; Death Strike</t>
+          <t>Air Barrage (A000); Death Strike (A001)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -22592,6 +23344,11 @@
         <f>IF(D18=0,"",AT18*(N18/725))</f>
         <v/>
       </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -22620,7 +23377,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Air Critical Strike II</t>
+          <t>Air Critical Strike II (A006)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -22731,6 +23488,11 @@
         <f>IF(D19=0,"",AT19*(N19/725))</f>
         <v/>
       </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -22759,7 +23521,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Slow Poison II; Air Critical Strike II</t>
+          <t>Slow Poison II (A008); Air Critical Strike II (A006)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -22892,6 +23654,11 @@
         <f>IF(D20=0,"",AT20*(N20/725))</f>
         <v/>
       </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -22941,6 +23708,11 @@
         <f>IF(D21=0,"",AT21*(N21/725))</f>
         <v/>
       </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -22990,9 +23762,14 @@
         <f>IF(D22=0,"",AT22*(N22/725))</f>
         <v/>
       </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AZ22"/>
+  <autoFilter ref="A1:BA22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23003,7 +23780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I105"/>
+  <dimension ref="A1:I113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -23067,12 +23844,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cleaving Attack (A007)</t>
+          <t>Air Barrage (A000)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A007</t>
+          <t>A000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -23082,12 +23859,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>25% of this unit's damage strikes through the primary target to hurt all nearby enemies in a 200 radius.</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>Fires a secondary volley of death energy that target nearby enemies. Hits up to 7 targets in this manner and deals 1000 damage each.</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -23095,19 +23867,19 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Insurrectionist Trow</t>
+          <t>Death Dragon</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>(Dummy Ability - Life Steal) (Aabr)</t>
+          <t>Death Strike (A001)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aabr</t>
+          <t>A001</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -23117,27 +23889,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>This tower's attack heals itself for a portion of damage dealt to enemy ground units.</t>
+          <t>The Death Dragon's attack instantly kills a non-hero ground unit.</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Chibidevil; Poison Dragon</t>
+          <t>Death Dragon</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Freezing Field (Aamk)</t>
+          <t>Frost II (A002)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aamk</t>
+          <t>A002</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -23147,27 +23919,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Costs 30 mana per attack, else the Field will stop.|n|nFreezing Field attacks deal 575 frost damage to nearby enemies and slows their movement rate and attack speed for 3 seconds.</t>
+          <t>Adds a cold effect to this unit's attacks that slows enemy units' movement speed for a medium period of time.</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Freezing Field</t>
+          <t>D-String; Apocalypse; Frozen Reaper</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Absolution</t>
+          <t>Ground Critical Strike I (A003)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A00S</t>
+          <t>A003</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -23177,27 +23949,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Skibi's magical attack has a 50% chance to deal 25 times normal damage against non-boss enemy units.</t>
+          <t>Gives a 35% chance to do 2 times normal damage on an attack. Crits against ground only.</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Astral Skibi</t>
+          <t>Duke Burnify; Chibidevil; Stealth Maiden</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bash II (ACbh)</t>
+          <t>Versatile Critical Strike I (A004)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ACbh</t>
+          <t>A004</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -23207,27 +23979,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Gives a 20% chance that an attack will do 235 bonus damage and stun a non-hero ground creep for 2 seconds.</t>
+          <t>Gives a 35% chance to do 2.5 times normal damage on an attack. Crits against all units.</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Impervious Armor; Captain Bartlebee; Battleship Mackinaw</t>
+          <t>Axeman; General Ninpou; Equipped Peasant 2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Thresh Arrow (ACca)</t>
+          <t>Air Critical Strike I (A005)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ACca</t>
+          <t>A005</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -23237,27 +24009,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>When Havocwing attacks, she tightens the pressure her bow and releases it in a blazing path. |nThe attack strikes enemies in a line for 475 damage.</t>
+          <t>Gives a 50% chance to do 1.5 times normal damage on an attack. Crits against air units.</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Havocwing</t>
+          <t>Spear Guard; War Beast; The Pride of Moon Star</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Healing Aura (ACce)</t>
+          <t>Air Critical Strike II (A006)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ACce</t>
+          <t>A006</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -23267,27 +24039,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>The Village Medic heals himself and nearby friendly towers for 2 hitpoints a second. Radius measured in game as under 800 (owner 2026-09-10); the tooltip states none.</t>
+          <t>Gives a 50% chance to do 4 times normal damage on an attack. Crits against air units.</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Village Medic</t>
+          <t>Tamed Game; Toxic Assassin; Father Dragon</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Hunter's Fervor (ACcl)</t>
+          <t>Cleaving Attack (A007)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ACcl</t>
+          <t>A007</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -23297,27 +24069,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Hurls a devastating ray of power that ricochets off the first foe and strikes 14 others at 5% less power. Deals 3000 on the first strike.</t>
+          <t>25% of this unit's damage strikes through the primary target to hurt all nearby enemies in a 200 radius.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Mercurial Predator; Unrivaled Destroyer</t>
+          <t>Insurrectionist Trow</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Winter's Bite (ACcw)</t>
+          <t>Slow Poison II (A008)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ACcw</t>
+          <t>A008</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -23327,27 +24104,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Adds 54 cold damage to an attack and slows target, but drains mana with each shot fired.</t>
+          <t>A vicious poison attack that deals 36 damage per second, and slows the target organic enemy's movement by 40%.|n|nAll poison types stacks with each other.</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Aspect of Cold</t>
+          <t>Axeman; Ruthless Warlord; Father Dragon</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Fury of the Gods (ACmo)</t>
+          <t>Air Deficiency (A009)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ACmo</t>
+          <t>A009</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -23357,27 +24134,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Calls down a storm of lightning to strike enemy units for 580 damage in a target area. |nLasts 10 seconds.</t>
+          <t>This unit cannot strike air units very efficiently, and deals only 25% damage on 50% of its attacks.</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Kazaana</t>
+          <t>Mercurial Predator; Severe Trauma; Promontory Disruptor</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Moon Stone Cannon (ACsh)</t>
+          <t>Ground Critical Strike II (A00A)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ACsh</t>
+          <t>A00A</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -23387,7 +24164,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Matter evaporates when the potent forces of this attack strikes flesh. Deals 1250 damage to units in a line. Very fast cooldown.</t>
+          <t>The Destroyer possesses the heart of a lion, and has a 50% chance to deal 5x damage to ground enemies.</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -23395,19 +24172,19 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Delphinus</t>
+          <t>Unrivaled Destroyer</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Starburst (AEsf)</t>
+          <t>Calamity (A00B)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AEsf</t>
+          <t>A00B</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -23417,7 +24194,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Calls down waves of falling stars that damage nearby enemy units in a huge radius. Each wave deals 1200 damage. |nCooldown = 15 seconds.</t>
+          <t>Slams the ground, dealing no damage to nearby ground units in a large radius, but slowing them for 15 seconds by 15%.|nDoes not stack with Vacuum Torpedo.</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -23425,19 +24202,19 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Star Buster</t>
+          <t>Apocalypse</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Life Boon (AEtq)</t>
+          <t>Judgement (A00N)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AEtq</t>
+          <t>A00N</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -23447,27 +24224,27 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Heals 30 HP per second for 30 seconds — 900 HP total. The map names this ability but leaves its description EMPTY, so the owner's in-game read (2026-09-10) is the only source.</t>
+          <t>Burns nearby enemy air units over time. Deals 100 damage per second. |nLasts 20 seconds.</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>General Ninpou</t>
+          <t>High Priest; Martyr</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Frost I (Afra)</t>
+          <t>Rail Driver (A00O)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Afra</t>
+          <t>A00O</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -23477,27 +24254,27 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Adds a cold effect to this unit's attacks that slows enemy units' movement speed for a short period of time</t>
+          <t>Summons two ethereal hands to erupt from the earth that instantly kills a non-hero ground unit.</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Shinobi; Orobos Slave; Impervious Armor</t>
+          <t>Delphinus</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Toughness Aura I (AHad)</t>
+          <t>Vacuum Torpedo (A00P)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AHad</t>
+          <t>A00P</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -23507,7 +24284,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Gives 2 additional armor to nearby friendly towers.|nThis aura stacks with Toughness Aura II.</t>
+          <t>Fires a torpedo straight into the soft earth that implodes the ground. The ethereal force ripples from Delphinus dealing 150 points of damage and greatly slows ground enemies for 8 seconds.|nDoes not stack with Calamity.</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -23515,19 +24292,19 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Protection Ward</t>
+          <t>Delphinus</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Divine Shield (AHds)</t>
+          <t>Tornado Shot (A00Q)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AHds</t>
+          <t>A00Q</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -23537,12 +24314,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Divine Shield</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>Summons 6 fast moving tornados whirling shrapnel and dust every second for 10 seconds. |nDamages air units in a small area of effect for 100 damage.</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -23550,19 +24322,19 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Lilianna Mai; Astral Skibi</t>
+          <t>Little Jack; Battleship Mackinaw</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kiss of Flame (AHfa)</t>
+          <t>Boss Assassin II (A00R)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AHfa</t>
+          <t>A00R</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -23572,27 +24344,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Adds 83 bonus fire damage to an attack against enemies, but drains mana with each shot fired.</t>
+          <t>Deals 8x damage to heroes. Crits 50% of the time.</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Aspect of Fire</t>
+          <t>Marksman; Ignatious; Astral Skibi</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Area Cure (AIha)</t>
+          <t>Absolution (A00S)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AIha</t>
+          <t>A00S</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -23602,7 +24374,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Heals &lt;AIha,DataA1&gt; hit points to all friendly structures around the caster when used.</t>
+          <t>Skibi's magical attack has a 50% chance to deal 25 times normal damage against non-boss enemy units.</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -23610,19 +24382,19 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Magical Breakthrough</t>
+          <t>Astral Skibi</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Electrify (AIhb)</t>
+          <t>Slow Poison III (A00T)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AIhb</t>
+          <t>A00T</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -23632,27 +24404,27 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Restores this tower's spell cooldown.</t>
+          <t>A poison attack that deals 250 damage per second, and slows the target organic enemy's movement by 65%.|n|nAll poison types stacks with each other.</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Aspect of Lightning; Electrocutioner; Blood Wraith</t>
+          <t>Toxic Assassin; Peppy Bronzebeard</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cold Snap (AIm2)</t>
+          <t>Air Critical Strike III (A00U)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AIm2</t>
+          <t>A00U</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -23662,27 +24434,27 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Restores this tower's MP completely.</t>
+          <t>Gives a 50% chance to do 7 times normal damage on an attack. Crits against air units.</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Aspect of Cold; Arctic Blaster; Chilly Bit Striker</t>
+          <t>Noir Heart; Shrine of Isis</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Air Barrage</t>
+          <t>Gravity Well (A00V)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>A000</t>
+          <t>A00V</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -23692,27 +24464,27 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Fires a secondary volley of death energy that target nearby enemies. Hits up to 7 targets in this manner and deals 1000 damage each.</t>
+          <t>Rips the fabric and essence from those that stand on the same ground as her ladyship. Enemy life is reduced by about 10% and movement speed permanently is cut by 5%. This damage cannot be prevented or reduced.</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Death Dragon</t>
+          <t>Lilianna Mai; Astral Skibi</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Air Critical Strike I</t>
+          <t>Cure All (A00X)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A005</t>
+          <t>A00X</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -23722,27 +24494,27 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Gives a 50% chance to do 1.5 times normal damage on an attack. Crits against air units.</t>
+          <t>Instantly heals the allies' buildings for 250. |n|nAffects allied buildings.</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Spear Guard; War Beast; The Pride of Moon Star</t>
+          <t>Protection Ward; Roseate Ward</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Air Critical Strike II</t>
+          <t>Combustion (A014)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>A006</t>
+          <t>A014</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -23752,27 +24524,27 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Gives a 50% chance to do 4 times normal damage on an attack. Crits against air units.</t>
+          <t>Increases the tower's attack rate by up to 50% for 15 seconds.</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tamed Game; Toxic Assassin; Frigid Dryad</t>
+          <t>Aspect of Fire; Scalding Tower; Fire Hydra</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Air Critical Strike III</t>
+          <t>Collapse (A019)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A00U</t>
+          <t>A019</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -23782,27 +24554,27 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Gives a 50% chance to do 7 times normal damage on an attack. Crits against air units.</t>
+          <t>Strikes from underneath the ground with a terribly powerful tentacle, permanently lowering a non-hero ground unit's movement speed to the minimum amount.</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Noir Heart; Shrine of Isis</t>
+          <t>Glacial Spike</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Air Deficiency</t>
+          <t>Sloth II (A01A)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>A009</t>
+          <t>A01A</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -23812,27 +24584,27 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>This unit cannot strike air units very efficiently, and deals only 25% damage on 50% of its attacks.</t>
+          <t>1/5th of this tower's attacks reduces a target creep's HP by 25% and permanently reduces movement speed by a large amount. |n|nThis curse stacks with itself.</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Mercurial Predator; Severe Trauma; Promontory Disruptor</t>
+          <t>Scarlet Ward</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Air Slow Poison</t>
+          <t>Supine Hex I (A01B)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A03X</t>
+          <t>A01B</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -23842,7 +24614,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>A non-lethal poison that slows the target organic air enemy's movement by 70%.|n|nAll poison types stacks with each other.</t>
+          <t>This ward's power permanently reduces a non-hero enemy's movement speed by 7. |n|nThis curse stacks with itself.</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -23850,19 +24622,19 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Ignatious</t>
+          <t>Sapphire Ward</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AIva</t>
+          <t>Supine Hex II (A01C)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AIva</t>
+          <t>A01C</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -23870,24 +24642,29 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>This ward's power permanently reduces a non-hero enemy's movement speed by 12. |n|nThis curse stacks with itself.</t>
+        </is>
+      </c>
       <c r="G28" t="n">
         <v>1</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Chibidevil</t>
+          <t>Purity Ward</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Phoenix Income (Amgl)</t>
+          <t>Versatile Critical Strike II (A01E)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Amgl</t>
+          <t>A01E</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -23897,27 +24674,27 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>You gain 1 gold for controlling this Phoenix Spawn after every Wave.</t>
+          <t>Gives a 60% chance to do 2.75 times normal damage on an attack. Crits against all units.</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Phoenix Spawn</t>
+          <t>Equipped Peasant 3; Equipped Peasant 4; Equipped Peasant 5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Phoenix Fire (Amgr)</t>
+          <t>Curse Boss II (A01G)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Amgr</t>
+          <t>A01G</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -23927,7 +24704,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Fires a stream of flame, lighting the primary target enemy on fire and burns it over time. Deals 50 damage a second for 5 seconds.</t>
+          <t>Cuts at the heart of evil, and reduces an enemy boss's movement speed by a medium portion.|nThis curse stacks with itself.</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -23935,19 +24712,19 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Judgement Fire</t>
+          <t>Malachite Ward</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Scald (ANbf)</t>
+          <t>Curse Boss I (A01H)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ANbf</t>
+          <t>A01H</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -23957,7 +24734,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Erupt a cone of fire at enemy units, dealing 110 damage. Max damage = 660.</t>
+          <t>Cuts at the heart of evil, and reduces an enemy boss's movement speed by a small portion.|nThis curse stacks with itself.</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -23965,19 +24742,19 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Scalding Tower</t>
+          <t>Lilac Ward</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Bash I (ANbh)</t>
+          <t>Sloth I (A01I)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ANbh</t>
+          <t>A01I</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -23987,27 +24764,27 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Gives a 20% chance that an attack will do 50 bonus damage and stun a non-hero ground creep for 1.5 seconds.</t>
+          <t>1/5th of this tower's attacks reduces a target creep's HP by 15% and permanently reduces movement speed by a medium amount. |n|nThis curse stacks with itself.</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Myrkridon Trow; Insurrectionist Trow; Tyr's Spirit</t>
+          <t>Ochre Ward</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Chilly Bits Grade Peorth (ANc1)</t>
+          <t>Multiple Shot (A01M)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ANc1</t>
+          <t>A01M</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -24017,7 +24794,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Bombards an area with pure chaos, stunning enemies within an area for 1 second and dealing up to 800 damage.</t>
+          <t>The tower's attacks home on enemies, and richochet to strike additional units.</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -24025,19 +24802,19 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Chilly Bit Striker</t>
+          <t>Porcus Maximus</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Upon Death - Unstable Flux (ANca)</t>
+          <t>Weak Ground Splash (A01V)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ANca</t>
+          <t>A01V</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -24047,27 +24824,27 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Upon death, the Unstable Flux banishes nearby enemies for 12 seconds. |n|nBanish turns enemies ethereal and slows their movement speed by 50% for 12 seconds. Ethereal creatures cannot attack, but they can cast spells and certain spells cast upon them will have a greater effect.</t>
+          <t>The tower's attacks splash when the missiles strike the enemy. The damage is distributed in the following radius from strongest to weakest: 25/50/75 |n|nSplash strikes ground units only.</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Unstable Flux</t>
+          <t>K Dig; Machination</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Activate / Deactivate Mana Detection (ANcl)</t>
+          <t>Ground Splash (A01W)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ANcl</t>
+          <t>A01W</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -24077,27 +24854,27 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Toggles the mana bar display for this tower.</t>
+          <t>The tower's attacks splash when the missiles strike the enemy. The damage is distributed in the following radius from strongest to weakest: 50/100/150 |n|nSplash strikes ground units only.</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Aspect of Cold; Arctic Blaster; Aspect of Fire</t>
+          <t>Grayson's Fort Buster; Xavier; Shrapnel Shooter</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Super Shock (ANfd)</t>
+          <t>Uber Ground Splash (A01X)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ANfd</t>
+          <t>A01X</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -24107,27 +24884,27 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Deals 18000 damage to target and completely heals the Blood Wraith.</t>
+          <t>The tower's attacks splash when the missiles strike the enemy. The damage is distributed in the following radius from strongest to weakest: 75/150/225 |n|nSplash strikes ground units only.</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Blood Wraith</t>
+          <t>Severe Trauma; Earth's Blood; Gigas Spike</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Forked Lightning (ANfl)</t>
+          <t>Supreme Ground Splash (A01Y)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ANfl</t>
+          <t>A01Y</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -24137,12 +24914,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Calls forth a cone of lightning at a target enemy unit, hitting up to &lt;ANfl,DataB1&gt; enemy units for &lt;ANfl,DataA1&gt; damage.</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>F</t>
+          <t>The tower's attacks splash when the missiles strike the enemy. The damage is distributed in the following radius from strongest to weakest: 150/0/0 |n|nSplash strikes ground units only.</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -24150,19 +24922,19 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Electrocutioner</t>
+          <t>Promontory Disruptor</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Healing Wave (ANhw)</t>
+          <t>Supreme Splash (A01Z)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ANhw</t>
+          <t>A01Z</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -24172,32 +24944,27 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Calls forth a wave of healing energy that bounces up to &lt;ANhw,DataB1&gt; times, healing &lt;ANhw,DataA1&gt; damage on the primary target.</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>e</t>
+          <t>The tower's attacks splash when the missiles strike the enemy. The damage is distributed in the following radius from strongest to weakest: 150/0/0 |n|nSplash strikes air and ground units.</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>K Dig; Xavier</t>
+          <t>Scarlet Ward</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Burnify (ANic)</t>
+          <t>Weak Splash (A020)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ANic</t>
+          <t>A020</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -24207,27 +24974,27 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Costs 6 mana per attack, else the Duke will stop.|n|nEach attack made is enhanced with living flames that cling to the target. These flames add &lt;ANic,DataA1&gt; damage on the first attack, twice as much on the second attack, three times as much on the third attack, etc.|n|nIf a unit dies while under this effect, it is incinerated, causing up to &lt;ANic,DataB1&gt; damage to all nearby hostile units.</t>
+          <t>The tower's attacks splash when the missiles strike the enemy. The damage is distributed in the following radius from strongest to weakest: 25/50/75 |n|nSplash strikes air and ground units.</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Duke Burnify</t>
+          <t>Shinobi; Lasher; Baby Dragon Den</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Electromagnetic Aura (AOr2)</t>
+          <t>Splash (A021)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AOr2</t>
+          <t>A021</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -24237,27 +25004,27 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Decreases nearby non-boss enemy units' movement speed and attack rate by 5%.</t>
+          <t>The tower's attacks splash when the missiles strike the enemy. The damage is distributed in the following radius from strongest to weakest: 50/100/150 |n|nSplash strikes air and ground units.</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Unstable Flux</t>
+          <t>Orobos Slave; Sewage Surprise; Frigid Dryad</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Apxf</t>
+          <t>Uber Splash (A022)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Apxf</t>
+          <t>A022</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -24265,24 +25032,29 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>The tower's attacks splash when the missiles strike the enemy. The damage is distributed in the following radius from strongest to weakest: 75/150/225 |n|nSplash strikes air and ground units.</t>
+        </is>
+      </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Judgement Fire</t>
+          <t>The Unborn; Malachite Ward; Arcadia</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Arctic Blast</t>
+          <t>Aviary Degeneration (A024)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>A07S</t>
+          <t>A024</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -24292,7 +25064,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Blasts enemy units with a wave of frost that slows and damages nearby enemies for 120 damage.</t>
+          <t>Reduces the movement speed of nearby flying enemy units by 20%.</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -24300,19 +25072,19 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Arctic Blaster</t>
+          <t>Shrine of Isis</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Fire Volley (Aroc)</t>
+          <t>Sell Tower (A028)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Aroc</t>
+          <t>A028</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -24322,27 +25094,27 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Costs 6 mana per attack, else the Hydra will stop.|n|nThe fire hydra's attacks strike multiple enemies for 355 damage, maximum 1065 damage.</t>
+          <t>Sell this tower for 50% of what you paid, including upgrade costs. |n|nRoyal Family towers return 90%. |n|nDamaged towers will return only a % of the costs based on remaining HP.</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Fire Hydra</t>
+          <t>Brahma's Fix-it Shop; Equipped Peasant 1; Equipped Peasant 2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Arpm</t>
+          <t>Bash III (A02E)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Arpm</t>
+          <t>A02E</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -24352,7 +25124,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Restores &lt;Arpm,DataB1&gt; mana to nearby friendly units in a 250 radius.</t>
+          <t>Gives a 33% chance that an attack will do 1500 bonus damage and stun a non-hero ground creep for 3 seconds.</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -24360,19 +25132,19 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Mana Well</t>
+          <t>Icy Skewer</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Slow Poison I (Aspo)</t>
+          <t>Prison of Ice (A02U)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Aspo</t>
+          <t>A02U</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -24382,27 +25154,27 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>A poison attack that deals 4 damage per second, and slows the target organic enemy's movement by 25%.|n|nAll poison types stacks with each other.</t>
+          <t>Absolute Zero's attacks freezes a target enemy for 3.5 seconds. During that time the enemy cannot move or attack.</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Spear Guard; Myrkridon Trow; War Beast</t>
+          <t>Absolute Zero</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Upon Death - Mana Well (Asth)</t>
+          <t>Gooify (A02X)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Asth</t>
+          <t>A02X</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -24412,7 +25184,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Upon death, the Mana Well will heal all nearby towers for 1000 HP.</t>
+          <t>Costs 6 mana per attack, else Krotas will stop.|n|nEach attack made is enhanced with living flames that cling to the target. These flames add 725 damage on the first attack, twice as much on the second attack, three times as much on the third attack, etc.|n|nIf a unit dies while under this effect, it is incinerated, causing up to 5000 damage to all nearby hostile units.|n|nUnits dealt a killing blow by Krotas will occasionally explode in a wave of frost that slows nearby enemies.</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -24420,19 +25192,19 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Mana Well</t>
+          <t>Krotas</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Upon Death - Phoenix (Atru)</t>
+          <t>Vindicator I (A02Y)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Atru</t>
+          <t>A02Y</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -24442,27 +25214,27 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Upon death, the Phoenix Spawn damages nearby enemies for 250 damage times the number of controlled Fire Reagents. This damage is not prevented by armor or abilities.</t>
+          <t>Gives a 50% chance to do 3.5 times normal damage on an attack. Crits against attacking units.</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Phoenix Spawn</t>
+          <t>Orobos Slave; Iron Mistress; Cloud Buster</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Foxfire Laser (AUcs)</t>
+          <t>Vindicator III (A02Z)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AUcs</t>
+          <t>A02Z</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -24472,27 +25244,27 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Upon acquiring an enemy target, the Foxfire Laser will channel a ball of destructive energy inside itself and release it at violent speeds. |nThe attack strikes enemies in a line for 290 damage for a maximum of 5800.</t>
+          <t>Gives a 50% chance to do 10 times normal damage on an attack. Crits against attacking units.</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Foxfire Laser</t>
+          <t>Hylgion Militia; Impervious Armor; Equipped Peasant 4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Aviary Degeneration</t>
+          <t>Vindicator II (A03C)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>A024</t>
+          <t>A03C</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -24502,27 +25274,27 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Reduces the movement speed of nearby flying enemy units by 20%.</t>
+          <t>Gives a 50% chance to do 6 times normal damage on an attack. Crits against attacking units.</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Shrine of Isis</t>
+          <t>Peasant; Bladesmith; Equipped Peasant 1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ball Lightning</t>
+          <t>Boss Assassin I (A03D)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>A07R</t>
+          <t>A03D</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -24532,27 +25304,27 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Hurls a bolt of electricity at target for 162 damage and jumps to strike 5 additional targets.</t>
+          <t>Deals 4x damage to heroes. Crits 50% of the time.</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Aspect of Lightning</t>
+          <t>Myrkridon Trow; Father Dragon; Hunter</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Bash III</t>
+          <t>Slow Aura I (A03M)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>A02E</t>
+          <t>A03M</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -24562,7 +25334,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Gives a 33% chance that an attack will do 1500 bonus damage and stun a non-hero ground creep for 3 seconds.</t>
+          <t>Decreases nearby enemy units' movement speed by 5% and attack rate by 5%.|nThis aura stacks with Slow Aura II.</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -24570,19 +25342,19 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Icy Skewer</t>
+          <t>Sapphire Ward</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Boss Assassin I</t>
+          <t>Slow Aura II (A03N)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>A03D</t>
+          <t>A03N</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -24592,27 +25364,27 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Deals 4x damage to heroes. Crits 50% of the time.</t>
+          <t>Decreases nearby enemy units' movement speed by 10% and attack rate by 10%.|nThis aura stacks with Slow Aura I.</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Myrkridon Trow; Hunter; Jailing Officer</t>
+          <t>Purity Ward</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Boss Assassin II</t>
+          <t>Toughness Aura II (A03P)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>A00R</t>
+          <t>A03P</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -24622,27 +25394,27 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Deals 8x damage to heroes. Crits 50% of the time.</t>
+          <t>Gives 3 additional armor to nearby friendly towers.|nThis aura stacks with Toughness Aura I.</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Marksman; Ignatious; Astral Skibi</t>
+          <t>Roseate Ward</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Calamity</t>
+          <t>Repel Aura (A03Q)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>A00B</t>
+          <t>A03Q</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -24652,7 +25424,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Slams the ground, dealing no damage to nearby ground units in a large radius, but slowing them for 15 seconds by 15%.|nDoes not stack with Vacuum Torpedo.</t>
+          <t>Decreases nearby attacking ground enemy units' attack rates by 20%.</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -24660,19 +25432,19 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Apocalypse</t>
+          <t>Repel</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Collapse</t>
+          <t>Missile Salvo I (A03R)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>A019</t>
+          <t>A03R</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -24682,7 +25454,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Strikes from underneath the ground with a terribly powerful tentacle, permanently lowering a non-hero ground unit's movement speed to the minimum amount.</t>
+          <t>Fires a secondary volley of boulders that target nearby enemies.</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -24690,19 +25462,19 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Glacial Spike</t>
+          <t>Bombardment</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Combustion</t>
+          <t>Missile Salvo II (A03S)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>A014</t>
+          <t>A03S</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -24712,27 +25484,27 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Increases the tower's attack rate by up to 50% for 15 seconds.</t>
+          <t>Fires a secondary volley of missiles that target nearby enemies.</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Aspect of Fire; Scalding Tower; Fire Hydra</t>
+          <t>Interceptor Factory</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cure All</t>
+          <t>Cure I (A03U)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>A00X</t>
+          <t>A03U</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -24742,27 +25514,27 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Instantly heals the allies' buildings for 250. |n|nAffects allied buildings.</t>
+          <t>Heals a target friendly tower for 1500 HP.|n|nCooldown = 50 seconds.</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Protection Ward; Roseate Ward</t>
+          <t>Frigid Dryad; The Pride of Moon Star; Slammer</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cure I</t>
+          <t>Cure II (A03V)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>A03U</t>
+          <t>A03V</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -24772,7 +25544,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Heals a target friendly tower for 1500 HP.|n|nCooldown = 50 seconds.</t>
+          <t>Heals a target friendly tower for 2500 HP. |n|nCooldown = 35 seconds.</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -24780,19 +25552,19 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Frigid Dryad; The Pride of Moon Star; Slammer</t>
+          <t>Delfino; Evolved Dweller; High Priest</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cure II</t>
+          <t>Regeneration (A03W)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>A03V</t>
+          <t>A03W</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -24802,7 +25574,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Heals a target friendly tower for 2500 HP. |n|nCooldown = 35 seconds.</t>
+          <t>This tower regenerates 12 HP per second.</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -24810,19 +25582,19 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Delfino; Evolved Dweller; High Priest</t>
+          <t>Exiled Soul; Quickshot; Cross Bow</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Curse Boss I</t>
+          <t>Air Slow Poison (A03X)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>A01H</t>
+          <t>A03X</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -24832,7 +25604,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Cuts at the heart of evil, and reduces an enemy boss's movement speed by a small portion.|nThis curse stacks with itself.</t>
+          <t>A non-lethal poison that slows the target organic air enemy's movement by 70%.|n|nAll poison types stacks with each other.</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -24840,19 +25612,19 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Lilac Ward</t>
+          <t>Ignatious</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Curse Boss II</t>
+          <t>Machine Critical Strike (A03Y)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>A01G</t>
+          <t>A03Y</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -24862,27 +25634,27 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Cuts at the heart of evil, and reduces an enemy boss's movement speed by a medium portion.|nThis curse stacks with itself.</t>
+          <t>Gives a 40% chance to do 3 times normal damage on an attack. Crits against mechanical units only.</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Malachite Ward</t>
+          <t>Brahma's Fix-it Shop; Sewage Surprise; Xavier</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Death Strike</t>
+          <t>Fortitude (A047)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>A047</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -24892,27 +25664,27 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>The Death Dragon's attack instantly kills a non-hero ground unit.</t>
+          <t>This unit has above average hitpoints and armor when compared to other towers of its tier.</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Death Dragon</t>
+          <t>Bladesmith; Impervious Armor; Evolved Dweller</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Fortitude</t>
+          <t>Super Regeneration (A070)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>A047</t>
+          <t>A070</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -24922,27 +25694,27 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>This unit has above average hitpoints and armor when compared to other towers of its tier.</t>
+          <t>This tower regenerates 45 HP per second.</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Bladesmith; Impervious Armor; Evolved Dweller</t>
+          <t>Brahma's Fix-it Shop</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Frost II</t>
+          <t>Sacrifice (A07P)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>A002</t>
+          <t>A07P</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -24952,7 +25724,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Adds a cold effect to this unit's attacks that slows enemy units' movement speed for a medium period of time.</t>
+          <t>Sacrifice this tower, activating its on-death ability.</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -24960,19 +25732,19 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>D-String; Apocalypse; Frozen Reaper</t>
+          <t>Mana Well; Phoenix Spawn; Unstable Flux</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Gravity Well</t>
+          <t>Ball Lightning (A07R)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>A00V</t>
+          <t>A07R</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -24982,27 +25754,27 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Rips the fabric and essence from those that stand on the same ground as her ladyship. Enemy life is reduced by about 10% and movement speed permanently is cut by 5%. This damage cannot be prevented or reduced.</t>
+          <t>Hurls a bolt of electricity at target for 162 damage and jumps to strike 5 additional targets.</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Lilianna Mai; Astral Skibi</t>
+          <t>Aspect of Lightning</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Ground Critical Strike I</t>
+          <t>Arctic Blast (A07S)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>A003</t>
+          <t>A07S</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -25012,27 +25784,27 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Gives a 35% chance to do 2 times normal damage on an attack. Crits against ground only.</t>
+          <t>Blasts enemy units with a wave of frost that slows and damages nearby enemies for 120 damage.</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Duke Burnify; Chibidevil; Stealth Maiden</t>
+          <t>Arctic Blaster</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Ground Critical Strike II</t>
+          <t>Tsukikaze (A07T)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>A00A</t>
+          <t>A07T</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -25042,7 +25814,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>The Destroyer possesses the heart of a lion, and has a 50% chance to deal 5x damage to ground enemies.</t>
+          <t>Hurts a bolt of electricity at target for 3700 damage and jumps to strike 10 additional targets.</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -25050,19 +25822,19 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Unrivaled Destroyer</t>
+          <t>Tsukikaze Warrior</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ground Splash</t>
+          <t>Soothe Foundation (A080)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>A01W</t>
+          <t>A080</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -25072,27 +25844,27 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>The tower's attacks splash when the missiles strike the enemy. The damage is distributed in the following radius from strongest to weakest: 50/100/150 |n|nSplash strikes ground units only.</t>
+          <t>Restores 15 hit points to nearby friendly units in a very large radius.</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Grayson's Fort Buster; Xavier; Shrapnel Shooter</t>
+          <t>Rebuilder</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Improved Glacial Spike</t>
+          <t>(Dummy Ability - Life Steal) (Aabr)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>S000</t>
+          <t>Aabr</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -25102,27 +25874,27 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Increases the attack speed of Glacial Spikes by 30%.</t>
+          <t>This tower's attack heals itself for a portion of damage dealt to enemy ground units.</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Glacial Spike</t>
+          <t>Heartseeker; Chibidevil; Poison Dragon</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Improved Ward</t>
+          <t>Freezing Field (Aamk)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>Aamk</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -25132,27 +25904,27 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Increases the attack speed of this Ward by 20%.</t>
+          <t>Costs 30 mana per attack, else the Field will stop.|n|nFreezing Field attacks deal 575 frost damage to nearby enemies and slows their movement rate and attack speed for 3 seconds.</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Sapphire Ward; Purity Ward; Lilac Ward</t>
+          <t>Freezing Field</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Judgement</t>
+          <t>Grounding Curse (Aap1)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>A00N</t>
+          <t>Aap1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -25162,27 +25934,27 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Burns nearby enemy air units over time. Deals 100 damage per second. |nLasts 20 seconds.</t>
+          <t>Damages nearby enemy ground units over time with a lightning curse. Deals 1000 damage per second. |nLasts 12 seconds.</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>High Priest; Martyr</t>
+          <t>Von Chillspeak</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Machine Critical Strike</t>
+          <t>Bash II (ACbh)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>A03Y</t>
+          <t>ACbh</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -25192,7 +25964,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Gives a 40% chance to do 3 times normal damage on an attack. Crits against mechanical units only.</t>
+          <t>Gives a 20% chance that an attack will do 235 bonus damage and stun a non-hero ground creep for 2 seconds.</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -25200,19 +25972,19 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Xavier; Sewer Barge; Frankenstone</t>
+          <t>Impervious Armor; Captain Bartlebee; Battleship Mackinaw</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Missile Salvo I</t>
+          <t>Thresh Arrow (ACca)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>A03R</t>
+          <t>ACca</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -25222,7 +25994,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Fires a secondary volley of boulders that target nearby enemies.</t>
+          <t>When Havocwing attacks, she tightens the pressure her bow and releases it in a blazing path. |nThe attack strikes enemies in a line for 475 damage.</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -25230,19 +26002,19 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Bombardment</t>
+          <t>Havocwing</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Missile Salvo II</t>
+          <t>Healing Aura (ACce)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>A03S</t>
+          <t>ACce</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -25252,7 +26024,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Fires a secondary volley of missiles that target nearby enemies.</t>
+          <t>The Village Medic heals himself and nearby friendly towers for 2 hitpoints a second. Radius measured in game as under 800 (owner 2026-09-10); the tooltip states none.</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -25260,19 +26032,19 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Interceptor Factory</t>
+          <t>Village Medic</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Multiple Shot</t>
+          <t>Hunter's Fervor (ACcl)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>A01M</t>
+          <t>ACcl</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -25282,27 +26054,27 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>The tower's attacks home on enemies, and richochet to strike additional units.</t>
+          <t>Hurls a devastating ray of power that ricochets off the first foe and strikes 14 others at 5% less power. Deals 3000 on the first strike.</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Porcus Maximus</t>
+          <t>Mercurial Predator; Unrivaled Destroyer</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Prison of Ice</t>
+          <t>Winter's Bite (ACcw)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>A02U</t>
+          <t>ACcw</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -25312,7 +26084,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Absolute Zero's attacks freezes a target enemy for 3.5 seconds. During that time the enemy cannot move or attack.</t>
+          <t>Adds 54 cold damage to an attack and slows target, but drains mana with each shot fired.</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -25320,19 +26092,19 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Absolute Zero</t>
+          <t>Aspect of Cold</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Rail Driver</t>
+          <t>Empathic Fix (AChv)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>A00O</t>
+          <t>AChv</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -25342,7 +26114,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Summons two ethereal hands to erupt from the earth that instantly kills a non-hero ground unit.</t>
+          <t>The unselfish Tinker "Brahma" attempts to fix a friendly tower for all its damage, but in the process damages his Shop for (1.5 * damage). This penalty is not applied if this spell is used to fix another Brahma Shop. |n|nThis spell will never take Brahma's Shop below 150 life.</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -25350,19 +26122,19 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Delphinus</t>
+          <t>Brahma's Fix-it Shop</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Regeneration</t>
+          <t>Fury of the Gods (ACmo)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>A03W</t>
+          <t>ACmo</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -25372,27 +26144,27 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>This tower regenerates 12 HP per second.</t>
+          <t>Calls down a storm of lightning to strike enemy units for 580 damage in a target area. |nLasts 10 seconds.</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Quickshot; Cross Bow; Frankenstone</t>
+          <t>Kazaana</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Repel Aura</t>
+          <t>Moon Stone Cannon (ACsh)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>A03Q</t>
+          <t>ACsh</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -25402,7 +26174,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Decreases nearby attacking ground enemy units' attack rates by 20%.</t>
+          <t>Matter evaporates when the potent forces of this attack strikes flesh. Deals 1250 damage to units in a line. Very fast cooldown.</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -25410,19 +26182,19 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Repel</t>
+          <t>Delphinus</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sacrifice</t>
+          <t>Vampiric Aura (ACvp)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>A07P</t>
+          <t>ACvp</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -25432,27 +26204,32 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Sacrifice this tower, activating its on-death ability.</t>
+          <t>Vampiric Aura (Passive)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Mana Well; Phoenix Spawn; Unstable Flux</t>
+          <t>Reaperspawn</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sloth I</t>
+          <t>Starburst (AEsf)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>A01I</t>
+          <t>AEsf</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -25462,7 +26239,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1/5th of this tower's attacks reduces a target creep's HP by 15% and permanently reduces movement speed by a medium amount. |n|nThis curse stacks with itself.</t>
+          <t>Calls down waves of falling stars that damage nearby enemy units in a huge radius. Each wave deals 1200 damage. |nCooldown = 15 seconds.</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -25470,19 +26247,19 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Ochre Ward</t>
+          <t>Star Buster</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sloth II</t>
+          <t>Life Boon (AEtq)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>A01A</t>
+          <t>AEtq</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -25492,7 +26269,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>1/5th of this tower's attacks reduces a target creep's HP by 25% and permanently reduces movement speed by a large amount. |n|nThis curse stacks with itself.</t>
+          <t>Heals 30 HP per second for 30 seconds — 900 HP total. The map names this ability but leaves its description EMPTY, so the owner's in-game read (2026-09-10) is the only source.</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -25500,19 +26277,19 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Scarlet Ward</t>
+          <t>General Ninpou</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Slow Aura I</t>
+          <t>Sunder Armor (Afbb)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>A03M</t>
+          <t>Afbb</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -25522,7 +26299,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Decreases nearby enemy units' movement speed by 5% and attack rate by 5%.|nThis aura stacks with Slow Aura II.</t>
+          <t>Heartseeker attacks have a chance to reduce the victim's armor by 3. This effect stacks up to 3 times.</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -25530,19 +26307,19 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Sapphire Ward</t>
+          <t>Heartseeker</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Slow Aura II</t>
+          <t>Frost I (Afra)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>A03N</t>
+          <t>Afra</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -25552,27 +26329,27 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Decreases nearby enemy units' movement speed by 10% and attack rate by 10%.|nThis aura stacks with Slow Aura I.</t>
+          <t>Adds a cold effect to this unit's attacks that slows enemy units' movement speed for a short period of time</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Purity Ward</t>
+          <t>Shinobi; Orobos Slave; Impervious Armor</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Slow Poison II</t>
+          <t>Stone Cold (Afrz)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>A008</t>
+          <t>Afrz</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -25582,27 +26359,27 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>A vicious poison attack that deals 36 damage per second, and slows the target organic enemy's movement by 40%.|n|nAll poison types stacks with each other.</t>
+          <t>Costs 175 mana per attack, else Von Chillspeak will stop.|n|nVon Chillspeak's attacks freeze a target enemy for 6.5 seconds. During that time the enemy cannot move or attack.</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Axeman; Ruthless Warlord; Jailing Officer</t>
+          <t>Von Chillspeak</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Slow Poison III</t>
+          <t>Toughness Aura I (AHad)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>A00T</t>
+          <t>AHad</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -25612,27 +26389,27 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>A poison attack that deals 250 damage per second, and slows the target organic enemy's movement by 65%.|n|nAll poison types stacks with each other.</t>
+          <t>Gives 2 additional armor to nearby friendly towers.|nThis aura stacks with Toughness Aura II.</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Toxic Assassin; Peppy Bronzebeard</t>
+          <t>Protection Ward</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Soothe Foundation</t>
+          <t>Divine Shield (AHds)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>A080</t>
+          <t>AHds</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -25642,27 +26419,32 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Restores 15 hit points to nearby friendly units in a very large radius.</t>
+          <t>Divine Shield</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Rebuilder</t>
+          <t>Lilianna Mai; Astral Skibi</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Splash</t>
+          <t>Kiss of Flame (AHfa)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>A021</t>
+          <t>AHfa</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -25672,27 +26454,27 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>The tower's attacks splash when the missiles strike the enemy. The damage is distributed in the following radius from strongest to weakest: 50/100/150 |n|nSplash strikes air and ground units.</t>
+          <t>Adds 83 bonus fire damage to an attack against enemies, but drains mana with each shot fired.</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Orobos Slave; Frigid Dryad; Iron Mistress</t>
+          <t>Aspect of Fire</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Supine Hex I</t>
+          <t>Area Cure (AIha)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>A01B</t>
+          <t>AIha</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -25702,7 +26484,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>This ward's power permanently reduces a non-hero enemy's movement speed by 7. |n|nThis curse stacks with itself.</t>
+          <t>Heals &lt;AIha,DataA1&gt; hit points to all friendly structures around the caster when used.</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -25710,19 +26492,19 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Sapphire Ward</t>
+          <t>Magical Breakthrough</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Supine Hex II</t>
+          <t>Electrify (AIhb)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>A01C</t>
+          <t>AIhb</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -25732,27 +26514,27 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>This ward's power permanently reduces a non-hero enemy's movement speed by 12. |n|nThis curse stacks with itself.</t>
+          <t>Restores this tower's spell cooldown.</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Purity Ward</t>
+          <t>Aspect of Lightning; Electrocutioner; Blood Wraith</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Supreme Ground Splash</t>
+          <t>Cold Snap (AIm2)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>A01Y</t>
+          <t>AIm2</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -25762,27 +26544,27 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>The tower's attacks splash when the missiles strike the enemy. The damage is distributed in the following radius from strongest to weakest: 150/0/0 |n|nSplash strikes ground units only.</t>
+          <t>Restores this tower's MP completely.</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Promontory Disruptor</t>
+          <t>Aspect of Cold; Arctic Blaster; Chilly Bit Striker</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Supreme Splash</t>
+          <t>AIva</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>A01Z</t>
+          <t>AIva</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -25790,29 +26572,24 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>The tower's attacks splash when the missiles strike the enemy. The damage is distributed in the following radius from strongest to weakest: 150/0/0 |n|nSplash strikes air and ground units.</t>
-        </is>
-      </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Scarlet Ward</t>
+          <t>Heartseeker; Chibidevil</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Tornado Shot</t>
+          <t>Phoenix Income (Amgl)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>A00Q</t>
+          <t>Amgl</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -25822,27 +26599,27 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Summons 6 fast moving tornados whirling shrapnel and dust every second for 10 seconds. |nDamages air units in a small area of effect for 100 damage.</t>
+          <t>You gain 1 gold for controlling this Phoenix Spawn after every Wave.</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Little Jack; Battleship Mackinaw</t>
+          <t>Phoenix Spawn</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Toughness Aura II</t>
+          <t>Phoenix Fire (Amgr)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>A03P</t>
+          <t>Amgr</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -25852,7 +26629,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Gives 3 additional armor to nearby friendly towers.|nThis aura stacks with Toughness Aura I.</t>
+          <t>Fires a stream of flame, lighting the primary target enemy on fire and burns it over time. Deals 50 damage a second for 5 seconds.</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -25860,19 +26637,19 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Roseate Ward</t>
+          <t>Judgement Fire</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Tsukikaze</t>
+          <t>Scald (ANbf)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>A07T</t>
+          <t>ANbf</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -25882,7 +26659,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Hurts a bolt of electricity at target for 3700 damage and jumps to strike 10 additional targets.</t>
+          <t>Erupt a cone of fire at enemy units, dealing 110 damage. Max damage = 660.</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -25890,19 +26667,19 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Tsukikaze Warrior</t>
+          <t>Scalding Tower</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Uber Ground Splash</t>
+          <t>Bash I (ANbh)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>A01X</t>
+          <t>ANbh</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -25912,27 +26689,27 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>The tower's attacks splash when the missiles strike the enemy. The damage is distributed in the following radius from strongest to weakest: 75/150/225 |n|nSplash strikes ground units only.</t>
+          <t>Gives a 20% chance that an attack will do 50 bonus damage and stun a non-hero ground creep for 1.5 seconds.</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Severe Trauma; Earth's Blood; Gigas Spike</t>
+          <t>Myrkridon Trow; Insurrectionist Trow; Equipped Peasant 5</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Uber Splash</t>
+          <t>Chilly Bits Grade Peorth (ANc1)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>A022</t>
+          <t>ANc1</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -25942,27 +26719,27 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>The tower's attacks splash when the missiles strike the enemy. The damage is distributed in the following radius from strongest to weakest: 75/150/225 |n|nSplash strikes air and ground units.</t>
+          <t>Bombards an area with pure chaos, stunning enemies within an area for 1 second and dealing up to 800 damage.</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>The Unborn; Malachite Ward; Arcadia</t>
+          <t>Chilly Bit Striker</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Vacuum Torpedo</t>
+          <t>Upon Death - Unstable Flux (ANca)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>A00P</t>
+          <t>ANca</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -25972,7 +26749,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Fires a torpedo straight into the soft earth that implodes the ground. The ethereal force ripples from Delphinus dealing 150 points of damage and greatly slows ground enemies for 8 seconds.|nDoes not stack with Calamity.</t>
+          <t>Upon death, the Unstable Flux banishes nearby enemies for 12 seconds. |n|nBanish turns enemies ethereal and slows their movement speed by 50% for 12 seconds. Ethereal creatures cannot attack, but they can cast spells and certain spells cast upon them will have a greater effect.</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -25980,19 +26757,19 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Delphinus</t>
+          <t>Unstable Flux</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Versatile Critical Strike I</t>
+          <t>Activate / Deactivate Mana Detection (ANcl)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>A004</t>
+          <t>ANcl</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -26002,27 +26779,27 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Gives a 35% chance to do 2.5 times normal damage on an attack. Crits against all units.</t>
+          <t>Toggles the mana bar display for this tower.</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Axeman; General Ninpou; Quickshot</t>
+          <t>Aspect of Cold; Arctic Blaster; Aspect of Fire</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Versatile Critical Strike II</t>
+          <t>Super Shock (ANfd)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>A01E</t>
+          <t>ANfd</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -26032,27 +26809,27 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Gives a 60% chance to do 2.75 times normal damage on an attack. Crits against all units.</t>
+          <t>Deals 18000 damage to target and completely heals the Blood Wraith.</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Cross Bow; D-String</t>
+          <t>Blood Wraith</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Vindicator I</t>
+          <t>Forked Lightning (ANfl)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>A02Y</t>
+          <t>ANfl</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -26062,27 +26839,32 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Gives a 50% chance to do 3.5 times normal damage on an attack. Crits against attacking units.</t>
+          <t>Calls forth a cone of lightning at a target enemy unit, hitting up to &lt;ANfl,DataB1&gt; enemy units for &lt;ANfl,DataA1&gt; damage.</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Orobos Slave; Iron Mistress; Cloud Buster</t>
+          <t>Electrocutioner</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Vindicator II</t>
+          <t>Healing Wave (ANhw)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>A03C</t>
+          <t>ANhw</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -26092,27 +26874,32 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Gives a 50% chance to do 6 times normal damage on an attack. Crits against attacking units.</t>
+          <t>Calls forth a wave of healing energy that bounces up to &lt;ANhw,DataB1&gt; times, healing &lt;ANhw,DataA1&gt; damage on the primary target.</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>e</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Peasant; Bladesmith; The Unborn</t>
+          <t>K Dig; Xavier</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Vindicator III</t>
+          <t>Burnify (ANic)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>A02Z</t>
+          <t>ANic</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -26122,27 +26909,27 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Gives a 50% chance to do 10 times normal damage on an attack. Crits against attacking units.</t>
+          <t>Costs 6 mana per attack, else the Duke will stop.|n|nEach attack made is enhanced with living flames that cling to the target. These flames add &lt;ANic,DataA1&gt; damage on the first attack, twice as much on the second attack, three times as much on the third attack, etc.|n|nIf a unit dies while under this effect, it is incinerated, causing up to &lt;ANic,DataB1&gt; damage to all nearby hostile units.</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Hylgion Militia; Impervious Armor; Severe Trauma</t>
+          <t>Duke Burnify</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Weak Ground Splash</t>
+          <t>Electromagnetic Aura (AOr2)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>A01V</t>
+          <t>AOr2</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -26152,27 +26939,27 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>The tower's attacks splash when the missiles strike the enemy. The damage is distributed in the following radius from strongest to weakest: 25/50/75 |n|nSplash strikes ground units only.</t>
+          <t>Decreases nearby non-boss enemy units' movement speed and attack rate by 5%.</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>K Dig; Machination</t>
+          <t>Unstable Flux</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Weak Splash</t>
+          <t>Apxf</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>A020</t>
+          <t>Apxf</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -26180,22 +26967,257 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>The tower's attacks splash when the missiles strike the enemy. The damage is distributed in the following radius from strongest to weakest: 25/50/75 |n|nSplash strikes air and ground units.</t>
-        </is>
-      </c>
       <c r="G105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Shinobi; Lasher; Baby Dragon Den</t>
+          <t>Judgement Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Fire Volley (Aroc)</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Aroc</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Costs 6 mana per attack, else the Hydra will stop.|n|nThe fire hydra's attacks strike multiple enemies for 355 damage, maximum 1065 damage.</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Fire Hydra</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Arpm</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Arpm</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Restores &lt;Arpm,DataB1&gt; mana to nearby friendly units in a 250 radius.</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Mana Well</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Slow Poison I (Aspo)</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Aspo</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>A poison attack that deals 4 damage per second, and slows the target organic enemy's movement by 25%.|n|nAll poison types stacks with each other.</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>16</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Spear Guard; Myrkridon Trow; War Beast</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Upon Death - Mana Well (Asth)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Asth</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Upon death, the Mana Well will heal all nearby towers for 1000 HP.</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Mana Well</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Upon Death - Phoenix (Atru)</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Atru</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Upon death, the Phoenix Spawn damages nearby enemies for 250 damage times the number of controlled Fire Reagents. This damage is not prevented by armor or abilities.</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Phoenix Spawn</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Foxfire Laser (AUcs)</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>AUcs</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Upon acquiring an enemy target, the Foxfire Laser will channel a ball of destructive energy inside itself and release it at violent speeds. |nThe attack strikes enemies in a line for 290 damage for a maximum of 5800.</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Foxfire Laser</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Improved Glacial Spike (S000)</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>S000</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Increases the attack speed of Glacial Spikes by 30%.</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Glacial Spike</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Improved Ward (S001)</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>S001</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Increases the attack speed of this Ward by 20%.</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>4</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sapphire Ward; Purity Ward; Lilac Ward</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I105"/>
+  <autoFilter ref="A1:I113"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -37943,13 +38965,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -38076,31 +39098,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aspect of Lightning</t>
+          <t>Scalding Tower</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ball Lightning</t>
+          <t>Scald</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>162</v>
+        <v>110</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>0.6</v>
       </c>
       <c r="H3" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -38108,10 +39130,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>48.6</v>
+        <v>47.3</v>
       </c>
       <c r="L3" t="n">
-        <v>3.24</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="4">
@@ -38122,46 +39144,316 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Aspect of Lightning</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Ball Lightning</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>162</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H4" t="n">
+        <v>50</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>arcane</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Chilly Bit Striker</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>230</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Chilly Bits Grade Peorth</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>800</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>95</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>58</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>arcane</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Blood Wraith</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>270</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Super Shock</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>105</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>857.1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3.17</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>arcane</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Tsukikaze Warrior</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C7" t="n">
         <v>550</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Tsukikaze</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E7" t="n">
         <v>3700</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F7" t="n">
         <v>11</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G7" t="n">
         <v>6</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H7" t="n">
         <v>225</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I7" t="n">
         <v>7.5</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>mana</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="K7" t="n">
         <v>1356.7</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L7" t="n">
         <v>2.47</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>scarlet_knight</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Foxfire Laser</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>235</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Foxfire Laser</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>290</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>217.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>scarlet_knight</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kazaana</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>280</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Fury of the Gods</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>580</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>cooldown</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>29</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tempest</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Havocwing</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>230</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Thresh Arrow</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>475</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mana</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>316.7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L4"/>
+  <autoFilter ref="A1:L10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -40133,7 +41425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW20"/>
+  <dimension ref="A1:AX20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -40185,6 +41477,7 @@
     <col width="9" customWidth="1" min="47" max="47"/>
     <col width="15" customWidth="1" min="48" max="48"/>
     <col width="22" customWidth="1" min="49" max="49"/>
+    <col width="14" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -40433,6 +41726,11 @@
           <t>dps_per_gold_x_range</t>
         </is>
       </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dps_source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -40461,7 +41759,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Vindicator II</t>
+          <t>Vindicator II (A03C)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -40560,6 +41858,11 @@
         <f>IF(D2=0,"",AQ2*(N2/725))</f>
         <v/>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -40588,7 +41891,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Vindicator III</t>
+          <t>Vindicator III (A02Z)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -40687,6 +41990,11 @@
         <f>IF(D3=0,"",AQ3*(N3/725))</f>
         <v/>
       </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -40715,7 +42023,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Air Critical Strike I; Slow Poison I (Aspo)</t>
+          <t>Air Critical Strike I (A005); Slow Poison I (Aspo)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -40817,6 +42125,11 @@
         <f>IF(D4=0,"",AQ4*(N4/725))</f>
         <v/>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -40845,7 +42158,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Versatile Critical Strike I; Slow Poison II</t>
+          <t>Versatile Critical Strike I (A004); Slow Poison II (A008)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -40947,6 +42260,11 @@
         <f>IF(D5=0,"",AQ5*(N5/725))</f>
         <v/>
       </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -40975,7 +42293,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Weak Splash; Frost I (Afra)</t>
+          <t>Weak Splash (A020); Frost I (Afra)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -41079,6 +42397,11 @@
         <f>IF(D6=0,"",AQ6*(N6/725))</f>
         <v/>
       </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -41107,7 +42430,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Splash; Vindicator I; Frost I (Afra)</t>
+          <t>Splash (A021); Vindicator I (A02Y); Frost I (Afra)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -41216,6 +42539,11 @@
         <f>IF(D7=0,"",AQ7*(N7/725))</f>
         <v/>
       </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -41239,7 +42567,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Slow Poison II</t>
+          <t>Slow Poison II (A008)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -41341,6 +42669,11 @@
         <f>IF(D8=0,"",AQ8*(N8/725))</f>
         <v/>
       </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -41463,6 +42796,11 @@
         <f>IF(D9=0,"",AQ9*(N9/725))</f>
         <v/>
       </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -41491,7 +42829,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Boss Assassin II</t>
+          <t>Boss Assassin II (A00R)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -41595,6 +42933,11 @@
         <f>IF(D10=0,"",AQ10*(N10/725))</f>
         <v/>
       </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -41623,7 +42966,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Air Critical Strike II</t>
+          <t>Air Critical Strike II (A006)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -41727,6 +43070,11 @@
         <f>IF(D11=0,"",AQ11*(N11/725))</f>
         <v/>
       </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -41755,7 +43103,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Fortitude; Vindicator II</t>
+          <t>Fortitude (A047); Vindicator II (A03C)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -41854,6 +43202,11 @@
         <f>IF(D12=0,"",AQ12*(N12/725))</f>
         <v/>
       </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -41882,7 +43235,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Fortitude; Vindicator III; Bash II (ACbh); Frost I (Afra)</t>
+          <t>Fortitude (A047); Vindicator III (A02Z); Bash II (ACbh); Frost I (Afra)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -41981,6 +43334,11 @@
         <f>IF(D13=0,"",AQ13*(N13/725))</f>
         <v/>
       </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -42004,7 +43362,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Life Boon (AEtq); Frost I (Afra); Versatile Critical Strike I</t>
+          <t>Life Boon (AEtq); Frost I (Afra); Versatile Critical Strike I (A004)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -42103,6 +43461,11 @@
         <f>IF(D14=0,"",AQ14*(N14/725))</f>
         <v/>
       </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -42131,7 +43494,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Bash I (ANbh); Boss Assassin I; Slow Poison I (Aspo)</t>
+          <t>Bash I (ANbh); Boss Assassin I (A03D); Slow Poison I (Aspo)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -42236,6 +43599,11 @@
         <f>IF(D15=0,"",AQ15*(N15/725))</f>
         <v/>
       </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -42376,6 +43744,11 @@
         <f>IF(D16=0,"",AQ16*(N16/725))</f>
         <v/>
       </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -42404,7 +43777,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Air Critical Strike I; Slow Poison I (Aspo)</t>
+          <t>Air Critical Strike I (A005); Slow Poison I (Aspo)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -42506,6 +43879,11 @@
         <f>IF(D17=0,"",AQ17*(N17/725))</f>
         <v/>
       </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -42534,7 +43912,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Air Critical Strike II; Slow Poison III</t>
+          <t>Air Critical Strike II (A006); Slow Poison III (A00T)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -42668,6 +44046,11 @@
         <f>IF(D18=0,"",AQ18*(N18/725))</f>
         <v/>
       </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -42696,7 +44079,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Air Deficiency; Hunter's Fervor (ACcl)</t>
+          <t>Air Deficiency (A009); Hunter's Fervor (ACcl)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -42792,6 +44175,11 @@
         <f>IF(D19=0,"",AQ19*(N19/725))</f>
         <v/>
       </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -42820,7 +44208,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Hunter's Fervor (ACcl); Ground Critical Strike II</t>
+          <t>Hunter's Fervor (ACcl); Ground Critical Strike II (A00A)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -42919,9 +44307,14 @@
         <f>IF(D20=0,"",AQ20*(N20/725))</f>
         <v/>
       </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>basic attack</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AW20"/>
+  <autoFilter ref="A1:AX20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/skibi-data.xlsx
+++ b/skibi-data.xlsx
@@ -58,7 +58,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -91,9 +93,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -786,33 +790,36 @@
       <c r="Z2" t="n">
         <v>0</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AA2" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="AL2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM2">
+      <c r="AK2" s="2" t="n"/>
+      <c r="AL2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM2" s="2">
         <f>AK2*AL2</f>
         <v/>
       </c>
-      <c r="AN2">
+      <c r="AN2" s="3">
         <f>IF(D2=0,"",AS2/D2)</f>
         <v/>
       </c>
-      <c r="AO2">
+      <c r="AO2" s="3">
         <f>(N2/725)^2</f>
         <v/>
       </c>
-      <c r="AP2">
+      <c r="AP2" s="3">
         <f>IF(D2=0,"",AN2*AO2)</f>
         <v/>
       </c>
-      <c r="AS2">
+      <c r="AQ2" s="2" t="n"/>
+      <c r="AR2" s="2" t="n"/>
+      <c r="AS2" s="2">
         <f>AM2+N(AQ2)+N(AR2)</f>
         <v/>
       </c>
-      <c r="AT2">
+      <c r="AT2" s="3">
         <f>IF(D2=0,"",AN2*(N2/725))</f>
         <v/>
       </c>
@@ -860,36 +867,38 @@
       <c r="Z3" t="n">
         <v>1</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AA3" s="2" t="n">
         <v>1250</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AK3" s="2" t="n">
         <v>39.8</v>
       </c>
-      <c r="AL3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM3">
+      <c r="AL3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" s="2">
         <f>AK3*AL3</f>
         <v/>
       </c>
-      <c r="AN3">
+      <c r="AN3" s="3">
         <f>IF(D3=0,"",AS3/D3)</f>
         <v/>
       </c>
-      <c r="AO3">
+      <c r="AO3" s="3">
         <f>(N3/725)^2</f>
         <v/>
       </c>
-      <c r="AP3">
+      <c r="AP3" s="3">
         <f>IF(D3=0,"",AN3*AO3)</f>
         <v/>
       </c>
-      <c r="AS3">
+      <c r="AQ3" s="2" t="n"/>
+      <c r="AR3" s="2" t="n"/>
+      <c r="AS3" s="2">
         <f>AM3+N(AQ3)+N(AR3)</f>
         <v/>
       </c>
-      <c r="AT3">
+      <c r="AT3" s="3">
         <f>IF(D3=0,"",AN3*(N3/725))</f>
         <v/>
       </c>
@@ -937,33 +946,36 @@
       <c r="Z4" t="n">
         <v>0</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AA4" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="AL4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM4">
+      <c r="AK4" s="2" t="n"/>
+      <c r="AL4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" s="2">
         <f>AK4*AL4</f>
         <v/>
       </c>
-      <c r="AN4">
+      <c r="AN4" s="3">
         <f>IF(D4=0,"",AS4/D4)</f>
         <v/>
       </c>
-      <c r="AO4">
+      <c r="AO4" s="3">
         <f>(N4/725)^2</f>
         <v/>
       </c>
-      <c r="AP4">
+      <c r="AP4" s="3">
         <f>IF(D4=0,"",AN4*AO4)</f>
         <v/>
       </c>
-      <c r="AS4">
+      <c r="AQ4" s="2" t="n"/>
+      <c r="AR4" s="2" t="n"/>
+      <c r="AS4" s="2">
         <f>AM4+N(AQ4)+N(AR4)</f>
         <v/>
       </c>
-      <c r="AT4">
+      <c r="AT4" s="3">
         <f>IF(D4=0,"",AN4*(N4/725))</f>
         <v/>
       </c>
@@ -1011,36 +1023,38 @@
       <c r="Z5" t="n">
         <v>1</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AA5" s="2" t="n">
         <v>1250</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AK5" s="2" t="n">
         <v>47.3</v>
       </c>
-      <c r="AL5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM5">
+      <c r="AL5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" s="2">
         <f>AK5*AL5</f>
         <v/>
       </c>
-      <c r="AN5">
+      <c r="AN5" s="3">
         <f>IF(D5=0,"",AS5/D5)</f>
         <v/>
       </c>
-      <c r="AO5">
+      <c r="AO5" s="3">
         <f>(N5/725)^2</f>
         <v/>
       </c>
-      <c r="AP5">
+      <c r="AP5" s="3">
         <f>IF(D5=0,"",AN5*AO5)</f>
         <v/>
       </c>
-      <c r="AS5">
+      <c r="AQ5" s="2" t="n"/>
+      <c r="AR5" s="2" t="n"/>
+      <c r="AS5" s="2">
         <f>AM5+N(AQ5)+N(AR5)</f>
         <v/>
       </c>
-      <c r="AT5">
+      <c r="AT5" s="3">
         <f>IF(D5=0,"",AN5*(N5/725))</f>
         <v/>
       </c>
@@ -1088,36 +1102,38 @@
       <c r="Z6" t="n">
         <v>0</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AA6" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AK6" s="2" t="n">
         <v>48.6</v>
       </c>
-      <c r="AL6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM6">
+      <c r="AL6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" s="2">
         <f>AK6*AL6</f>
         <v/>
       </c>
-      <c r="AN6">
+      <c r="AN6" s="3">
         <f>IF(D6=0,"",AS6/D6)</f>
         <v/>
       </c>
-      <c r="AO6">
+      <c r="AO6" s="3">
         <f>(N6/725)^2</f>
         <v/>
       </c>
-      <c r="AP6">
+      <c r="AP6" s="3">
         <f>IF(D6=0,"",AN6*AO6)</f>
         <v/>
       </c>
-      <c r="AS6">
+      <c r="AQ6" s="2" t="n"/>
+      <c r="AR6" s="2" t="n"/>
+      <c r="AS6" s="2">
         <f>AM6+N(AQ6)+N(AR6)</f>
         <v/>
       </c>
-      <c r="AT6">
+      <c r="AT6" s="3">
         <f>IF(D6=0,"",AN6*(N6/725))</f>
         <v/>
       </c>
@@ -1165,33 +1181,36 @@
       <c r="Z7" t="n">
         <v>1</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AA7" s="2" t="n">
         <v>1250</v>
       </c>
-      <c r="AL7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM7">
+      <c r="AK7" s="2" t="n"/>
+      <c r="AL7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM7" s="2">
         <f>AK7*AL7</f>
         <v/>
       </c>
-      <c r="AN7">
+      <c r="AN7" s="3">
         <f>IF(D7=0,"",AS7/D7)</f>
         <v/>
       </c>
-      <c r="AO7">
+      <c r="AO7" s="3">
         <f>(N7/725)^2</f>
         <v/>
       </c>
-      <c r="AP7">
+      <c r="AP7" s="3">
         <f>IF(D7=0,"",AN7*AO7)</f>
         <v/>
       </c>
-      <c r="AS7">
+      <c r="AQ7" s="2" t="n"/>
+      <c r="AR7" s="2" t="n"/>
+      <c r="AS7" s="2">
         <f>AM7+N(AQ7)+N(AR7)</f>
         <v/>
       </c>
-      <c r="AT7">
+      <c r="AT7" s="3">
         <f>IF(D7=0,"",AN7*(N7/725))</f>
         <v/>
       </c>
@@ -1229,33 +1248,36 @@
       <c r="Z8" t="n">
         <v>1</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AA8" s="2" t="n">
         <v>1250</v>
       </c>
-      <c r="AL8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM8">
+      <c r="AK8" s="2" t="n"/>
+      <c r="AL8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM8" s="2">
         <f>AK8*AL8</f>
         <v/>
       </c>
-      <c r="AN8">
+      <c r="AN8" s="3">
         <f>IF(D8=0,"",AS8/D8)</f>
         <v/>
       </c>
-      <c r="AO8">
+      <c r="AO8" s="3">
         <f>(N8/725)^2</f>
         <v/>
       </c>
-      <c r="AP8">
+      <c r="AP8" s="3">
         <f>IF(D8=0,"",AN8*AO8)</f>
         <v/>
       </c>
-      <c r="AS8">
+      <c r="AQ8" s="2" t="n"/>
+      <c r="AR8" s="2" t="n"/>
+      <c r="AS8" s="2">
         <f>AM8+N(AQ8)+N(AR8)</f>
         <v/>
       </c>
-      <c r="AT8">
+      <c r="AT8" s="3">
         <f>IF(D8=0,"",AN8*(N8/725))</f>
         <v/>
       </c>
@@ -1303,36 +1325,38 @@
       <c r="Z9" t="n">
         <v>2</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AA9" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AK9" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="AL9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM9">
+      <c r="AL9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM9" s="2">
         <f>AK9*AL9</f>
         <v/>
       </c>
-      <c r="AN9">
+      <c r="AN9" s="3">
         <f>IF(D9=0,"",AS9/D9)</f>
         <v/>
       </c>
-      <c r="AO9">
+      <c r="AO9" s="3">
         <f>(N9/725)^2</f>
         <v/>
       </c>
-      <c r="AP9">
+      <c r="AP9" s="3">
         <f>IF(D9=0,"",AN9*AO9)</f>
         <v/>
       </c>
-      <c r="AS9">
+      <c r="AQ9" s="2" t="n"/>
+      <c r="AR9" s="2" t="n"/>
+      <c r="AS9" s="2">
         <f>AM9+N(AQ9)+N(AR9)</f>
         <v/>
       </c>
-      <c r="AT9">
+      <c r="AT9" s="3">
         <f>IF(D9=0,"",AN9*(N9/725))</f>
         <v/>
       </c>
@@ -1380,33 +1404,36 @@
       <c r="Z10" t="n">
         <v>3</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AA10" s="2" t="n">
         <v>1750</v>
       </c>
-      <c r="AL10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM10">
+      <c r="AK10" s="2" t="n"/>
+      <c r="AL10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM10" s="2">
         <f>AK10*AL10</f>
         <v/>
       </c>
-      <c r="AN10">
+      <c r="AN10" s="3">
         <f>IF(D10=0,"",AS10/D10)</f>
         <v/>
       </c>
-      <c r="AO10">
+      <c r="AO10" s="3">
         <f>(N10/725)^2</f>
         <v/>
       </c>
-      <c r="AP10">
+      <c r="AP10" s="3">
         <f>IF(D10=0,"",AN10*AO10)</f>
         <v/>
       </c>
-      <c r="AS10">
+      <c r="AQ10" s="2" t="n"/>
+      <c r="AR10" s="2" t="n"/>
+      <c r="AS10" s="2">
         <f>AM10+N(AQ10)+N(AR10)</f>
         <v/>
       </c>
-      <c r="AT10">
+      <c r="AT10" s="3">
         <f>IF(D10=0,"",AN10*(N10/725))</f>
         <v/>
       </c>
@@ -1477,7 +1504,7 @@
       <c r="Z11" t="n">
         <v>2</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AA11" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="AB11" t="n">
@@ -1517,33 +1544,35 @@
           <t>Build Fire Hydra ( S ) - 255</t>
         </is>
       </c>
-      <c r="AK11" t="n">
+      <c r="AK11" s="2" t="n">
         <v>710</v>
       </c>
-      <c r="AL11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM11">
+      <c r="AL11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM11" s="2">
         <f>AK11*AL11</f>
         <v/>
       </c>
-      <c r="AN11">
+      <c r="AN11" s="3">
         <f>IF(D11=0,"",AS11/D11)</f>
         <v/>
       </c>
-      <c r="AO11">
+      <c r="AO11" s="3">
         <f>(N11/725)^2</f>
         <v/>
       </c>
-      <c r="AP11">
+      <c r="AP11" s="3">
         <f>IF(D11=0,"",AN11*AO11)</f>
         <v/>
       </c>
-      <c r="AS11">
+      <c r="AQ11" s="2" t="n"/>
+      <c r="AR11" s="2" t="n"/>
+      <c r="AS11" s="2">
         <f>AM11+N(AQ11)+N(AR11)</f>
         <v/>
       </c>
-      <c r="AT11">
+      <c r="AT11" s="3">
         <f>IF(D11=0,"",AN11*(N11/725))</f>
         <v/>
       </c>
@@ -1614,7 +1643,7 @@
       <c r="Z12" t="n">
         <v>3</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AA12" s="2" t="n">
         <v>1750</v>
       </c>
       <c r="AB12" t="n">
@@ -1654,33 +1683,35 @@
           <t>U pgrade to Duke Burnify - 400</t>
         </is>
       </c>
-      <c r="AK12" t="n">
+      <c r="AK12" s="2" t="n">
         <v>481</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AL12" s="3" t="n">
         <v>1.35</v>
       </c>
-      <c r="AM12">
+      <c r="AM12" s="2">
         <f>AK12*AL12</f>
         <v/>
       </c>
-      <c r="AN12">
+      <c r="AN12" s="3">
         <f>IF(D12=0,"",AS12/D12)</f>
         <v/>
       </c>
-      <c r="AO12">
+      <c r="AO12" s="3">
         <f>(N12/725)^2</f>
         <v/>
       </c>
-      <c r="AP12">
+      <c r="AP12" s="3">
         <f>IF(D12=0,"",AN12*AO12)</f>
         <v/>
       </c>
-      <c r="AS12">
+      <c r="AQ12" s="2" t="n"/>
+      <c r="AR12" s="2" t="n"/>
+      <c r="AS12" s="2">
         <f>AM12+N(AQ12)+N(AR12)</f>
         <v/>
       </c>
-      <c r="AT12">
+      <c r="AT12" s="3">
         <f>IF(D12=0,"",AN12*(N12/725))</f>
         <v/>
       </c>
@@ -1728,36 +1759,38 @@
       <c r="Z13" t="n">
         <v>2</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AA13" s="2" t="n">
         <v>1500</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AK13" s="2" t="n">
         <v>857.1</v>
       </c>
-      <c r="AL13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM13">
+      <c r="AL13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM13" s="2">
         <f>AK13*AL13</f>
         <v/>
       </c>
-      <c r="AN13">
+      <c r="AN13" s="3">
         <f>IF(D13=0,"",AS13/D13)</f>
         <v/>
       </c>
-      <c r="AO13">
+      <c r="AO13" s="3">
         <f>(N13/725)^2</f>
         <v/>
       </c>
-      <c r="AP13">
+      <c r="AP13" s="3">
         <f>IF(D13=0,"",AN13*AO13)</f>
         <v/>
       </c>
-      <c r="AS13">
+      <c r="AQ13" s="2" t="n"/>
+      <c r="AR13" s="2" t="n"/>
+      <c r="AS13" s="2">
         <f>AM13+N(AQ13)+N(AR13)</f>
         <v/>
       </c>
-      <c r="AT13">
+      <c r="AT13" s="3">
         <f>IF(D13=0,"",AN13*(N13/725))</f>
         <v/>
       </c>
@@ -1805,36 +1838,38 @@
       <c r="Z14" t="n">
         <v>3</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AA14" s="2" t="n">
         <v>1750</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AK14" s="2" t="n">
         <v>1356.7</v>
       </c>
-      <c r="AL14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM14">
+      <c r="AL14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM14" s="2">
         <f>AK14*AL14</f>
         <v/>
       </c>
-      <c r="AN14">
+      <c r="AN14" s="3">
         <f>IF(D14=0,"",AS14/D14)</f>
         <v/>
       </c>
-      <c r="AO14">
+      <c r="AO14" s="3">
         <f>(N14/725)^2</f>
         <v/>
       </c>
-      <c r="AP14">
+      <c r="AP14" s="3">
         <f>IF(D14=0,"",AN14*AO14)</f>
         <v/>
       </c>
-      <c r="AS14">
+      <c r="AQ14" s="2" t="n"/>
+      <c r="AR14" s="2" t="n"/>
+      <c r="AS14" s="2">
         <f>AM14+N(AQ14)+N(AR14)</f>
         <v/>
       </c>
-      <c r="AT14">
+      <c r="AT14" s="3">
         <f>IF(D14=0,"",AN14*(N14/725))</f>
         <v/>
       </c>
@@ -1867,33 +1902,36 @@
       <c r="Z15" t="n">
         <v>4</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AA15" s="2" t="n">
         <v>750</v>
       </c>
-      <c r="AL15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM15">
+      <c r="AK15" s="2" t="n"/>
+      <c r="AL15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM15" s="2">
         <f>AK15*AL15</f>
         <v/>
       </c>
-      <c r="AN15">
+      <c r="AN15" s="3">
         <f>IF(D15=0,"",AS15/D15)</f>
         <v/>
       </c>
-      <c r="AO15">
+      <c r="AO15" s="3">
         <f>(N15/725)^2</f>
         <v/>
       </c>
-      <c r="AP15">
+      <c r="AP15" s="3">
         <f>IF(D15=0,"",AN15*AO15)</f>
         <v/>
       </c>
-      <c r="AS15">
+      <c r="AQ15" s="2" t="n"/>
+      <c r="AR15" s="2" t="n"/>
+      <c r="AS15" s="2">
         <f>AM15+N(AQ15)+N(AR15)</f>
         <v/>
       </c>
-      <c r="AT15">
+      <c r="AT15" s="3">
         <f>IF(D15=0,"",AN15*(N15/725))</f>
         <v/>
       </c>
@@ -1931,30 +1969,34 @@
       <c r="Z16" t="n">
         <v>0</v>
       </c>
-      <c r="AL16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM16">
+      <c r="AA16" s="2" t="n"/>
+      <c r="AK16" s="2" t="n"/>
+      <c r="AL16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM16" s="2">
         <f>AK16*AL16</f>
         <v/>
       </c>
-      <c r="AN16">
+      <c r="AN16" s="3">
         <f>IF(D16=0,"",AS16/D16)</f>
         <v/>
       </c>
-      <c r="AO16">
+      <c r="AO16" s="3">
         <f>(N16/725)^2</f>
         <v/>
       </c>
-      <c r="AP16">
+      <c r="AP16" s="3">
         <f>IF(D16=0,"",AN16*AO16)</f>
         <v/>
       </c>
-      <c r="AS16">
+      <c r="AQ16" s="2" t="n"/>
+      <c r="AR16" s="2" t="n"/>
+      <c r="AS16" s="2">
         <f>AM16+N(AQ16)+N(AR16)</f>
         <v/>
       </c>
-      <c r="AT16">
+      <c r="AT16" s="3">
         <f>IF(D16=0,"",AN16*(N16/725))</f>
         <v/>
       </c>
@@ -1992,30 +2034,34 @@
       <c r="Z17" t="n">
         <v>0</v>
       </c>
-      <c r="AL17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM17">
+      <c r="AA17" s="2" t="n"/>
+      <c r="AK17" s="2" t="n"/>
+      <c r="AL17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM17" s="2">
         <f>AK17*AL17</f>
         <v/>
       </c>
-      <c r="AN17">
+      <c r="AN17" s="3">
         <f>IF(D17=0,"",AS17/D17)</f>
         <v/>
       </c>
-      <c r="AO17">
+      <c r="AO17" s="3">
         <f>(N17/725)^2</f>
         <v/>
       </c>
-      <c r="AP17">
+      <c r="AP17" s="3">
         <f>IF(D17=0,"",AN17*AO17)</f>
         <v/>
       </c>
-      <c r="AS17">
+      <c r="AQ17" s="2" t="n"/>
+      <c r="AR17" s="2" t="n"/>
+      <c r="AS17" s="2">
         <f>AM17+N(AQ17)+N(AR17)</f>
         <v/>
       </c>
-      <c r="AT17">
+      <c r="AT17" s="3">
         <f>IF(D17=0,"",AN17*(N17/725))</f>
         <v/>
       </c>
@@ -2053,30 +2099,34 @@
       <c r="Z18" t="n">
         <v>0</v>
       </c>
-      <c r="AL18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM18">
+      <c r="AA18" s="2" t="n"/>
+      <c r="AK18" s="2" t="n"/>
+      <c r="AL18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM18" s="2">
         <f>AK18*AL18</f>
         <v/>
       </c>
-      <c r="AN18">
+      <c r="AN18" s="3">
         <f>IF(D18=0,"",AS18/D18)</f>
         <v/>
       </c>
-      <c r="AO18">
+      <c r="AO18" s="3">
         <f>(N18/725)^2</f>
         <v/>
       </c>
-      <c r="AP18">
+      <c r="AP18" s="3">
         <f>IF(D18=0,"",AN18*AO18)</f>
         <v/>
       </c>
-      <c r="AS18">
+      <c r="AQ18" s="2" t="n"/>
+      <c r="AR18" s="2" t="n"/>
+      <c r="AS18" s="2">
         <f>AM18+N(AQ18)+N(AR18)</f>
         <v/>
       </c>
-      <c r="AT18">
+      <c r="AT18" s="3">
         <f>IF(D18=0,"",AN18*(N18/725))</f>
         <v/>
       </c>
@@ -5863,7 +5913,7 @@
       <c r="AD2" t="n">
         <v>7</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AE2" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="AF2" t="inlineStr">
@@ -5881,33 +5931,35 @@
           <t>Machine Critical Strike (A03Y); Super Regeneration (A070); Empathic Fix (AChv); Sell Tower (A028)</t>
         </is>
       </c>
-      <c r="AL2" t="n">
+      <c r="AL2" s="2" t="n">
         <v>116.7</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AM2" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="AN2">
+      <c r="AN2" s="2">
         <f>AL2*AM2</f>
         <v/>
       </c>
-      <c r="AQ2">
+      <c r="AO2" s="2" t="n"/>
+      <c r="AP2" s="2" t="n"/>
+      <c r="AQ2" s="2">
         <f>AN2+N(AO2)+N(AP2)</f>
         <v/>
       </c>
-      <c r="AR2">
+      <c r="AR2" s="3">
         <f>IF(C2=0,"",AQ2/C2)</f>
         <v/>
       </c>
-      <c r="AS2">
+      <c r="AS2" s="3">
         <f>IF(C2=0,"",AR2*(K2/725))</f>
         <v/>
       </c>
-      <c r="AT2">
+      <c r="AT2" s="3">
         <f>(K2/725)^2</f>
         <v/>
       </c>
-      <c r="AU2">
+      <c r="AU2" s="3">
         <f>IF(C2=0,"",AR2*AT2)</f>
         <v/>
       </c>
@@ -5979,7 +6031,7 @@
       <c r="AD3" t="n">
         <v>0</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AE3" s="2" t="n">
         <v>1250</v>
       </c>
       <c r="AF3" t="inlineStr">
@@ -5992,33 +6044,35 @@
           <t>Vindicator II (A03C); Sell Tower (A028)</t>
         </is>
       </c>
-      <c r="AL3" t="n">
+      <c r="AL3" s="2" t="n">
         <v>33.3</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AM3" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="AN3">
+      <c r="AN3" s="2">
         <f>AL3*AM3</f>
         <v/>
       </c>
-      <c r="AQ3">
+      <c r="AO3" s="2" t="n"/>
+      <c r="AP3" s="2" t="n"/>
+      <c r="AQ3" s="2">
         <f>AN3+N(AO3)+N(AP3)</f>
         <v/>
       </c>
-      <c r="AR3">
+      <c r="AR3" s="3">
         <f>IF(C3=0,"",AQ3/C3)</f>
         <v/>
       </c>
-      <c r="AS3">
+      <c r="AS3" s="3">
         <f>IF(C3=0,"",AR3*(K3/725))</f>
         <v/>
       </c>
-      <c r="AT3">
+      <c r="AT3" s="3">
         <f>(K3/725)^2</f>
         <v/>
       </c>
-      <c r="AU3">
+      <c r="AU3" s="3">
         <f>IF(C3=0,"",AR3*AT3)</f>
         <v/>
       </c>
@@ -6090,7 +6144,7 @@
       <c r="AD4" t="n">
         <v>0</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AE4" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="AF4" t="inlineStr">
@@ -6103,33 +6157,35 @@
           <t>Vindicator II (A03C); Versatile Critical Strike I (A004); Sell Tower (A028)</t>
         </is>
       </c>
-      <c r="AL4" t="n">
+      <c r="AL4" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AM4" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="AN4">
+      <c r="AN4" s="2">
         <f>AL4*AM4</f>
         <v/>
       </c>
-      <c r="AQ4">
+      <c r="AO4" s="2" t="n"/>
+      <c r="AP4" s="2" t="n"/>
+      <c r="AQ4" s="2">
         <f>AN4+N(AO4)+N(AP4)</f>
         <v/>
       </c>
-      <c r="AR4">
+      <c r="AR4" s="3">
         <f>IF(C4=0,"",AQ4/C4)</f>
         <v/>
       </c>
-      <c r="AS4">
+      <c r="AS4" s="3">
         <f>IF(C4=0,"",AR4*(K4/725))</f>
         <v/>
       </c>
-      <c r="AT4">
+      <c r="AT4" s="3">
         <f>(K4/725)^2</f>
         <v/>
       </c>
-      <c r="AU4">
+      <c r="AU4" s="3">
         <f>IF(C4=0,"",AR4*AT4)</f>
         <v/>
       </c>
@@ -6201,7 +6257,7 @@
       <c r="AD5" t="n">
         <v>1</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AE5" s="2" t="n">
         <v>1750</v>
       </c>
       <c r="AF5" t="inlineStr">
@@ -6214,33 +6270,35 @@
           <t>Vindicator II (A03C); Versatile Critical Strike II (A01E); Sell Tower (A028)</t>
         </is>
       </c>
-      <c r="AL5" t="n">
+      <c r="AL5" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AM5" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="AN5">
+      <c r="AN5" s="2">
         <f>AL5*AM5</f>
         <v/>
       </c>
-      <c r="AQ5">
+      <c r="AO5" s="2" t="n"/>
+      <c r="AP5" s="2" t="n"/>
+      <c r="AQ5" s="2">
         <f>AN5+N(AO5)+N(AP5)</f>
         <v/>
       </c>
-      <c r="AR5">
+      <c r="AR5" s="3">
         <f>IF(C5=0,"",AQ5/C5)</f>
         <v/>
       </c>
-      <c r="AS5">
+      <c r="AS5" s="3">
         <f>IF(C5=0,"",AR5*(K5/725))</f>
         <v/>
       </c>
-      <c r="AT5">
+      <c r="AT5" s="3">
         <f>(K5/725)^2</f>
         <v/>
       </c>
-      <c r="AU5">
+      <c r="AU5" s="3">
         <f>IF(C5=0,"",AR5*AT5)</f>
         <v/>
       </c>
@@ -6312,7 +6370,7 @@
       <c r="AD6" t="n">
         <v>2</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AE6" s="2" t="n">
         <v>2000</v>
       </c>
       <c r="AF6" t="inlineStr">
@@ -6325,33 +6383,35 @@
           <t>Vindicator III (A02Z); Versatile Critical Strike II (A01E); Sell Tower (A028)</t>
         </is>
       </c>
-      <c r="AL6" t="n">
+      <c r="AL6" s="2" t="n">
         <v>46.7</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AM6" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="AN6">
+      <c r="AN6" s="2">
         <f>AL6*AM6</f>
         <v/>
       </c>
-      <c r="AQ6">
+      <c r="AO6" s="2" t="n"/>
+      <c r="AP6" s="2" t="n"/>
+      <c r="AQ6" s="2">
         <f>AN6+N(AO6)+N(AP6)</f>
         <v/>
       </c>
-      <c r="AR6">
+      <c r="AR6" s="3">
         <f>IF(C6=0,"",AQ6/C6)</f>
         <v/>
       </c>
-      <c r="AS6">
+      <c r="AS6" s="3">
         <f>IF(C6=0,"",AR6*(K6/725))</f>
         <v/>
       </c>
-      <c r="AT6">
+      <c r="AT6" s="3">
         <f>(K6/725)^2</f>
         <v/>
       </c>
-      <c r="AU6">
+      <c r="AU6" s="3">
         <f>IF(C6=0,"",AR6*AT6)</f>
         <v/>
       </c>
@@ -6423,7 +6483,7 @@
       <c r="AD7" t="n">
         <v>4</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AE7" s="2" t="n">
         <v>2250</v>
       </c>
       <c r="AF7" t="inlineStr">
@@ -6436,36 +6496,37 @@
           <t>Bash I (ANbh); Vindicator III (A02Z); Versatile Critical Strike II (A01E); Sell Tower (A028)</t>
         </is>
       </c>
-      <c r="AL7" t="n">
+      <c r="AL7" s="2" t="n">
         <v>71.7</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AM7" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="AN7">
+      <c r="AN7" s="2">
         <f>AL7*AM7</f>
         <v/>
       </c>
-      <c r="AO7" t="n">
+      <c r="AO7" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="AQ7">
+      <c r="AP7" s="2" t="n"/>
+      <c r="AQ7" s="2">
         <f>AN7+N(AO7)+N(AP7)</f>
         <v/>
       </c>
-      <c r="AR7">
+      <c r="AR7" s="3">
         <f>IF(C7=0,"",AQ7/C7)</f>
         <v/>
       </c>
-      <c r="AS7">
+      <c r="AS7" s="3">
         <f>IF(C7=0,"",AR7*(K7/725))</f>
         <v/>
       </c>
-      <c r="AT7">
+      <c r="AT7" s="3">
         <f>(K7/725)^2</f>
         <v/>
       </c>
-      <c r="AU7">
+      <c r="AU7" s="3">
         <f>IF(C7=0,"",AR7*AT7)</f>
         <v/>
       </c>
@@ -6542,7 +6603,7 @@
       <c r="AD8" t="n">
         <v>2</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AE8" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="AF8" t="inlineStr">
@@ -6560,33 +6621,35 @@
           <t>Regeneration (A03W); Sell Tower (A028); Frost I (Afra)</t>
         </is>
       </c>
-      <c r="AL8" t="n">
+      <c r="AL8" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="AM8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN8">
+      <c r="AM8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN8" s="2">
         <f>AL8*AM8</f>
         <v/>
       </c>
-      <c r="AQ8">
+      <c r="AO8" s="2" t="n"/>
+      <c r="AP8" s="2" t="n"/>
+      <c r="AQ8" s="2">
         <f>AN8+N(AO8)+N(AP8)</f>
         <v/>
       </c>
-      <c r="AR8">
+      <c r="AR8" s="3">
         <f>IF(C8=0,"",AQ8/C8)</f>
         <v/>
       </c>
-      <c r="AS8">
+      <c r="AS8" s="3">
         <f>IF(C8=0,"",AR8*(K8/725))</f>
         <v/>
       </c>
-      <c r="AT8">
+      <c r="AT8" s="3">
         <f>(K8/725)^2</f>
         <v/>
       </c>
-      <c r="AU8">
+      <c r="AU8" s="3">
         <f>IF(C8=0,"",AR8*AT8)</f>
         <v/>
       </c>
@@ -6663,7 +6726,7 @@
       <c r="AD9" t="n">
         <v>2</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AE9" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="AF9" t="inlineStr">
@@ -6696,36 +6759,37 @@
           <t>Boss Assassin I (A03D); Sell Tower (A028); Air Critical Strike II (A006); Slow Poison II (A008)</t>
         </is>
       </c>
-      <c r="AL9" t="n">
+      <c r="AL9" s="2" t="n">
         <v>425.7</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AM9" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="AN9">
+      <c r="AN9" s="2">
         <f>AL9*AM9</f>
         <v/>
       </c>
-      <c r="AP9" t="n">
+      <c r="AO9" s="2" t="n"/>
+      <c r="AP9" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="AQ9">
+      <c r="AQ9" s="2">
         <f>AN9+N(AO9)+N(AP9)</f>
         <v/>
       </c>
-      <c r="AR9">
+      <c r="AR9" s="3">
         <f>IF(C9=0,"",AQ9/C9)</f>
         <v/>
       </c>
-      <c r="AS9">
+      <c r="AS9" s="3">
         <f>IF(C9=0,"",AR9*(K9/725))</f>
         <v/>
       </c>
-      <c r="AT9">
+      <c r="AT9" s="3">
         <f>(K9/725)^2</f>
         <v/>
       </c>
-      <c r="AU9">
+      <c r="AU9" s="3">
         <f>IF(C9=0,"",AR9*AT9)</f>
         <v/>
       </c>
@@ -6797,7 +6861,7 @@
       <c r="AD10" t="n">
         <v>1</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AE10" s="2" t="n">
         <v>1250</v>
       </c>
       <c r="AF10" t="inlineStr">
@@ -6815,36 +6879,37 @@
           <t>Bash I (ANbh); Sell Tower (A028)</t>
         </is>
       </c>
-      <c r="AL10" t="n">
+      <c r="AL10" s="2" t="n">
         <v>290</v>
       </c>
-      <c r="AM10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN10">
+      <c r="AM10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN10" s="2">
         <f>AL10*AM10</f>
         <v/>
       </c>
-      <c r="AO10" t="n">
+      <c r="AO10" s="2" t="n">
         <v>33.3</v>
       </c>
-      <c r="AQ10">
+      <c r="AP10" s="2" t="n"/>
+      <c r="AQ10" s="2">
         <f>AN10+N(AO10)+N(AP10)</f>
         <v/>
       </c>
-      <c r="AR10">
+      <c r="AR10" s="3">
         <f>IF(C10=0,"",AQ10/C10)</f>
         <v/>
       </c>
-      <c r="AS10">
+      <c r="AS10" s="3">
         <f>IF(C10=0,"",AR10*(K10/725))</f>
         <v/>
       </c>
-      <c r="AT10">
+      <c r="AT10" s="3">
         <f>(K10/725)^2</f>
         <v/>
       </c>
-      <c r="AU10">
+      <c r="AU10" s="3">
         <f>IF(C10=0,"",AR10*AT10)</f>
         <v/>
       </c>
@@ -6921,7 +6986,7 @@
       <c r="AD11" t="n">
         <v>2</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AE11" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="AF11" t="inlineStr">
@@ -6939,33 +7004,35 @@
           <t>Sunder Armor (Afbb); (Dummy Ability - Life Steal) (Aabr); AIva (AIva); Versatile Critical Strike II (A01E); Sell Tower (A028)</t>
         </is>
       </c>
-      <c r="AL11" t="n">
+      <c r="AL11" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AM11" s="3" t="n">
         <v>2.05</v>
       </c>
-      <c r="AN11">
+      <c r="AN11" s="2">
         <f>AL11*AM11</f>
         <v/>
       </c>
-      <c r="AQ11">
+      <c r="AO11" s="2" t="n"/>
+      <c r="AP11" s="2" t="n"/>
+      <c r="AQ11" s="2">
         <f>AN11+N(AO11)+N(AP11)</f>
         <v/>
       </c>
-      <c r="AR11">
+      <c r="AR11" s="3">
         <f>IF(C11=0,"",AQ11/C11)</f>
         <v/>
       </c>
-      <c r="AS11">
+      <c r="AS11" s="3">
         <f>IF(C11=0,"",AR11*(K11/725))</f>
         <v/>
       </c>
-      <c r="AT11">
+      <c r="AT11" s="3">
         <f>(K11/725)^2</f>
         <v/>
       </c>
-      <c r="AU11">
+      <c r="AU11" s="3">
         <f>IF(C11=0,"",AR11*AT11)</f>
         <v/>
       </c>
@@ -7042,7 +7109,7 @@
           <t>hhou</t>
         </is>
       </c>
-      <c r="AE12" t="n">
+      <c r="AE12" s="2" t="n">
         <v>2500</v>
       </c>
       <c r="AF12" t="inlineStr">
@@ -7060,33 +7127,35 @@
           <t>Activate / Deactivate Mana Detection (ANcl); Versatile Critical Strike I (A004); Gooify (A02X); Combustion (A014); Sell Tower (A028)</t>
         </is>
       </c>
-      <c r="AL12" t="n">
+      <c r="AL12" s="2" t="n">
         <v>2589.4</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AM12" s="3" t="n">
         <v>1.52</v>
       </c>
-      <c r="AN12">
+      <c r="AN12" s="2">
         <f>AL12*AM12</f>
         <v/>
       </c>
-      <c r="AQ12">
+      <c r="AO12" s="2" t="n"/>
+      <c r="AP12" s="2" t="n"/>
+      <c r="AQ12" s="2">
         <f>AN12+N(AO12)+N(AP12)</f>
         <v/>
       </c>
-      <c r="AR12">
+      <c r="AR12" s="3">
         <f>IF(C12=0,"",AQ12/C12)</f>
         <v/>
       </c>
-      <c r="AS12">
+      <c r="AS12" s="3">
         <f>IF(C12=0,"",AR12*(K12/725))</f>
         <v/>
       </c>
-      <c r="AT12">
+      <c r="AT12" s="3">
         <f>(K12/725)^2</f>
         <v/>
       </c>
-      <c r="AU12">
+      <c r="AU12" s="3">
         <f>IF(C12=0,"",AR12*AT12)</f>
         <v/>
       </c>
@@ -7163,7 +7232,7 @@
       <c r="AD13" t="n">
         <v>2</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AE13" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="AF13" t="inlineStr">
@@ -7196,33 +7265,35 @@
           <t>Air Critical Strike II (A006); Sell Tower (A028); Vampiric Aura (ACvp)</t>
         </is>
       </c>
-      <c r="AL13" t="n">
+      <c r="AL13" s="2" t="n">
         <v>358.8</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AM13" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="AN13">
+      <c r="AN13" s="2">
         <f>AL13*AM13</f>
         <v/>
       </c>
-      <c r="AQ13">
+      <c r="AO13" s="2" t="n"/>
+      <c r="AP13" s="2" t="n"/>
+      <c r="AQ13" s="2">
         <f>AN13+N(AO13)+N(AP13)</f>
         <v/>
       </c>
-      <c r="AR13">
+      <c r="AR13" s="3">
         <f>IF(C13=0,"",AQ13/C13)</f>
         <v/>
       </c>
-      <c r="AS13">
+      <c r="AS13" s="3">
         <f>IF(C13=0,"",AR13*(K13/725))</f>
         <v/>
       </c>
-      <c r="AT13">
+      <c r="AT13" s="3">
         <f>(K13/725)^2</f>
         <v/>
       </c>
-      <c r="AU13">
+      <c r="AU13" s="3">
         <f>IF(C13=0,"",AR13*AT13)</f>
         <v/>
       </c>
@@ -7299,7 +7370,7 @@
       <c r="AD14" t="n">
         <v>7</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AE14" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="AF14" t="inlineStr">
@@ -7332,33 +7403,35 @@
           <t>Machine Critical Strike (A03Y); Splash (A021); Sell Tower (A028); Frost I (Afra)</t>
         </is>
       </c>
-      <c r="AL14" t="n">
+      <c r="AL14" s="2" t="n">
         <v>289.4</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AM14" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="AN14">
+      <c r="AN14" s="2">
         <f>AL14*AM14</f>
         <v/>
       </c>
-      <c r="AQ14">
+      <c r="AO14" s="2" t="n"/>
+      <c r="AP14" s="2" t="n"/>
+      <c r="AQ14" s="2">
         <f>AN14+N(AO14)+N(AP14)</f>
         <v/>
       </c>
-      <c r="AR14">
+      <c r="AR14" s="3">
         <f>IF(C14=0,"",AQ14/C14)</f>
         <v/>
       </c>
-      <c r="AS14">
+      <c r="AS14" s="3">
         <f>IF(C14=0,"",AR14*(K14/725))</f>
         <v/>
       </c>
-      <c r="AT14">
+      <c r="AT14" s="3">
         <f>(K14/725)^2</f>
         <v/>
       </c>
-      <c r="AU14">
+      <c r="AU14" s="3">
         <f>IF(C14=0,"",AR14*AT14)</f>
         <v/>
       </c>
@@ -7435,7 +7508,7 @@
           <t>hhou</t>
         </is>
       </c>
-      <c r="AE15" t="n">
+      <c r="AE15" s="2" t="n">
         <v>2500</v>
       </c>
       <c r="AF15" t="inlineStr">
@@ -7453,36 +7526,37 @@
           <t>Activate / Deactivate Mana Detection (ANcl); Stone Cold (Afrz); Grounding Curse (Aap1); Cold Snap (AIm2); Sell Tower (A028)</t>
         </is>
       </c>
-      <c r="AL15" t="n">
+      <c r="AL15" s="2" t="n">
         <v>6000</v>
       </c>
-      <c r="AM15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN15">
+      <c r="AM15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN15" s="2">
         <f>AL15*AM15</f>
         <v/>
       </c>
-      <c r="AP15" t="n">
+      <c r="AO15" s="2" t="n"/>
+      <c r="AP15" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="AQ15">
+      <c r="AQ15" s="2">
         <f>AN15+N(AO15)+N(AP15)</f>
         <v/>
       </c>
-      <c r="AR15">
+      <c r="AR15" s="3">
         <f>IF(C15=0,"",AQ15/C15)</f>
         <v/>
       </c>
-      <c r="AS15">
+      <c r="AS15" s="3">
         <f>IF(C15=0,"",AR15*(K15/725))</f>
         <v/>
       </c>
-      <c r="AT15">
+      <c r="AT15" s="3">
         <f>(K15/725)^2</f>
         <v/>
       </c>
-      <c r="AU15">
+      <c r="AU15" s="3">
         <f>IF(C15=0,"",AR15*AT15)</f>
         <v/>
       </c>
@@ -7854,7 +7928,7 @@
       <c r="Z2" t="n">
         <v>0</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AA2" s="2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
@@ -7894,33 +7968,35 @@
           <t>Build Quickshot ( Q )</t>
         </is>
       </c>
-      <c r="AK2" t="n">
+      <c r="AK2" s="2" t="n">
         <v>30.7</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AL2" s="3" t="n">
         <v>1.52</v>
       </c>
-      <c r="AM2">
+      <c r="AM2" s="2">
         <f>AK2*AL2</f>
         <v/>
       </c>
-      <c r="AN2">
+      <c r="AN2" s="3">
         <f>IF(D2=0,"",AS2/D2)</f>
         <v/>
       </c>
-      <c r="AO2">
+      <c r="AO2" s="3">
         <f>(N2/725)^2</f>
         <v/>
       </c>
-      <c r="AP2">
+      <c r="AP2" s="3">
         <f>IF(D2=0,"",AN2*AO2)</f>
         <v/>
       </c>
-      <c r="AS2">
+      <c r="AQ2" s="2" t="n"/>
+      <c r="AR2" s="2" t="n"/>
+      <c r="AS2" s="2">
         <f>AM2+N(AQ2)+N(AR2)</f>
         <v/>
       </c>
-      <c r="AT2">
+      <c r="AT2" s="3">
         <f>IF(D2=0,"",AN2*(N2/725))</f>
         <v/>
       </c>
@@ -7991,7 +8067,7 @@
       <c r="Z3" t="n">
         <v>0</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AA3" s="2" t="n">
         <v>1250</v>
       </c>
       <c r="AB3" t="n">
@@ -8031,33 +8107,35 @@
           <t>U pgrade to Cross Bow</t>
         </is>
       </c>
-      <c r="AK3" t="n">
+      <c r="AK3" s="2" t="n">
         <v>168.3</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AL3" s="3" t="n">
         <v>2.05</v>
       </c>
-      <c r="AM3">
+      <c r="AM3" s="2">
         <f>AK3*AL3</f>
         <v/>
       </c>
-      <c r="AN3">
+      <c r="AN3" s="3">
         <f>IF(D3=0,"",AS3/D3)</f>
         <v/>
       </c>
-      <c r="AO3">
+      <c r="AO3" s="3">
         <f>(N3/725)^2</f>
         <v/>
       </c>
-      <c r="AP3">
+      <c r="AP3" s="3">
         <f>IF(D3=0,"",AN3*AO3)</f>
         <v/>
       </c>
-      <c r="AS3">
+      <c r="AQ3" s="2" t="n"/>
+      <c r="AR3" s="2" t="n"/>
+      <c r="AS3" s="2">
         <f>AM3+N(AQ3)+N(AR3)</f>
         <v/>
       </c>
-      <c r="AT3">
+      <c r="AT3" s="3">
         <f>IF(D3=0,"",AN3*(N3/725))</f>
         <v/>
       </c>
@@ -8133,7 +8211,7 @@
       <c r="Z4" t="n">
         <v>0</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AA4" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="AB4" t="n">
@@ -8173,33 +8251,35 @@
           <t>Build Frigid Dryad ( W )</t>
         </is>
       </c>
-      <c r="AK4" t="n">
+      <c r="AK4" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AL4" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="AM4">
+      <c r="AM4" s="2">
         <f>AK4*AL4</f>
         <v/>
       </c>
-      <c r="AN4">
+      <c r="AN4" s="3">
         <f>IF(D4=0,"",AS4/D4)</f>
         <v/>
       </c>
-      <c r="AO4">
+      <c r="AO4" s="3">
         <f>(N4/725)^2</f>
         <v/>
       </c>
-      <c r="AP4">
+      <c r="AP4" s="3">
         <f>IF(D4=0,"",AN4*AO4)</f>
         <v/>
       </c>
-      <c r="AS4">
+      <c r="AQ4" s="2" t="n"/>
+      <c r="AR4" s="2" t="n"/>
+      <c r="AS4" s="2">
         <f>AM4+N(AQ4)+N(AR4)</f>
         <v/>
       </c>
-      <c r="AT4">
+      <c r="AT4" s="3">
         <f>IF(D4=0,"",AN4*(N4/725))</f>
         <v/>
       </c>
@@ -8270,7 +8350,7 @@
       <c r="Z5" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AA5" s="2" t="n">
         <v>2000</v>
       </c>
       <c r="AB5" t="n">
@@ -8310,36 +8390,37 @@
           <t>U pgrade to The Pride of Moon Star</t>
         </is>
       </c>
-      <c r="AK5" t="n">
+      <c r="AK5" s="2" t="n">
         <v>998.5</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AL5" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="AM5">
+      <c r="AM5" s="2">
         <f>AK5*AL5</f>
         <v/>
       </c>
-      <c r="AN5">
+      <c r="AN5" s="3">
         <f>IF(D5=0,"",AS5/D5)</f>
         <v/>
       </c>
-      <c r="AO5">
+      <c r="AO5" s="3">
         <f>(N5/725)^2</f>
         <v/>
       </c>
-      <c r="AP5">
+      <c r="AP5" s="3">
         <f>IF(D5=0,"",AN5*AO5)</f>
         <v/>
       </c>
-      <c r="AR5" t="n">
+      <c r="AQ5" s="2" t="n"/>
+      <c r="AR5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AS5">
+      <c r="AS5" s="2">
         <f>AM5+N(AQ5)+N(AR5)</f>
         <v/>
       </c>
-      <c r="AT5">
+      <c r="AT5" s="3">
         <f>IF(D5=0,"",AN5*(N5/725))</f>
         <v/>
       </c>
@@ -8410,7 +8491,7 @@
       <c r="Z6" t="n">
         <v>0</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AA6" s="2" t="n">
         <v>1750</v>
       </c>
       <c r="AB6" t="n">
@@ -8450,36 +8531,37 @@
           <t>Build Hunter ( E )</t>
         </is>
       </c>
-      <c r="AK6" t="n">
+      <c r="AK6" s="2" t="n">
         <v>270</v>
       </c>
-      <c r="AL6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM6">
+      <c r="AL6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" s="2">
         <f>AK6*AL6</f>
         <v/>
       </c>
-      <c r="AN6">
+      <c r="AN6" s="3">
         <f>IF(D6=0,"",AS6/D6)</f>
         <v/>
       </c>
-      <c r="AO6">
+      <c r="AO6" s="3">
         <f>(N6/725)^2</f>
         <v/>
       </c>
-      <c r="AP6">
+      <c r="AP6" s="3">
         <f>IF(D6=0,"",AN6*AO6)</f>
         <v/>
       </c>
-      <c r="AR6" t="n">
+      <c r="AQ6" s="2" t="n"/>
+      <c r="AR6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AS6">
+      <c r="AS6" s="2">
         <f>AM6+N(AQ6)+N(AR6)</f>
         <v/>
       </c>
-      <c r="AT6">
+      <c r="AT6" s="3">
         <f>IF(D6=0,"",AN6*(N6/725))</f>
         <v/>
       </c>
@@ -8550,7 +8632,7 @@
       <c r="Z7" t="n">
         <v>0</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AA7" s="2" t="n">
         <v>2000</v>
       </c>
       <c r="AB7" t="n">
@@ -8590,36 +8672,37 @@
           <t>U pgrade to Jailing Officer</t>
         </is>
       </c>
-      <c r="AK7" t="n">
+      <c r="AK7" s="2" t="n">
         <v>971</v>
       </c>
-      <c r="AL7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM7">
+      <c r="AL7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM7" s="2">
         <f>AK7*AL7</f>
         <v/>
       </c>
-      <c r="AN7">
+      <c r="AN7" s="3">
         <f>IF(D7=0,"",AS7/D7)</f>
         <v/>
       </c>
-      <c r="AO7">
+      <c r="AO7" s="3">
         <f>(N7/725)^2</f>
         <v/>
       </c>
-      <c r="AP7">
+      <c r="AP7" s="3">
         <f>IF(D7=0,"",AN7*AO7)</f>
         <v/>
       </c>
-      <c r="AR7" t="n">
+      <c r="AQ7" s="2" t="n"/>
+      <c r="AR7" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="AS7">
+      <c r="AS7" s="2">
         <f>AM7+N(AQ7)+N(AR7)</f>
         <v/>
       </c>
-      <c r="AT7">
+      <c r="AT7" s="3">
         <f>IF(D7=0,"",AN7*(N7/725))</f>
         <v/>
       </c>
@@ -8690,7 +8773,7 @@
       <c r="Z8" t="n">
         <v>0</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AA8" s="2" t="n">
         <v>2250</v>
       </c>
       <c r="AB8" t="n">
@@ -8730,33 +8813,35 @@
           <t>Build Iron Mistress ( R )</t>
         </is>
       </c>
-      <c r="AK8" t="n">
+      <c r="AK8" s="2" t="n">
         <v>1127.5</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AL8" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="AM8">
+      <c r="AM8" s="2">
         <f>AK8*AL8</f>
         <v/>
       </c>
-      <c r="AN8">
+      <c r="AN8" s="3">
         <f>IF(D8=0,"",AS8/D8)</f>
         <v/>
       </c>
-      <c r="AO8">
+      <c r="AO8" s="3">
         <f>(N8/725)^2</f>
         <v/>
       </c>
-      <c r="AP8">
+      <c r="AP8" s="3">
         <f>IF(D8=0,"",AN8*AO8)</f>
         <v/>
       </c>
-      <c r="AS8">
+      <c r="AQ8" s="2" t="n"/>
+      <c r="AR8" s="2" t="n"/>
+      <c r="AS8" s="2">
         <f>AM8+N(AQ8)+N(AR8)</f>
         <v/>
       </c>
-      <c r="AT8">
+      <c r="AT8" s="3">
         <f>IF(D8=0,"",AN8*(N8/725))</f>
         <v/>
       </c>
@@ -8822,7 +8907,7 @@
       <c r="Z9" t="n">
         <v>1</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AA9" s="2" t="n">
         <v>1250</v>
       </c>
       <c r="AB9" t="n">
@@ -8862,33 +8947,35 @@
           <t>Build Chibidevil ( A )</t>
         </is>
       </c>
-      <c r="AK9" t="n">
+      <c r="AK9" s="2" t="n">
         <v>83.7</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AL9" s="3" t="n">
         <v>1.35</v>
       </c>
-      <c r="AM9">
+      <c r="AM9" s="2">
         <f>AK9*AL9</f>
         <v/>
       </c>
-      <c r="AN9">
+      <c r="AN9" s="3">
         <f>IF(D9=0,"",AS9/D9)</f>
         <v/>
       </c>
-      <c r="AO9">
+      <c r="AO9" s="3">
         <f>(N9/725)^2</f>
         <v/>
       </c>
-      <c r="AP9">
+      <c r="AP9" s="3">
         <f>IF(D9=0,"",AN9*AO9)</f>
         <v/>
       </c>
-      <c r="AS9">
+      <c r="AQ9" s="2" t="n"/>
+      <c r="AR9" s="2" t="n"/>
+      <c r="AS9" s="2">
         <f>AM9+N(AQ9)+N(AR9)</f>
         <v/>
       </c>
-      <c r="AT9">
+      <c r="AT9" s="3">
         <f>IF(D9=0,"",AN9*(N9/725))</f>
         <v/>
       </c>
@@ -8964,7 +9051,7 @@
       <c r="Z10" t="n">
         <v>1</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AA10" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="AB10" t="n">
@@ -9004,33 +9091,35 @@
           <t>Build The Unborn ( S )</t>
         </is>
       </c>
-      <c r="AK10" t="n">
+      <c r="AK10" s="2" t="n">
         <v>155</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AL10" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="AM10">
+      <c r="AM10" s="2">
         <f>AK10*AL10</f>
         <v/>
       </c>
-      <c r="AN10">
+      <c r="AN10" s="3">
         <f>IF(D10=0,"",AS10/D10)</f>
         <v/>
       </c>
-      <c r="AO10">
+      <c r="AO10" s="3">
         <f>(N10/725)^2</f>
         <v/>
       </c>
-      <c r="AP10">
+      <c r="AP10" s="3">
         <f>IF(D10=0,"",AN10*AO10)</f>
         <v/>
       </c>
-      <c r="AS10">
+      <c r="AQ10" s="2" t="n"/>
+      <c r="AR10" s="2" t="n"/>
+      <c r="AS10" s="2">
         <f>AM10+N(AQ10)+N(AR10)</f>
         <v/>
       </c>
-      <c r="AT10">
+      <c r="AT10" s="3">
         <f>IF(D10=0,"",AN10*(N10/725))</f>
         <v/>
       </c>
@@ -9106,7 +9195,7 @@
       <c r="Z11" t="n">
         <v>2</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AA11" s="2" t="n">
         <v>1750</v>
       </c>
       <c r="AB11" t="n">
@@ -9146,33 +9235,35 @@
           <t>U pgrade to Severe Trauma</t>
         </is>
       </c>
-      <c r="AK11" t="n">
+      <c r="AK11" s="2" t="n">
         <v>611.3</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AL11" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="AM11">
+      <c r="AM11" s="2">
         <f>AK11*AL11</f>
         <v/>
       </c>
-      <c r="AN11">
+      <c r="AN11" s="3">
         <f>IF(D11=0,"",AS11/D11)</f>
         <v/>
       </c>
-      <c r="AO11">
+      <c r="AO11" s="3">
         <f>(N11/725)^2</f>
         <v/>
       </c>
-      <c r="AP11">
+      <c r="AP11" s="3">
         <f>IF(D11=0,"",AN11*AO11)</f>
         <v/>
       </c>
-      <c r="AS11">
+      <c r="AQ11" s="2" t="n"/>
+      <c r="AR11" s="2" t="n"/>
+      <c r="AS11" s="2">
         <f>AM11+N(AQ11)+N(AR11)</f>
         <v/>
       </c>
-      <c r="AT11">
+      <c r="AT11" s="3">
         <f>IF(D11=0,"",AN11*(N11/725))</f>
         <v/>
       </c>
@@ -9243,7 +9334,7 @@
       <c r="Z12" t="n">
         <v>1</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AA12" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="AB12" t="n">
@@ -9283,36 +9374,37 @@
           <t>Build Lich Baron ( D )</t>
         </is>
       </c>
-      <c r="AK12" t="n">
+      <c r="AK12" s="2" t="n">
         <v>286.2</v>
       </c>
-      <c r="AL12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM12">
+      <c r="AL12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM12" s="2">
         <f>AK12*AL12</f>
         <v/>
       </c>
-      <c r="AN12">
+      <c r="AN12" s="3">
         <f>IF(D12=0,"",AS12/D12)</f>
         <v/>
       </c>
-      <c r="AO12">
+      <c r="AO12" s="3">
         <f>(N12/725)^2</f>
         <v/>
       </c>
-      <c r="AP12">
+      <c r="AP12" s="3">
         <f>IF(D12=0,"",AN12*AO12)</f>
         <v/>
       </c>
-      <c r="AR12" t="n">
+      <c r="AQ12" s="2" t="n"/>
+      <c r="AR12" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="AS12">
+      <c r="AS12" s="2">
         <f>AM12+N(AQ12)+N(AR12)</f>
         <v/>
       </c>
-      <c r="AT12">
+      <c r="AT12" s="3">
         <f>IF(D12=0,"",AN12*(N12/725))</f>
         <v/>
       </c>
@@ -9388,7 +9480,7 @@
       <c r="Z13" t="n">
         <v>2</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AA13" s="2" t="n">
         <v>2250</v>
       </c>
       <c r="AB13" t="n">
@@ -9428,33 +9520,35 @@
           <t>U pgrade to Demon Warlord</t>
         </is>
       </c>
-      <c r="AK13" t="n">
+      <c r="AK13" s="2" t="n">
         <v>851.5</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AL13" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="AM13">
+      <c r="AM13" s="2">
         <f>AK13*AL13</f>
         <v/>
       </c>
-      <c r="AN13">
+      <c r="AN13" s="3">
         <f>IF(D13=0,"",AS13/D13)</f>
         <v/>
       </c>
-      <c r="AO13">
+      <c r="AO13" s="3">
         <f>(N13/725)^2</f>
         <v/>
       </c>
-      <c r="AP13">
+      <c r="AP13" s="3">
         <f>IF(D13=0,"",AN13*AO13)</f>
         <v/>
       </c>
-      <c r="AS13">
+      <c r="AQ13" s="2" t="n"/>
+      <c r="AR13" s="2" t="n"/>
+      <c r="AS13" s="2">
         <f>AM13+N(AQ13)+N(AR13)</f>
         <v/>
       </c>
-      <c r="AT13">
+      <c r="AT13" s="3">
         <f>IF(D13=0,"",AN13*(N13/725))</f>
         <v/>
       </c>
@@ -9525,7 +9619,7 @@
       <c r="Z14" t="n">
         <v>3</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AA14" s="2" t="n">
         <v>2500</v>
       </c>
       <c r="AB14" t="n">
@@ -9565,33 +9659,35 @@
           <t>Build Promontory Disruptor ( F )</t>
         </is>
       </c>
-      <c r="AK14" t="n">
+      <c r="AK14" s="2" t="n">
         <v>975</v>
       </c>
-      <c r="AL14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM14">
+      <c r="AL14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM14" s="2">
         <f>AK14*AL14</f>
         <v/>
       </c>
-      <c r="AN14">
+      <c r="AN14" s="3">
         <f>IF(D14=0,"",AS14/D14)</f>
         <v/>
       </c>
-      <c r="AO14">
+      <c r="AO14" s="3">
         <f>(N14/725)^2</f>
         <v/>
       </c>
-      <c r="AP14">
+      <c r="AP14" s="3">
         <f>IF(D14=0,"",AN14*AO14)</f>
         <v/>
       </c>
-      <c r="AS14">
+      <c r="AQ14" s="2" t="n"/>
+      <c r="AR14" s="2" t="n"/>
+      <c r="AS14" s="2">
         <f>AM14+N(AQ14)+N(AR14)</f>
         <v/>
       </c>
-      <c r="AT14">
+      <c r="AT14" s="3">
         <f>IF(D14=0,"",AN14*(N14/725))</f>
         <v/>
       </c>
@@ -9662,7 +9758,7 @@
       <c r="Z15" t="n">
         <v>2</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AA15" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="AB15" t="n">
@@ -9702,33 +9798,35 @@
           <t>Build Delfino ( Z )</t>
         </is>
       </c>
-      <c r="AK15" t="n">
+      <c r="AK15" s="2" t="n">
         <v>452</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AL15" s="3" t="n">
         <v>1.52</v>
       </c>
-      <c r="AM15">
+      <c r="AM15" s="2">
         <f>AK15*AL15</f>
         <v/>
       </c>
-      <c r="AN15">
+      <c r="AN15" s="3">
         <f>IF(D15=0,"",AS15/D15)</f>
         <v/>
       </c>
-      <c r="AO15">
+      <c r="AO15" s="3">
         <f>(N15/725)^2</f>
         <v/>
       </c>
-      <c r="AP15">
+      <c r="AP15" s="3">
         <f>IF(D15=0,"",AN15*AO15)</f>
         <v/>
       </c>
-      <c r="AS15">
+      <c r="AQ15" s="2" t="n"/>
+      <c r="AR15" s="2" t="n"/>
+      <c r="AS15" s="2">
         <f>AM15+N(AQ15)+N(AR15)</f>
         <v/>
       </c>
-      <c r="AT15">
+      <c r="AT15" s="3">
         <f>IF(D15=0,"",AN15*(N15/725))</f>
         <v/>
       </c>
@@ -9799,7 +9897,7 @@
       <c r="Z16" t="n">
         <v>6</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AA16" s="2" t="n">
         <v>2250</v>
       </c>
       <c r="AB16" t="n">
@@ -9839,36 +9937,37 @@
           <t>U pgrade to Evolved Dweller</t>
         </is>
       </c>
-      <c r="AK16" t="n">
+      <c r="AK16" s="2" t="n">
         <v>1879.4</v>
       </c>
-      <c r="AL16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM16">
+      <c r="AL16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM16" s="2">
         <f>AK16*AL16</f>
         <v/>
       </c>
-      <c r="AN16">
+      <c r="AN16" s="3">
         <f>IF(D16=0,"",AS16/D16)</f>
         <v/>
       </c>
-      <c r="AO16">
+      <c r="AO16" s="3">
         <f>(N16/725)^2</f>
         <v/>
       </c>
-      <c r="AP16">
+      <c r="AP16" s="3">
         <f>IF(D16=0,"",AN16*AO16)</f>
         <v/>
       </c>
-      <c r="AR16" t="n">
+      <c r="AQ16" s="2" t="n"/>
+      <c r="AR16" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AS16">
+      <c r="AS16" s="2">
         <f>AM16+N(AQ16)+N(AR16)</f>
         <v/>
       </c>
-      <c r="AT16">
+      <c r="AT16" s="3">
         <f>IF(D16=0,"",AN16*(N16/725))</f>
         <v/>
       </c>
@@ -9939,7 +10038,7 @@
       <c r="Z17" t="n">
         <v>3</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AA17" s="2" t="n">
         <v>2250</v>
       </c>
       <c r="AB17" t="n">
@@ -9979,36 +10078,37 @@
           <t>Build Blackguard ( X )</t>
         </is>
       </c>
-      <c r="AK17" t="n">
+      <c r="AK17" s="2" t="n">
         <v>1948.3</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AL17" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="AM17">
+      <c r="AM17" s="2">
         <f>AK17*AL17</f>
         <v/>
       </c>
-      <c r="AN17">
+      <c r="AN17" s="3">
         <f>IF(D17=0,"",AS17/D17)</f>
         <v/>
       </c>
-      <c r="AO17">
+      <c r="AO17" s="3">
         <f>(N17/725)^2</f>
         <v/>
       </c>
-      <c r="AP17">
+      <c r="AP17" s="3">
         <f>IF(D17=0,"",AN17*AO17)</f>
         <v/>
       </c>
-      <c r="AR17" t="n">
+      <c r="AQ17" s="2" t="n"/>
+      <c r="AR17" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AS17">
+      <c r="AS17" s="2">
         <f>AM17+N(AQ17)+N(AR17)</f>
         <v/>
       </c>
-      <c r="AT17">
+      <c r="AT17" s="3">
         <f>IF(D17=0,"",AN17*(N17/725))</f>
         <v/>
       </c>
@@ -10079,7 +10179,7 @@
       <c r="Z18" t="n">
         <v>4</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AA18" s="2" t="n">
         <v>2750</v>
       </c>
       <c r="AB18" t="n">
@@ -10119,36 +10219,37 @@
           <t>U pgrade to Noir Heart</t>
         </is>
       </c>
-      <c r="AK18" t="n">
+      <c r="AK18" s="2" t="n">
         <v>3731.1</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AL18" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="AM18">
+      <c r="AM18" s="2">
         <f>AK18*AL18</f>
         <v/>
       </c>
-      <c r="AN18">
+      <c r="AN18" s="3">
         <f>IF(D18=0,"",AS18/D18)</f>
         <v/>
       </c>
-      <c r="AO18">
+      <c r="AO18" s="3">
         <f>(N18/725)^2</f>
         <v/>
       </c>
-      <c r="AP18">
+      <c r="AP18" s="3">
         <f>IF(D18=0,"",AN18*AO18)</f>
         <v/>
       </c>
-      <c r="AR18" t="n">
+      <c r="AQ18" s="2" t="n"/>
+      <c r="AR18" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="AS18">
+      <c r="AS18" s="2">
         <f>AM18+N(AQ18)+N(AR18)</f>
         <v/>
       </c>
-      <c r="AT18">
+      <c r="AT18" s="3">
         <f>IF(D18=0,"",AN18*(N18/725))</f>
         <v/>
       </c>
@@ -10216,7 +10317,7 @@
       <c r="P19" t="n">
         <v>4037.3</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AA19" s="2" t="n">
         <v>3000</v>
       </c>
       <c r="AB19" t="n">
@@ -10256,36 +10357,37 @@
           <t>Build Terra Warrior ( C )</t>
         </is>
       </c>
-      <c r="AK19" t="n">
+      <c r="AK19" s="2" t="n">
         <v>4037.3</v>
       </c>
-      <c r="AL19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM19">
+      <c r="AL19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM19" s="2">
         <f>AK19*AL19</f>
         <v/>
       </c>
-      <c r="AN19">
+      <c r="AN19" s="3">
         <f>IF(D19=0,"",AS19/D19)</f>
         <v/>
       </c>
-      <c r="AO19">
+      <c r="AO19" s="3">
         <f>(N19/725)^2</f>
         <v/>
       </c>
-      <c r="AP19">
+      <c r="AP19" s="3">
         <f>IF(D19=0,"",AN19*AO19)</f>
         <v/>
       </c>
-      <c r="AR19" t="n">
+      <c r="AQ19" s="2" t="n"/>
+      <c r="AR19" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AS19">
+      <c r="AS19" s="2">
         <f>AM19+N(AQ19)+N(AR19)</f>
         <v/>
       </c>
-      <c r="AT19">
+      <c r="AT19" s="3">
         <f>IF(D19=0,"",AN19*(N19/725))</f>
         <v/>
       </c>
@@ -10361,7 +10463,7 @@
       <c r="Z20" t="n">
         <v>7</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AA20" s="2" t="n">
         <v>3500</v>
       </c>
       <c r="AB20" t="n">
@@ -10401,33 +10503,35 @@
           <t>U pgrade to Gaia's Avatar</t>
         </is>
       </c>
-      <c r="AK20" t="n">
+      <c r="AK20" s="2" t="n">
         <v>6926.1</v>
       </c>
-      <c r="AL20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM20">
+      <c r="AL20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM20" s="2">
         <f>AK20*AL20</f>
         <v/>
       </c>
-      <c r="AN20">
+      <c r="AN20" s="3">
         <f>IF(D20=0,"",AS20/D20)</f>
         <v/>
       </c>
-      <c r="AO20">
+      <c r="AO20" s="3">
         <f>(N20/725)^2</f>
         <v/>
       </c>
-      <c r="AP20">
+      <c r="AP20" s="3">
         <f>IF(D20=0,"",AN20*AO20)</f>
         <v/>
       </c>
-      <c r="AS20">
+      <c r="AQ20" s="2" t="n"/>
+      <c r="AR20" s="2" t="n"/>
+      <c r="AS20" s="2">
         <f>AM20+N(AQ20)+N(AR20)</f>
         <v/>
       </c>
-      <c r="AT20">
+      <c r="AT20" s="3">
         <f>IF(D20=0,"",AN20*(N20/725))</f>
         <v/>
       </c>
@@ -10835,7 +10939,7 @@
       <c r="Z2" t="n">
         <v>10</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AA2" s="2" t="n">
         <v>2750</v>
       </c>
       <c r="AB2" t="n">
@@ -10875,33 +10979,35 @@
           <t>Build Grayson's Fort Buster ( R )</t>
         </is>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AQ2" s="2" t="n">
         <v>2147.1</v>
       </c>
-      <c r="AR2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS2">
+      <c r="AR2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS2" s="2">
         <f>AQ2*AR2</f>
         <v/>
       </c>
-      <c r="AT2">
+      <c r="AT2" s="3">
         <f>IF(D2=0,"",AY2/D2)</f>
         <v/>
       </c>
-      <c r="AU2">
+      <c r="AU2" s="3">
         <f>(N2/725)^2</f>
         <v/>
       </c>
-      <c r="AV2">
+      <c r="AV2" s="3">
         <f>IF(D2=0,"",AT2*AU2)</f>
         <v/>
       </c>
-      <c r="AY2">
+      <c r="AW2" s="2" t="n"/>
+      <c r="AX2" s="2" t="n"/>
+      <c r="AY2" s="2">
         <f>AS2+N(AW2)+N(AX2)</f>
         <v/>
       </c>
-      <c r="AZ2">
+      <c r="AZ2" s="3">
         <f>IF(D2=0,"",AT2*(N2/725))</f>
         <v/>
       </c>
@@ -10972,7 +11078,7 @@
       <c r="Z3" t="n">
         <v>1</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AA3" s="2" t="n">
         <v>1250</v>
       </c>
       <c r="AB3" t="n">
@@ -11022,33 +11128,35 @@
           <t>HERO attack type - a third attack type after magic and chaos, and stock WC3 Hero damage takes reduced penalties from most armour types.</t>
         </is>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AQ3" s="2" t="n">
         <v>117.5</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AR3" s="3" t="n">
         <v>1.35</v>
       </c>
-      <c r="AS3">
+      <c r="AS3" s="2">
         <f>AQ3*AR3</f>
         <v/>
       </c>
-      <c r="AT3">
+      <c r="AT3" s="3">
         <f>IF(D3=0,"",AY3/D3)</f>
         <v/>
       </c>
-      <c r="AU3">
+      <c r="AU3" s="3">
         <f>(N3/725)^2</f>
         <v/>
       </c>
-      <c r="AV3">
+      <c r="AV3" s="3">
         <f>IF(D3=0,"",AT3*AU3)</f>
         <v/>
       </c>
-      <c r="AY3">
+      <c r="AW3" s="2" t="n"/>
+      <c r="AX3" s="2" t="n"/>
+      <c r="AY3" s="2">
         <f>AS3+N(AW3)+N(AX3)</f>
         <v/>
       </c>
-      <c r="AZ3">
+      <c r="AZ3" s="3">
         <f>IF(D3=0,"",AT3*(N3/725))</f>
         <v/>
       </c>
@@ -11116,7 +11224,7 @@
       <c r="Z4" t="n">
         <v>2</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AA4" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="AO4" t="inlineStr">
@@ -11129,36 +11237,37 @@
           <t>x2.9 damage over its base and nearly DOUBLE the range (550 -&gt; 975), which is the biggest range gain recorded on any upgrade.</t>
         </is>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AQ4" s="2" t="n">
         <v>279</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="AR4" s="3" t="n">
         <v>1.35</v>
       </c>
-      <c r="AS4">
+      <c r="AS4" s="2">
         <f>AQ4*AR4</f>
         <v/>
       </c>
-      <c r="AT4">
+      <c r="AT4" s="3">
         <f>IF(D4=0,"",AY4/D4)</f>
         <v/>
       </c>
-      <c r="AU4">
+      <c r="AU4" s="3">
         <f>(N4/725)^2</f>
         <v/>
       </c>
-      <c r="AV4">
+      <c r="AV4" s="3">
         <f>IF(D4=0,"",AT4*AU4)</f>
         <v/>
       </c>
-      <c r="AX4" t="n">
+      <c r="AW4" s="2" t="n"/>
+      <c r="AX4" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AY4">
+      <c r="AY4" s="2">
         <f>AS4+N(AW4)+N(AX4)</f>
         <v/>
       </c>
-      <c r="AZ4">
+      <c r="AZ4" s="3">
         <f>IF(D4=0,"",AT4*(N4/725))</f>
         <v/>
       </c>
@@ -11229,7 +11338,7 @@
       <c r="Z5" t="n">
         <v>3</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AA5" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="AB5" t="n">
@@ -11269,39 +11378,39 @@
           <t>Build Tyr's Spirit ( W )</t>
         </is>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AQ5" s="2" t="n">
         <v>388</v>
       </c>
-      <c r="AR5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS5">
+      <c r="AR5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS5" s="2">
         <f>AQ5*AR5</f>
         <v/>
       </c>
-      <c r="AT5">
+      <c r="AT5" s="3">
         <f>IF(D5=0,"",AY5/D5)</f>
         <v/>
       </c>
-      <c r="AU5">
+      <c r="AU5" s="3">
         <f>(N5/725)^2</f>
         <v/>
       </c>
-      <c r="AV5">
+      <c r="AV5" s="3">
         <f>IF(D5=0,"",AT5*AU5)</f>
         <v/>
       </c>
-      <c r="AW5" t="n">
+      <c r="AW5" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="AX5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AY5">
+      <c r="AY5" s="2">
         <f>AS5+N(AW5)+N(AX5)</f>
         <v/>
       </c>
-      <c r="AZ5">
+      <c r="AZ5" s="3">
         <f>IF(D5=0,"",AT5*(N5/725))</f>
         <v/>
       </c>
@@ -11377,7 +11486,7 @@
       <c r="Z6" t="n">
         <v>4</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AA6" s="2" t="n">
         <v>2000</v>
       </c>
       <c r="AB6" t="n">
@@ -11427,33 +11536,35 @@
           <t>STRONGEST TOWER RECORDED IN ANY KIT: 34.19 range-adjusted vs heroes, ahead of Absolute Zero (26.60) and Arcadia (23.90). FULL TRAIT SWAP: Tyr Spirit carried Bash I + slow poison I; this carries Boss Assassin I + splash - BOTH traits replaced, not merely one, alongside x6.5 damage. Also CONFIRMS Boss Assassin I at 50% x4 vs heroes, which had been inferred from the II tier.</t>
         </is>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AQ6" s="2" t="n">
         <v>1580</v>
       </c>
-      <c r="AR6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS6">
+      <c r="AR6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" s="2">
         <f>AQ6*AR6</f>
         <v/>
       </c>
-      <c r="AT6">
+      <c r="AT6" s="3">
         <f>IF(D6=0,"",AY6/D6)</f>
         <v/>
       </c>
-      <c r="AU6">
+      <c r="AU6" s="3">
         <f>(N6/725)^2</f>
         <v/>
       </c>
-      <c r="AV6">
+      <c r="AV6" s="3">
         <f>IF(D6=0,"",AT6*AU6)</f>
         <v/>
       </c>
-      <c r="AY6">
+      <c r="AW6" s="2" t="n"/>
+      <c r="AX6" s="2" t="n"/>
+      <c r="AY6" s="2">
         <f>AS6+N(AW6)+N(AX6)</f>
         <v/>
       </c>
-      <c r="AZ6">
+      <c r="AZ6" s="3">
         <f>IF(D6=0,"",AT6*(N6/725))</f>
         <v/>
       </c>
@@ -11521,7 +11632,7 @@
       <c r="P7" t="n">
         <v>1485</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AA7" s="2" t="n">
         <v>1750</v>
       </c>
       <c r="AB7" t="n">
@@ -11561,36 +11672,37 @@
           <t>Build Peppy Bronzebeard ( E )</t>
         </is>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AQ7" s="2" t="n">
         <v>1485</v>
       </c>
-      <c r="AR7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS7">
+      <c r="AR7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" s="2">
         <f>AQ7*AR7</f>
         <v/>
       </c>
-      <c r="AT7">
+      <c r="AT7" s="3">
         <f>IF(D7=0,"",AY7/D7)</f>
         <v/>
       </c>
-      <c r="AU7">
+      <c r="AU7" s="3">
         <f>(N7/725)^2</f>
         <v/>
       </c>
-      <c r="AV7">
+      <c r="AV7" s="3">
         <f>IF(D7=0,"",AT7*AU7)</f>
         <v/>
       </c>
-      <c r="AX7" t="n">
+      <c r="AW7" s="2" t="n"/>
+      <c r="AX7" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="AY7">
+      <c r="AY7" s="2">
         <f>AS7+N(AW7)+N(AX7)</f>
         <v/>
       </c>
-      <c r="AZ7">
+      <c r="AZ7" s="3">
         <f>IF(D7=0,"",AT7*(N7/725))</f>
         <v/>
       </c>
@@ -11689,7 +11801,7 @@
       <c r="Z8" t="n">
         <v>6</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AA8" s="2" t="n">
         <v>2250</v>
       </c>
       <c r="AB8" t="n">
@@ -11743,33 +11855,35 @@
           <t>ONLY DUAL-ATTACK-TYPE TOWER RECORDED: it deals hero AND magic damage in the same volley. That is a HEDGE AGAINST THE ARMOUR MATRIX - against a pure-hero tower of the same total damage it is -9% on Medium, level on Heavy, and +15% on FORTIFIED where hero damage is halved. So it trades peak for floor: it can never be fully countered by armour type. ASSUMPTION: both profiles fire each cycle. If they alternate, halve every figure here - worth confirming. 20.83 vs air on the both-fire reading.</t>
         </is>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AQ8" s="2" t="n">
         <v>1728.9</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="AR8" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="AS8">
+      <c r="AS8" s="2">
         <f>AQ8*AR8</f>
         <v/>
       </c>
-      <c r="AT8">
+      <c r="AT8" s="3">
         <f>IF(D8=0,"",AY8/D8)</f>
         <v/>
       </c>
-      <c r="AU8">
+      <c r="AU8" s="3">
         <f>(N8/725)^2</f>
         <v/>
       </c>
-      <c r="AV8">
+      <c r="AV8" s="3">
         <f>IF(D8=0,"",AT8*AU8)</f>
         <v/>
       </c>
-      <c r="AY8">
+      <c r="AW8" s="2" t="n"/>
+      <c r="AX8" s="2" t="n"/>
+      <c r="AY8" s="2">
         <f>AS8+N(AW8)+N(AX8)</f>
         <v/>
       </c>
-      <c r="AZ8">
+      <c r="AZ8" s="3">
         <f>IF(D8=0,"",AT8*(N8/725))</f>
         <v/>
       </c>
@@ -11840,7 +11954,7 @@
       <c r="Z9" t="n">
         <v>1</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AA9" s="2" t="n">
         <v>1250</v>
       </c>
       <c r="AB9" t="n">
@@ -11890,33 +12004,35 @@
           <t>The 70% slow is the strongest slow recorded anywhere - Poison II is 40%. Note it is AIR slow poison, so the tower answers air by CONTROL while answering bosses by DAMAGE.</t>
         </is>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AQ9" s="2" t="n">
         <v>158.2</v>
       </c>
-      <c r="AR9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS9">
+      <c r="AR9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS9" s="2">
         <f>AQ9*AR9</f>
         <v/>
       </c>
-      <c r="AT9">
+      <c r="AT9" s="3">
         <f>IF(D9=0,"",AY9/D9)</f>
         <v/>
       </c>
-      <c r="AU9">
+      <c r="AU9" s="3">
         <f>(N9/725)^2</f>
         <v/>
       </c>
-      <c r="AV9">
+      <c r="AV9" s="3">
         <f>IF(D9=0,"",AT9*AU9)</f>
         <v/>
       </c>
-      <c r="AY9">
+      <c r="AW9" s="2" t="n"/>
+      <c r="AX9" s="2" t="n"/>
+      <c r="AY9" s="2">
         <f>AS9+N(AW9)+N(AX9)</f>
         <v/>
       </c>
-      <c r="AZ9">
+      <c r="AZ9" s="3">
         <f>IF(D9=0,"",AT9*(N9/725))</f>
         <v/>
       </c>
@@ -11992,7 +12108,7 @@
       <c r="Z10" t="n">
         <v>2</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AA10" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="AB10" t="n">
@@ -12042,33 +12158,35 @@
           <t>TRAIT SWAP - CONFIRMED by the owner 2026-09-05. The upgrade TRADES Boss Assassin II for Air Critical Strike I: it stops being the anti-boss tower and becomes an anti-air one. So an upgrade here is a ROLE decision, not a power decision. Note the efficiency consequence: Ignatious is 14.40 range-adjusted vs heroes, Prince Delphian is 4.27 vs air - upgrading is a straight LOSS unless you need the role it swaps to.</t>
         </is>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AQ10" s="2" t="n">
         <v>417.5</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="AR10" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="AS10">
+      <c r="AS10" s="2">
         <f>AQ10*AR10</f>
         <v/>
       </c>
-      <c r="AT10">
+      <c r="AT10" s="3">
         <f>IF(D10=0,"",AY10/D10)</f>
         <v/>
       </c>
-      <c r="AU10">
+      <c r="AU10" s="3">
         <f>(N10/725)^2</f>
         <v/>
       </c>
-      <c r="AV10">
+      <c r="AV10" s="3">
         <f>IF(D10=0,"",AT10*AU10)</f>
         <v/>
       </c>
-      <c r="AY10">
+      <c r="AW10" s="2" t="n"/>
+      <c r="AX10" s="2" t="n"/>
+      <c r="AY10" s="2">
         <f>AS10+N(AW10)+N(AX10)</f>
         <v/>
       </c>
-      <c r="AZ10">
+      <c r="AZ10" s="3">
         <f>IF(D10=0,"",AT10*(N10/725))</f>
         <v/>
       </c>
@@ -12139,7 +12257,7 @@
       <c r="Z11" t="n">
         <v>3</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AA11" s="2" t="n">
         <v>1750</v>
       </c>
       <c r="AB11" t="n">
@@ -12189,36 +12307,37 @@
           <t>Unlock confirmed by the owner 2026-09-05. THREE named traits on one tower - the most recorded, and the clearest single piece of evidence that towers are ASSEMBLED from a shared library rather than authored as bespoke stat blocks. Two of the three match towers in OTHER kits: Vindicator II (50% x6 attacking) is what the treant Arcadia has been carrying unnamed, and Judgement (100 dps vs air) is the same 100 dps as Little Jack's tornado, at 20s here against 10s there. 15.45 range-adjusted vs attacking, 4.41 untyped.</t>
         </is>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AQ11" s="2" t="n">
         <v>466.7</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="AR11" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="AS11">
+      <c r="AS11" s="2">
         <f>AQ11*AR11</f>
         <v/>
       </c>
-      <c r="AT11">
+      <c r="AT11" s="3">
         <f>IF(D11=0,"",AY11/D11)</f>
         <v/>
       </c>
-      <c r="AU11">
+      <c r="AU11" s="3">
         <f>(N11/725)^2</f>
         <v/>
       </c>
-      <c r="AV11">
+      <c r="AV11" s="3">
         <f>IF(D11=0,"",AT11*AU11)</f>
         <v/>
       </c>
-      <c r="AX11" t="n">
+      <c r="AW11" s="2" t="n"/>
+      <c r="AX11" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="AY11">
+      <c r="AY11" s="2">
         <f>AS11+N(AW11)+N(AX11)</f>
         <v/>
       </c>
-      <c r="AZ11">
+      <c r="AZ11" s="3">
         <f>IF(D11=0,"",AT11*(N11/725))</f>
         <v/>
       </c>
@@ -12289,7 +12408,7 @@
       <c r="Z12" t="n">
         <v>4</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AA12" s="2" t="n">
         <v>2000</v>
       </c>
       <c r="AB12" t="n">
@@ -12339,36 +12458,37 @@
           <t>SECOND-STRONGEST TOWER RECORDED (23.75 vs attacking, behind only Odin's Soul at 34.19) AND genuinely dual-role at 10.79 vs air. Four named traits, the most on any tower. Against its base High Priest it keeps Cure II and Judgement, tier-bumps Vindicator II -&gt; III, and adds Air Critical Strike II - three kinds of edit in one upgrade.</t>
         </is>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AQ12" s="2" t="n">
         <v>1266</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="AR12" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="AS12">
+      <c r="AS12" s="2">
         <f>AQ12*AR12</f>
         <v/>
       </c>
-      <c r="AT12">
+      <c r="AT12" s="3">
         <f>IF(D12=0,"",AY12/D12)</f>
         <v/>
       </c>
-      <c r="AU12">
+      <c r="AU12" s="3">
         <f>(N12/725)^2</f>
         <v/>
       </c>
-      <c r="AV12">
+      <c r="AV12" s="3">
         <f>IF(D12=0,"",AT12*AU12)</f>
         <v/>
       </c>
-      <c r="AX12" t="n">
+      <c r="AW12" s="2" t="n"/>
+      <c r="AX12" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="AY12">
+      <c r="AY12" s="2">
         <f>AS12+N(AW12)+N(AX12)</f>
         <v/>
       </c>
-      <c r="AZ12">
+      <c r="AZ12" s="3">
         <f>IF(D12=0,"",AT12*(N12/725))</f>
         <v/>
       </c>
@@ -12444,7 +12564,7 @@
       <c r="Z13" t="n">
         <v>8</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AA13" s="2" t="n">
         <v>3000</v>
       </c>
       <c r="AB13" t="n">
@@ -12484,33 +12604,35 @@
           <t>Build Petrified Cell ( C )</t>
         </is>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AQ13" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="AR13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS13">
+      <c r="AR13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS13" s="2">
         <f>AQ13*AR13</f>
         <v/>
       </c>
-      <c r="AT13">
+      <c r="AT13" s="3">
         <f>IF(D13=0,"",AY13/D13)</f>
         <v/>
       </c>
-      <c r="AU13">
+      <c r="AU13" s="3">
         <f>(N13/725)^2</f>
         <v/>
       </c>
-      <c r="AV13">
+      <c r="AV13" s="3">
         <f>IF(D13=0,"",AT13*AU13)</f>
         <v/>
       </c>
-      <c r="AY13">
+      <c r="AW13" s="2" t="n"/>
+      <c r="AX13" s="2" t="n"/>
+      <c r="AY13" s="2">
         <f>AS13+N(AW13)+N(AX13)</f>
         <v/>
       </c>
-      <c r="AZ13">
+      <c r="AZ13" s="3">
         <f>IF(D13=0,"",AT13*(N13/725))</f>
         <v/>
       </c>
@@ -12586,7 +12708,7 @@
       <c r="Z14" t="n">
         <v>9</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AA14" s="2" t="n">
         <v>3250</v>
       </c>
       <c r="AB14" t="n">
@@ -12631,33 +12753,35 @@
           <t>AN UPGRADE THAT LOWERS RAW DAMAGE: Petrified Shell is 600, this is 326 (-46%). It wins it back through crit RELIABILITY - Versatile II at 65% x2.75 gives an expected hit of 698 vs the base 600, so +16% despite the smaller number. VERSATILE II = 65% x2.75 against I's 35% x2.5: the CHANCE nearly doubled while the multiplier barely moved, so this tier scales reliability rather than peak. FROST TIERS SCALE DURATION, not the slow value (owner) - different again from Slow Poison, where both dps and slow% moved. So the scaling AXIS is per-trait too, not just the rate. Very rapid at 800 range gives 4.90 range-adjusted - and since Versatile hits ALL units, that applies on EVERY wave rather than on a schedule.</t>
         </is>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AQ14" s="2" t="n">
         <v>1306</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="AR14" s="3" t="n">
         <v>2.05</v>
       </c>
-      <c r="AS14">
+      <c r="AS14" s="2">
         <f>AQ14*AR14</f>
         <v/>
       </c>
-      <c r="AT14">
+      <c r="AT14" s="3">
         <f>IF(D14=0,"",AY14/D14)</f>
         <v/>
       </c>
-      <c r="AU14">
+      <c r="AU14" s="3">
         <f>(N14/725)^2</f>
         <v/>
       </c>
-      <c r="AV14">
+      <c r="AV14" s="3">
         <f>IF(D14=0,"",AT14*AU14)</f>
         <v/>
       </c>
-      <c r="AY14">
+      <c r="AW14" s="2" t="n"/>
+      <c r="AX14" s="2" t="n"/>
+      <c r="AY14" s="2">
         <f>AS14+N(AW14)+N(AX14)</f>
         <v/>
       </c>
-      <c r="AZ14">
+      <c r="AZ14" s="3">
         <f>IF(D14=0,"",AT14*(N14/725))</f>
         <v/>
       </c>
@@ -12733,7 +12857,7 @@
       <c r="Z15" t="n">
         <v>1</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AA15" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="AB15" t="n">
@@ -12783,33 +12907,35 @@
           <t>THREE firsts. (1) SIEGE attack type - fourth after magic, chaos and hero. (2) AIR DEFICIENCY is the first NEGATIVE trait recorded: 25% of hits deal quarter damage vs air, so it does 81.2% damage to air. The trait library contains DRAWBACKS, not only bonuses. (3) STRUCTURAL: DIRECTLY AVAILABLE - a third starting tower alongside D1 and D2. The owner first called it "T3" meaning third-available, then clarified the D3 slot is Tyr Spirit, so this sits outside the numbered progression. Low output (2.13 range-adj) - like Slammer, a UTILITY tower bought for its multi-target heal.</t>
         </is>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AQ15" s="2" t="n">
         <v>324</v>
       </c>
-      <c r="AR15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS15">
+      <c r="AR15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS15" s="2">
         <f>AQ15*AR15</f>
         <v/>
       </c>
-      <c r="AT15">
+      <c r="AT15" s="3">
         <f>IF(D15=0,"",AY15/D15)</f>
         <v/>
       </c>
-      <c r="AU15">
+      <c r="AU15" s="3">
         <f>(N15/725)^2</f>
         <v/>
       </c>
-      <c r="AV15">
+      <c r="AV15" s="3">
         <f>IF(D15=0,"",AT15*AU15)</f>
         <v/>
       </c>
-      <c r="AY15">
+      <c r="AW15" s="2" t="n"/>
+      <c r="AX15" s="2" t="n"/>
+      <c r="AY15" s="2">
         <f>AS15+N(AW15)+N(AX15)</f>
         <v/>
       </c>
-      <c r="AZ15">
+      <c r="AZ15" s="3">
         <f>IF(D15=0,"",AT15*(N15/725))</f>
         <v/>
       </c>
@@ -12885,7 +13011,7 @@
       <c r="Z16" t="n">
         <v>2</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AA16" s="2" t="n">
         <v>1750</v>
       </c>
       <c r="AB16" t="n">
@@ -12935,33 +13061,35 @@
           <t>A huge step over K-Dig: damage x3.9 (81 -&gt; 312), range 700 -&gt; 900, and 2.13 -&gt; 13.41 range-adjusted vs mechanical. The upgrade KEEPS the heal (owner-confirmed) and ADDS Machine Critical Strike, so this kit does all three upgrade flavours - Ignatious SWAPS a trait, this one KEEPS and ADDS. CONFIRMED 2026-09-05: the upgrade REMOVES Air Deficiency. So this kit demonstrates all THREE upgrade flavours - Ignatious swaps a trait away, Xavier keeps one, adds one, and drops a drawback. "Remove a negative" is a real upgrade payoff here.</t>
         </is>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AQ16" s="2" t="n">
         <v>693.3</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="AR16" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="AS16">
+      <c r="AS16" s="2">
         <f>AQ16*AR16</f>
         <v/>
       </c>
-      <c r="AT16">
+      <c r="AT16" s="3">
         <f>IF(D16=0,"",AY16/D16)</f>
         <v/>
       </c>
-      <c r="AU16">
+      <c r="AU16" s="3">
         <f>(N16/725)^2</f>
         <v/>
       </c>
-      <c r="AV16">
+      <c r="AV16" s="3">
         <f>IF(D16=0,"",AT16*AU16)</f>
         <v/>
       </c>
-      <c r="AY16">
+      <c r="AW16" s="2" t="n"/>
+      <c r="AX16" s="2" t="n"/>
+      <c r="AY16" s="2">
         <f>AS16+N(AW16)+N(AX16)</f>
         <v/>
       </c>
-      <c r="AZ16">
+      <c r="AZ16" s="3">
         <f>IF(D16=0,"",AT16*(N16/725))</f>
         <v/>
       </c>
@@ -13032,7 +13160,7 @@
       <c r="Z17" t="n">
         <v>3</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AA17" s="2" t="n">
         <v>2000</v>
       </c>
       <c r="AB17" t="n">
@@ -13077,36 +13205,37 @@
           <t>Its Versatile Critical Strike is tier I, confirmed 2026-09-05 as identical to Delphinus's (35% x2.5). BUY IT FOR PERMANENT STUN, NOT DAMAGE. Bash II on a very-rapid chassis procs every ~1.75s against a 2s stun, so it holds ~100% STUN UPTIME on ground non-hero units. The treant Battleship Mackinaw carries the SAME Bash II on medium fire and gets only ~40% - the same library entry worth ~2.5x more here, purely from fire rate. Damage reads a poor 2.89 range-adjusted because its 350 range is the WORST recorded in any kit (coverage 0.48). VERSATILE CRITICAL STRIKE is the first crit recorded that hits ALL units, so its 35% x2.5 applies on every wave rather than on a schedule.</t>
         </is>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AQ17" s="2" t="n">
         <v>721</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="AR17" s="3" t="n">
         <v>1.52</v>
       </c>
-      <c r="AS17">
+      <c r="AS17" s="2">
         <f>AQ17*AR17</f>
         <v/>
       </c>
-      <c r="AT17">
+      <c r="AT17" s="3">
         <f>IF(D17=0,"",AY17/D17)</f>
         <v/>
       </c>
-      <c r="AU17">
+      <c r="AU17" s="3">
         <f>(N17/725)^2</f>
         <v/>
       </c>
-      <c r="AV17">
+      <c r="AV17" s="3">
         <f>IF(D17=0,"",AT17*AU17)</f>
         <v/>
       </c>
-      <c r="AW17" t="n">
+      <c r="AW17" s="2" t="n">
         <v>94</v>
       </c>
-      <c r="AY17">
+      <c r="AX17" s="2" t="n"/>
+      <c r="AY17" s="2">
         <f>AS17+N(AW17)+N(AX17)</f>
         <v/>
       </c>
-      <c r="AZ17">
+      <c r="AZ17" s="3">
         <f>IF(D17=0,"",AT17*(N17/725))</f>
         <v/>
       </c>
@@ -13177,7 +13306,7 @@
       <c r="Z18" t="n">
         <v>4</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AA18" s="2" t="n">
         <v>2500</v>
       </c>
       <c r="AB18" t="n">
@@ -13222,33 +13351,35 @@
           <t>CORRECTED 2026-09-05: it KEEPS Versatile Critical Strike (tier I) and has THREE spells, not four. An earlier note here said it had no crit and a full trait wipe - wrong on both. It drops only BASH II. Since Versatile hits ALL units, its 8.63 applies on every wave. CONFIRMED 2026-09-05: Bartlebee and Delphinus carry the SAME Versatile Critical Strike I (35% x2.5), so the upgrade keeps the trait flat and adds mana and spells on top. RAIL DRIVER IS AN EXECUTE, and executes scale with the HP ramp instead of falling behind it: worth 335 damage at wave 5 and 6300 at wave 20, so it goes from a quarter of Moon Tone Cannon's value to FIVE TIMES it with no scaling text anywhere. ANSWERS THE TIER-1 QUESTION: it does NOT keep Bash II, so the K-Dig line stops being the stun answer - though Vacuum Torpedo's 8s AoE slow keeps it a CONTROL tower, changing the mechanism rather than the job. FIRST MANA TOWER outside the Archimonde hero, so mana is a per-tower property rather than a whole-hero identity.</t>
         </is>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AQ18" s="2" t="n">
         <v>2668</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="AR18" s="3" t="n">
         <v>1.52</v>
       </c>
-      <c r="AS18">
+      <c r="AS18" s="2">
         <f>AQ18*AR18</f>
         <v/>
       </c>
-      <c r="AT18">
+      <c r="AT18" s="3">
         <f>IF(D18=0,"",AY18/D18)</f>
         <v/>
       </c>
-      <c r="AU18">
+      <c r="AU18" s="3">
         <f>(N18/725)^2</f>
         <v/>
       </c>
-      <c r="AV18">
+      <c r="AV18" s="3">
         <f>IF(D18=0,"",AT18*AU18)</f>
         <v/>
       </c>
-      <c r="AY18">
+      <c r="AW18" s="2" t="n"/>
+      <c r="AX18" s="2" t="n"/>
+      <c r="AY18" s="2">
         <f>AS18+N(AW18)+N(AX18)</f>
         <v/>
       </c>
-      <c r="AZ18">
+      <c r="AZ18" s="3">
         <f>IF(D18=0,"",AT18*(N18/725))</f>
         <v/>
       </c>
@@ -13316,7 +13447,7 @@
       <c r="P19" t="n">
         <v>1707.5</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AA19" s="2" t="n">
         <v>1750</v>
       </c>
       <c r="AB19" t="n">
@@ -13361,33 +13492,35 @@
           <t>LONGEST RANGE RECORDED IN ANY KIT at 1200 (coverage 1.66 vs the 725 baseline), and that range is most of why it scores 18.35 vs air - third overall behind Odin's Soul 34.19 and Absolute Zero 26.60, and by far the Royal Family's best air answer (Martyr is 10.79). TIER IS NOT A POWER LADDER: 440g and deeper than Martyr, yet carries Vindicator I where the 260g Martyr carries Vindicator III - a new tower unlocked by Martyr, not its upgrade. Vindicator I's multiplier is still unread, so the vs-attacking figure is uncomputed.</t>
         </is>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AQ19" s="2" t="n">
         <v>1707.5</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="AR19" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="AS19">
+      <c r="AS19" s="2">
         <f>AQ19*AR19</f>
         <v/>
       </c>
-      <c r="AT19">
+      <c r="AT19" s="3">
         <f>IF(D19=0,"",AY19/D19)</f>
         <v/>
       </c>
-      <c r="AU19">
+      <c r="AU19" s="3">
         <f>(N19/725)^2</f>
         <v/>
       </c>
-      <c r="AV19">
+      <c r="AV19" s="3">
         <f>IF(D19=0,"",AT19*AU19)</f>
         <v/>
       </c>
-      <c r="AY19">
+      <c r="AW19" s="2" t="n"/>
+      <c r="AX19" s="2" t="n"/>
+      <c r="AY19" s="2">
         <f>AS19+N(AW19)+N(AX19)</f>
         <v/>
       </c>
-      <c r="AZ19">
+      <c r="AZ19" s="3">
         <f>IF(D19=0,"",AT19*(N19/725))</f>
         <v/>
       </c>
@@ -13458,7 +13591,7 @@
       <c r="Z20" t="n">
         <v>6</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AA20" s="2" t="n">
         <v>2500</v>
       </c>
       <c r="AB20" t="n">
@@ -13503,33 +13636,35 @@
           <t>AVIARY DEGENERATION RESOLVED: a 20% AURA SLOW on nearby AIR units - a debuff applied to enemies, not a self-penalty. FIRST TOWER AURA recorded; the only other aura seen anywhere is the wave-15 boss armour aura. AIR CRITICAL STRIKE III completes that curve at 50% x7 (I x1.5 -&gt; II x4 -&gt; III x7). ⚠️ CAVEAT: air waves carry LIGERA/LIGHT armour and the Light matrix row is NOT captured. This tower is MAGIC, so if magic is weak into Light the 18.39 overstates it on precisely the waves it exists for. Cloud Buster's upgrade; gates Lilliana May.</t>
         </is>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AQ20" s="2" t="n">
         <v>1251.4</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="AR20" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="AS20">
+      <c r="AS20" s="2">
         <f>AQ20*AR20</f>
         <v/>
       </c>
-      <c r="AT20">
+      <c r="AT20" s="3">
         <f>IF(D20=0,"",AY20/D20)</f>
         <v/>
       </c>
-      <c r="AU20">
+      <c r="AU20" s="3">
         <f>(N20/725)^2</f>
         <v/>
       </c>
-      <c r="AV20">
+      <c r="AV20" s="3">
         <f>IF(D20=0,"",AT20*AU20)</f>
         <v/>
       </c>
-      <c r="AY20">
+      <c r="AW20" s="2" t="n"/>
+      <c r="AX20" s="2" t="n"/>
+      <c r="AY20" s="2">
         <f>AS20+N(AW20)+N(AX20)</f>
         <v/>
       </c>
-      <c r="AZ20">
+      <c r="AZ20" s="3">
         <f>IF(D20=0,"",AT20*(N20/725))</f>
         <v/>
       </c>
@@ -13600,7 +13735,7 @@
       <c r="Z21" t="n">
         <v>8</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AA21" s="2" t="n">
         <v>3000</v>
       </c>
       <c r="AB21" t="n">
@@ -13640,33 +13775,35 @@
           <t>Build Lilianna Mai ( F )</t>
         </is>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AQ21" s="2" t="n">
         <v>4910</v>
       </c>
-      <c r="AR21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS21">
+      <c r="AR21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS21" s="2">
         <f>AQ21*AR21</f>
         <v/>
       </c>
-      <c r="AT21">
+      <c r="AT21" s="3">
         <f>IF(D21=0,"",AY21/D21)</f>
         <v/>
       </c>
-      <c r="AU21">
+      <c r="AU21" s="3">
         <f>(N21/725)^2</f>
         <v/>
       </c>
-      <c r="AV21">
+      <c r="AV21" s="3">
         <f>IF(D21=0,"",AT21*AU21)</f>
         <v/>
       </c>
-      <c r="AY21">
+      <c r="AW21" s="2" t="n"/>
+      <c r="AX21" s="2" t="n"/>
+      <c r="AY21" s="2">
         <f>AS21+N(AW21)+N(AX21)</f>
         <v/>
       </c>
-      <c r="AZ21">
+      <c r="AZ21" s="3">
         <f>IF(D21=0,"",AT21*(N21/725))</f>
         <v/>
       </c>
@@ -13760,7 +13897,7 @@
       <c r="Z22" t="n">
         <v>10</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AA22" s="2" t="n">
         <v>3500</v>
       </c>
       <c r="AB22" t="n">
@@ -13814,33 +13951,35 @@
           <t>THE CAPSTONE, AND IT HAS NO WEAKNESS. Two crits covering complementary target classes: ABSOLUTION at 50% x25 vs NON-BOSS (the largest multiplier recorded anywhere - previous max was Vindicator III x10) and BOSS ASSASSIN II at 50% x8 vs heroes. So it shreds hordes AND handles bosses. It also carries DUAL ATTACK TYPES like Sky Sweeper, hedging the armour matrix, but with DIFFERENT RANGES per profile (600 hero / 800 magic) - the only tower recorded where the two profiles differ in range. Plus both of Lilliana May's spells. 198.29 range-adjusted vs non-boss against a previous best of 42.74 anywhere in the capture. FOOD: the upgrade itself adds no food cost, but the BASE tower's slot stays consumed (owner 2026-09-05) - so this still occupies 1 of the 5. An earlier note here said the upgrade frees a slot; that was wrong. That is what ~6389g across all three lines plus a permanent food slot buys.</t>
         </is>
       </c>
-      <c r="AQ22" t="n">
+      <c r="AQ22" s="2" t="n">
         <v>3333.3</v>
       </c>
-      <c r="AR22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS22">
+      <c r="AR22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS22" s="2">
         <f>AQ22*AR22</f>
         <v/>
       </c>
-      <c r="AT22">
+      <c r="AT22" s="3">
         <f>IF(D22=0,"",AY22/D22)</f>
         <v/>
       </c>
-      <c r="AU22">
+      <c r="AU22" s="3">
         <f>(N22/725)^2</f>
         <v/>
       </c>
-      <c r="AV22">
+      <c r="AV22" s="3">
         <f>IF(D22=0,"",AT22*AU22)</f>
         <v/>
       </c>
-      <c r="AY22">
+      <c r="AW22" s="2" t="n"/>
+      <c r="AX22" s="2" t="n"/>
+      <c r="AY22" s="2">
         <f>AS22+N(AW22)+N(AX22)</f>
         <v/>
       </c>
-      <c r="AZ22">
+      <c r="AZ22" s="3">
         <f>IF(D22=0,"",AT22*(N22/725))</f>
         <v/>
       </c>
@@ -13856,6 +13995,7 @@
           <t>Tyr Spirit</t>
         </is>
       </c>
+      <c r="AA23" s="2" t="n"/>
       <c r="AN23" t="inlineStr">
         <is>
           <t>hand capture only — no extracted counterpart</t>
@@ -13871,30 +14011,33 @@
           <t>Unlock confirmed by the owner 2026-09-05. BOUGHT FOR THE STUN, NOT THE DAMAGE. At very rapid fire a 20% proc lands every ~1.75s and the stun lasts 1.5s, so it holds ~86% STUN UPTIME on non-hero ground units - near-permanent lockdown. Damage is a modest 3.63 range-adjusted. BASH is a named tier trait: the treant Battleship Mackinaw carries a higher one (20%, +235, 2.0s, non-boss) - same 20% chance and same shape, and its "non-boss" is the same exclusion as this one's "non-hero".</t>
         </is>
       </c>
-      <c r="AR23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS23">
+      <c r="AQ23" s="2" t="n"/>
+      <c r="AR23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS23" s="2">
         <f>AQ23*AR23</f>
         <v/>
       </c>
-      <c r="AT23">
+      <c r="AT23" s="3">
         <f>IF(D23=0,"",AY23/D23)</f>
         <v/>
       </c>
-      <c r="AU23">
+      <c r="AU23" s="3">
         <f>(N23/725)^2</f>
         <v/>
       </c>
-      <c r="AV23">
+      <c r="AV23" s="3">
         <f>IF(D23=0,"",AT23*AU23)</f>
         <v/>
       </c>
-      <c r="AY23">
+      <c r="AW23" s="2" t="n"/>
+      <c r="AX23" s="2" t="n"/>
+      <c r="AY23" s="2">
         <f>AS23+N(AW23)+N(AX23)</f>
         <v/>
       </c>
-      <c r="AZ23">
+      <c r="AZ23" s="3">
         <f>IF(D23=0,"",AT23*(N23/725))</f>
         <v/>
       </c>
@@ -13910,6 +14053,7 @@
           <t>Royal Base II</t>
         </is>
       </c>
+      <c r="AA24" s="2" t="n"/>
       <c r="AN24" t="inlineStr">
         <is>
           <t>hand capture only — no extracted counterpart</t>
@@ -13920,30 +14064,33 @@
           <t>NOT A TOWER and not a "base tower" either - it is an upgrade purchased at the HERO SELECTION BUILDING (owner 2026-09-05). At 50g it is a pure tech gate for Peepy Bronzebeard, Cloud Buster, Lilliana May and Petrified Shell. It has no stat block to collect. The mechanism is per-hero: the Tempest Hawk has no equivalent.</t>
         </is>
       </c>
-      <c r="AR24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS24">
+      <c r="AQ24" s="2" t="n"/>
+      <c r="AR24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS24" s="2">
         <f>AQ24*AR24</f>
         <v/>
       </c>
-      <c r="AT24">
+      <c r="AT24" s="3">
         <f>IF(D24=0,"",AY24/D24)</f>
         <v/>
       </c>
-      <c r="AU24">
+      <c r="AU24" s="3">
         <f>(N24/725)^2</f>
         <v/>
       </c>
-      <c r="AV24">
+      <c r="AV24" s="3">
         <f>IF(D24=0,"",AT24*AU24)</f>
         <v/>
       </c>
-      <c r="AY24">
+      <c r="AW24" s="2" t="n"/>
+      <c r="AX24" s="2" t="n"/>
+      <c r="AY24" s="2">
         <f>AS24+N(AW24)+N(AX24)</f>
         <v/>
       </c>
-      <c r="AZ24">
+      <c r="AZ24" s="3">
         <f>IF(D24=0,"",AT24*(N24/725))</f>
         <v/>
       </c>
@@ -13959,6 +14106,7 @@
           <t>Peepy Bronzebeard</t>
         </is>
       </c>
+      <c r="AA25" s="2" t="n"/>
       <c r="AN25" t="inlineStr">
         <is>
           <t>hand capture only — no extracted counterpart</t>
@@ -13969,30 +14117,33 @@
           <t>NO CRIT - untyped damage, so its 8.33 applies on EVERY wave rather than on a schedule, unlike most elite towers here. SLOW POISON III is the headline: 260 dps and 65% slow. The 260 dps alone out-damages several whole towers (treant Machination 54 dps, hawk Lasher 74 dps), so at tier III a debuff is worth more than a cheap tower. Completes the Slow Poison curve: 4 -&gt; 36 -&gt; 260 dps, 25% -&gt; 40% -&gt; 65% slow.</t>
         </is>
       </c>
-      <c r="AR25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS25">
+      <c r="AQ25" s="2" t="n"/>
+      <c r="AR25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS25" s="2">
         <f>AQ25*AR25</f>
         <v/>
       </c>
-      <c r="AT25">
+      <c r="AT25" s="3">
         <f>IF(D25=0,"",AY25/D25)</f>
         <v/>
       </c>
-      <c r="AU25">
+      <c r="AU25" s="3">
         <f>(N25/725)^2</f>
         <v/>
       </c>
-      <c r="AV25">
+      <c r="AV25" s="3">
         <f>IF(D25=0,"",AT25*AU25)</f>
         <v/>
       </c>
-      <c r="AY25">
+      <c r="AW25" s="2" t="n"/>
+      <c r="AX25" s="2" t="n"/>
+      <c r="AY25" s="2">
         <f>AS25+N(AW25)+N(AX25)</f>
         <v/>
       </c>
-      <c r="AZ25">
+      <c r="AZ25" s="3">
         <f>IF(D25=0,"",AT25*(N25/725))</f>
         <v/>
       </c>
@@ -14008,6 +14159,7 @@
           <t>Grayson Fort Buster</t>
         </is>
       </c>
+      <c r="AA26" s="2" t="n"/>
       <c r="AN26" t="inlineStr">
         <is>
           <t>hand capture only — no extracted counterpart</t>
@@ -14018,30 +14170,33 @@
           <t>COSTS 1 FOOD - a THIRD resource beyond gold and tiles, capped at 5 and unlocked partway through the run. So gold is not its real cost: at 175g it is the best gold-efficiency in the kit after Odin's Soul, but you can field at most FIVE food towers all run, and it competes against every other food tower rather than against 175g of anything else. SIEGE, so 13.82 becomes 22.11 on the Fortified waves (3, 8, 13, 18). Wave-20 gated.</t>
         </is>
       </c>
-      <c r="AR26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS26">
+      <c r="AQ26" s="2" t="n"/>
+      <c r="AR26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS26" s="2">
         <f>AQ26*AR26</f>
         <v/>
       </c>
-      <c r="AT26">
+      <c r="AT26" s="3">
         <f>IF(D26=0,"",AY26/D26)</f>
         <v/>
       </c>
-      <c r="AU26">
+      <c r="AU26" s="3">
         <f>(N26/725)^2</f>
         <v/>
       </c>
-      <c r="AV26">
+      <c r="AV26" s="3">
         <f>IF(D26=0,"",AT26*AU26)</f>
         <v/>
       </c>
-      <c r="AY26">
+      <c r="AW26" s="2" t="n"/>
+      <c r="AX26" s="2" t="n"/>
+      <c r="AY26" s="2">
         <f>AS26+N(AW26)+N(AX26)</f>
         <v/>
       </c>
-      <c r="AZ26">
+      <c r="AZ26" s="3">
         <f>IF(D26=0,"",AT26*(N26/725))</f>
         <v/>
       </c>
@@ -14057,6 +14212,7 @@
           <t>Lilliana May</t>
         </is>
       </c>
+      <c r="AA27" s="2" t="n"/>
       <c r="AN27" t="inlineStr">
         <is>
           <t>hand capture only — no extracted counterpart</t>
@@ -14067,30 +14223,33 @@
           <t>CORRECTED 2026-09-05: damage is 1000-1455 (a normal 1.46x roll), not 100-1455. An earlier note here called it the widest spread recorded and read it as a deliberately unreliable autoattack - that was built on the typo and is WITHDRAWN. At 5.12 range-adjusted it is still modest for 850g plus a food slot, so it is still bought for its spells, but by the ordinary reading rather than a variance argument. GRAVITY WELL CORRECTED: 10% of LIFE as damage plus a 5% PERMANENT speed reduction - double the damage I first recorded, and a smaller but PERMANENT slow. "Permanent" implies it may STACK across casts, which would make it a different mechanic class from every other slow here. Worth confirming whether it stacks. DIVINE SHIELD makes the TOWER immune for 10s, the answer to the tower-destroying boss the owner flagged in their first message. Priciest Royal Family tower AND food-capped.</t>
         </is>
       </c>
-      <c r="AR27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS27">
+      <c r="AQ27" s="2" t="n"/>
+      <c r="AR27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS27" s="2">
         <f>AQ27*AR27</f>
         <v/>
       </c>
-      <c r="AT27">
+      <c r="AT27" s="3">
         <f>IF(D27=0,"",AY27/D27)</f>
         <v/>
       </c>
-      <c r="AU27">
+      <c r="AU27" s="3">
         <f>(N27/725)^2</f>
         <v/>
       </c>
-      <c r="AV27">
+      <c r="AV27" s="3">
         <f>IF(D27=0,"",AT27*AU27)</f>
         <v/>
       </c>
-      <c r="AY27">
+      <c r="AW27" s="2" t="n"/>
+      <c r="AX27" s="2" t="n"/>
+      <c r="AY27" s="2">
         <f>AS27+N(AW27)+N(AX27)</f>
         <v/>
       </c>
-      <c r="AZ27">
+      <c r="AZ27" s="3">
         <f>IF(D27=0,"",AT27*(N27/725))</f>
         <v/>
       </c>
@@ -14106,6 +14265,7 @@
           <t>Petrified Shell</t>
         </is>
       </c>
+      <c r="AA28" s="2" t="n"/>
       <c r="AN28" t="inlineStr">
         <is>
           <t>hand capture only — no extracted counterpart</t>
@@ -14116,30 +14276,33 @@
           <t>THE K-DIG LINE ENDS IN A TANK. 3.22 range-adjusted is low, but FORTITUDE is durability + splash and eff/g cannot see survivability - the same caveat as the treant Ruby Scorpion, and a tower that dies is worth 0. Note the line's arc: K-Dig (siege utility/heal) -&gt; Xavier (siege damage) -&gt; Bartlebee (stun) -&gt; Delphinus (mana + spells) -&gt; this (tank). FIVE different jobs down one line. TWO NEW TRAITS: FROST I (the treant Sewage Surprise carries an unlabelled "frost", so that is probably the same family) and FORTITUDE. FAST = RAPID confirmed by the owner 2026-09-05, so the five bands stand.</t>
         </is>
       </c>
-      <c r="AR28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS28">
+      <c r="AQ28" s="2" t="n"/>
+      <c r="AR28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS28" s="2">
         <f>AQ28*AR28</f>
         <v/>
       </c>
-      <c r="AT28">
+      <c r="AT28" s="3">
         <f>IF(D28=0,"",AY28/D28)</f>
         <v/>
       </c>
-      <c r="AU28">
+      <c r="AU28" s="3">
         <f>(N28/725)^2</f>
         <v/>
       </c>
-      <c r="AV28">
+      <c r="AV28" s="3">
         <f>IF(D28=0,"",AT28*AU28)</f>
         <v/>
       </c>
-      <c r="AY28">
+      <c r="AW28" s="2" t="n"/>
+      <c r="AX28" s="2" t="n"/>
+      <c r="AY28" s="2">
         <f>AS28+N(AW28)+N(AX28)</f>
         <v/>
       </c>
-      <c r="AZ28">
+      <c r="AZ28" s="3">
         <f>IF(D28=0,"",AT28*(N28/725))</f>
         <v/>
       </c>
@@ -14506,7 +14669,7 @@
       <c r="Z2" t="n">
         <v>0</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AA2" s="2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
@@ -14546,33 +14709,35 @@
           <t>Build Repel ( Q )</t>
         </is>
       </c>
-      <c r="AK2" t="n">
+      <c r="AK2" s="2" t="n">
         <v>63.6</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AL2" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="AM2">
+      <c r="AM2" s="2">
         <f>AK2*AL2</f>
         <v/>
       </c>
-      <c r="AN2">
+      <c r="AN2" s="3">
         <f>IF(D2=0,"",AS2/D2)</f>
         <v/>
       </c>
-      <c r="AO2">
+      <c r="AO2" s="3">
         <f>(N2/725)^2</f>
         <v/>
       </c>
-      <c r="AP2">
+      <c r="AP2" s="3">
         <f>IF(D2=0,"",AN2*AO2)</f>
         <v/>
       </c>
-      <c r="AS2">
+      <c r="AQ2" s="2" t="n"/>
+      <c r="AR2" s="2" t="n"/>
+      <c r="AS2" s="2">
         <f>AM2+N(AQ2)+N(AR2)</f>
         <v/>
       </c>
-      <c r="AT2">
+      <c r="AT2" s="3">
         <f>IF(D2=0,"",AN2*(N2/725))</f>
         <v/>
       </c>
@@ -14638,7 +14803,7 @@
       <c r="Z3" t="n">
         <v>4</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AA3" s="2" t="n">
         <v>1750</v>
       </c>
       <c r="AB3" t="n">
@@ -14678,36 +14843,37 @@
           <t>U pgrade to Corruption</t>
         </is>
       </c>
-      <c r="AK3" t="n">
+      <c r="AK3" s="2" t="n">
         <v>103.3</v>
       </c>
-      <c r="AL3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM3">
+      <c r="AL3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" s="2">
         <f>AK3*AL3</f>
         <v/>
       </c>
-      <c r="AN3">
+      <c r="AN3" s="3">
         <f>IF(D3=0,"",AS3/D3)</f>
         <v/>
       </c>
-      <c r="AO3">
+      <c r="AO3" s="3">
         <f>(N3/725)^2</f>
         <v/>
       </c>
-      <c r="AP3">
+      <c r="AP3" s="3">
         <f>IF(D3=0,"",AN3*AO3)</f>
         <v/>
       </c>
-      <c r="AR3" t="n">
+      <c r="AQ3" s="2" t="n"/>
+      <c r="AR3" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AS3">
+      <c r="AS3" s="2">
         <f>AM3+N(AQ3)+N(AR3)</f>
         <v/>
       </c>
-      <c r="AT3">
+      <c r="AT3" s="3">
         <f>IF(D3=0,"",AN3*(N3/725))</f>
         <v/>
       </c>
@@ -14783,7 +14949,7 @@
       <c r="Z4" t="n">
         <v>3</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AA4" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="AB4" t="n">
@@ -14823,33 +14989,35 @@
           <t>Build Holy Fire Launcher ( W )</t>
         </is>
       </c>
-      <c r="AK4" t="n">
+      <c r="AK4" s="2" t="n">
         <v>572.7</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AL4" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="AM4">
+      <c r="AM4" s="2">
         <f>AK4*AL4</f>
         <v/>
       </c>
-      <c r="AN4">
+      <c r="AN4" s="3">
         <f>IF(D4=0,"",AS4/D4)</f>
         <v/>
       </c>
-      <c r="AO4">
+      <c r="AO4" s="3">
         <f>(N4/725)^2</f>
         <v/>
       </c>
-      <c r="AP4">
+      <c r="AP4" s="3">
         <f>IF(D4=0,"",AN4*AO4)</f>
         <v/>
       </c>
-      <c r="AS4">
+      <c r="AQ4" s="2" t="n"/>
+      <c r="AR4" s="2" t="n"/>
+      <c r="AS4" s="2">
         <f>AM4+N(AQ4)+N(AR4)</f>
         <v/>
       </c>
-      <c r="AT4">
+      <c r="AT4" s="3">
         <f>IF(D4=0,"",AN4*(N4/725))</f>
         <v/>
       </c>
@@ -14902,36 +15070,38 @@
       <c r="Z5" t="n">
         <v>2</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AA5" s="2" t="n">
         <v>1250</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AK5" s="2" t="n">
         <v>217.5</v>
       </c>
-      <c r="AL5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM5">
+      <c r="AL5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" s="2">
         <f>AK5*AL5</f>
         <v/>
       </c>
-      <c r="AN5">
+      <c r="AN5" s="3">
         <f>IF(D5=0,"",AS5/D5)</f>
         <v/>
       </c>
-      <c r="AO5">
+      <c r="AO5" s="3">
         <f>(N5/725)^2</f>
         <v/>
       </c>
-      <c r="AP5">
+      <c r="AP5" s="3">
         <f>IF(D5=0,"",AN5*AO5)</f>
         <v/>
       </c>
-      <c r="AS5">
+      <c r="AQ5" s="2" t="n"/>
+      <c r="AR5" s="2" t="n"/>
+      <c r="AS5" s="2">
         <f>AM5+N(AQ5)+N(AR5)</f>
         <v/>
       </c>
-      <c r="AT5">
+      <c r="AT5" s="3">
         <f>IF(D5=0,"",AN5*(N5/725))</f>
         <v/>
       </c>
@@ -15007,7 +15177,7 @@
       <c r="Z6" t="n">
         <v>1</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AA6" s="2" t="n">
         <v>1750</v>
       </c>
       <c r="AB6" t="n">
@@ -15047,33 +15217,35 @@
           <t>Build Sapphire Ward ( E )</t>
         </is>
       </c>
-      <c r="AK6" t="n">
+      <c r="AK6" s="2" t="n">
         <v>206.6</v>
       </c>
-      <c r="AL6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM6">
+      <c r="AL6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" s="2">
         <f>AK6*AL6</f>
         <v/>
       </c>
-      <c r="AN6">
+      <c r="AN6" s="3">
         <f>IF(D6=0,"",AS6/D6)</f>
         <v/>
       </c>
-      <c r="AO6">
+      <c r="AO6" s="3">
         <f>(N6/725)^2</f>
         <v/>
       </c>
-      <c r="AP6">
+      <c r="AP6" s="3">
         <f>IF(D6=0,"",AN6*AO6)</f>
         <v/>
       </c>
-      <c r="AS6">
+      <c r="AQ6" s="2" t="n"/>
+      <c r="AR6" s="2" t="n"/>
+      <c r="AS6" s="2">
         <f>AM6+N(AQ6)+N(AR6)</f>
         <v/>
       </c>
-      <c r="AT6">
+      <c r="AT6" s="3">
         <f>IF(D6=0,"",AN6*(N6/725))</f>
         <v/>
       </c>
@@ -15149,7 +15321,7 @@
       <c r="Z7" t="n">
         <v>2</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AA7" s="2" t="n">
         <v>2250</v>
       </c>
       <c r="AB7" t="n">
@@ -15189,33 +15361,35 @@
           <t>U pgrade to Purity Ward</t>
         </is>
       </c>
-      <c r="AK7" t="n">
+      <c r="AK7" s="2" t="n">
         <v>535.5</v>
       </c>
-      <c r="AL7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM7">
+      <c r="AL7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM7" s="2">
         <f>AK7*AL7</f>
         <v/>
       </c>
-      <c r="AN7">
+      <c r="AN7" s="3">
         <f>IF(D7=0,"",AS7/D7)</f>
         <v/>
       </c>
-      <c r="AO7">
+      <c r="AO7" s="3">
         <f>(N7/725)^2</f>
         <v/>
       </c>
-      <c r="AP7">
+      <c r="AP7" s="3">
         <f>IF(D7=0,"",AN7*AO7)</f>
         <v/>
       </c>
-      <c r="AS7">
+      <c r="AQ7" s="2" t="n"/>
+      <c r="AR7" s="2" t="n"/>
+      <c r="AS7" s="2">
         <f>AM7+N(AQ7)+N(AR7)</f>
         <v/>
       </c>
-      <c r="AT7">
+      <c r="AT7" s="3">
         <f>IF(D7=0,"",AN7*(N7/725))</f>
         <v/>
       </c>
@@ -15281,7 +15455,7 @@
       <c r="Z8" t="n">
         <v>1</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AA8" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="AB8" t="n">
@@ -15321,33 +15495,35 @@
           <t>Build Ochre Ward ( R )</t>
         </is>
       </c>
-      <c r="AK8" t="n">
+      <c r="AK8" s="2" t="n">
         <v>152.5</v>
       </c>
-      <c r="AL8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM8">
+      <c r="AL8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM8" s="2">
         <f>AK8*AL8</f>
         <v/>
       </c>
-      <c r="AN8">
+      <c r="AN8" s="3">
         <f>IF(D8=0,"",AS8/D8)</f>
         <v/>
       </c>
-      <c r="AO8">
+      <c r="AO8" s="3">
         <f>(N8/725)^2</f>
         <v/>
       </c>
-      <c r="AP8">
+      <c r="AP8" s="3">
         <f>IF(D8=0,"",AN8*AO8)</f>
         <v/>
       </c>
-      <c r="AS8">
+      <c r="AQ8" s="2" t="n"/>
+      <c r="AR8" s="2" t="n"/>
+      <c r="AS8" s="2">
         <f>AM8+N(AQ8)+N(AR8)</f>
         <v/>
       </c>
-      <c r="AT8">
+      <c r="AT8" s="3">
         <f>IF(D8=0,"",AN8*(N8/725))</f>
         <v/>
       </c>
@@ -15418,7 +15594,7 @@
       <c r="Z9" t="n">
         <v>2</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AA9" s="2" t="n">
         <v>1750</v>
       </c>
       <c r="AB9" t="n">
@@ -15458,33 +15634,35 @@
           <t>U pgrade to Scarlet Ward</t>
         </is>
       </c>
-      <c r="AK9" t="n">
+      <c r="AK9" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="AL9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM9">
+      <c r="AL9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM9" s="2">
         <f>AK9*AL9</f>
         <v/>
       </c>
-      <c r="AN9">
+      <c r="AN9" s="3">
         <f>IF(D9=0,"",AS9/D9)</f>
         <v/>
       </c>
-      <c r="AO9">
+      <c r="AO9" s="3">
         <f>(N9/725)^2</f>
         <v/>
       </c>
-      <c r="AP9">
+      <c r="AP9" s="3">
         <f>IF(D9=0,"",AN9*AO9)</f>
         <v/>
       </c>
-      <c r="AS9">
+      <c r="AQ9" s="2" t="n"/>
+      <c r="AR9" s="2" t="n"/>
+      <c r="AS9" s="2">
         <f>AM9+N(AQ9)+N(AR9)</f>
         <v/>
       </c>
-      <c r="AT9">
+      <c r="AT9" s="3">
         <f>IF(D9=0,"",AN9*(N9/725))</f>
         <v/>
       </c>
@@ -15560,7 +15738,7 @@
       <c r="Z10" t="n">
         <v>3</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AA10" s="2" t="n">
         <v>1250</v>
       </c>
       <c r="AB10" t="n">
@@ -15600,33 +15778,35 @@
           <t>Build Bombardment ( A )</t>
         </is>
       </c>
-      <c r="AK10" t="n">
+      <c r="AK10" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="AL10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM10">
+      <c r="AL10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM10" s="2">
         <f>AK10*AL10</f>
         <v/>
       </c>
-      <c r="AN10">
+      <c r="AN10" s="3">
         <f>IF(D10=0,"",AS10/D10)</f>
         <v/>
       </c>
-      <c r="AO10">
+      <c r="AO10" s="3">
         <f>(N10/725)^2</f>
         <v/>
       </c>
-      <c r="AP10">
+      <c r="AP10" s="3">
         <f>IF(D10=0,"",AN10*AO10)</f>
         <v/>
       </c>
-      <c r="AS10">
+      <c r="AQ10" s="2" t="n"/>
+      <c r="AR10" s="2" t="n"/>
+      <c r="AS10" s="2">
         <f>AM10+N(AQ10)+N(AR10)</f>
         <v/>
       </c>
-      <c r="AT10">
+      <c r="AT10" s="3">
         <f>IF(D10=0,"",AN10*(N10/725))</f>
         <v/>
       </c>
@@ -15702,7 +15882,7 @@
       <c r="Z11" t="n">
         <v>4</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AA11" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="AB11" t="n">
@@ -15742,33 +15922,35 @@
           <t>U pgrade to Interceptor Factory</t>
         </is>
       </c>
-      <c r="AK11" t="n">
+      <c r="AK11" s="2" t="n">
         <v>800</v>
       </c>
-      <c r="AL11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM11">
+      <c r="AL11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM11" s="2">
         <f>AK11*AL11</f>
         <v/>
       </c>
-      <c r="AN11">
+      <c r="AN11" s="3">
         <f>IF(D11=0,"",AS11/D11)</f>
         <v/>
       </c>
-      <c r="AO11">
+      <c r="AO11" s="3">
         <f>(N11/725)^2</f>
         <v/>
       </c>
-      <c r="AP11">
+      <c r="AP11" s="3">
         <f>IF(D11=0,"",AN11*AO11)</f>
         <v/>
       </c>
-      <c r="AS11">
+      <c r="AQ11" s="2" t="n"/>
+      <c r="AR11" s="2" t="n"/>
+      <c r="AS11" s="2">
         <f>AM11+N(AQ11)+N(AR11)</f>
         <v/>
       </c>
-      <c r="AT11">
+      <c r="AT11" s="3">
         <f>IF(D11=0,"",AN11*(N11/725))</f>
         <v/>
       </c>
@@ -15821,36 +16003,38 @@
       <c r="Z12" t="n">
         <v>3</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AA12" s="2" t="n">
         <v>2250</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AK12" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="AL12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM12">
+      <c r="AL12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM12" s="2">
         <f>AK12*AL12</f>
         <v/>
       </c>
-      <c r="AN12">
+      <c r="AN12" s="3">
         <f>IF(D12=0,"",AS12/D12)</f>
         <v/>
       </c>
-      <c r="AO12">
+      <c r="AO12" s="3">
         <f>(N12/725)^2</f>
         <v/>
       </c>
-      <c r="AP12">
+      <c r="AP12" s="3">
         <f>IF(D12=0,"",AN12*AO12)</f>
         <v/>
       </c>
-      <c r="AS12">
+      <c r="AQ12" s="2" t="n"/>
+      <c r="AR12" s="2" t="n"/>
+      <c r="AS12" s="2">
         <f>AM12+N(AQ12)+N(AR12)</f>
         <v/>
       </c>
-      <c r="AT12">
+      <c r="AT12" s="3">
         <f>IF(D12=0,"",AN12*(N12/725))</f>
         <v/>
       </c>
@@ -15921,7 +16105,7 @@
       <c r="Z13" t="n">
         <v>4</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AA13" s="2" t="n">
         <v>2250</v>
       </c>
       <c r="AB13" t="n">
@@ -15961,33 +16145,35 @@
           <t>U pgrade to Star Buster</t>
         </is>
       </c>
-      <c r="AK13" t="n">
+      <c r="AK13" s="2" t="n">
         <v>469.2</v>
       </c>
-      <c r="AL13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM13">
+      <c r="AL13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM13" s="2">
         <f>AK13*AL13</f>
         <v/>
       </c>
-      <c r="AN13">
+      <c r="AN13" s="3">
         <f>IF(D13=0,"",AS13/D13)</f>
         <v/>
       </c>
-      <c r="AO13">
+      <c r="AO13" s="3">
         <f>(N13/725)^2</f>
         <v/>
       </c>
-      <c r="AP13">
+      <c r="AP13" s="3">
         <f>IF(D13=0,"",AN13*AO13)</f>
         <v/>
       </c>
-      <c r="AS13">
+      <c r="AQ13" s="2" t="n"/>
+      <c r="AR13" s="2" t="n"/>
+      <c r="AS13" s="2">
         <f>AM13+N(AQ13)+N(AR13)</f>
         <v/>
       </c>
-      <c r="AT13">
+      <c r="AT13" s="3">
         <f>IF(D13=0,"",AN13*(N13/725))</f>
         <v/>
       </c>
@@ -16060,7 +16246,7 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
-      <c r="AA14" t="n">
+      <c r="AA14" s="2" t="n">
         <v>2000</v>
       </c>
       <c r="AB14" t="n">
@@ -16100,33 +16286,35 @@
           <t>Build Protection Ward  ( D )</t>
         </is>
       </c>
-      <c r="AK14" t="n">
+      <c r="AK14" s="2" t="n">
         <v>317.5</v>
       </c>
-      <c r="AL14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM14">
+      <c r="AL14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM14" s="2">
         <f>AK14*AL14</f>
         <v/>
       </c>
-      <c r="AN14">
+      <c r="AN14" s="3">
         <f>IF(D14=0,"",AS14/D14)</f>
         <v/>
       </c>
-      <c r="AO14">
+      <c r="AO14" s="3">
         <f>(N14/725)^2</f>
         <v/>
       </c>
-      <c r="AP14">
+      <c r="AP14" s="3">
         <f>IF(D14=0,"",AN14*AO14)</f>
         <v/>
       </c>
-      <c r="AS14">
+      <c r="AQ14" s="2" t="n"/>
+      <c r="AR14" s="2" t="n"/>
+      <c r="AS14" s="2">
         <f>AM14+N(AQ14)+N(AR14)</f>
         <v/>
       </c>
-      <c r="AT14">
+      <c r="AT14" s="3">
         <f>IF(D14=0,"",AN14*(N14/725))</f>
         <v/>
       </c>
@@ -16199,7 +16387,7 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
-      <c r="AA15" t="n">
+      <c r="AA15" s="2" t="n">
         <v>2500</v>
       </c>
       <c r="AB15" t="n">
@@ -16239,33 +16427,35 @@
           <t>U pgrade to Roseate Ward</t>
         </is>
       </c>
-      <c r="AK15" t="n">
+      <c r="AK15" s="2" t="n">
         <v>811.2</v>
       </c>
-      <c r="AL15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM15">
+      <c r="AL15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM15" s="2">
         <f>AK15*AL15</f>
         <v/>
       </c>
-      <c r="AN15">
+      <c r="AN15" s="3">
         <f>IF(D15=0,"",AS15/D15)</f>
         <v/>
       </c>
-      <c r="AO15">
+      <c r="AO15" s="3">
         <f>(N15/725)^2</f>
         <v/>
       </c>
-      <c r="AP15">
+      <c r="AP15" s="3">
         <f>IF(D15=0,"",AN15*AO15)</f>
         <v/>
       </c>
-      <c r="AS15">
+      <c r="AQ15" s="2" t="n"/>
+      <c r="AR15" s="2" t="n"/>
+      <c r="AS15" s="2">
         <f>AM15+N(AQ15)+N(AR15)</f>
         <v/>
       </c>
-      <c r="AT15">
+      <c r="AT15" s="3">
         <f>IF(D15=0,"",AN15*(N15/725))</f>
         <v/>
       </c>
@@ -16341,7 +16531,7 @@
       <c r="Z16" t="n">
         <v>3</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AA16" s="2" t="n">
         <v>1750</v>
       </c>
       <c r="AB16" t="n">
@@ -16381,33 +16571,35 @@
           <t>Build Lilac Ward ( F )</t>
         </is>
       </c>
-      <c r="AK16" t="n">
+      <c r="AK16" s="2" t="n">
         <v>470</v>
       </c>
-      <c r="AL16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM16">
+      <c r="AL16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM16" s="2">
         <f>AK16*AL16</f>
         <v/>
       </c>
-      <c r="AN16">
+      <c r="AN16" s="3">
         <f>IF(D16=0,"",AS16/D16)</f>
         <v/>
       </c>
-      <c r="AO16">
+      <c r="AO16" s="3">
         <f>(N16/725)^2</f>
         <v/>
       </c>
-      <c r="AP16">
+      <c r="AP16" s="3">
         <f>IF(D16=0,"",AN16*AO16)</f>
         <v/>
       </c>
-      <c r="AS16">
+      <c r="AQ16" s="2" t="n"/>
+      <c r="AR16" s="2" t="n"/>
+      <c r="AS16" s="2">
         <f>AM16+N(AQ16)+N(AR16)</f>
         <v/>
       </c>
-      <c r="AT16">
+      <c r="AT16" s="3">
         <f>IF(D16=0,"",AN16*(N16/725))</f>
         <v/>
       </c>
@@ -16483,7 +16675,7 @@
       <c r="Z17" t="n">
         <v>4</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AA17" s="2" t="n">
         <v>2000</v>
       </c>
       <c r="AB17" t="n">
@@ -16523,33 +16715,35 @@
           <t>U pgrade to Malachite Ward</t>
         </is>
       </c>
-      <c r="AK17" t="n">
+      <c r="AK17" s="2" t="n">
         <v>429</v>
       </c>
-      <c r="AL17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM17">
+      <c r="AL17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM17" s="2">
         <f>AK17*AL17</f>
         <v/>
       </c>
-      <c r="AN17">
+      <c r="AN17" s="3">
         <f>IF(D17=0,"",AS17/D17)</f>
         <v/>
       </c>
-      <c r="AO17">
+      <c r="AO17" s="3">
         <f>(N17/725)^2</f>
         <v/>
       </c>
-      <c r="AP17">
+      <c r="AP17" s="3">
         <f>IF(D17=0,"",AN17*AO17)</f>
         <v/>
       </c>
-      <c r="AS17">
+      <c r="AQ17" s="2" t="n"/>
+      <c r="AR17" s="2" t="n"/>
+      <c r="AS17" s="2">
         <f>AM17+N(AQ17)+N(AR17)</f>
         <v/>
       </c>
-      <c r="AT17">
+      <c r="AT17" s="3">
         <f>IF(D17=0,"",AN17*(N17/725))</f>
         <v/>
       </c>
@@ -16620,7 +16814,7 @@
       <c r="Z18" t="n">
         <v>8</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AA18" s="2" t="n">
         <v>3500</v>
       </c>
       <c r="AB18" t="n">
@@ -16660,33 +16854,35 @@
           <t>Build Porcus Maximus ( Z )</t>
         </is>
       </c>
-      <c r="AK18" t="n">
+      <c r="AK18" s="2" t="n">
         <v>963.5</v>
       </c>
-      <c r="AL18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM18">
+      <c r="AL18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM18" s="2">
         <f>AK18*AL18</f>
         <v/>
       </c>
-      <c r="AN18">
+      <c r="AN18" s="3">
         <f>IF(D18=0,"",AS18/D18)</f>
         <v/>
       </c>
-      <c r="AO18">
+      <c r="AO18" s="3">
         <f>(N18/725)^2</f>
         <v/>
       </c>
-      <c r="AP18">
+      <c r="AP18" s="3">
         <f>IF(D18=0,"",AN18*AO18)</f>
         <v/>
       </c>
-      <c r="AS18">
+      <c r="AQ18" s="2" t="n"/>
+      <c r="AR18" s="2" t="n"/>
+      <c r="AS18" s="2">
         <f>AM18+N(AQ18)+N(AR18)</f>
         <v/>
       </c>
-      <c r="AT18">
+      <c r="AT18" s="3">
         <f>IF(D18=0,"",AN18*(N18/725))</f>
         <v/>
       </c>
@@ -16754,7 +16950,7 @@
           <t>enemies,ground,nonancient</t>
         </is>
       </c>
-      <c r="AA19" t="n">
+      <c r="AA19" s="2" t="n">
         <v>2750</v>
       </c>
       <c r="AB19" t="n">
@@ -16794,33 +16990,35 @@
           <t>Build Earth's Blood ( X )</t>
         </is>
       </c>
-      <c r="AK19" t="n">
+      <c r="AK19" s="2" t="n">
         <v>1075</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AL19" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="AM19">
+      <c r="AM19" s="2">
         <f>AK19*AL19</f>
         <v/>
       </c>
-      <c r="AN19">
+      <c r="AN19" s="3">
         <f>IF(D19=0,"",AS19/D19)</f>
         <v/>
       </c>
-      <c r="AO19">
+      <c r="AO19" s="3">
         <f>(N19/725)^2</f>
         <v/>
       </c>
-      <c r="AP19">
+      <c r="AP19" s="3">
         <f>IF(D19=0,"",AN19*AO19)</f>
         <v/>
       </c>
-      <c r="AS19">
+      <c r="AQ19" s="2" t="n"/>
+      <c r="AR19" s="2" t="n"/>
+      <c r="AS19" s="2">
         <f>AM19+N(AQ19)+N(AR19)</f>
         <v/>
       </c>
-      <c r="AT19">
+      <c r="AT19" s="3">
         <f>IF(D19=0,"",AN19*(N19/725))</f>
         <v/>
       </c>
@@ -16891,7 +17089,7 @@
       <c r="Z20" t="n">
         <v>6</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AA20" s="2" t="n">
         <v>3250</v>
       </c>
       <c r="AB20" t="n">
@@ -16931,36 +17129,37 @@
           <t>Build Icy Skewer ( C )</t>
         </is>
       </c>
-      <c r="AK20" t="n">
+      <c r="AK20" s="2" t="n">
         <v>4444.4</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AL20" s="3" t="n">
         <v>1.52</v>
       </c>
-      <c r="AM20">
+      <c r="AM20" s="2">
         <f>AK20*AL20</f>
         <v/>
       </c>
-      <c r="AN20">
+      <c r="AN20" s="3">
         <f>IF(D20=0,"",AS20/D20)</f>
         <v/>
       </c>
-      <c r="AO20">
+      <c r="AO20" s="3">
         <f>(N20/725)^2</f>
         <v/>
       </c>
-      <c r="AP20">
+      <c r="AP20" s="3">
         <f>IF(D20=0,"",AN20*AO20)</f>
         <v/>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AQ20" s="2" t="n">
         <v>550</v>
       </c>
-      <c r="AS20">
+      <c r="AR20" s="2" t="n"/>
+      <c r="AS20" s="2">
         <f>AM20+N(AQ20)+N(AR20)</f>
         <v/>
       </c>
-      <c r="AT20">
+      <c r="AT20" s="3">
         <f>IF(D20=0,"",AN20*(N20/725))</f>
         <v/>
       </c>
@@ -17031,7 +17230,7 @@
       <c r="Z21" t="n">
         <v>7</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AA21" s="2" t="n">
         <v>3500</v>
       </c>
       <c r="AB21" t="n">
@@ -17071,33 +17270,35 @@
           <t>U pgrade to Glacial Spike</t>
         </is>
       </c>
-      <c r="AK21" t="n">
+      <c r="AK21" s="2" t="n">
         <v>13333.3</v>
       </c>
-      <c r="AL21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM21">
+      <c r="AL21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM21" s="2">
         <f>AK21*AL21</f>
         <v/>
       </c>
-      <c r="AN21">
+      <c r="AN21" s="3">
         <f>IF(D21=0,"",AS21/D21)</f>
         <v/>
       </c>
-      <c r="AO21">
+      <c r="AO21" s="3">
         <f>(N21/725)^2</f>
         <v/>
       </c>
-      <c r="AP21">
+      <c r="AP21" s="3">
         <f>IF(D21=0,"",AN21*AO21)</f>
         <v/>
       </c>
-      <c r="AS21">
+      <c r="AQ21" s="2" t="n"/>
+      <c r="AR21" s="2" t="n"/>
+      <c r="AS21" s="2">
         <f>AM21+N(AQ21)+N(AR21)</f>
         <v/>
       </c>
-      <c r="AT21">
+      <c r="AT21" s="3">
         <f>IF(D21=0,"",AN21*(N21/725))</f>
         <v/>
       </c>
@@ -17498,7 +17699,7 @@
       <c r="Z2" t="n">
         <v>8</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AA2" s="2" t="n">
         <v>1750</v>
       </c>
       <c r="AB2" t="n">
@@ -17548,33 +17749,35 @@
           <t>SIEGE attack type (owner 2026-09-06): 160% vs Fortified (waves 3/8/13/18), 85% vs Hero (boss waves), 100% vs Heavy. Starter. Its UPGRADE is what unlocks T3 and T4.</t>
         </is>
       </c>
-      <c r="AO2" t="n">
+      <c r="AO2" s="2" t="n">
         <v>25.3</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AP2" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="AQ2">
+      <c r="AQ2" s="2">
         <f>AO2*AP2</f>
         <v/>
       </c>
-      <c r="AR2">
+      <c r="AR2" s="3">
         <f>IF(D2=0,"",AW2/D2)</f>
         <v/>
       </c>
-      <c r="AS2">
+      <c r="AS2" s="3">
         <f>(N2/725)^2</f>
         <v/>
       </c>
-      <c r="AT2">
+      <c r="AT2" s="3">
         <f>IF(D2=0,"",AR2*AS2)</f>
         <v/>
       </c>
-      <c r="AW2">
+      <c r="AU2" s="2" t="n"/>
+      <c r="AV2" s="2" t="n"/>
+      <c r="AW2" s="2">
         <f>AQ2+N(AU2)+N(AV2)</f>
         <v/>
       </c>
-      <c r="AX2">
+      <c r="AX2" s="3">
         <f>IF(D2=0,"",AR2*(N2/725))</f>
         <v/>
       </c>
@@ -17650,7 +17853,7 @@
       <c r="Z3" t="n">
         <v>8</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AA3" s="2" t="n">
         <v>2000</v>
       </c>
       <c r="AB3" t="n">
@@ -17700,33 +17903,35 @@
           <t>SIEGE attack type (owner 2026-09-06): 160% vs Fortified (waves 3/8/13/18), 85% vs Hero (boss waves), 100% vs Heavy. NO CRIT (owner-confirmed 2026-09-06) - only ground splash and Fortitude. Its 4.00 was previously flagged as a floor pending unknown crit values; there are none, so the figure stands as final. Unlocks BOTH Kill Crank and Spike Shooter.</t>
         </is>
       </c>
-      <c r="AO3" t="n">
+      <c r="AO3" s="2" t="n">
         <v>105.5</v>
       </c>
-      <c r="AP3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ3">
+      <c r="AP3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" s="2">
         <f>AO3*AP3</f>
         <v/>
       </c>
-      <c r="AR3">
+      <c r="AR3" s="3">
         <f>IF(D3=0,"",AW3/D3)</f>
         <v/>
       </c>
-      <c r="AS3">
+      <c r="AS3" s="3">
         <f>(N3/725)^2</f>
         <v/>
       </c>
-      <c r="AT3">
+      <c r="AT3" s="3">
         <f>IF(D3=0,"",AR3*AS3)</f>
         <v/>
       </c>
-      <c r="AW3">
+      <c r="AU3" s="2" t="n"/>
+      <c r="AV3" s="2" t="n"/>
+      <c r="AW3" s="2">
         <f>AQ3+N(AU3)+N(AV3)</f>
         <v/>
       </c>
-      <c r="AX3">
+      <c r="AX3" s="3">
         <f>IF(D3=0,"",AR3*(N3/725))</f>
         <v/>
       </c>
@@ -17799,7 +18004,7 @@
           <t>enemies,ground,nonancient</t>
         </is>
       </c>
-      <c r="AA4" t="n">
+      <c r="AA4" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="AB4" t="n">
@@ -17849,33 +18054,35 @@
           <t xml:space="preserve">CHAOS attack type (owner 2026-09-06) - the kit's only one. In stock WC3 chaos deals 100% to every armour type, i.e. it ignores the matrix; UNVERIFIED for this map. If true it is the treant's only matrix-proof tower. RESOLVED 2026-09-05: the trait is named "Boss Assassin" but TARGETS HEROES - the owner read "boss assassin II (50% x8 against heroes)" on a Royal Family tower. So the earlier boss-vs-hero ambiguity was the GAME conflating them, not a transcription slip. Both readings were right. Anti-boss specialist. Low RAW dmg/gold (1.11) - the crit is what pays for it. </t>
         </is>
       </c>
-      <c r="AO4" t="n">
+      <c r="AO4" s="2" t="n">
         <v>246.7</v>
       </c>
-      <c r="AP4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ4">
+      <c r="AP4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" s="2">
         <f>AO4*AP4</f>
         <v/>
       </c>
-      <c r="AR4">
+      <c r="AR4" s="3">
         <f>IF(D4=0,"",AW4/D4)</f>
         <v/>
       </c>
-      <c r="AS4">
+      <c r="AS4" s="3">
         <f>(N4/725)^2</f>
         <v/>
       </c>
-      <c r="AT4">
+      <c r="AT4" s="3">
         <f>IF(D4=0,"",AR4*AS4)</f>
         <v/>
       </c>
-      <c r="AW4">
+      <c r="AU4" s="2" t="n"/>
+      <c r="AV4" s="2" t="n"/>
+      <c r="AW4" s="2">
         <f>AQ4+N(AU4)+N(AV4)</f>
         <v/>
       </c>
-      <c r="AX4">
+      <c r="AX4" s="3">
         <f>IF(D4=0,"",AR4*(N4/725))</f>
         <v/>
       </c>
@@ -17948,7 +18155,7 @@
           <t>enemies,ground,nonancient</t>
         </is>
       </c>
-      <c r="AA5" t="n">
+      <c r="AA5" s="2" t="n">
         <v>1750</v>
       </c>
       <c r="AB5" t="n">
@@ -17988,33 +18195,35 @@
           <t>U pgrade to Gigas Spike</t>
         </is>
       </c>
-      <c r="AO5" t="n">
+      <c r="AO5" s="2" t="n">
         <v>477.8</v>
       </c>
-      <c r="AP5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ5">
+      <c r="AP5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" s="2">
         <f>AO5*AP5</f>
         <v/>
       </c>
-      <c r="AR5">
+      <c r="AR5" s="3">
         <f>IF(D5=0,"",AW5/D5)</f>
         <v/>
       </c>
-      <c r="AS5">
+      <c r="AS5" s="3">
         <f>(N5/725)^2</f>
         <v/>
       </c>
-      <c r="AT5">
+      <c r="AT5" s="3">
         <f>IF(D5=0,"",AR5*AS5)</f>
         <v/>
       </c>
-      <c r="AW5">
+      <c r="AU5" s="2" t="n"/>
+      <c r="AV5" s="2" t="n"/>
+      <c r="AW5" s="2">
         <f>AQ5+N(AU5)+N(AV5)</f>
         <v/>
       </c>
-      <c r="AX5">
+      <c r="AX5" s="3">
         <f>IF(D5=0,"",AR5*(N5/725))</f>
         <v/>
       </c>
@@ -18082,7 +18291,7 @@
       <c r="P6" t="n">
         <v>575.8</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AA6" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="AB6" t="n">
@@ -18132,36 +18341,37 @@
           <t>RESOLVED 2026-09-06: its crit is vs GROUND, not vs all, and it carries Slow Poison I. 35% x2 vs ground is GROUND CRITICAL STRIKE I, the same named tier as Little Jack, Phlogiston, Stone Experiment, Stealth Maiden and Loki. The 4.14-5.59 span this row carried collapses to 5.59 vs ground (4.14 vs air, 8.95 on Fortified where siege is 160%). The long-running vs-ALL crit dispute is settled for THIS tower.</t>
         </is>
       </c>
-      <c r="AO6" t="n">
+      <c r="AO6" s="2" t="n">
         <v>575.8</v>
       </c>
-      <c r="AP6" t="n">
+      <c r="AP6" s="3" t="n">
         <v>1.35</v>
       </c>
-      <c r="AQ6">
+      <c r="AQ6" s="2">
         <f>AO6*AP6</f>
         <v/>
       </c>
-      <c r="AR6">
+      <c r="AR6" s="3">
         <f>IF(D6=0,"",AW6/D6)</f>
         <v/>
       </c>
-      <c r="AS6">
+      <c r="AS6" s="3">
         <f>(N6/725)^2</f>
         <v/>
       </c>
-      <c r="AT6">
+      <c r="AT6" s="3">
         <f>IF(D6=0,"",AR6*AS6)</f>
         <v/>
       </c>
-      <c r="AV6" t="n">
+      <c r="AU6" s="2" t="n"/>
+      <c r="AV6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AW6">
+      <c r="AW6" s="2">
         <f>AQ6+N(AU6)+N(AV6)</f>
         <v/>
       </c>
-      <c r="AX6">
+      <c r="AX6" s="3">
         <f>IF(D6=0,"",AR6*(N6/725))</f>
         <v/>
       </c>
@@ -18229,7 +18439,7 @@
       <c r="P7" t="n">
         <v>812.5</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AA7" s="2" t="n">
         <v>1750</v>
       </c>
       <c r="AB7" t="n">
@@ -18279,36 +18489,37 @@
           <t>DISPUTE RESOLVED 2026-09-06: the vs-ALL crit is THIS tower's, and it is Versatile Critical Strike I - the same named tier as the Royal Family's Captain Bartlebee and Delphinus. The upgrade from Kill Crank is a crit SWAP: Ground Critical Strike I (35% x2 vs ground) becomes Versatile I (35% x2.5 vs ALL), so the expected multiplier goes 1.35 -&gt; 1.525 vs ground and 1.00 -&gt; 1.525 vs AIR. Slow Poison I carries over. THE TREANT'S ONLY UNTYPED CRIT: the kit is 9/15 siege with no air bonus and every other crit is target-restricted, so this is the one tower whose crit fires on every wave. That reframes the Kill Crank line as not just the Fortified line but the only one ending in wave-agnostic damage. 5.72 range-adjusted, and because Versatile is untyped that figure applies on EVERY wave rather than on a schedule - which is why it ranks higher in practice than its nominal position suggests. Against its base Kill Crank it carries LOWER damage (325 vs 345) but nearly DOUBLE the range (600 vs 350): the range is where the upgrade lives. ATTACK TYPE still unread; if siege like its base, 9.15 on Fortified and 4.86 on boss waves.</t>
         </is>
       </c>
-      <c r="AO7" t="n">
+      <c r="AO7" s="2" t="n">
         <v>812.5</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AP7" s="3" t="n">
         <v>1.52</v>
       </c>
-      <c r="AQ7">
+      <c r="AQ7" s="2">
         <f>AO7*AP7</f>
         <v/>
       </c>
-      <c r="AR7">
+      <c r="AR7" s="3">
         <f>IF(D7=0,"",AW7/D7)</f>
         <v/>
       </c>
-      <c r="AS7">
+      <c r="AS7" s="3">
         <f>(N7/725)^2</f>
         <v/>
       </c>
-      <c r="AT7">
+      <c r="AT7" s="3">
         <f>IF(D7=0,"",AR7*AS7)</f>
         <v/>
       </c>
-      <c r="AV7" t="n">
+      <c r="AU7" s="2" t="n"/>
+      <c r="AV7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AW7">
+      <c r="AW7" s="2">
         <f>AQ7+N(AU7)+N(AV7)</f>
         <v/>
       </c>
-      <c r="AX7">
+      <c r="AX7" s="3">
         <f>IF(D7=0,"",AR7*(N7/725))</f>
         <v/>
       </c>
@@ -18371,7 +18582,7 @@
           <t>enemies,ground,nonancient</t>
         </is>
       </c>
-      <c r="AA8" t="n">
+      <c r="AA8" s="2" t="n">
         <v>2250</v>
       </c>
       <c r="AB8" t="n">
@@ -18421,33 +18632,35 @@
           <t>NORMAL attack type (owner 2026-09-06): 125% vs Medium, 100% Heavy, 75% Fortified, 95% Hero. TERMINAL - no upgrade; the end of the T3+T4 convergent line, reached at 1035g cumulative. Ranks POORLY on single-target gold efficiency (5.66 range-adjusted vs Little Jack's 8.74 at 195g): 85% dearer for 20% more damage. Its value is GROUND SPLASH, which these columns do not model - against 60-unit waves that is plausibly worth several times its single-target rating. Do not read its low rank as weak.</t>
         </is>
       </c>
-      <c r="AO8" t="n">
+      <c r="AO8" s="2" t="n">
         <v>1115.6</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AP8" s="3" t="n">
         <v>1.35</v>
       </c>
-      <c r="AQ8">
+      <c r="AQ8" s="2">
         <f>AO8*AP8</f>
         <v/>
       </c>
-      <c r="AR8">
+      <c r="AR8" s="3">
         <f>IF(D8=0,"",AW8/D8)</f>
         <v/>
       </c>
-      <c r="AS8">
+      <c r="AS8" s="3">
         <f>(N8/725)^2</f>
         <v/>
       </c>
-      <c r="AT8">
+      <c r="AT8" s="3">
         <f>IF(D8=0,"",AR8*AS8)</f>
         <v/>
       </c>
-      <c r="AW8">
+      <c r="AU8" s="2" t="n"/>
+      <c r="AV8" s="2" t="n"/>
+      <c r="AW8" s="2">
         <f>AQ8+N(AU8)+N(AV8)</f>
         <v/>
       </c>
-      <c r="AX8">
+      <c r="AX8" s="3">
         <f>IF(D8=0,"",AR8*(N8/725))</f>
         <v/>
       </c>
@@ -18513,7 +18726,7 @@
       <c r="Z9" t="n">
         <v>6</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AA9" s="2" t="n">
         <v>1250</v>
       </c>
       <c r="AB9" t="n">
@@ -18563,33 +18776,35 @@
           <t>SIEGE (owner 2026-09-06): 160% vs Fortified, 8.10 there against its nominal 5.06. Note its upgrade Sewage Surprise is MAGIC, so upgrading CHANGES the matchup profile - see that row. Starter. Its two upgrade branches are the run-defining fork.</t>
         </is>
       </c>
-      <c r="AO9" t="n">
+      <c r="AO9" s="2" t="n">
         <v>98.09999999999999</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AP9" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="AQ9">
+      <c r="AQ9" s="2">
         <f>AO9*AP9</f>
         <v/>
       </c>
-      <c r="AR9">
+      <c r="AR9" s="3">
         <f>IF(D9=0,"",AW9/D9)</f>
         <v/>
       </c>
-      <c r="AS9">
+      <c r="AS9" s="3">
         <f>(N9/725)^2</f>
         <v/>
       </c>
-      <c r="AT9">
+      <c r="AT9" s="3">
         <f>IF(D9=0,"",AR9*AS9)</f>
         <v/>
       </c>
-      <c r="AW9">
+      <c r="AU9" s="2" t="n"/>
+      <c r="AV9" s="2" t="n"/>
+      <c r="AW9" s="2">
         <f>AQ9+N(AU9)+N(AV9)</f>
         <v/>
       </c>
-      <c r="AX9">
+      <c r="AX9" s="3">
         <f>IF(D9=0,"",AR9*(N9/725))</f>
         <v/>
       </c>
@@ -18665,7 +18880,7 @@
       <c r="Z10" t="n">
         <v>6</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AA10" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="AB10" t="n">
@@ -18715,33 +18930,35 @@
           <t>MAGIC (owner 2026-09-06) - so the air line is built on the right type: magic is 140% vs Light, which the cycle puts on every air wave. 3.66 nominal becomes 5.12 on air waves. Base cost 155g inferred from the owner naming 'Interceptor' at 155g - the only unfilled base cost in the kit, and an anti-air name fits its 50% x1.5 vs air. Weak on its own; it is the GATE to its upgrade, the kit's strongest tower.</t>
         </is>
       </c>
-      <c r="AO10" t="n">
+      <c r="AO10" s="2" t="n">
         <v>255</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AP10" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="AQ10">
+      <c r="AQ10" s="2">
         <f>AO10*AP10</f>
         <v/>
       </c>
-      <c r="AR10">
+      <c r="AR10" s="3">
         <f>IF(D10=0,"",AW10/D10)</f>
         <v/>
       </c>
-      <c r="AS10">
+      <c r="AS10" s="3">
         <f>(N10/725)^2</f>
         <v/>
       </c>
-      <c r="AT10">
+      <c r="AT10" s="3">
         <f>IF(D10=0,"",AR10*AS10)</f>
         <v/>
       </c>
-      <c r="AW10">
+      <c r="AU10" s="2" t="n"/>
+      <c r="AV10" s="2" t="n"/>
+      <c r="AW10" s="2">
         <f>AQ10+N(AU10)+N(AV10)</f>
         <v/>
       </c>
-      <c r="AX10">
+      <c r="AX10" s="3">
         <f>IF(D10=0,"",AR10*(N10/725))</f>
         <v/>
       </c>
@@ -18817,7 +19034,7 @@
       <c r="Z11" t="n">
         <v>9</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AA11" s="2" t="n">
         <v>2500</v>
       </c>
       <c r="AB11" t="n">
@@ -18867,33 +19084,35 @@
           <t>MAGIC (owner 2026-09-06) - so the ENTIRE air branch is magic (Sewage Surprise, Interceptor, Arcadia), converted from the siege base. On AIR waves its 8.53 becomes 11.94 (Light, magic 140%). BUT its headline 23.90 vs attacking overstates the real case: attacker waves are 23, 32, 38, 45, and 23/38 are FORTIFIED where magic is 75%, giving 17.93 there. Only wave 32 (Heavy, 110%) reads above nominal at 26.29. VINDICATOR II IDENTIFIED 2026-09-05: the Royal Family High Priest names "vindicator II (50% crit x6 against attacking units)" - identical numbers, so this tower has been carrying Vindicator II unnamed. FIRST tower in the kit with TWO crit lines. Beats Mackinaw (22.07) on the 4 attacking waves (23/32/38/45) and is the best PASSIVE anti-air in the kit, but only 6.83 against everything else. A dual-specialist, not a generalist.</t>
         </is>
       </c>
-      <c r="AO11" t="n">
+      <c r="AO11" s="2" t="n">
         <v>550</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AP11" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="AQ11">
+      <c r="AQ11" s="2">
         <f>AO11*AP11</f>
         <v/>
       </c>
-      <c r="AR11">
+      <c r="AR11" s="3">
         <f>IF(D11=0,"",AW11/D11)</f>
         <v/>
       </c>
-      <c r="AS11">
+      <c r="AS11" s="3">
         <f>(N11/725)^2</f>
         <v/>
       </c>
-      <c r="AT11">
+      <c r="AT11" s="3">
         <f>IF(D11=0,"",AR11*AS11)</f>
         <v/>
       </c>
-      <c r="AW11">
+      <c r="AU11" s="2" t="n"/>
+      <c r="AV11" s="2" t="n"/>
+      <c r="AW11" s="2">
         <f>AQ11+N(AU11)+N(AV11)</f>
         <v/>
       </c>
-      <c r="AX11">
+      <c r="AX11" s="3">
         <f>IF(D11=0,"",AR11*(N11/725))</f>
         <v/>
       </c>
@@ -18964,7 +19183,7 @@
       <c r="Z12" t="n">
         <v>6</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AA12" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="AB12" t="n">
@@ -19014,33 +19233,35 @@
           <t xml:space="preserve">SIEGE (owner 2026-09-06) - which matters: its TORNADO answers air, but its AUTOATTACK gets no air bonus, since siege is absent from the Light bonus list. The tornado is a SPELL, not a passive trait (owner 2026-09-05) - so it is NOT the same thing as the Royal Family High Priest's "Judgement" trait, despite both doing 100 dps vs air. An earlier note here claimed they were tiers of one trait; that is withdrawn. </t>
         </is>
       </c>
-      <c r="AO12" t="n">
+      <c r="AO12" s="2" t="n">
         <v>1050</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AP12" s="3" t="n">
         <v>1.35</v>
       </c>
-      <c r="AQ12">
+      <c r="AQ12" s="2">
         <f>AO12*AP12</f>
         <v/>
       </c>
-      <c r="AR12">
+      <c r="AR12" s="3">
         <f>IF(D12=0,"",AW12/D12)</f>
         <v/>
       </c>
-      <c r="AS12">
+      <c r="AS12" s="3">
         <f>(N12/725)^2</f>
         <v/>
       </c>
-      <c r="AT12">
+      <c r="AT12" s="3">
         <f>IF(D12=0,"",AR12*AS12)</f>
         <v/>
       </c>
-      <c r="AW12">
+      <c r="AU12" s="2" t="n"/>
+      <c r="AV12" s="2" t="n"/>
+      <c r="AW12" s="2">
         <f>AQ12+N(AU12)+N(AV12)</f>
         <v/>
       </c>
-      <c r="AX12">
+      <c r="AX12" s="3">
         <f>IF(D12=0,"",AR12*(N12/725))</f>
         <v/>
       </c>
@@ -19111,7 +19332,7 @@
       <c r="Z13" t="n">
         <v>10</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AA13" s="2" t="n">
         <v>2250</v>
       </c>
       <c r="AB13" t="n">
@@ -19161,39 +19382,39 @@
           <t>SIEGE (owner 2026-09-06) - the last treant attack type read, 15/15. Its 22.07 becomes 35.31 on FORTIFIED waves (3/8/13/18/23...), the highest figure recorded in this kit by a wide margin, and 18.76 on boss waves (85%). Confirms branch B as the Fortified powerhouse: Sewer Barge -&gt; Brahma -&gt; Little Jack -&gt; Mackinaw is siege the whole way down. BASH II CONFIRMED 2026-09-05: the Royal Family Captain Bartlebee names it - 20%, +235, 2s stun, ground non-hero, identical to this tower. Note the chassis difference: on medium fire this yields ~40% stun uptime against Bartlebee's ~100% on very rapid. Stun uptime here is ~40% (medium fire) against Tyr Spirit's ~86%. THE kit's outlier: 22.07 range-adjusted, 2.5x the next best. 9.0x its own base's damage - the largest upgrade jump in the kit. Whether it keeps Little Jack's 35% x2 ground crit is UNSTATED, so these figures exclude it and are a FLOOR. Longest range in the kit (1000). Fire rate drops very rapid -&gt; medium, which the dps already accounts for. CRIT TARGET AMBIGUOUS (owner 2026-09-05): recorded as "boss" but the owner reports sometimes writing boss where the tooltip said HERO. "hero" is a stock WC3 ARMOUR TYPE (observed on wave 5), so this may be a crit vs an armour type rather than vs a unit role. Efficiency figures are unaffected either way (same chance and multiplier); only WHAT IT APPLIES TO is in doubt. REVERIFY.</t>
         </is>
       </c>
-      <c r="AO13" t="n">
+      <c r="AO13" s="2" t="n">
         <v>2167.1</v>
       </c>
-      <c r="AP13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ13">
+      <c r="AP13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ13" s="2">
         <f>AO13*AP13</f>
         <v/>
       </c>
-      <c r="AR13">
+      <c r="AR13" s="3">
         <f>IF(D13=0,"",AW13/D13)</f>
         <v/>
       </c>
-      <c r="AS13">
+      <c r="AS13" s="3">
         <f>(N13/725)^2</f>
         <v/>
       </c>
-      <c r="AT13">
+      <c r="AT13" s="3">
         <f>IF(D13=0,"",AR13*AS13)</f>
         <v/>
       </c>
-      <c r="AU13" t="n">
+      <c r="AU13" s="2" t="n">
         <v>26.9</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="AV13" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="AW13">
+      <c r="AW13" s="2">
         <f>AQ13+N(AU13)+N(AV13)</f>
         <v/>
       </c>
-      <c r="AX13">
+      <c r="AX13" s="3">
         <f>IF(D13=0,"",AR13*(N13/725))</f>
         <v/>
       </c>
@@ -19275,7 +19496,7 @@
       <c r="Z14" t="n">
         <v>11</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AA14" s="2" t="n">
         <v>3000</v>
       </c>
       <c r="AB14" t="n">
@@ -19328,33 +19549,35 @@
           <t>SIEGE (owner 2026-09-06): 160% on Fortified, so its 5.78 becomes 9.25 there. CONVERGENCE TOWER: it needs Arcadia AND Mackinaw, i.e. both T2 branches taken to their ends. Reaching it costs 550g (air branch) + 570g (generalist branch) + 450g = 1570g. That reframes its 5.78 - you are not choosing it over other towers, you are receiving it for having built both branches out. POSSIBLE VERSATILE CRITICAL STRIKE: the Royal Family Captain Bartlebee carries "Versatile Critical Strike (35% x2.5 vs ALL units)" - identical chance and multiplier to this tower, but this one was recorded as vs ATTACKING, not vs all. Either the target was mis-transcribed, or these are different traits sharing numbers. NOT assumed either way. If it is Versatile, this tower is far better than its 5.78 suggests, since the crit would apply on every wave. VERIFY. Priciest base tower seen and STILL type-specialised. 5.78 vs its own type against Arcadia 23.90 for 250g. eff/g ignores durability, and this is high-durability + attacking-crit = built to survive the waves that destroy towers.</t>
         </is>
       </c>
-      <c r="AO14" t="n">
+      <c r="AO14" s="2" t="n">
         <v>1310.6</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AP14" s="3" t="n">
         <v>1.52</v>
       </c>
-      <c r="AQ14">
+      <c r="AQ14" s="2">
         <f>AO14*AP14</f>
         <v/>
       </c>
-      <c r="AR14">
+      <c r="AR14" s="3">
         <f>IF(D14=0,"",AW14/D14)</f>
         <v/>
       </c>
-      <c r="AS14">
+      <c r="AS14" s="3">
         <f>(N14/725)^2</f>
         <v/>
       </c>
-      <c r="AT14">
+      <c r="AT14" s="3">
         <f>IF(D14=0,"",AR14*AS14)</f>
         <v/>
       </c>
-      <c r="AW14">
+      <c r="AU14" s="2" t="n"/>
+      <c r="AV14" s="2" t="n"/>
+      <c r="AW14" s="2">
         <f>AQ14+N(AU14)+N(AV14)</f>
         <v/>
       </c>
-      <c r="AX14">
+      <c r="AX14" s="3">
         <f>IF(D14=0,"",AR14*(N14/725))</f>
         <v/>
       </c>
@@ -19430,7 +19653,7 @@
       <c r="Z15" t="n">
         <v>7</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AA15" s="2" t="n">
         <v>2250</v>
       </c>
       <c r="AB15" t="n">
@@ -19480,33 +19703,35 @@
           <t>SIEGE (owner 2026-09-06): 3.13 becomes 5.01 on Fortified. NOT A CHEAP TRAP - A CONVERGENCE TOWER. Reaching it costs ~1125g plus the specialist base, and it requires Little Jack AND Interceptor, which sit on OPPOSITE branches of the T2 fork - so you must build two Sewer Barges and take both. That makes the fork a matter of TIMING, never a permanent lockout. Earlier notes here called it the worst tower in the kit at 3.13 and advised skipping it; the 3.13 stands, but "skip" was the wrong frame for something you cannot reach early regardless. Upgrade is Frankenstone (300g). Rapid (not very rapid) and only 500 range - weak on both efficiency axes despite high raw damage. WAVE-GATED at 10 - pairs with Warpath at 20 on a 10-wave cadence.</t>
         </is>
       </c>
-      <c r="AO15" t="n">
+      <c r="AO15" s="2" t="n">
         <v>475.5</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AP15" s="3" t="n">
         <v>1.35</v>
       </c>
-      <c r="AQ15">
+      <c r="AQ15" s="2">
         <f>AO15*AP15</f>
         <v/>
       </c>
-      <c r="AR15">
+      <c r="AR15" s="3">
         <f>IF(D15=0,"",AW15/D15)</f>
         <v/>
       </c>
-      <c r="AS15">
+      <c r="AS15" s="3">
         <f>(N15/725)^2</f>
         <v/>
       </c>
-      <c r="AT15">
+      <c r="AT15" s="3">
         <f>IF(D15=0,"",AR15*AS15)</f>
         <v/>
       </c>
-      <c r="AW15">
+      <c r="AU15" s="2" t="n"/>
+      <c r="AV15" s="2" t="n"/>
+      <c r="AW15" s="2">
         <f>AQ15+N(AU15)+N(AV15)</f>
         <v/>
       </c>
-      <c r="AX15">
+      <c r="AX15" s="3">
         <f>IF(D15=0,"",AR15*(N15/725))</f>
         <v/>
       </c>
@@ -19582,7 +19807,7 @@
       <c r="Z16" t="n">
         <v>8</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AA16" s="2" t="n">
         <v>2500</v>
       </c>
       <c r="AB16" t="n">
@@ -19632,33 +19857,35 @@
           <t>THE SKIP QUESTION IS SETTLED, and the answer is "right conclusion, wrong reason". At 7.41 range-adjusted (10.01 if it keeps the ground crit, unstated) it is well short of Mackinaw 22.07 and Arcadia 23.90, so buying INTO this line for damage was never correct. But Stone Experiment is a convergence tower you receive for building the rest of the tree anyway, and 300g to go 3.13 -&gt; 7.41 is a fine upgrade once you have it. THE GAIN IS IN FIRE RATE, NOT DAMAGE: damage is x2.37 but the rate DOUBLES (rapid -&gt; very rapid), while RANGE STAYS AT 500 so coverage remains a poor 0.69. PREDICTION POST-MORTEM: I modelled three damage multiples and said x9 would tie the best in the kit. The real multiple is x2.37 - but my error was holding the CHASSIS fixed. I varied damage and assumed speed and range would not move; speed doubled. SIEGE (owner 2026-09-06). Upgrade of Stone Experiment, 300g. No stats captured.</t>
         </is>
       </c>
-      <c r="AO16" t="n">
+      <c r="AO16" s="2" t="n">
         <v>1253.9</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AP16" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="AQ16">
+      <c r="AQ16" s="2">
         <f>AO16*AP16</f>
         <v/>
       </c>
-      <c r="AR16">
+      <c r="AR16" s="3">
         <f>IF(D16=0,"",AW16/D16)</f>
         <v/>
       </c>
-      <c r="AS16">
+      <c r="AS16" s="3">
         <f>(N16/725)^2</f>
         <v/>
       </c>
-      <c r="AT16">
+      <c r="AT16" s="3">
         <f>IF(D16=0,"",AR16*AS16)</f>
         <v/>
       </c>
-      <c r="AW16">
+      <c r="AU16" s="2" t="n"/>
+      <c r="AV16" s="2" t="n"/>
+      <c r="AW16" s="2">
         <f>AQ16+N(AU16)+N(AV16)</f>
         <v/>
       </c>
-      <c r="AX16">
+      <c r="AX16" s="3">
         <f>IF(D16=0,"",AR16*(N16/725))</f>
         <v/>
       </c>
@@ -19734,7 +19961,7 @@
       <c r="Z17" t="n">
         <v>11</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AA17" s="2" t="n">
         <v>3000</v>
       </c>
       <c r="AB17" t="n">
@@ -19784,33 +20011,35 @@
           <t>SIEGE (owner 2026-09-06). Gated behind the Stone Experiment line: needs Frankenstone, which needs Stone Experiment, which itself needs the specialist base and four towers. So Warpath sits at the end of the kit's longest single chain. WAVE-GATED unlock - the menu grows on a schedule, not only by spending. Stats not yet recorded.</t>
         </is>
       </c>
-      <c r="AO17" t="n">
+      <c r="AO17" s="2" t="n">
         <v>1059.2</v>
       </c>
-      <c r="AP17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ17">
+      <c r="AP17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ17" s="2">
         <f>AO17*AP17</f>
         <v/>
       </c>
-      <c r="AR17">
+      <c r="AR17" s="3">
         <f>IF(D17=0,"",AW17/D17)</f>
         <v/>
       </c>
-      <c r="AS17">
+      <c r="AS17" s="3">
         <f>(N17/725)^2</f>
         <v/>
       </c>
-      <c r="AT17">
+      <c r="AT17" s="3">
         <f>IF(D17=0,"",AR17*AS17)</f>
         <v/>
       </c>
-      <c r="AW17">
+      <c r="AU17" s="2" t="n"/>
+      <c r="AV17" s="2" t="n"/>
+      <c r="AW17" s="2">
         <f>AQ17+N(AU17)+N(AV17)</f>
         <v/>
       </c>
-      <c r="AX17">
+      <c r="AX17" s="3">
         <f>IF(D17=0,"",AR17*(N17/725))</f>
         <v/>
       </c>
@@ -19886,7 +20115,7 @@
       <c r="Z18" t="n">
         <v>12</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AA18" s="2" t="n">
         <v>3250</v>
       </c>
       <c r="AB18" t="n">
@@ -19931,33 +20160,35 @@
           <t>Appears ONLY as a Raiden requirement (owner 2026-09-06). Never otherwise seen - not in any build, not in any earlier list. The last unmapped node in the treant tree.</t>
         </is>
       </c>
-      <c r="AO18" t="n">
+      <c r="AO18" s="2" t="n">
         <v>1802.5</v>
       </c>
-      <c r="AP18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ18">
+      <c r="AP18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ18" s="2">
         <f>AO18*AP18</f>
         <v/>
       </c>
-      <c r="AR18">
+      <c r="AR18" s="3">
         <f>IF(D18=0,"",AW18/D18)</f>
         <v/>
       </c>
-      <c r="AS18">
+      <c r="AS18" s="3">
         <f>(N18/725)^2</f>
         <v/>
       </c>
-      <c r="AT18">
+      <c r="AT18" s="3">
         <f>IF(D18=0,"",AR18*AS18)</f>
         <v/>
       </c>
-      <c r="AW18">
+      <c r="AU18" s="2" t="n"/>
+      <c r="AV18" s="2" t="n"/>
+      <c r="AW18" s="2">
         <f>AQ18+N(AU18)+N(AV18)</f>
         <v/>
       </c>
-      <c r="AX18">
+      <c r="AX18" s="3">
         <f>IF(D18=0,"",AR18*(N18/725))</f>
         <v/>
       </c>
@@ -20033,7 +20264,7 @@
       <c r="Z19" t="n">
         <v>10</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AA19" s="2" t="n">
         <v>3000</v>
       </c>
       <c r="AB19" t="n">
@@ -20083,33 +20314,35 @@
           <t>MAGIC (owner 2026-09-06) - so the CAPSTONE breaks from the kit's siege identity, moving to 140% vs Light (air) and 75% vs Fortified. The capstone answers what the rest of the kit cannot. THE CAPSTONE, and it requires ESSENTIALLY THE WHOLE TREE: Phlogiston converges both T1 children, Ruby Scorpion converges both T2 branches, and Drunk Rock is a tower we have never otherwise seen. Priceable prerequisites come to 2605g, before Drunk Rock, the specialist base, or Raiden itself. Same shape as the Royal Family capstone (Astral Skibi, ~6389g path). Cost and stats unread.</t>
         </is>
       </c>
-      <c r="AO19" t="n">
+      <c r="AO19" s="2" t="n">
         <v>3180.6</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AP19" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="AQ19">
+      <c r="AQ19" s="2">
         <f>AO19*AP19</f>
         <v/>
       </c>
-      <c r="AR19">
+      <c r="AR19" s="3">
         <f>IF(D19=0,"",AW19/D19)</f>
         <v/>
       </c>
-      <c r="AS19">
+      <c r="AS19" s="3">
         <f>(N19/725)^2</f>
         <v/>
       </c>
-      <c r="AT19">
+      <c r="AT19" s="3">
         <f>IF(D19=0,"",AR19*AS19)</f>
         <v/>
       </c>
-      <c r="AW19">
+      <c r="AU19" s="2" t="n"/>
+      <c r="AV19" s="2" t="n"/>
+      <c r="AW19" s="2">
         <f>AQ19+N(AU19)+N(AV19)</f>
         <v/>
       </c>
-      <c r="AX19">
+      <c r="AX19" s="3">
         <f>IF(D19=0,"",AR19*(N19/725))</f>
         <v/>
       </c>
@@ -20185,7 +20418,7 @@
       <c r="Z20" t="n">
         <v>15</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AA20" s="2" t="n">
         <v>4000</v>
       </c>
       <c r="AB20" t="n">
@@ -20225,33 +20458,35 @@
           <t>U pgrade to Apocalypse</t>
         </is>
       </c>
-      <c r="AO20" t="n">
+      <c r="AO20" s="2" t="n">
         <v>4613.6</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AP20" s="3" t="n">
         <v>1.52</v>
       </c>
-      <c r="AQ20">
+      <c r="AQ20" s="2">
         <f>AO20*AP20</f>
         <v/>
       </c>
-      <c r="AR20">
+      <c r="AR20" s="3">
         <f>IF(D20=0,"",AW20/D20)</f>
         <v/>
       </c>
-      <c r="AS20">
+      <c r="AS20" s="3">
         <f>(N20/725)^2</f>
         <v/>
       </c>
-      <c r="AT20">
+      <c r="AT20" s="3">
         <f>IF(D20=0,"",AR20*AS20)</f>
         <v/>
       </c>
-      <c r="AW20">
+      <c r="AU20" s="2" t="n"/>
+      <c r="AV20" s="2" t="n"/>
+      <c r="AW20" s="2">
         <f>AQ20+N(AU20)+N(AV20)</f>
         <v/>
       </c>
-      <c r="AX20">
+      <c r="AX20" s="3">
         <f>IF(D20=0,"",AR20*(N20/725))</f>
         <v/>
       </c>
@@ -20267,6 +20502,7 @@
           <t>Sewage Surprise</t>
         </is>
       </c>
+      <c r="AA21" s="2" t="n"/>
       <c r="AL21" t="inlineStr">
         <is>
           <t>hand capture only — no extracted counterpart</t>
@@ -20282,30 +20518,33 @@
           <t>MAGIC (owner 2026-09-06), where its BASE Sewer Barge is siege - so attack type is NOT inherited on upgrade. Consequence: the upgrade gains everywhere except FORTIFIED, where siege 160% vs magic 75% leaves the base nearly as strong as its own upgrade (8.10 vs 5.92). Upgrading is a downgrade on 1 wave in 5. THE AIR BRANCH: this is the T2 upgrade that leads to Interceptor and Arcadia. Choosing the other branch (Brahma Fix It Shop) forfeits the treant's only passive air answer on that Sewer Barge. 'crit mecha like base' - the anti-mecha crit carries.</t>
         </is>
       </c>
-      <c r="AP21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ21">
+      <c r="AO21" s="2" t="n"/>
+      <c r="AP21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ21" s="2">
         <f>AO21*AP21</f>
         <v/>
       </c>
-      <c r="AR21">
+      <c r="AR21" s="3">
         <f>IF(D21=0,"",AW21/D21)</f>
         <v/>
       </c>
-      <c r="AS21">
+      <c r="AS21" s="3">
         <f>(N21/725)^2</f>
         <v/>
       </c>
-      <c r="AT21">
+      <c r="AT21" s="3">
         <f>IF(D21=0,"",AR21*AS21)</f>
         <v/>
       </c>
-      <c r="AW21">
+      <c r="AU21" s="2" t="n"/>
+      <c r="AV21" s="2" t="n"/>
+      <c r="AW21" s="2">
         <f>AQ21+N(AU21)+N(AV21)</f>
         <v/>
       </c>
-      <c r="AX21">
+      <c r="AX21" s="3">
         <f>IF(D21=0,"",AR21*(N21/725))</f>
         <v/>
       </c>
@@ -20321,6 +20560,7 @@
           <t>Brahma Fix It Shop</t>
         </is>
       </c>
+      <c r="AA22" s="2" t="n"/>
       <c r="AL22" t="inlineStr">
         <is>
           <t>hand capture only — no extracted counterpart</t>
@@ -20336,30 +20576,33 @@
           <t>SIEGE (owner 2026-09-06) - and that sharpens the T2 fork: the air branch (Sewage Surprise) switches the line to MAGIC, while this branch KEEPS siege. So the fork is siege-stays vs magic-switch, not two arbitrary paths. Its 4.67 becomes 7.47 on Fortified. THE GENERALIST BRANCH: leads to Little Jack and Battleship Mackinaw (22.07 untyped, the kit's best all-purpose tower). The opposite branch leads to the air line. Support branch. Longest range in the captured kit (1100). 'same passive to crit unit' - target type not stated.</t>
         </is>
       </c>
-      <c r="AP22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ22">
+      <c r="AO22" s="2" t="n"/>
+      <c r="AP22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ22" s="2">
         <f>AO22*AP22</f>
         <v/>
       </c>
-      <c r="AR22">
+      <c r="AR22" s="3">
         <f>IF(D22=0,"",AW22/D22)</f>
         <v/>
       </c>
-      <c r="AS22">
+      <c r="AS22" s="3">
         <f>(N22/725)^2</f>
         <v/>
       </c>
-      <c r="AT22">
+      <c r="AT22" s="3">
         <f>IF(D22=0,"",AR22*AS22)</f>
         <v/>
       </c>
-      <c r="AW22">
+      <c r="AU22" s="2" t="n"/>
+      <c r="AV22" s="2" t="n"/>
+      <c r="AW22" s="2">
         <f>AQ22+N(AU22)+N(AV22)</f>
         <v/>
       </c>
-      <c r="AX22">
+      <c r="AX22" s="3">
         <f>IF(D22=0,"",AR22*(N22/725))</f>
         <v/>
       </c>
@@ -20375,6 +20618,7 @@
           <t>Giga Spikes</t>
         </is>
       </c>
+      <c r="AA23" s="2" t="n"/>
       <c r="AL23" t="inlineStr">
         <is>
           <t>hand capture only — no extracted counterpart</t>
@@ -20390,30 +20634,33 @@
           <t xml:space="preserve">SIEGE (owner 2026-09-06) - note its BASE Spike Shooter is CHAOS, so this upgrade CHANGES type, the second confirmed case after Sewer Barge -&gt; Sewage Surprise. 4.95 becomes 7.92 on Fortified. RESOLVED 2026-09-05: the trait is named "Boss Assassin" but TARGETS HEROES - the owner read "boss assassin II (50% x8 against heroes)" on a Royal Family tower. So the earlier boss-vs-hero ambiguity was the GAME conflating them, not a transcription slip. Both readings were right. Upgrade of Spike Shooter. Keeps the anti-boss crit - 'same passive against boss', confirmed by the owner checking Giga Spikes directly (2026-09-03). Range jumps 600-&gt;900. </t>
         </is>
       </c>
-      <c r="AP23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ23">
+      <c r="AO23" s="2" t="n"/>
+      <c r="AP23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ23" s="2">
         <f>AO23*AP23</f>
         <v/>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="3">
         <f>IF(D23=0,"",AW23/D23)</f>
         <v/>
       </c>
-      <c r="AS23">
+      <c r="AS23" s="3">
         <f>(N23/725)^2</f>
         <v/>
       </c>
-      <c r="AT23">
+      <c r="AT23" s="3">
         <f>IF(D23=0,"",AR23*AS23)</f>
         <v/>
       </c>
-      <c r="AW23">
+      <c r="AU23" s="2" t="n"/>
+      <c r="AV23" s="2" t="n"/>
+      <c r="AW23" s="2">
         <f>AQ23+N(AU23)+N(AV23)</f>
         <v/>
       </c>
-      <c r="AX23">
+      <c r="AX23" s="3">
         <f>IF(D23=0,"",AR23*(N23/725))</f>
         <v/>
       </c>
@@ -20429,6 +20676,7 @@
           <t>Specialist Base</t>
         </is>
       </c>
+      <c r="AA24" s="2" t="n"/>
       <c r="AL24" t="inlineStr">
         <is>
           <t>hand capture only — no extracted counterpart</t>
@@ -20439,30 +20687,33 @@
           <t>THE TREANT HAS A BASE UPGRADE TOO. Analogous to the Royal Family's Royal Base II, which is bought at the hero-selection building. So base upgrades are present in 2 of 3 captured kits - the Tempest Hawk, which has none, is the exception. Cost and purchase location unread.</t>
         </is>
       </c>
-      <c r="AP24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ24">
+      <c r="AO24" s="2" t="n"/>
+      <c r="AP24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ24" s="2">
         <f>AO24*AP24</f>
         <v/>
       </c>
-      <c r="AR24">
+      <c r="AR24" s="3">
         <f>IF(D24=0,"",AW24/D24)</f>
         <v/>
       </c>
-      <c r="AS24">
+      <c r="AS24" s="3">
         <f>(N24/725)^2</f>
         <v/>
       </c>
-      <c r="AT24">
+      <c r="AT24" s="3">
         <f>IF(D24=0,"",AR24*AS24)</f>
         <v/>
       </c>
-      <c r="AW24">
+      <c r="AU24" s="2" t="n"/>
+      <c r="AV24" s="2" t="n"/>
+      <c r="AW24" s="2">
         <f>AQ24+N(AU24)+N(AV24)</f>
         <v/>
       </c>
-      <c r="AX24">
+      <c r="AX24" s="3">
         <f>IF(D24=0,"",AR24*(N24/725))</f>
         <v/>
       </c>
@@ -20875,7 +21126,7 @@
       <c r="Z2" t="n">
         <v>0</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AA2" s="2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
@@ -20925,33 +21176,35 @@
           <t>AIR CRITICAL STRIKE II identified 2026-09-05 (the Royal Family named the tier: 50% x4). ENTIRE KIT crits 50% x4 vs AIR. At 15g this is 17.13 range-adjusted vs air - comparable to the treant kit's BEST tower, which costs 250g.</t>
         </is>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AQ2" s="2" t="n">
         <v>32.5</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AR2" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="AS2">
+      <c r="AS2" s="2">
         <f>AQ2*AR2</f>
         <v/>
       </c>
-      <c r="AT2">
+      <c r="AT2" s="3">
         <f>IF(D2=0,"",AY2/D2)</f>
         <v/>
       </c>
-      <c r="AU2">
+      <c r="AU2" s="3">
         <f>(N2/725)^2</f>
         <v/>
       </c>
-      <c r="AV2">
+      <c r="AV2" s="3">
         <f>IF(D2=0,"",AT2*AU2)</f>
         <v/>
       </c>
-      <c r="AY2">
+      <c r="AW2" s="2" t="n"/>
+      <c r="AX2" s="2" t="n"/>
+      <c r="AY2" s="2">
         <f>AS2+N(AW2)+N(AX2)</f>
         <v/>
       </c>
-      <c r="AZ2">
+      <c r="AZ2" s="3">
         <f>IF(D2=0,"",AT2*(N2/725))</f>
         <v/>
       </c>
@@ -21022,7 +21275,7 @@
       <c r="Z3" t="n">
         <v>0</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AA3" s="2" t="n">
         <v>1250</v>
       </c>
       <c r="AB3" t="n">
@@ -21072,36 +21325,37 @@
           <t>AIR CRITICAL STRIKE II identified 2026-09-05 (the Royal Family named the tier: 50% x4). Highest range-adjusted figure recorded in ANY kit so far (25.94 vs air) - for 35 gold.</t>
         </is>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AQ3" s="2" t="n">
         <v>143.7</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AR3" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="AS3">
+      <c r="AS3" s="2">
         <f>AQ3*AR3</f>
         <v/>
       </c>
-      <c r="AT3">
+      <c r="AT3" s="3">
         <f>IF(D3=0,"",AY3/D3)</f>
         <v/>
       </c>
-      <c r="AU3">
+      <c r="AU3" s="3">
         <f>(N3/725)^2</f>
         <v/>
       </c>
-      <c r="AV3">
+      <c r="AV3" s="3">
         <f>IF(D3=0,"",AT3*AU3)</f>
         <v/>
       </c>
-      <c r="AX3" t="n">
+      <c r="AW3" s="2" t="n"/>
+      <c r="AX3" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AY3">
+      <c r="AY3" s="2">
         <f>AS3+N(AW3)+N(AX3)</f>
         <v/>
       </c>
-      <c r="AZ3">
+      <c r="AZ3" s="3">
         <f>IF(D3=0,"",AT3*(N3/725))</f>
         <v/>
       </c>
@@ -21177,7 +21431,7 @@
       <c r="Z4" t="n">
         <v>0</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AA4" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="AB4" t="n">
@@ -21227,33 +21481,35 @@
           <t>NOTE the weaker air crit: x1.5 where the rest of the kit is x4. Only 5.61 range-adjusted vs air. Bought for the HEALING SPELL, not for damage.</t>
         </is>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AQ4" s="2" t="n">
         <v>105.6</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="AR4" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="AS4">
+      <c r="AS4" s="2">
         <f>AQ4*AR4</f>
         <v/>
       </c>
-      <c r="AT4">
+      <c r="AT4" s="3">
         <f>IF(D4=0,"",AY4/D4)</f>
         <v/>
       </c>
-      <c r="AU4">
+      <c r="AU4" s="3">
         <f>(N4/725)^2</f>
         <v/>
       </c>
-      <c r="AV4">
+      <c r="AV4" s="3">
         <f>IF(D4=0,"",AT4*AU4)</f>
         <v/>
       </c>
-      <c r="AY4">
+      <c r="AW4" s="2" t="n"/>
+      <c r="AX4" s="2" t="n"/>
+      <c r="AY4" s="2">
         <f>AS4+N(AW4)+N(AX4)</f>
         <v/>
       </c>
-      <c r="AZ4">
+      <c r="AZ4" s="3">
         <f>IF(D4=0,"",AT4*(N4/725))</f>
         <v/>
       </c>
@@ -21329,7 +21585,7 @@
       <c r="Z5" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AA5" s="2" t="n">
         <v>1750</v>
       </c>
       <c r="AB5" t="n">
@@ -21379,33 +21635,35 @@
           <t>Stats not captured.</t>
         </is>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AQ5" s="2" t="n">
         <v>210</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AR5" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="AS5">
+      <c r="AS5" s="2">
         <f>AQ5*AR5</f>
         <v/>
       </c>
-      <c r="AT5">
+      <c r="AT5" s="3">
         <f>IF(D5=0,"",AY5/D5)</f>
         <v/>
       </c>
-      <c r="AU5">
+      <c r="AU5" s="3">
         <f>(N5/725)^2</f>
         <v/>
       </c>
-      <c r="AV5">
+      <c r="AV5" s="3">
         <f>IF(D5=0,"",AT5*AU5)</f>
         <v/>
       </c>
-      <c r="AY5">
+      <c r="AW5" s="2" t="n"/>
+      <c r="AX5" s="2" t="n"/>
+      <c r="AY5" s="2">
         <f>AS5+N(AW5)+N(AX5)</f>
         <v/>
       </c>
-      <c r="AZ5">
+      <c r="AZ5" s="3">
         <f>IF(D5=0,"",AT5*(N5/725))</f>
         <v/>
       </c>
@@ -21476,7 +21734,7 @@
       <c r="Z6" t="n">
         <v>0</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AA6" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="AB6" t="n">
@@ -21526,36 +21784,37 @@
           <t>NO crit reported - the first Tempest Hawk tower without the air crit. 7.23 range-adjusted untyped.</t>
         </is>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AQ6" s="2" t="n">
         <v>305.6</v>
       </c>
-      <c r="AR6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS6">
+      <c r="AR6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" s="2">
         <f>AQ6*AR6</f>
         <v/>
       </c>
-      <c r="AT6">
+      <c r="AT6" s="3">
         <f>IF(D6=0,"",AY6/D6)</f>
         <v/>
       </c>
-      <c r="AU6">
+      <c r="AU6" s="3">
         <f>(N6/725)^2</f>
         <v/>
       </c>
-      <c r="AV6">
+      <c r="AV6" s="3">
         <f>IF(D6=0,"",AT6*AU6)</f>
         <v/>
       </c>
-      <c r="AX6" t="n">
+      <c r="AW6" s="2" t="n"/>
+      <c r="AX6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AY6">
+      <c r="AY6" s="2">
         <f>AS6+N(AW6)+N(AX6)</f>
         <v/>
       </c>
-      <c r="AZ6">
+      <c r="AZ6" s="3">
         <f>IF(D6=0,"",AT6*(N6/725))</f>
         <v/>
       </c>
@@ -21626,7 +21885,7 @@
       <c r="Z7" t="n">
         <v>0</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AA7" s="2" t="n">
         <v>2000</v>
       </c>
       <c r="AB7" t="n">
@@ -21676,33 +21935,35 @@
           <t>AIR CRITICAL STRIKE II identified 2026-09-05 (the Royal Family named the tier: 50% x4). UPGRADE OF SHADOW (owner-confirmed 2026-09-05). THE ANTI-BOSS TOWER, and it ties the armour-type data together: wave 5 (a BOSS wave) was observed with armour type "hero", and this tower does x8 vs heroes. So "hero" armour marks the boss and this is the built answer to it. THE FREEZE IS THE HEADLINE: 3.5s freeze on a 2.5s attack cycle = 1.4x uptime = PERMANENT lockdown of a single target, which on a boss is a hard counter rather than a damage boost. 2500 per hit is the largest single hit recorded in any kit. CONFIRMED 2026-09-05: the x8 hero line is Boss Assassin II, whose chance is 50% - so the 26.60 figure is no longer provisional.</t>
         </is>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AQ7" s="2" t="n">
         <v>625</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AR7" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="AS7">
+      <c r="AS7" s="2">
         <f>AQ7*AR7</f>
         <v/>
       </c>
-      <c r="AT7">
+      <c r="AT7" s="3">
         <f>IF(D7=0,"",AY7/D7)</f>
         <v/>
       </c>
-      <c r="AU7">
+      <c r="AU7" s="3">
         <f>(N7/725)^2</f>
         <v/>
       </c>
-      <c r="AV7">
+      <c r="AV7" s="3">
         <f>IF(D7=0,"",AT7*AU7)</f>
         <v/>
       </c>
-      <c r="AY7">
+      <c r="AW7" s="2" t="n"/>
+      <c r="AX7" s="2" t="n"/>
+      <c r="AY7" s="2">
         <f>AS7+N(AW7)+N(AX7)</f>
         <v/>
       </c>
-      <c r="AZ7">
+      <c r="AZ7" s="3">
         <f>IF(D7=0,"",AT7*(N7/725))</f>
         <v/>
       </c>
@@ -21773,7 +22034,7 @@
       <c r="Z8" t="n">
         <v>0</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AA8" s="2" t="n">
         <v>2500</v>
       </c>
       <c r="AB8" t="n">
@@ -21823,33 +22084,35 @@
           <t>Convergent unlock - needs BOTH T3 and T4 lines upgraded.</t>
         </is>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AQ8" s="2" t="n">
         <v>650.4</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="AR8" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="AS8">
+      <c r="AS8" s="2">
         <f>AQ8*AR8</f>
         <v/>
       </c>
-      <c r="AT8">
+      <c r="AT8" s="3">
         <f>IF(D8=0,"",AY8/D8)</f>
         <v/>
       </c>
-      <c r="AU8">
+      <c r="AU8" s="3">
         <f>(N8/725)^2</f>
         <v/>
       </c>
-      <c r="AV8">
+      <c r="AV8" s="3">
         <f>IF(D8=0,"",AT8*AU8)</f>
         <v/>
       </c>
-      <c r="AY8">
+      <c r="AW8" s="2" t="n"/>
+      <c r="AX8" s="2" t="n"/>
+      <c r="AY8" s="2">
         <f>AS8+N(AW8)+N(AX8)</f>
         <v/>
       </c>
-      <c r="AZ8">
+      <c r="AZ8" s="3">
         <f>IF(D8=0,"",AT8*(N8/725))</f>
         <v/>
       </c>
@@ -21920,7 +22183,7 @@
       <c r="Z9" t="n">
         <v>1</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AA9" s="2" t="n">
         <v>1250</v>
       </c>
       <c r="AB9" t="n">
@@ -21970,33 +22233,35 @@
           <t>AIR CRITICAL STRIKE II identified 2026-09-05 (the Royal Family named the tier: 50% x4). T2 forks into an exclusive choice, same shape as the treant T2.</t>
         </is>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AQ9" s="2" t="n">
         <v>106.2</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="AR9" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="AS9">
+      <c r="AS9" s="2">
         <f>AQ9*AR9</f>
         <v/>
       </c>
-      <c r="AT9">
+      <c r="AT9" s="3">
         <f>IF(D9=0,"",AY9/D9)</f>
         <v/>
       </c>
-      <c r="AU9">
+      <c r="AU9" s="3">
         <f>(N9/725)^2</f>
         <v/>
       </c>
-      <c r="AV9">
+      <c r="AV9" s="3">
         <f>IF(D9=0,"",AT9*AU9)</f>
         <v/>
       </c>
-      <c r="AY9">
+      <c r="AW9" s="2" t="n"/>
+      <c r="AX9" s="2" t="n"/>
+      <c r="AY9" s="2">
         <f>AS9+N(AW9)+N(AX9)</f>
         <v/>
       </c>
-      <c r="AZ9">
+      <c r="AZ9" s="3">
         <f>IF(D9=0,"",AT9*(N9/725))</f>
         <v/>
       </c>
@@ -22072,7 +22337,7 @@
       <c r="Z10" t="n">
         <v>1</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AA10" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="AB10" t="n">
@@ -22122,33 +22387,35 @@
           <t>Stats not captured.</t>
         </is>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AQ10" s="2" t="n">
         <v>253.7</v>
       </c>
-      <c r="AR10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS10">
+      <c r="AR10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS10" s="2">
         <f>AQ10*AR10</f>
         <v/>
       </c>
-      <c r="AT10">
+      <c r="AT10" s="3">
         <f>IF(D10=0,"",AY10/D10)</f>
         <v/>
       </c>
-      <c r="AU10">
+      <c r="AU10" s="3">
         <f>(N10/725)^2</f>
         <v/>
       </c>
-      <c r="AV10">
+      <c r="AV10" s="3">
         <f>IF(D10=0,"",AT10*AU10)</f>
         <v/>
       </c>
-      <c r="AY10">
+      <c r="AW10" s="2" t="n"/>
+      <c r="AX10" s="2" t="n"/>
+      <c r="AY10" s="2">
         <f>AS10+N(AW10)+N(AX10)</f>
         <v/>
       </c>
-      <c r="AZ10">
+      <c r="AZ10" s="3">
         <f>IF(D10=0,"",AT10*(N10/725))</f>
         <v/>
       </c>
@@ -22239,7 +22506,7 @@
       <c r="W11" t="n">
         <v>1438.7</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AA11" s="2" t="n">
         <v>2500</v>
       </c>
       <c r="AB11" t="n">
@@ -22298,36 +22565,37 @@
           <t>Name only.</t>
         </is>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AQ11" s="2" t="n">
         <v>2763.7</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="AR11" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="AS11">
+      <c r="AS11" s="2">
         <f>AQ11*AR11</f>
         <v/>
       </c>
-      <c r="AT11">
+      <c r="AT11" s="3">
         <f>IF(D11=0,"",AY11/D11)</f>
         <v/>
       </c>
-      <c r="AU11">
+      <c r="AU11" s="3">
         <f>(N11/725)^2</f>
         <v/>
       </c>
-      <c r="AV11">
+      <c r="AV11" s="3">
         <f>IF(D11=0,"",AT11*AU11)</f>
         <v/>
       </c>
-      <c r="AX11" t="n">
+      <c r="AW11" s="2" t="n"/>
+      <c r="AX11" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="AY11">
+      <c r="AY11" s="2">
         <f>AS11+N(AW11)+N(AX11)</f>
         <v/>
       </c>
-      <c r="AZ11">
+      <c r="AZ11" s="3">
         <f>IF(D11=0,"",AT11*(N11/725))</f>
         <v/>
       </c>
@@ -22398,7 +22666,7 @@
       <c r="Z12" t="n">
         <v>1</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AA12" s="2" t="n">
         <v>2000</v>
       </c>
       <c r="AB12" t="n">
@@ -22448,36 +22716,37 @@
           <t>Stats not captured. NOTE: the two T2 branches are NOT dead ends - each opens its own late tower, so the "exclusive fork" may be a fork in TIMING rather than a permanent lockout. Unverified.</t>
         </is>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AQ12" s="2" t="n">
         <v>380</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="AR12" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="AS12">
+      <c r="AS12" s="2">
         <f>AQ12*AR12</f>
         <v/>
       </c>
-      <c r="AT12">
+      <c r="AT12" s="3">
         <f>IF(D12=0,"",AY12/D12)</f>
         <v/>
       </c>
-      <c r="AU12">
+      <c r="AU12" s="3">
         <f>(N12/725)^2</f>
         <v/>
       </c>
-      <c r="AV12">
+      <c r="AV12" s="3">
         <f>IF(D12=0,"",AT12*AU12)</f>
         <v/>
       </c>
-      <c r="AX12" t="n">
+      <c r="AW12" s="2" t="n"/>
+      <c r="AX12" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="AY12">
+      <c r="AY12" s="2">
         <f>AS12+N(AW12)+N(AX12)</f>
         <v/>
       </c>
-      <c r="AZ12">
+      <c r="AZ12" s="3">
         <f>IF(D12=0,"",AT12*(N12/725))</f>
         <v/>
       </c>
@@ -22548,7 +22817,7 @@
       <c r="Z13" t="n">
         <v>0</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AA13" s="2" t="n">
         <v>2250</v>
       </c>
       <c r="AB13" t="n">
@@ -22598,36 +22867,37 @@
           <t>Name only.</t>
         </is>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AQ13" s="2" t="n">
         <v>1333.3</v>
       </c>
-      <c r="AR13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS13">
+      <c r="AR13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS13" s="2">
         <f>AQ13*AR13</f>
         <v/>
       </c>
-      <c r="AT13">
+      <c r="AT13" s="3">
         <f>IF(D13=0,"",AY13/D13)</f>
         <v/>
       </c>
-      <c r="AU13">
+      <c r="AU13" s="3">
         <f>(N13/725)^2</f>
         <v/>
       </c>
-      <c r="AV13">
+      <c r="AV13" s="3">
         <f>IF(D13=0,"",AT13*AU13)</f>
         <v/>
       </c>
-      <c r="AX13" t="n">
+      <c r="AW13" s="2" t="n"/>
+      <c r="AX13" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="AY13">
+      <c r="AY13" s="2">
         <f>AS13+N(AW13)+N(AX13)</f>
         <v/>
       </c>
-      <c r="AZ13">
+      <c r="AZ13" s="3">
         <f>IF(D13=0,"",AT13*(N13/725))</f>
         <v/>
       </c>
@@ -22698,7 +22968,7 @@
       <c r="Z14" t="n">
         <v>3</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AA14" s="2" t="n">
         <v>2500</v>
       </c>
       <c r="AB14" t="n">
@@ -22748,33 +23018,35 @@
           <t>Convergent unlock across BOTH T2 branches.</t>
         </is>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AQ14" s="2" t="n">
         <v>1169.2</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="AR14" s="3" t="n">
         <v>1.52</v>
       </c>
-      <c r="AS14">
+      <c r="AS14" s="2">
         <f>AQ14*AR14</f>
         <v/>
       </c>
-      <c r="AT14">
+      <c r="AT14" s="3">
         <f>IF(D14=0,"",AY14/D14)</f>
         <v/>
       </c>
-      <c r="AU14">
+      <c r="AU14" s="3">
         <f>(N14/725)^2</f>
         <v/>
       </c>
-      <c r="AV14">
+      <c r="AV14" s="3">
         <f>IF(D14=0,"",AT14*AU14)</f>
         <v/>
       </c>
-      <c r="AY14">
+      <c r="AW14" s="2" t="n"/>
+      <c r="AX14" s="2" t="n"/>
+      <c r="AY14" s="2">
         <f>AS14+N(AW14)+N(AX14)</f>
         <v/>
       </c>
-      <c r="AZ14">
+      <c r="AZ14" s="3">
         <f>IF(D14=0,"",AT14*(N14/725))</f>
         <v/>
       </c>
@@ -22845,7 +23117,7 @@
       <c r="Z15" t="n">
         <v>2</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AA15" s="2" t="n">
         <v>1750</v>
       </c>
       <c r="AB15" t="n">
@@ -22895,39 +23167,39 @@
           <t>CORRECTED 2026-09-05: "Tempest Base" is a TOWER, and this hero has NO base upgrade (owner). An earlier note here read it as the hero base acting as a tech gate, by analogy with the Royal Family's Royal Base II - that analogy was wrong. Base upgrades are a PER-HERO feature, not a system rule. FIVE requirements - the widest gate recorded in any kit. Owner wrote "Teannage roc".</t>
         </is>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AQ15" s="2" t="n">
         <v>652</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="AR15" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="AS15">
+      <c r="AS15" s="2">
         <f>AQ15*AR15</f>
         <v/>
       </c>
-      <c r="AT15">
+      <c r="AT15" s="3">
         <f>IF(D15=0,"",AY15/D15)</f>
         <v/>
       </c>
-      <c r="AU15">
+      <c r="AU15" s="3">
         <f>(N15/725)^2</f>
         <v/>
       </c>
-      <c r="AV15">
+      <c r="AV15" s="3">
         <f>IF(D15=0,"",AT15*AU15)</f>
         <v/>
       </c>
-      <c r="AW15" t="n">
+      <c r="AW15" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="AX15" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AY15">
+      <c r="AY15" s="2">
         <f>AS15+N(AW15)+N(AX15)</f>
         <v/>
       </c>
-      <c r="AZ15">
+      <c r="AZ15" s="3">
         <f>IF(D15=0,"",AT15*(N15/725))</f>
         <v/>
       </c>
@@ -22975,7 +23247,7 @@
       <c r="Z16" t="n">
         <v>3</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AA16" s="2" t="n">
         <v>2000</v>
       </c>
       <c r="AO16" t="inlineStr">
@@ -22988,33 +23260,35 @@
           <t>Slot inferred, not observed. The kit rule is "each tower has at most ONE upgrade, and that upgrade unlocks a new tower type" - Havoc Wing is a REQUIREMENT of Death Shrine (T10) and sits between T9 and T10, so it is most likely Teenage Roc's upgrade. VERIFY.</t>
         </is>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AQ16" s="2" t="n">
         <v>316.7</v>
       </c>
-      <c r="AR16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS16">
+      <c r="AR16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS16" s="2">
         <f>AQ16*AR16</f>
         <v/>
       </c>
-      <c r="AT16">
+      <c r="AT16" s="3">
         <f>IF(D16=0,"",AY16/D16)</f>
         <v/>
       </c>
-      <c r="AU16">
+      <c r="AU16" s="3">
         <f>(N16/725)^2</f>
         <v/>
       </c>
-      <c r="AV16">
+      <c r="AV16" s="3">
         <f>IF(D16=0,"",AT16*AU16)</f>
         <v/>
       </c>
-      <c r="AY16">
+      <c r="AW16" s="2" t="n"/>
+      <c r="AX16" s="2" t="n"/>
+      <c r="AY16" s="2">
         <f>AS16+N(AW16)+N(AX16)</f>
         <v/>
       </c>
-      <c r="AZ16">
+      <c r="AZ16" s="3">
         <f>IF(D16=0,"",AT16*(N16/725))</f>
         <v/>
       </c>
@@ -23085,7 +23359,7 @@
       <c r="Z17" t="n">
         <v>3</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AA17" s="2" t="n">
         <v>2500</v>
       </c>
       <c r="AB17" t="n">
@@ -23135,33 +23409,35 @@
           <t>CORRECTED 2026-09-05: "Tempest Base" is a TOWER, and this hero has NO base upgrade (owner). An earlier note here read it as the hero base acting as a tech gate, by analogy with the Royal Family's Royal Base II - that analogy was wrong. Base upgrades are a PER-HERO feature, not a system rule. WAVE-GATED at 20, like the treant Warpath. Second confirmation that wave gates are a cross-hero system.</t>
         </is>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AQ17" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="AR17" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="AS17">
+      <c r="AS17" s="2">
         <f>AQ17*AR17</f>
         <v/>
       </c>
-      <c r="AT17">
+      <c r="AT17" s="3">
         <f>IF(D17=0,"",AY17/D17)</f>
         <v/>
       </c>
-      <c r="AU17">
+      <c r="AU17" s="3">
         <f>(N17/725)^2</f>
         <v/>
       </c>
-      <c r="AV17">
+      <c r="AV17" s="3">
         <f>IF(D17=0,"",AT17*AU17)</f>
         <v/>
       </c>
-      <c r="AY17">
+      <c r="AW17" s="2" t="n"/>
+      <c r="AX17" s="2" t="n"/>
+      <c r="AY17" s="2">
         <f>AS17+N(AW17)+N(AX17)</f>
         <v/>
       </c>
-      <c r="AZ17">
+      <c r="AZ17" s="3">
         <f>IF(D17=0,"",AT17*(N17/725))</f>
         <v/>
       </c>
@@ -23255,7 +23531,7 @@
       <c r="Z18" t="n">
         <v>4</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AA18" s="2" t="n">
         <v>2750</v>
       </c>
       <c r="AB18" t="n">
@@ -23314,33 +23590,35 @@
           <t>Slot inferred, not observed. Death Dragon is a REQUIREMENT of The Fallen (T11) and sits between T10 and T11, so it is most likely Death Shrine's upgrade. The owner listed "death dragon 700g" adjacently, so the 700g may belong to THIS tower rather than to The Fallen. VERIFY both.</t>
         </is>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AQ18" s="2" t="n">
         <v>95.09999999999999</v>
       </c>
-      <c r="AR18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS18">
+      <c r="AR18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS18" s="2">
         <f>AQ18*AR18</f>
         <v/>
       </c>
-      <c r="AT18">
+      <c r="AT18" s="3">
         <f>IF(D18=0,"",AY18/D18)</f>
         <v/>
       </c>
-      <c r="AU18">
+      <c r="AU18" s="3">
         <f>(N18/725)^2</f>
         <v/>
       </c>
-      <c r="AV18">
+      <c r="AV18" s="3">
         <f>IF(D18=0,"",AT18*AU18)</f>
         <v/>
       </c>
-      <c r="AY18">
+      <c r="AW18" s="2" t="n"/>
+      <c r="AX18" s="2" t="n"/>
+      <c r="AY18" s="2">
         <f>AS18+N(AW18)+N(AX18)</f>
         <v/>
       </c>
-      <c r="AZ18">
+      <c r="AZ18" s="3">
         <f>IF(D18=0,"",AT18*(N18/725))</f>
         <v/>
       </c>
@@ -23408,7 +23686,7 @@
       <c r="P19" t="n">
         <v>6531.7</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AA19" s="2" t="n">
         <v>3000</v>
       </c>
       <c r="AB19" t="n">
@@ -23458,33 +23736,35 @@
           <t>CORRECTED 2026-09-05: "Tempest Base" is a TOWER, and this hero has NO base upgrade (owner). An earlier note here read it as the hero base acting as a tech gate, by analogy with the Royal Family's Royal Base II - that analogy was wrong. Base upgrades are a PER-HERO feature, not a system rule. THE CAPSTONE. 700g, and the cost may instead belong to Death Dragon - the owner listed them adjacently. Likely the "700g unique (upgrade cost 800g)" the owner reported succeeding with, since this hero also has the 15g starter they mentioned; INFERENCE, not stated.</t>
         </is>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AQ19" s="2" t="n">
         <v>6531.7</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="AR19" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="AS19">
+      <c r="AS19" s="2">
         <f>AQ19*AR19</f>
         <v/>
       </c>
-      <c r="AT19">
+      <c r="AT19" s="3">
         <f>IF(D19=0,"",AY19/D19)</f>
         <v/>
       </c>
-      <c r="AU19">
+      <c r="AU19" s="3">
         <f>(N19/725)^2</f>
         <v/>
       </c>
-      <c r="AV19">
+      <c r="AV19" s="3">
         <f>IF(D19=0,"",AT19*AU19)</f>
         <v/>
       </c>
-      <c r="AY19">
+      <c r="AW19" s="2" t="n"/>
+      <c r="AX19" s="2" t="n"/>
+      <c r="AY19" s="2">
         <f>AS19+N(AW19)+N(AX19)</f>
         <v/>
       </c>
-      <c r="AZ19">
+      <c r="AZ19" s="3">
         <f>IF(D19=0,"",AT19*(N19/725))</f>
         <v/>
       </c>
@@ -23572,7 +23852,7 @@
       <c r="Z20" t="n">
         <v>7</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AA20" s="2" t="n">
         <v>3500</v>
       </c>
       <c r="AB20" t="n">
@@ -23621,36 +23901,37 @@
       <c r="AM20" t="n">
         <v>13</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AQ20" s="2" t="n">
         <v>8674.200000000001</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="AR20" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="AS20">
+      <c r="AS20" s="2">
         <f>AQ20*AR20</f>
         <v/>
       </c>
-      <c r="AT20">
+      <c r="AT20" s="3">
         <f>IF(D20=0,"",AY20/D20)</f>
         <v/>
       </c>
-      <c r="AU20">
+      <c r="AU20" s="3">
         <f>(N20/725)^2</f>
         <v/>
       </c>
-      <c r="AV20">
+      <c r="AV20" s="3">
         <f>IF(D20=0,"",AT20*AU20)</f>
         <v/>
       </c>
-      <c r="AX20" t="n">
+      <c r="AW20" s="2" t="n"/>
+      <c r="AX20" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="AY20">
+      <c r="AY20" s="2">
         <f>AS20+N(AW20)+N(AX20)</f>
         <v/>
       </c>
-      <c r="AZ20">
+      <c r="AZ20" s="3">
         <f>IF(D20=0,"",AT20*(N20/725))</f>
         <v/>
       </c>
@@ -23666,6 +23947,7 @@
           <t>Father Dragon</t>
         </is>
       </c>
+      <c r="AA21" s="2" t="n"/>
       <c r="AN21" t="inlineStr">
         <is>
           <t>hand capture only — no extracted counterpart</t>
@@ -23681,30 +23963,33 @@
           <t xml:space="preserve">AIR CRITICAL STRIKE II identified 2026-09-05 (the Royal Family named the tier: 50% x4). RESOLVED 2026-09-05: the trait is named "Boss Assassin" but TARGETS HEROES - the owner read "boss assassin II (50% x8 against heroes)" on a Royal Family tower. So the earlier boss-vs-hero ambiguity was the GAME conflating them, not a transcription slip. Both readings were right. DUAL crit (air AND boss) at 50% x4 each. 16.78 range-adjusted against either. Its 600 range is short for the kit. </t>
         </is>
       </c>
-      <c r="AR21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS21">
+      <c r="AQ21" s="2" t="n"/>
+      <c r="AR21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS21" s="2">
         <f>AQ21*AR21</f>
         <v/>
       </c>
-      <c r="AT21">
+      <c r="AT21" s="3">
         <f>IF(D21=0,"",AY21/D21)</f>
         <v/>
       </c>
-      <c r="AU21">
+      <c r="AU21" s="3">
         <f>(N21/725)^2</f>
         <v/>
       </c>
-      <c r="AV21">
+      <c r="AV21" s="3">
         <f>IF(D21=0,"",AT21*AU21)</f>
         <v/>
       </c>
-      <c r="AY21">
+      <c r="AW21" s="2" t="n"/>
+      <c r="AX21" s="2" t="n"/>
+      <c r="AY21" s="2">
         <f>AS21+N(AW21)+N(AX21)</f>
         <v/>
       </c>
-      <c r="AZ21">
+      <c r="AZ21" s="3">
         <f>IF(D21=0,"",AT21*(N21/725))</f>
         <v/>
       </c>
@@ -23720,6 +24005,7 @@
           <t>Reaper Spawn</t>
         </is>
       </c>
+      <c r="AA22" s="2" t="n"/>
       <c r="AN22" t="inlineStr">
         <is>
           <t>hand capture only — no extracted counterpart</t>
@@ -23735,30 +24021,33 @@
           <t>AIR CRITICAL STRIKE II identified 2026-09-05 (the Royal Family named the tier: 50% x4). CHAOS attack type - the kit's ONLY non-magic tower. In stock WC3 chaos deals full damage to every armour type, i.e. it ignores the matrix entirely; UNVERIFIED for this map. Melee, but DOES hit air when the flyer passes directly above it (owner 2026-09-05) - so it is a positional anti-air, not a blind spot. 23.90 raw dps/gold is among the best recorded, but it is unadjustable for range and demands exact placement under the flight path.</t>
         </is>
       </c>
-      <c r="AR22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS22">
+      <c r="AQ22" s="2" t="n"/>
+      <c r="AR22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS22" s="2">
         <f>AQ22*AR22</f>
         <v/>
       </c>
-      <c r="AT22">
+      <c r="AT22" s="3">
         <f>IF(D22=0,"",AY22/D22)</f>
         <v/>
       </c>
-      <c r="AU22">
+      <c r="AU22" s="3">
         <f>(N22/725)^2</f>
         <v/>
       </c>
-      <c r="AV22">
+      <c r="AV22" s="3">
         <f>IF(D22=0,"",AT22*AU22)</f>
         <v/>
       </c>
-      <c r="AY22">
+      <c r="AW22" s="2" t="n"/>
+      <c r="AX22" s="2" t="n"/>
+      <c r="AY22" s="2">
         <f>AS22+N(AW22)+N(AX22)</f>
         <v/>
       </c>
-      <c r="AZ22">
+      <c r="AZ22" s="3">
         <f>IF(D22=0,"",AT22*(N22/725))</f>
         <v/>
       </c>
@@ -30959,7 +31248,7 @@
           <t>Lesser Demon Spawn</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="2" t="n">
         <v>55</v>
       </c>
       <c r="F2" t="inlineStr">
@@ -31020,7 +31309,7 @@
           <t>Greater Demon Spawn</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="2" t="n">
         <v>61</v>
       </c>
       <c r="F3" t="inlineStr">
@@ -31086,7 +31375,7 @@
           <t>Diseased Bear</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="2" t="n">
         <v>155</v>
       </c>
       <c r="F4" t="inlineStr">
@@ -31147,7 +31436,7 @@
           <t>Pus-Filled Skink</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="2" t="n">
         <v>171</v>
       </c>
       <c r="E5" t="n">
@@ -31213,7 +31502,7 @@
           <t>Siege Machine</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="2" t="n">
         <v>235</v>
       </c>
       <c r="E6" t="n">
@@ -31277,7 +31566,7 @@
           <t>Castle Destroyer</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="2" t="n">
         <v>260</v>
       </c>
       <c r="E7" t="n">
@@ -31341,7 +31630,7 @@
           <t>Dark Wind Rider</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="2" t="n">
         <v>285</v>
       </c>
       <c r="E8" t="n">
@@ -31410,7 +31699,7 @@
           <t>The Dark One's Eyes</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="2" t="n">
         <v>480</v>
       </c>
       <c r="E9" t="n">
@@ -31484,7 +31773,7 @@
           <t>Condemned Councilman</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="2" t="n">
         <v>335</v>
       </c>
       <c r="E10" t="n">
@@ -31548,7 +31837,7 @@
           <t>Freakish Troll</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="2" t="n">
         <v>270</v>
       </c>
       <c r="E11" t="n">
@@ -31617,7 +31906,7 @@
           <t>Warped Wizard</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="2" t="n">
         <v>549</v>
       </c>
       <c r="E12" t="n">
@@ -31681,7 +31970,7 @@
           <t>Mutant Mage</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="2" t="n">
         <v>615</v>
       </c>
       <c r="E13" t="n">
@@ -31745,7 +32034,7 @@
           <t>Hell Bovine</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="2" t="n">
         <v>657</v>
       </c>
       <c r="E14" t="n">
@@ -31809,7 +32098,7 @@
           <t>Extra Fast Cow King</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="2" t="n">
         <v>1350</v>
       </c>
       <c r="E15" t="n">
@@ -31873,7 +32162,7 @@
           <t>Possessed Haroi</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="2" t="n">
         <v>847</v>
       </c>
       <c r="E16" t="n">
@@ -31942,7 +32231,7 @@
           <t>Dire Mammoth</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="2" t="n">
         <v>948</v>
       </c>
       <c r="E17" t="n">
@@ -32011,7 +32300,7 @@
           <t>Winged Scout</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="2" t="n">
         <v>754</v>
       </c>
       <c r="E18" t="n">
@@ -32080,7 +32369,7 @@
           <t>Aviary Lord</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="2" t="n">
         <v>1900</v>
       </c>
       <c r="E19" t="n">
@@ -32149,7 +32438,7 @@
           <t>Mutated Stag</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="2" t="n">
         <v>1109</v>
       </c>
       <c r="E20" t="n">
@@ -32213,7 +32502,7 @@
           <t>Forest Avatar</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="2" t="n">
         <v>1246</v>
       </c>
       <c r="E21" t="n">
@@ -32282,7 +32571,7 @@
           <t>Death's Breath</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="2" t="n">
         <v>1600</v>
       </c>
       <c r="E22" t="n">
@@ -32346,7 +32635,7 @@
           <t>Revived Dead</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="2" t="n">
         <v>1800</v>
       </c>
       <c r="E23" t="n">
@@ -32410,7 +32699,7 @@
           <t>Forsaken</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="2" t="n">
         <v>3346</v>
       </c>
       <c r="E24" t="n">
@@ -32474,7 +32763,7 @@
           <t>Toad Assassin</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="2" t="n">
         <v>3776</v>
       </c>
       <c r="E25" t="n">
@@ -32543,7 +32832,7 @@
           <t>Demented Beast</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="2" t="n">
         <v>2574</v>
       </c>
       <c r="E26" t="n">
@@ -32607,7 +32896,7 @@
           <t>Hell's Embrace</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="2" t="n">
         <v>6512</v>
       </c>
       <c r="E27" t="n">
@@ -32676,7 +32965,7 @@
           <t>Bonus Box I</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="2" t="n">
         <v>2400</v>
       </c>
       <c r="E28" t="n">
@@ -32745,7 +33034,7 @@
           <t>Bonus Seafood I</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="2" t="n">
         <v>3250</v>
       </c>
       <c r="E29" t="n">
@@ -32809,7 +33098,7 @@
           <t>Skeletor</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="2" t="n">
         <v>2993</v>
       </c>
       <c r="E30" t="n">
@@ -32878,7 +33167,7 @@
           <t>Greater Lich</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="2" t="n">
         <v>3399</v>
       </c>
       <c r="E31" t="n">
@@ -32947,7 +33236,7 @@
           <t>Damned Traitor</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="2" t="n">
         <v>3697</v>
       </c>
       <c r="E32" t="n">
@@ -33016,7 +33305,7 @@
           <t>Mirage</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="2" t="n">
         <v>3400</v>
       </c>
       <c r="E33" t="n">
@@ -33085,7 +33374,7 @@
           <t>Murk Dweller</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="2" t="n">
         <v>4291</v>
       </c>
       <c r="E34" t="n">
@@ -33149,7 +33438,7 @@
           <t>Scary Fish</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="2" t="n">
         <v>8657</v>
       </c>
       <c r="E35" t="n">
@@ -33213,7 +33502,7 @@
           <t>Nether Arachnoid</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="2" t="n">
         <v>4460</v>
       </c>
       <c r="E36" t="n">
@@ -33282,7 +33571,7 @@
           <t>Nether Ambusher</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="2" t="n">
         <v>5100</v>
       </c>
       <c r="E37" t="n">
@@ -33346,7 +33635,7 @@
           <t>Chilled Owls</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="2" t="n">
         <v>4200</v>
       </c>
       <c r="E38" t="n">
@@ -33415,7 +33704,7 @@
           <t>Ice Spirit</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="2" t="n">
         <v>4800</v>
       </c>
       <c r="E39" t="n">
@@ -33489,7 +33778,7 @@
           <t>Turtle Juggernaut</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="2" t="n">
         <v>6300</v>
       </c>
       <c r="E40" t="n">
@@ -33550,7 +33839,7 @@
           <t>Supreme Tortoise</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="2" t="n">
         <v>7230</v>
       </c>
       <c r="E41" t="n">
@@ -33611,7 +33900,7 @@
           <t>Flame Ogre</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="2" t="n">
         <v>11500</v>
       </c>
       <c r="E42" t="n">
@@ -33680,7 +33969,7 @@
           <t>Fire Strider</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="2" t="n">
         <v>13225</v>
       </c>
       <c r="E43" t="n">
@@ -33749,7 +34038,7 @@
           <t>Master Assassin</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="2" t="n">
         <v>8141</v>
       </c>
       <c r="E44" t="n">
@@ -33813,7 +34102,7 @@
           <t>Shogun</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="2" t="n">
         <v>9381</v>
       </c>
       <c r="E45" t="n">
@@ -33877,7 +34166,7 @@
           <t>Enraged Wendigo</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="2" t="n">
         <v>9910</v>
       </c>
       <c r="E46" t="n">
@@ -33938,7 +34227,7 @@
           <t>Feral Wendigo</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="2" t="n">
         <v>11443</v>
       </c>
       <c r="E47" t="n">
@@ -34002,7 +34291,7 @@
           <t>Bonus Box II</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="2" t="n">
         <v>6523</v>
       </c>
       <c r="E48" t="n">
@@ -34066,7 +34355,7 @@
           <t>Bonus Seafood II</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="2" t="n">
         <v>6725</v>
       </c>
       <c r="E49" t="n">
@@ -34125,7 +34414,7 @@
           <t>Divine Forger</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="2" t="n">
         <v>10262</v>
       </c>
       <c r="E50" t="n">
@@ -34184,7 +34473,7 @@
           <t>Iconocutioner</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="2" t="n">
         <v>10568</v>
       </c>
       <c r="E51" t="n">
@@ -34248,7 +34537,7 @@
           <t>Great Protector</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="2" t="n">
         <v>50000</v>
       </c>
       <c r="E52" t="n">
@@ -34304,7 +34593,7 @@
           <t>Brood Lizard</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="2" t="n">
         <v>4865</v>
       </c>
       <c r="E53" t="n">
@@ -34368,7 +34657,7 @@
           <t>Frenzied Lizard</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="2" t="n">
         <v>4746</v>
       </c>
       <c r="E54" t="n">
@@ -34437,7 +34726,7 @@
           <t>King Lizard</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="2" t="n">
         <v>13500</v>
       </c>
       <c r="E55" t="n">
@@ -34506,7 +34795,7 @@
           <t>Sporadic Asp</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="2" t="n">
         <v>11868</v>
       </c>
       <c r="E56" t="n">
@@ -34570,7 +34859,7 @@
           <t>Sayonara Mecha</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="2" t="n">
         <v>13818</v>
       </c>
       <c r="E57" t="n">
@@ -34634,7 +34923,7 @@
           <t>Demised Spirit</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="2" t="n">
         <v>12542</v>
       </c>
       <c r="E58" t="n">
@@ -34698,7 +34987,7 @@
           <t>Ethereal Wraith</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="2" t="n">
         <v>14632</v>
       </c>
       <c r="E59" t="n">
@@ -34764,7 +35053,7 @@
           <t>Deformed Witches</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="2" t="n">
         <v>9429</v>
       </c>
       <c r="E60" t="n">
@@ -34833,7 +35122,7 @@
           <t>Dragon Immortal</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="2" t="n">
         <v>11023</v>
       </c>
       <c r="E61" t="n">
@@ -34907,7 +35196,7 @@
           <t>Dog of War</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="2" t="n">
         <v>11848</v>
       </c>
       <c r="E62" t="n">
@@ -34971,7 +35260,7 @@
           <t>Shadow Wolf</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="2" t="n">
         <v>13879</v>
       </c>
       <c r="E63" t="n">
@@ -35035,7 +35324,7 @@
           <t>Hellfire Bug</t>
         </is>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="2" t="n">
         <v>12605</v>
       </c>
       <c r="E64" t="n">
@@ -35099,7 +35388,7 @@
           <t>Fire Ant</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="2" t="n">
         <v>14796</v>
       </c>
       <c r="E65" t="n">
@@ -35163,7 +35452,7 @@
           <t>Sacrificial Chosen</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="2" t="n">
         <v>9853</v>
       </c>
       <c r="E66" t="n">
@@ -35227,7 +35516,7 @@
           <t>Elite Evil</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="2" t="n">
         <v>2500</v>
       </c>
       <c r="E67" t="n">
@@ -35291,7 +35580,7 @@
           <t>Hangman's Oak</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="2" t="n">
         <v>35842</v>
       </c>
       <c r="E68" t="n">
@@ -35355,7 +35644,7 @@
           <t>Tree of Ill Omen</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="2" t="n">
         <v>63579</v>
       </c>
       <c r="E69" t="n">
@@ -35424,7 +35713,7 @@
           <t>Animated Sphinx</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="2" t="n">
         <v>12013</v>
       </c>
       <c r="E70" t="n">
@@ -35488,7 +35777,7 @@
           <t>Rydik's Statue</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="2" t="n">
         <v>23456</v>
       </c>
       <c r="E71" t="n">
@@ -35552,7 +35841,7 @@
           <t>Vampire</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="2" t="n">
         <v>21000</v>
       </c>
       <c r="E72" t="n">
@@ -35611,7 +35900,7 @@
           <t>Mummified Stalker</t>
         </is>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="2" t="n">
         <v>24500</v>
       </c>
       <c r="E73" t="n">
@@ -35670,7 +35959,7 @@
           <t>Soulless Fiend</t>
         </is>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="2" t="n">
         <v>26374</v>
       </c>
       <c r="E74" t="n">
@@ -35729,7 +36018,7 @@
           <t>Bad Seed</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F75" t="inlineStr">
@@ -35790,7 +36079,7 @@
           <t>Angel Executioner</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="2" t="n">
         <v>31272</v>
       </c>
       <c r="E76" t="n">
@@ -35854,7 +36143,7 @@
           <t>Ancient Crab</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="2" t="n">
         <v>28632</v>
       </c>
       <c r="E77" t="n">
@@ -35918,7 +36207,7 @@
           <t>Valiant Crustacean</t>
         </is>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" s="2" t="n">
         <v>34018</v>
       </c>
       <c r="E78" t="n">
@@ -35974,7 +36263,7 @@
           <t>Adrenalized Hiresword</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" s="2" t="n">
         <v>33954</v>
       </c>
       <c r="E79" t="n">
@@ -36033,7 +36322,7 @@
           <t>Fire Lord</t>
         </is>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="2" t="n">
         <v>23568</v>
       </c>
       <c r="E80" t="n">
@@ -36089,7 +36378,7 @@
           <t>Lava Spawn</t>
         </is>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="2" t="n">
         <v>21357</v>
       </c>
       <c r="E81" t="n">
@@ -36148,7 +36437,7 @@
           <t>Indomitable Sky Barge</t>
         </is>
       </c>
-      <c r="D82" t="n">
+      <c r="D82" s="2" t="n">
         <v>35806</v>
       </c>
       <c r="E82" t="n">
@@ -36214,7 +36503,7 @@
           <t>Super Evil Eagle</t>
         </is>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" s="2" t="n">
         <v>62450</v>
       </c>
       <c r="E83" t="n">
@@ -36283,7 +36572,7 @@
           <t>The Unfaithful</t>
         </is>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="2" t="n">
         <v>36822</v>
       </c>
       <c r="E84" t="n">
@@ -36347,7 +36636,7 @@
           <t>Acolyte of Flame</t>
         </is>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" s="2" t="n">
         <v>88024</v>
       </c>
       <c r="E85" t="n">
@@ -36411,7 +36700,7 @@
           <t>Evil One's Fingers</t>
         </is>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" s="2" t="n">
         <v>55000</v>
       </c>
       <c r="E86" t="n">
@@ -36470,7 +36759,7 @@
           <t>Evil One's Machines</t>
         </is>
       </c>
-      <c r="D87" t="n">
+      <c r="D87" s="2" t="n">
         <v>62500</v>
       </c>
       <c r="E87" t="n">
@@ -36524,7 +36813,7 @@
           <t>Gorishi Warrior</t>
         </is>
       </c>
-      <c r="D88" t="n">
+      <c r="D88" s="2" t="n">
         <v>90000</v>
       </c>
       <c r="E88" t="n">
@@ -36588,7 +36877,7 @@
           <t>Anti-Nova</t>
         </is>
       </c>
-      <c r="D89" t="n">
+      <c r="D89" s="2" t="n">
         <v>75000</v>
       </c>
       <c r="E89" t="n">
@@ -36652,7 +36941,7 @@
           <t>Æther Storm</t>
         </is>
       </c>
-      <c r="D90" t="n">
+      <c r="D90" s="2" t="n">
         <v>250000</v>
       </c>
       <c r="E90" t="n">
@@ -36708,7 +36997,7 @@
           <t>The Last Samurai</t>
         </is>
       </c>
-      <c r="D91" t="n">
+      <c r="D91" s="2" t="n">
         <v>175000</v>
       </c>
       <c r="E91" t="n">
@@ -36764,7 +37053,7 @@
           <t>Miasma Ghost</t>
         </is>
       </c>
-      <c r="D92" t="n">
+      <c r="D92" s="2" t="n">
         <v>7500</v>
       </c>
       <c r="E92" t="n">
@@ -36828,7 +37117,7 @@
           <t>Arioch's Warbird</t>
         </is>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" s="2" t="n">
         <v>24531</v>
       </c>
       <c r="E93" t="n">
@@ -37012,7 +37301,7 @@
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="2" t="n">
         <v>145000</v>
       </c>
       <c r="G2" t="n">
@@ -37063,7 +37352,7 @@
       <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="2" t="n">
         <v>105000</v>
       </c>
       <c r="G3" t="n">
@@ -37114,7 +37403,7 @@
       <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="2" t="n">
         <v>90000</v>
       </c>
       <c r="G4" t="n">
@@ -37165,7 +37454,7 @@
       <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="2" t="n">
         <v>47500</v>
       </c>
       <c r="G5" t="n">
@@ -37221,7 +37510,7 @@
       <c r="E6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="2" t="n">
         <v>41000</v>
       </c>
       <c r="G6" t="n">
@@ -37277,7 +37566,7 @@
       <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="2" t="n">
         <v>23000</v>
       </c>
       <c r="G7" t="n">
@@ -37328,7 +37617,7 @@
       <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="2" t="n">
         <v>280</v>
       </c>
       <c r="G8" t="n">
@@ -37369,7 +37658,7 @@
       <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="2" t="n">
         <v>13500</v>
       </c>
       <c r="G9" t="n">
@@ -37420,7 +37709,7 @@
       <c r="E10" t="n">
         <v>0</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="2" t="n">
         <v>12000</v>
       </c>
       <c r="G10" t="n">
@@ -37471,7 +37760,7 @@
       <c r="E11" t="n">
         <v>0</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="2" t="n">
         <v>800</v>
       </c>
       <c r="J11" t="n">
@@ -37510,7 +37799,7 @@
       <c r="E12" t="n">
         <v>0</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="n">
@@ -37554,7 +37843,7 @@
       <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="2" t="n">
         <v>4500</v>
       </c>
       <c r="G13" t="n">
@@ -37605,7 +37894,7 @@
       <c r="E14" t="n">
         <v>0</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="2" t="n">
         <v>140</v>
       </c>
       <c r="H14" t="inlineStr">
@@ -37649,7 +37938,7 @@
       <c r="E15" t="n">
         <v>0</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="2" t="n">
         <v>70</v>
       </c>
       <c r="G15" t="n">
@@ -37696,7 +37985,7 @@
       <c r="E16" t="n">
         <v>0</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G16" t="n">
@@ -37742,7 +38031,7 @@
       <c r="E17" t="n">
         <v>0</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="2" t="n">
         <v>25</v>
       </c>
       <c r="G17" t="n">
@@ -37789,7 +38078,7 @@
       <c r="E18" t="n">
         <v>0</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="2" t="n">
         <v>1490</v>
       </c>
       <c r="G18" t="n">
@@ -37840,7 +38129,7 @@
       <c r="E19" t="n">
         <v>0</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="2" t="n">
         <v>1340</v>
       </c>
       <c r="G19" t="n">
@@ -37891,7 +38180,7 @@
       <c r="E20" t="n">
         <v>0</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="2" t="n">
         <v>100</v>
       </c>
       <c r="L20" t="n">
@@ -37927,7 +38216,7 @@
       <c r="E21" t="n">
         <v>0</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G21" t="n">
@@ -37968,7 +38257,7 @@
       <c r="E22" t="n">
         <v>0</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" s="2" t="n">
         <v>5</v>
       </c>
       <c r="N22" t="inlineStr">
@@ -37992,7 +38281,7 @@
       <c r="C23" t="n">
         <v>5</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
@@ -38023,7 +38312,7 @@
       <c r="E24" t="n">
         <v>0</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" s="2" t="n">
         <v>50</v>
       </c>
       <c r="G24" t="n">
@@ -38065,7 +38354,7 @@
       <c r="E25" t="n">
         <v>0</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" s="2" t="n">
         <v>15</v>
       </c>
       <c r="G25" t="n">
@@ -38112,7 +38401,7 @@
       <c r="E26" t="n">
         <v>0</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G26" t="n">
@@ -38155,7 +38444,7 @@
       <c r="E27" t="n">
         <v>0</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G27" t="n">
@@ -38201,7 +38490,7 @@
       <c r="E28" t="n">
         <v>0</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28" s="2" t="n">
         <v>325</v>
       </c>
       <c r="G28" t="n">
@@ -38237,7 +38526,7 @@
       <c r="E29" t="n">
         <v>0</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" s="2" t="n">
         <v>40</v>
       </c>
       <c r="G29" t="n">
@@ -38275,7 +38564,7 @@
       <c r="E30" t="n">
         <v>0</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30" s="2" t="n">
         <v>37</v>
       </c>
       <c r="G30" t="n">
@@ -38316,7 +38605,7 @@
       <c r="E31" t="n">
         <v>0</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="J31" t="n">
@@ -38355,7 +38644,7 @@
       <c r="E32" t="n">
         <v>0</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G32" t="n">
@@ -38401,7 +38690,7 @@
       <c r="E33" t="n">
         <v>0</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33" s="2" t="n">
         <v>5</v>
       </c>
       <c r="J33" t="n">
@@ -38435,7 +38724,7 @@
       <c r="E34" t="n">
         <v>0</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G34" t="n">
@@ -38476,7 +38765,7 @@
       <c r="E35" t="n">
         <v>0</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35" s="2" t="n">
         <v>240</v>
       </c>
       <c r="J35" t="n">
@@ -38504,7 +38793,7 @@
       <c r="E36" t="n">
         <v>0</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36" s="2" t="n">
         <v>45</v>
       </c>
       <c r="H36" t="inlineStr">
@@ -38553,7 +38842,7 @@
       <c r="E37" t="n">
         <v>0</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37" s="2" t="n">
         <v>45</v>
       </c>
       <c r="J37" t="n">
@@ -38587,7 +38876,7 @@
       <c r="E38" t="n">
         <v>0</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38" s="2" t="n">
         <v>20</v>
       </c>
       <c r="G38" t="n">
@@ -38625,7 +38914,7 @@
       <c r="D39" t="n">
         <v>0</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39" s="2" t="n">
         <v>20</v>
       </c>
       <c r="I39" t="inlineStr">
@@ -38658,7 +38947,7 @@
       <c r="C40" t="n">
         <v>2</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40" s="2" t="n">
         <v>8</v>
       </c>
       <c r="J40" t="n">
@@ -38689,7 +38978,7 @@
       <c r="E41" t="n">
         <v>0</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H41" t="inlineStr">
@@ -38727,7 +39016,7 @@
       <c r="E42" t="n">
         <v>0</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J42" t="n">
@@ -38760,7 +39049,7 @@
       <c r="E43" t="n">
         <v>0</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G43" t="n">
@@ -38796,7 +39085,7 @@
       <c r="E44" t="n">
         <v>0</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G44" t="n">
@@ -38838,7 +39127,7 @@
       <c r="E45" t="n">
         <v>0</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45" s="2" t="n">
         <v>80</v>
       </c>
       <c r="J45" t="n">
@@ -38866,7 +39155,7 @@
       <c r="E46" t="n">
         <v>0</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46" s="2" t="n">
         <v>35</v>
       </c>
       <c r="H46" t="inlineStr">
@@ -38907,7 +39196,7 @@
       <c r="E47" t="n">
         <v>0</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47" s="2" t="n">
         <v>35</v>
       </c>
       <c r="G47" t="n">
@@ -38945,7 +39234,7 @@
       <c r="C48" t="n">
         <v>1</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48" s="2" t="n">
         <v>8</v>
       </c>
       <c r="M48" t="n">
@@ -39083,10 +39372,10 @@
           <t>mana</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="2" t="n">
         <v>39.8</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="3" t="n">
         <v>1.33</v>
       </c>
     </row>
@@ -39129,10 +39418,10 @@
           <t>mana</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="2" t="n">
         <v>47.3</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="3" t="n">
         <v>1.35</v>
       </c>
     </row>
@@ -39175,10 +39464,10 @@
           <t>mana</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="2" t="n">
         <v>48.6</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="3" t="n">
         <v>3.24</v>
       </c>
     </row>
@@ -39221,10 +39510,10 @@
           <t>mana</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="3" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -39267,10 +39556,10 @@
           <t>mana</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="2" t="n">
         <v>857.1</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="3" t="n">
         <v>3.17</v>
       </c>
     </row>
@@ -39313,10 +39602,10 @@
           <t>mana</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="2" t="n">
         <v>1356.7</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="3" t="n">
         <v>2.47</v>
       </c>
     </row>
@@ -39359,10 +39648,10 @@
           <t>mana</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="2" t="n">
         <v>217.5</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="3" t="n">
         <v>0.93</v>
       </c>
     </row>
@@ -39399,10 +39688,10 @@
           <t>cooldown</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="3" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -39445,10 +39734,10 @@
           <t>mana</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="2" t="n">
         <v>316.7</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="3" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -41788,7 +42077,7 @@
       <c r="Z2" t="n">
         <v>0</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AA2" s="2" t="n">
         <v>1250</v>
       </c>
       <c r="AB2" t="n">
@@ -41828,33 +42117,35 @@
           <t>Build Peasant ( Q )</t>
         </is>
       </c>
-      <c r="AN2" t="n">
+      <c r="AN2" s="2" t="n">
         <v>26.7</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AO2" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="AP2">
+      <c r="AP2" s="2">
         <f>AN2*AO2</f>
         <v/>
       </c>
-      <c r="AQ2">
+      <c r="AQ2" s="3">
         <f>IF(D2=0,"",AV2/D2)</f>
         <v/>
       </c>
-      <c r="AR2">
+      <c r="AR2" s="3">
         <f>(N2/725)^2</f>
         <v/>
       </c>
-      <c r="AS2">
+      <c r="AS2" s="3">
         <f>IF(D2=0,"",AQ2*AR2)</f>
         <v/>
       </c>
-      <c r="AV2">
+      <c r="AT2" s="2" t="n"/>
+      <c r="AU2" s="2" t="n"/>
+      <c r="AV2" s="2">
         <f>AP2+N(AT2)+N(AU2)</f>
         <v/>
       </c>
-      <c r="AW2">
+      <c r="AW2" s="3">
         <f>IF(D2=0,"",AQ2*(N2/725))</f>
         <v/>
       </c>
@@ -41920,7 +42211,7 @@
       <c r="Z3" t="n">
         <v>0</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AA3" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="AB3" t="n">
@@ -41960,33 +42251,35 @@
           <t>U pgrade to Hylgion Militia</t>
         </is>
       </c>
-      <c r="AN3" t="n">
+      <c r="AN3" s="2" t="n">
         <v>141.7</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AO3" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="AP3">
+      <c r="AP3" s="2">
         <f>AN3*AO3</f>
         <v/>
       </c>
-      <c r="AQ3">
+      <c r="AQ3" s="3">
         <f>IF(D3=0,"",AV3/D3)</f>
         <v/>
       </c>
-      <c r="AR3">
+      <c r="AR3" s="3">
         <f>(N3/725)^2</f>
         <v/>
       </c>
-      <c r="AS3">
+      <c r="AS3" s="3">
         <f>IF(D3=0,"",AQ3*AR3)</f>
         <v/>
       </c>
-      <c r="AV3">
+      <c r="AT3" s="2" t="n"/>
+      <c r="AU3" s="2" t="n"/>
+      <c r="AV3" s="2">
         <f>AP3+N(AT3)+N(AU3)</f>
         <v/>
       </c>
-      <c r="AW3">
+      <c r="AW3" s="3">
         <f>IF(D3=0,"",AQ3*(N3/725))</f>
         <v/>
       </c>
@@ -42052,7 +42345,7 @@
       <c r="Z4" t="n">
         <v>0</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AA4" s="2" t="n">
         <v>1750</v>
       </c>
       <c r="AB4" t="n">
@@ -42092,36 +42385,37 @@
           <t>Build Spear Guard ( W )</t>
         </is>
       </c>
-      <c r="AN4" t="n">
+      <c r="AN4" s="2" t="n">
         <v>171.7</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AO4" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="AP4">
+      <c r="AP4" s="2">
         <f>AN4*AO4</f>
         <v/>
       </c>
-      <c r="AQ4">
+      <c r="AQ4" s="3">
         <f>IF(D4=0,"",AV4/D4)</f>
         <v/>
       </c>
-      <c r="AR4">
+      <c r="AR4" s="3">
         <f>(N4/725)^2</f>
         <v/>
       </c>
-      <c r="AS4">
+      <c r="AS4" s="3">
         <f>IF(D4=0,"",AQ4*AR4)</f>
         <v/>
       </c>
-      <c r="AU4" t="n">
+      <c r="AT4" s="2" t="n"/>
+      <c r="AU4" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AV4">
+      <c r="AV4" s="2">
         <f>AP4+N(AT4)+N(AU4)</f>
         <v/>
       </c>
-      <c r="AW4">
+      <c r="AW4" s="3">
         <f>IF(D4=0,"",AQ4*(N4/725))</f>
         <v/>
       </c>
@@ -42187,7 +42481,7 @@
       <c r="Z5" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AA5" s="2" t="n">
         <v>2000</v>
       </c>
       <c r="AB5" t="n">
@@ -42227,36 +42521,37 @@
           <t>U pgrade to Axeman</t>
         </is>
       </c>
-      <c r="AN5" t="n">
+      <c r="AN5" s="2" t="n">
         <v>1173.3</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AO5" s="3" t="n">
         <v>1.52</v>
       </c>
-      <c r="AP5">
+      <c r="AP5" s="2">
         <f>AN5*AO5</f>
         <v/>
       </c>
-      <c r="AQ5">
+      <c r="AQ5" s="3">
         <f>IF(D5=0,"",AV5/D5)</f>
         <v/>
       </c>
-      <c r="AR5">
+      <c r="AR5" s="3">
         <f>(N5/725)^2</f>
         <v/>
       </c>
-      <c r="AS5">
+      <c r="AS5" s="3">
         <f>IF(D5=0,"",AQ5*AR5)</f>
         <v/>
       </c>
-      <c r="AU5" t="n">
+      <c r="AT5" s="2" t="n"/>
+      <c r="AU5" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="AV5">
+      <c r="AV5" s="2">
         <f>AP5+N(AT5)+N(AU5)</f>
         <v/>
       </c>
-      <c r="AW5">
+      <c r="AW5" s="3">
         <f>IF(D5=0,"",AQ5*(N5/725))</f>
         <v/>
       </c>
@@ -42327,7 +42622,7 @@
       <c r="Z6" t="n">
         <v>0</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AA6" s="2" t="n">
         <v>1750</v>
       </c>
       <c r="AB6" t="n">
@@ -42367,33 +42662,35 @@
           <t>Build Shinobi ( E )</t>
         </is>
       </c>
-      <c r="AN6" t="n">
+      <c r="AN6" s="2" t="n">
         <v>175</v>
       </c>
-      <c r="AO6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP6">
+      <c r="AO6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" s="2">
         <f>AN6*AO6</f>
         <v/>
       </c>
-      <c r="AQ6">
+      <c r="AQ6" s="3">
         <f>IF(D6=0,"",AV6/D6)</f>
         <v/>
       </c>
-      <c r="AR6">
+      <c r="AR6" s="3">
         <f>(N6/725)^2</f>
         <v/>
       </c>
-      <c r="AS6">
+      <c r="AS6" s="3">
         <f>IF(D6=0,"",AQ6*AR6)</f>
         <v/>
       </c>
-      <c r="AV6">
+      <c r="AT6" s="2" t="n"/>
+      <c r="AU6" s="2" t="n"/>
+      <c r="AV6" s="2">
         <f>AP6+N(AT6)+N(AU6)</f>
         <v/>
       </c>
-      <c r="AW6">
+      <c r="AW6" s="3">
         <f>IF(D6=0,"",AQ6*(N6/725))</f>
         <v/>
       </c>
@@ -42469,7 +42766,7 @@
       <c r="Z7" t="n">
         <v>0</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AA7" s="2" t="n">
         <v>2000</v>
       </c>
       <c r="AB7" t="n">
@@ -42509,33 +42806,35 @@
           <t>U pgrade to Orobos Slave</t>
         </is>
       </c>
-      <c r="AN7" t="n">
+      <c r="AN7" s="2" t="n">
         <v>916.7</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AO7" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="AP7">
+      <c r="AP7" s="2">
         <f>AN7*AO7</f>
         <v/>
       </c>
-      <c r="AQ7">
+      <c r="AQ7" s="3">
         <f>IF(D7=0,"",AV7/D7)</f>
         <v/>
       </c>
-      <c r="AR7">
+      <c r="AR7" s="3">
         <f>(N7/725)^2</f>
         <v/>
       </c>
-      <c r="AS7">
+      <c r="AS7" s="3">
         <f>IF(D7=0,"",AQ7*AR7)</f>
         <v/>
       </c>
-      <c r="AV7">
+      <c r="AT7" s="2" t="n"/>
+      <c r="AU7" s="2" t="n"/>
+      <c r="AV7" s="2">
         <f>AP7+N(AT7)+N(AU7)</f>
         <v/>
       </c>
-      <c r="AW7">
+      <c r="AW7" s="3">
         <f>IF(D7=0,"",AQ7*(N7/725))</f>
         <v/>
       </c>
@@ -42596,7 +42895,7 @@
       <c r="Z8" t="n">
         <v>0</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AA8" s="2" t="n">
         <v>2250</v>
       </c>
       <c r="AB8" t="n">
@@ -42636,36 +42935,37 @@
           <t>Build Ruthless Warlord ( R )</t>
         </is>
       </c>
-      <c r="AN8" t="n">
+      <c r="AN8" s="2" t="n">
         <v>3120</v>
       </c>
-      <c r="AO8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP8">
+      <c r="AO8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" s="2">
         <f>AN8*AO8</f>
         <v/>
       </c>
-      <c r="AQ8">
+      <c r="AQ8" s="3">
         <f>IF(D8=0,"",AV8/D8)</f>
         <v/>
       </c>
-      <c r="AR8">
+      <c r="AR8" s="3">
         <f>(N8/725)^2</f>
         <v/>
       </c>
-      <c r="AS8">
+      <c r="AS8" s="3">
         <f>IF(D8=0,"",AQ8*AR8)</f>
         <v/>
       </c>
-      <c r="AU8" t="n">
+      <c r="AT8" s="2" t="n"/>
+      <c r="AU8" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="AV8">
+      <c r="AV8" s="2">
         <f>AP8+N(AT8)+N(AU8)</f>
         <v/>
       </c>
-      <c r="AW8">
+      <c r="AW8" s="3">
         <f>IF(D8=0,"",AQ8*(N8/725))</f>
         <v/>
       </c>
@@ -42726,7 +43026,7 @@
       <c r="Z9" t="n">
         <v>2</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AA9" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="AB9" t="n">
@@ -42766,33 +43066,35 @@
           <t>Build Village Medic ( A )</t>
         </is>
       </c>
-      <c r="AN9" t="n">
+      <c r="AN9" s="2" t="n">
         <v>81.7</v>
       </c>
-      <c r="AO9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP9">
+      <c r="AO9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP9" s="2">
         <f>AN9*AO9</f>
         <v/>
       </c>
-      <c r="AQ9">
+      <c r="AQ9" s="3">
         <f>IF(D9=0,"",AV9/D9)</f>
         <v/>
       </c>
-      <c r="AR9">
+      <c r="AR9" s="3">
         <f>(N9/725)^2</f>
         <v/>
       </c>
-      <c r="AS9">
+      <c r="AS9" s="3">
         <f>IF(D9=0,"",AQ9*AR9)</f>
         <v/>
       </c>
-      <c r="AV9">
+      <c r="AT9" s="2" t="n"/>
+      <c r="AU9" s="2" t="n"/>
+      <c r="AV9" s="2">
         <f>AP9+N(AT9)+N(AU9)</f>
         <v/>
       </c>
-      <c r="AW9">
+      <c r="AW9" s="3">
         <f>IF(D9=0,"",AQ9*(N9/725))</f>
         <v/>
       </c>
@@ -42863,7 +43165,7 @@
       <c r="Z10" t="n">
         <v>1</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AA10" s="2" t="n">
         <v>1500</v>
       </c>
       <c r="AB10" t="n">
@@ -42903,33 +43205,35 @@
           <t>Build Marksman ( S )</t>
         </is>
       </c>
-      <c r="AN10" t="n">
+      <c r="AN10" s="2" t="n">
         <v>363</v>
       </c>
-      <c r="AO10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP10">
+      <c r="AO10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP10" s="2">
         <f>AN10*AO10</f>
         <v/>
       </c>
-      <c r="AQ10">
+      <c r="AQ10" s="3">
         <f>IF(D10=0,"",AV10/D10)</f>
         <v/>
       </c>
-      <c r="AR10">
+      <c r="AR10" s="3">
         <f>(N10/725)^2</f>
         <v/>
       </c>
-      <c r="AS10">
+      <c r="AS10" s="3">
         <f>IF(D10=0,"",AQ10*AR10)</f>
         <v/>
       </c>
-      <c r="AV10">
+      <c r="AT10" s="2" t="n"/>
+      <c r="AU10" s="2" t="n"/>
+      <c r="AV10" s="2">
         <f>AP10+N(AT10)+N(AU10)</f>
         <v/>
       </c>
-      <c r="AW10">
+      <c r="AW10" s="3">
         <f>IF(D10=0,"",AQ10*(N10/725))</f>
         <v/>
       </c>
@@ -43000,7 +43304,7 @@
       <c r="Z11" t="n">
         <v>2</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AA11" s="2" t="n">
         <v>2000</v>
       </c>
       <c r="AB11" t="n">
@@ -43040,33 +43344,35 @@
           <t>U pgrade to Tamed Game</t>
         </is>
       </c>
-      <c r="AN11" t="n">
+      <c r="AN11" s="2" t="n">
         <v>803</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AO11" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="AP11">
+      <c r="AP11" s="2">
         <f>AN11*AO11</f>
         <v/>
       </c>
-      <c r="AQ11">
+      <c r="AQ11" s="3">
         <f>IF(D11=0,"",AV11/D11)</f>
         <v/>
       </c>
-      <c r="AR11">
+      <c r="AR11" s="3">
         <f>(N11/725)^2</f>
         <v/>
       </c>
-      <c r="AS11">
+      <c r="AS11" s="3">
         <f>IF(D11=0,"",AQ11*AR11)</f>
         <v/>
       </c>
-      <c r="AV11">
+      <c r="AT11" s="2" t="n"/>
+      <c r="AU11" s="2" t="n"/>
+      <c r="AV11" s="2">
         <f>AP11+N(AT11)+N(AU11)</f>
         <v/>
       </c>
-      <c r="AW11">
+      <c r="AW11" s="3">
         <f>IF(D11=0,"",AQ11*(N11/725))</f>
         <v/>
       </c>
@@ -43132,7 +43438,7 @@
       <c r="Z12" t="n">
         <v>4</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AA12" s="2" t="n">
         <v>2000</v>
       </c>
       <c r="AB12" t="n">
@@ -43172,33 +43478,35 @@
           <t>Build Bladesmith ( D )</t>
         </is>
       </c>
-      <c r="AN12" t="n">
+      <c r="AN12" s="2" t="n">
         <v>680</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AO12" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="AP12">
+      <c r="AP12" s="2">
         <f>AN12*AO12</f>
         <v/>
       </c>
-      <c r="AQ12">
+      <c r="AQ12" s="3">
         <f>IF(D12=0,"",AV12/D12)</f>
         <v/>
       </c>
-      <c r="AR12">
+      <c r="AR12" s="3">
         <f>(N12/725)^2</f>
         <v/>
       </c>
-      <c r="AS12">
+      <c r="AS12" s="3">
         <f>IF(D12=0,"",AQ12*AR12)</f>
         <v/>
       </c>
-      <c r="AV12">
+      <c r="AT12" s="2" t="n"/>
+      <c r="AU12" s="2" t="n"/>
+      <c r="AV12" s="2">
         <f>AP12+N(AT12)+N(AU12)</f>
         <v/>
       </c>
-      <c r="AW12">
+      <c r="AW12" s="3">
         <f>IF(D12=0,"",AQ12*(N12/725))</f>
         <v/>
       </c>
@@ -43261,7 +43569,7 @@
       <c r="P13" t="n">
         <v>1624</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AA13" s="2" t="n">
         <v>3000</v>
       </c>
       <c r="AB13" t="n">
@@ -43301,36 +43609,37 @@
           <t>U pgrade to Impervious Armor</t>
         </is>
       </c>
-      <c r="AN13" t="n">
+      <c r="AN13" s="2" t="n">
         <v>1624</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AO13" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="AP13">
+      <c r="AP13" s="2">
         <f>AN13*AO13</f>
         <v/>
       </c>
-      <c r="AQ13">
+      <c r="AQ13" s="3">
         <f>IF(D13=0,"",AV13/D13)</f>
         <v/>
       </c>
-      <c r="AR13">
+      <c r="AR13" s="3">
         <f>(N13/725)^2</f>
         <v/>
       </c>
-      <c r="AS13">
+      <c r="AS13" s="3">
         <f>IF(D13=0,"",AQ13*AR13)</f>
         <v/>
       </c>
-      <c r="AT13" t="n">
+      <c r="AT13" s="2" t="n">
         <v>94</v>
       </c>
-      <c r="AV13">
+      <c r="AU13" s="2" t="n"/>
+      <c r="AV13" s="2">
         <f>AP13+N(AT13)+N(AU13)</f>
         <v/>
       </c>
-      <c r="AW13">
+      <c r="AW13" s="3">
         <f>IF(D13=0,"",AQ13*(N13/725))</f>
         <v/>
       </c>
@@ -43391,7 +43700,7 @@
       <c r="Z14" t="n">
         <v>3</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AA14" s="2" t="n">
         <v>3000</v>
       </c>
       <c r="AB14" t="n">
@@ -43431,33 +43740,35 @@
           <t>Build General Ninpou ( F )</t>
         </is>
       </c>
-      <c r="AN14" t="n">
+      <c r="AN14" s="2" t="n">
         <v>3230</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AO14" s="3" t="n">
         <v>1.52</v>
       </c>
-      <c r="AP14">
+      <c r="AP14" s="2">
         <f>AN14*AO14</f>
         <v/>
       </c>
-      <c r="AQ14">
+      <c r="AQ14" s="3">
         <f>IF(D14=0,"",AV14/D14)</f>
         <v/>
       </c>
-      <c r="AR14">
+      <c r="AR14" s="3">
         <f>(N14/725)^2</f>
         <v/>
       </c>
-      <c r="AS14">
+      <c r="AS14" s="3">
         <f>IF(D14=0,"",AQ14*AR14)</f>
         <v/>
       </c>
-      <c r="AV14">
+      <c r="AT14" s="2" t="n"/>
+      <c r="AU14" s="2" t="n"/>
+      <c r="AV14" s="2">
         <f>AP14+N(AT14)+N(AU14)</f>
         <v/>
       </c>
-      <c r="AW14">
+      <c r="AW14" s="3">
         <f>IF(D14=0,"",AQ14*(N14/725))</f>
         <v/>
       </c>
@@ -43523,7 +43834,7 @@
       <c r="Z15" t="n">
         <v>2</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AA15" s="2" t="n">
         <v>1750</v>
       </c>
       <c r="AB15" t="n">
@@ -43563,39 +43874,39 @@
           <t>Build Myrkridon Trow ( Z )</t>
         </is>
       </c>
-      <c r="AN15" t="n">
+      <c r="AN15" s="2" t="n">
         <v>703</v>
       </c>
-      <c r="AO15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP15">
+      <c r="AO15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP15" s="2">
         <f>AN15*AO15</f>
         <v/>
       </c>
-      <c r="AQ15">
+      <c r="AQ15" s="3">
         <f>IF(D15=0,"",AV15/D15)</f>
         <v/>
       </c>
-      <c r="AR15">
+      <c r="AR15" s="3">
         <f>(N15/725)^2</f>
         <v/>
       </c>
-      <c r="AS15">
+      <c r="AS15" s="3">
         <f>IF(D15=0,"",AQ15*AR15)</f>
         <v/>
       </c>
-      <c r="AT15" t="n">
+      <c r="AT15" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="AU15" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AV15">
+      <c r="AV15" s="2">
         <f>AP15+N(AT15)+N(AU15)</f>
         <v/>
       </c>
-      <c r="AW15">
+      <c r="AW15" s="3">
         <f>IF(D15=0,"",AQ15*(N15/725))</f>
         <v/>
       </c>
@@ -43671,7 +43982,7 @@
       <c r="Z16" t="n">
         <v>3</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AA16" s="2" t="n">
         <v>2000</v>
       </c>
       <c r="AB16" t="n">
@@ -43711,36 +44022,37 @@
           <t>U pgrade to Insurrectionist Trow</t>
         </is>
       </c>
-      <c r="AN16" t="n">
+      <c r="AN16" s="2" t="n">
         <v>2093.7</v>
       </c>
-      <c r="AO16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP16">
+      <c r="AO16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP16" s="2">
         <f>AN16*AO16</f>
         <v/>
       </c>
-      <c r="AQ16">
+      <c r="AQ16" s="3">
         <f>IF(D16=0,"",AV16/D16)</f>
         <v/>
       </c>
-      <c r="AR16">
+      <c r="AR16" s="3">
         <f>(N16/725)^2</f>
         <v/>
       </c>
-      <c r="AS16">
+      <c r="AS16" s="3">
         <f>IF(D16=0,"",AQ16*AR16)</f>
         <v/>
       </c>
-      <c r="AT16" t="n">
+      <c r="AT16" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="AV16">
+      <c r="AU16" s="2" t="n"/>
+      <c r="AV16" s="2">
         <f>AP16+N(AT16)+N(AU16)</f>
         <v/>
       </c>
-      <c r="AW16">
+      <c r="AW16" s="3">
         <f>IF(D16=0,"",AQ16*(N16/725))</f>
         <v/>
       </c>
@@ -43806,7 +44118,7 @@
       <c r="Z17" t="n">
         <v>3</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AA17" s="2" t="n">
         <v>2250</v>
       </c>
       <c r="AB17" t="n">
@@ -43846,36 +44158,37 @@
           <t>Build War Beast ( X )</t>
         </is>
       </c>
-      <c r="AN17" t="n">
+      <c r="AN17" s="2" t="n">
         <v>1442.9</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="AO17" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="AP17">
+      <c r="AP17" s="2">
         <f>AN17*AO17</f>
         <v/>
       </c>
-      <c r="AQ17">
+      <c r="AQ17" s="3">
         <f>IF(D17=0,"",AV17/D17)</f>
         <v/>
       </c>
-      <c r="AR17">
+      <c r="AR17" s="3">
         <f>(N17/725)^2</f>
         <v/>
       </c>
-      <c r="AS17">
+      <c r="AS17" s="3">
         <f>IF(D17=0,"",AQ17*AR17)</f>
         <v/>
       </c>
-      <c r="AU17" t="n">
+      <c r="AT17" s="2" t="n"/>
+      <c r="AU17" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="AV17">
+      <c r="AV17" s="2">
         <f>AP17+N(AT17)+N(AU17)</f>
         <v/>
       </c>
-      <c r="AW17">
+      <c r="AW17" s="3">
         <f>IF(D17=0,"",AQ17*(N17/725))</f>
         <v/>
       </c>
@@ -43964,7 +44277,7 @@
       <c r="Z18" t="n">
         <v>4</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AA18" s="2" t="n">
         <v>2500</v>
       </c>
       <c r="AB18" t="n">
@@ -44013,36 +44326,37 @@
       <c r="AM18" t="n">
         <v>6</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AN18" s="2" t="n">
         <v>552.2</v>
       </c>
-      <c r="AO18" t="n">
+      <c r="AO18" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="AP18">
+      <c r="AP18" s="2">
         <f>AN18*AO18</f>
         <v/>
       </c>
-      <c r="AQ18">
+      <c r="AQ18" s="3">
         <f>IF(D18=0,"",AV18/D18)</f>
         <v/>
       </c>
-      <c r="AR18">
+      <c r="AR18" s="3">
         <f>(N18/725)^2</f>
         <v/>
       </c>
-      <c r="AS18">
+      <c r="AS18" s="3">
         <f>IF(D18=0,"",AQ18*AR18)</f>
         <v/>
       </c>
-      <c r="AU18" t="n">
+      <c r="AT18" s="2" t="n"/>
+      <c r="AU18" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="AV18">
+      <c r="AV18" s="2">
         <f>AP18+N(AT18)+N(AU18)</f>
         <v/>
       </c>
-      <c r="AW18">
+      <c r="AW18" s="3">
         <f>IF(D18=0,"",AQ18*(N18/725))</f>
         <v/>
       </c>
@@ -44105,7 +44419,7 @@
       <c r="P19" t="n">
         <v>5275</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AA19" s="2" t="n">
         <v>3000</v>
       </c>
       <c r="AB19" t="n">
@@ -44145,33 +44459,35 @@
           <t>Build Mercurial Predator ( C )</t>
         </is>
       </c>
-      <c r="AN19" t="n">
+      <c r="AN19" s="2" t="n">
         <v>5275</v>
       </c>
-      <c r="AO19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP19">
+      <c r="AO19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP19" s="2">
         <f>AN19*AO19</f>
         <v/>
       </c>
-      <c r="AQ19">
+      <c r="AQ19" s="3">
         <f>IF(D19=0,"",AV19/D19)</f>
         <v/>
       </c>
-      <c r="AR19">
+      <c r="AR19" s="3">
         <f>(N19/725)^2</f>
         <v/>
       </c>
-      <c r="AS19">
+      <c r="AS19" s="3">
         <f>IF(D19=0,"",AQ19*AR19)</f>
         <v/>
       </c>
-      <c r="AV19">
+      <c r="AT19" s="2" t="n"/>
+      <c r="AU19" s="2" t="n"/>
+      <c r="AV19" s="2">
         <f>AP19+N(AT19)+N(AU19)</f>
         <v/>
       </c>
-      <c r="AW19">
+      <c r="AW19" s="3">
         <f>IF(D19=0,"",AQ19*(N19/725))</f>
         <v/>
       </c>
@@ -44237,7 +44553,7 @@
       <c r="Z20" t="n">
         <v>7</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AA20" s="2" t="n">
         <v>3500</v>
       </c>
       <c r="AB20" t="n">
@@ -44277,33 +44593,35 @@
           <t>U pgrade to Unrivaled Destroyer</t>
         </is>
       </c>
-      <c r="AN20" t="n">
+      <c r="AN20" s="2" t="n">
         <v>8905.6</v>
       </c>
-      <c r="AO20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP20">
+      <c r="AO20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP20" s="2">
         <f>AN20*AO20</f>
         <v/>
       </c>
-      <c r="AQ20">
+      <c r="AQ20" s="3">
         <f>IF(D20=0,"",AV20/D20)</f>
         <v/>
       </c>
-      <c r="AR20">
+      <c r="AR20" s="3">
         <f>(N20/725)^2</f>
         <v/>
       </c>
-      <c r="AS20">
+      <c r="AS20" s="3">
         <f>IF(D20=0,"",AQ20*AR20)</f>
         <v/>
       </c>
-      <c r="AV20">
+      <c r="AT20" s="2" t="n"/>
+      <c r="AU20" s="2" t="n"/>
+      <c r="AV20" s="2">
         <f>AP20+N(AT20)+N(AU20)</f>
         <v/>
       </c>
-      <c r="AW20">
+      <c r="AW20" s="3">
         <f>IF(D20=0,"",AQ20*(N20/725))</f>
         <v/>
       </c>

--- a/skibi-data.xlsx
+++ b/skibi-data.xlsx
@@ -30,23 +30,23 @@
     <sheet name="waves" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'arcane'!$A$1:$AU$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'arcane'!$A$1:$AV$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'armour_matrix'!$A$1:$F$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'bosses'!$A$1:$O$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'caster_dps'!$A$1:$L$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'game_modes'!$A$1:$I$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'hero_ranking'!$A$1:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'heroes'!$A$1:$H$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'military'!$A$1:$AX$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'military'!$A$1:$AY$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'minigame_items'!$A$1:$D$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'minigame_readings'!$A$1:$G$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'minigames'!$A$1:$I$80</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'other_towers'!$A$1:$AV$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'ranger'!$A$1:$AU$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'royal_family'!$A$1:$BA$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'scarlet_knight'!$A$1:$AU$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'specialist'!$A$1:$AY$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'tempest'!$A$1:$BA$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'other_towers'!$A$1:$AW$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'ranger'!$A$1:$AV$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'royal_family'!$A$1:$BB$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'scarlet_knight'!$A$1:$AV$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'specialist'!$A$1:$AZ$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'tempest'!$A$1:$BB$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'tower_traits'!$A$1:$I$113</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'wave_modifiers'!$A$1:$D$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'wave_traits'!$A$1:$K$51</definedName>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU18"/>
+  <dimension ref="A1:AV18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -513,6 +513,7 @@
     <col width="15" customWidth="1" min="45" max="45"/>
     <col width="22" customWidth="1" min="46" max="46"/>
     <col width="48" customWidth="1" min="47" max="47"/>
+    <col width="13" customWidth="1" min="48" max="48"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -751,6 +752,11 @@
           <t>dps_source</t>
         </is>
       </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>cost_source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -828,6 +834,11 @@
           <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
         </is>
       </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -907,6 +918,11 @@
           <t>caster: Arctic Blast (sustained, mana-limited)</t>
         </is>
       </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -984,6 +1000,11 @@
           <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
         </is>
       </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1063,6 +1084,11 @@
           <t>caster: Scald (sustained, mana-limited)</t>
         </is>
       </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1142,6 +1168,11 @@
           <t>caster: Ball Lightning (sustained, mana-limited)</t>
         </is>
       </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1219,6 +1250,11 @@
           <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
         </is>
       </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1286,6 +1322,11 @@
           <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
         </is>
       </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1365,6 +1406,11 @@
           <t>caster: Chilly Bits Grade Peorth (sustained, mana-limited)</t>
         </is>
       </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1442,6 +1488,11 @@
           <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
         </is>
       </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1581,6 +1632,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1720,6 +1776,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1799,6 +1860,11 @@
           <t>caster: Super Shock (sustained, mana-limited)</t>
         </is>
       </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1878,6 +1944,11 @@
           <t>caster: Tsukikaze (sustained, mana-limited)</t>
         </is>
       </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1940,6 +2011,11 @@
           <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
         </is>
       </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2005,6 +2081,11 @@
           <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
         </is>
       </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2070,6 +2151,11 @@
           <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
         </is>
       </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2135,9 +2221,14 @@
           <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
         </is>
       </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AU18"/>
+  <autoFilter ref="A1:AV18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5551,7 +5642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV15"/>
+  <dimension ref="A1:AW15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5602,6 +5693,7 @@
     <col width="17" customWidth="1" min="46" max="46"/>
     <col width="27" customWidth="1" min="47" max="47"/>
     <col width="14" customWidth="1" min="48" max="48"/>
+    <col width="13" customWidth="1" min="49" max="49"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5845,6 +5937,11 @@
           <t>dps_source</t>
         </is>
       </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>cost_source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5968,6 +6065,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6081,6 +6183,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6194,6 +6301,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6307,6 +6419,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6420,6 +6537,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6533,6 +6655,11 @@
       <c r="AV7" t="inlineStr">
         <is>
           <t>basic attack</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
@@ -6658,6 +6785,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6798,6 +6930,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6916,6 +7053,11 @@
       <c r="AV10" t="inlineStr">
         <is>
           <t>basic attack</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
@@ -7041,6 +7183,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7164,6 +7311,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7302,6 +7454,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7440,6 +7597,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7565,9 +7727,14 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AV15"/>
+  <autoFilter ref="A1:AW15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7578,7 +7745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU20"/>
+  <dimension ref="A1:AV20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7628,6 +7795,7 @@
     <col width="15" customWidth="1" min="45" max="45"/>
     <col width="22" customWidth="1" min="46" max="46"/>
     <col width="14" customWidth="1" min="47" max="47"/>
+    <col width="13" customWidth="1" min="48" max="48"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7866,6 +8034,11 @@
           <t>dps_source</t>
         </is>
       </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>cost_source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8005,6 +8178,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8144,6 +8322,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8288,6 +8471,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8429,6 +8617,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8570,6 +8763,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8709,6 +8907,11 @@
       <c r="AU7" t="inlineStr">
         <is>
           <t>basic attack</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
@@ -8850,6 +9053,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8984,6 +9192,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9128,6 +9341,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9272,6 +9490,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9411,6 +9634,11 @@
       <c r="AU12" t="inlineStr">
         <is>
           <t>basic attack</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
@@ -9557,6 +9785,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9696,6 +9929,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9835,6 +10073,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9976,6 +10219,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -10117,6 +10365,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10258,6 +10511,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10394,6 +10652,11 @@
       <c r="AU19" t="inlineStr">
         <is>
           <t>basic attack</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
@@ -10540,9 +10803,14 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AU20"/>
+  <autoFilter ref="A1:AV20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10553,7 +10821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA28"/>
+  <dimension ref="A1:BB28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10609,6 +10877,7 @@
     <col width="15" customWidth="1" min="51" max="51"/>
     <col width="22" customWidth="1" min="52" max="52"/>
     <col width="48" customWidth="1" min="53" max="53"/>
+    <col width="48" customWidth="1" min="54" max="54"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10877,6 +11146,11 @@
           <t>dps_source</t>
         </is>
       </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>cost_source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11016,6 +11290,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11165,6 +11444,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11179,6 +11463,9 @@
       </c>
       <c r="C4" t="n">
         <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>80</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -11276,6 +11563,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>owner read in game 2026-09-12; the map sets no gold cost for this unit</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11417,6 +11709,11 @@
       <c r="BA5" t="inlineStr">
         <is>
           <t>basic attack</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
@@ -11573,6 +11870,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11709,6 +12011,11 @@
       <c r="BA7" t="inlineStr">
         <is>
           <t>basic attack</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
@@ -11892,6 +12199,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12041,6 +12353,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12195,6 +12512,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12346,6 +12668,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12495,6 +12822,11 @@
       <c r="BA12" t="inlineStr">
         <is>
           <t>basic attack</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
@@ -12641,6 +12973,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12790,6 +13127,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12944,6 +13286,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13098,6 +13445,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13242,6 +13594,11 @@
       <c r="BA17" t="inlineStr">
         <is>
           <t>basic attack</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
@@ -13388,6 +13745,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -13529,6 +13891,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -13673,6 +14040,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -13812,6 +14184,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -13988,6 +14365,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -14313,7 +14695,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BA28"/>
+  <autoFilter ref="A1:BB28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14324,7 +14706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU21"/>
+  <dimension ref="A1:AV21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -14374,6 +14756,7 @@
     <col width="15" customWidth="1" min="45" max="45"/>
     <col width="22" customWidth="1" min="46" max="46"/>
     <col width="48" customWidth="1" min="47" max="47"/>
+    <col width="13" customWidth="1" min="48" max="48"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14612,6 +14995,11 @@
           <t>dps_source</t>
         </is>
       </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>cost_source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14746,6 +15134,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14880,6 +15273,11 @@
       <c r="AU3" t="inlineStr">
         <is>
           <t>basic attack</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
@@ -15026,6 +15424,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15110,6 +15513,11 @@
           <t>caster: Foxfire Laser (sustained, mana-limited)</t>
         </is>
       </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15254,6 +15662,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15398,6 +15811,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15532,6 +15950,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15671,6 +16094,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15815,6 +16243,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15959,6 +16392,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -16043,6 +16481,11 @@
           <t>caster: Fury of the Gods (sustained, mana-limited)</t>
         </is>
       </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16182,6 +16625,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16323,6 +16771,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -16464,6 +16917,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -16608,6 +17066,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -16752,6 +17215,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -16891,6 +17359,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -17027,6 +17500,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -17166,6 +17644,11 @@
       <c r="AU20" t="inlineStr">
         <is>
           <t>basic attack</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
@@ -17307,9 +17790,14 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AU21"/>
+  <autoFilter ref="A1:AV21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17320,7 +17808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -17374,6 +17862,7 @@
     <col width="15" customWidth="1" min="49" max="49"/>
     <col width="22" customWidth="1" min="50" max="50"/>
     <col width="48" customWidth="1" min="51" max="51"/>
+    <col width="13" customWidth="1" min="52" max="52"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17632,6 +18121,11 @@
           <t>dps_source</t>
         </is>
       </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>cost_source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17786,6 +18280,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17940,6 +18439,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18091,6 +18595,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18232,6 +18741,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18380,6 +18894,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18526,6 +19045,11 @@
       <c r="AY7" t="inlineStr">
         <is>
           <t>basic attack</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
@@ -18669,6 +19193,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18813,6 +19342,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18967,6 +19501,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -19121,6 +19660,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -19270,6 +19814,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -19421,6 +19970,11 @@
       <c r="AY13" t="inlineStr">
         <is>
           <t>basic attack</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
@@ -19586,6 +20140,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -19740,6 +20299,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -19894,6 +20458,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -20048,6 +20617,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -20197,6 +20771,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -20351,6 +20930,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -20495,6 +21079,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -20724,7 +21313,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AY24"/>
+  <autoFilter ref="A1:AZ24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20735,7 +21324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA22"/>
+  <dimension ref="A1:BB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -20791,6 +21380,7 @@
     <col width="15" customWidth="1" min="51" max="51"/>
     <col width="22" customWidth="1" min="52" max="52"/>
     <col width="48" customWidth="1" min="53" max="53"/>
+    <col width="13" customWidth="1" min="54" max="54"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21059,6 +21649,11 @@
           <t>dps_source</t>
         </is>
       </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>cost_source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21213,6 +21808,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21362,6 +21962,11 @@
       <c r="BA3" t="inlineStr">
         <is>
           <t>basic attack</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
@@ -21518,6 +22123,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -21672,6 +22282,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21821,6 +22436,11 @@
       <c r="BA6" t="inlineStr">
         <is>
           <t>basic attack</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
@@ -21972,6 +22592,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22121,6 +22746,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22270,6 +22900,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22424,6 +23059,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -22604,6 +23244,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -22755,6 +23400,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -22904,6 +23554,11 @@
       <c r="BA13" t="inlineStr">
         <is>
           <t>basic attack</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
@@ -23055,6 +23710,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -23206,6 +23866,11 @@
       <c r="BA15" t="inlineStr">
         <is>
           <t>basic attack</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
@@ -23297,6 +23962,11 @@
           <t>caster: Thresh Arrow (sustained, mana-limited)</t>
         </is>
       </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -23446,6 +24116,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -23627,6 +24302,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -23773,6 +24453,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -23938,6 +24623,11 @@
       <c r="BA20" t="inlineStr">
         <is>
           <t>basic attack</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
@@ -24058,7 +24748,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BA22"/>
+  <autoFilter ref="A1:BB22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -40060,16 +40750,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="D2" t="n">
         <v>1300</v>
       </c>
       <c r="E2" t="n">
-        <v>9.31</v>
+        <v>8.56</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -40096,16 +40786,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>5.87</v>
+        <v>5.78</v>
       </c>
       <c r="D3" t="n">
         <v>700</v>
       </c>
       <c r="E3" t="n">
-        <v>6.52</v>
+        <v>7.26</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -40128,34 +40818,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tempest</t>
+          <t>ranger</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>4.12</v>
+        <v>5.11</v>
       </c>
       <c r="D4" t="n">
-        <v>850</v>
+        <v>800</v>
       </c>
       <c r="E4" t="n">
-        <v>5.84</v>
+        <v>5.82</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jenovaroth</t>
+          <t>Noir Heart</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>800</v>
+        <v>415</v>
       </c>
       <c r="H4" t="n">
-        <v>101.08</v>
+        <v>68.42</v>
       </c>
       <c r="I4" t="n">
-        <v>21686</v>
+        <v>14924</v>
       </c>
       <c r="J4" t="n">
         <v>5</v>
@@ -40164,34 +40854,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ranger</t>
+          <t>tempest</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>5.11</v>
+        <v>4.08</v>
       </c>
       <c r="D5" t="n">
         <v>800</v>
       </c>
       <c r="E5" t="n">
-        <v>5.82</v>
+        <v>5.22</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Noir Heart</t>
+          <t>Jenovaroth</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>415</v>
+        <v>800</v>
       </c>
       <c r="H5" t="n">
-        <v>68.42</v>
+        <v>101.08</v>
       </c>
       <c r="I5" t="n">
-        <v>14924</v>
+        <v>21686</v>
       </c>
       <c r="J5" t="n">
         <v>5</v>
@@ -40240,16 +40930,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>2.47</v>
+        <v>2.05</v>
       </c>
       <c r="D7" t="n">
         <v>725</v>
       </c>
       <c r="E7" t="n">
-        <v>3.24</v>
+        <v>2.82</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -41714,7 +42404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX20"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -41767,6 +42457,7 @@
     <col width="15" customWidth="1" min="48" max="48"/>
     <col width="22" customWidth="1" min="49" max="49"/>
     <col width="14" customWidth="1" min="50" max="50"/>
+    <col width="13" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -42020,6 +42711,11 @@
           <t>dps_source</t>
         </is>
       </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>cost_source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -42154,6 +42850,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -42288,6 +42989,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -42424,6 +43130,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -42558,6 +43269,11 @@
       <c r="AX5" t="inlineStr">
         <is>
           <t>basic attack</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
@@ -42699,6 +43415,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -42843,6 +43564,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -42972,6 +43698,11 @@
       <c r="AX8" t="inlineStr">
         <is>
           <t>basic attack</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
@@ -43103,6 +43834,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -43242,6 +43978,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -43381,6 +44122,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -43515,6 +44261,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -43646,6 +44397,11 @@
       <c r="AX13" t="inlineStr">
         <is>
           <t>basic attack</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
@@ -43777,6 +44533,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -43913,6 +44674,11 @@
       <c r="AX15" t="inlineStr">
         <is>
           <t>basic attack</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
@@ -44061,6 +44827,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -44197,6 +44968,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -44363,6 +45139,11 @@
       <c r="AX18" t="inlineStr">
         <is>
           <t>basic attack</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
@@ -44496,6 +45277,11 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -44630,9 +45416,14 @@
           <t>basic attack</t>
         </is>
       </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AX20"/>
+  <autoFilter ref="A1:AY20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/skibi-data.xlsx
+++ b/skibi-data.xlsx
@@ -35,7 +35,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'bosses'!$A$1:$O$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'caster_dps'!$A$1:$L$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'game_modes'!$A$1:$I$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'hero_ranking'!$A$1:$J$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'hero_ranking'!$A$1:$K$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'heroes'!$A$1:$H$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'military'!$A$1:$AY$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'minigame_items'!$A$1:$D$22</definedName>
@@ -10877,7 +10877,7 @@
     <col width="15" customWidth="1" min="51" max="51"/>
     <col width="22" customWidth="1" min="52" max="52"/>
     <col width="48" customWidth="1" min="53" max="53"/>
-    <col width="48" customWidth="1" min="54" max="54"/>
+    <col width="13" customWidth="1" min="54" max="54"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>owner read in game 2026-09-12; the map sets no gold cost for this unit</t>
+          <t>map</t>
         </is>
       </c>
     </row>
@@ -40676,19 +40676,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="29" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="29" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -40699,45 +40700,50 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>towers</t>
+          <t>towers_scored</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>towers_total</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>median_dps_per_gold</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>median_range</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>median_coverage_adj_eff</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>best_tower</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>best_tower_cost</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>best_tower_coverage_adj_eff</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>peak_dps</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>hero_abilities</t>
         </is>
@@ -40753,29 +40759,32 @@
         <v>20</v>
       </c>
       <c r="C2" t="n">
-        <v>2.75</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E2" t="n">
         <v>1300</v>
       </c>
-      <c r="E2" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>Glacial Spike</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>935</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>45.85</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>13333</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -40789,29 +40798,32 @@
         <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>5.78</v>
+        <v>27</v>
       </c>
       <c r="D3" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="E3" t="n">
         <v>700</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>7.26</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Martyr</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>260</v>
       </c>
-      <c r="H3" t="n">
-        <v>41.27</v>
-      </c>
       <c r="I3" t="n">
-        <v>6963</v>
+        <v>41.86</v>
       </c>
       <c r="J3" t="n">
+        <v>7063</v>
+      </c>
+      <c r="K3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -40825,29 +40837,32 @@
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>5.11</v>
+        <v>19</v>
       </c>
       <c r="D4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E4" t="n">
         <v>800</v>
       </c>
-      <c r="E4" t="n">
-        <v>5.82</v>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>Noir Heart</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>415</v>
       </c>
-      <c r="H4" t="n">
-        <v>68.42</v>
-      </c>
       <c r="I4" t="n">
-        <v>14924</v>
+        <v>68.58</v>
       </c>
       <c r="J4" t="n">
+        <v>14960</v>
+      </c>
+      <c r="K4" t="n">
         <v>5</v>
       </c>
     </row>
@@ -40861,101 +40876,110 @@
         <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>4.08</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>850</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Jenovaroth</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
         <v>800</v>
       </c>
-      <c r="E5" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Jenovaroth</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>800</v>
-      </c>
-      <c r="H5" t="n">
-        <v>101.08</v>
-      </c>
       <c r="I5" t="n">
-        <v>21686</v>
+        <v>101.25</v>
       </c>
       <c r="J5" t="n">
+        <v>21722</v>
+      </c>
+      <c r="K5" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>specialist</t>
+          <t>arcane</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>4.41</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>800</v>
+        <v>2.04</v>
       </c>
       <c r="E6" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Apocalypse</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>800</v>
+        <v>1150</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fire Hydra</t>
+        </is>
       </c>
       <c r="H6" t="n">
-        <v>28.28</v>
+        <v>255</v>
       </c>
       <c r="I6" t="n">
-        <v>7036</v>
+        <v>6.41</v>
       </c>
       <c r="J6" t="n">
+        <v>1357</v>
+      </c>
+      <c r="K6" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>arcane</t>
+          <t>specialist</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>2.05</v>
+        <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>725</v>
+        <v>4.41</v>
       </c>
       <c r="E7" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Fire Hydra</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>255</v>
+        <v>800</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Apocalypse</t>
+        </is>
       </c>
       <c r="H7" t="n">
-        <v>6.41</v>
+        <v>800</v>
       </c>
       <c r="I7" t="n">
-        <v>1357</v>
+        <v>28.28</v>
       </c>
       <c r="J7" t="n">
+        <v>7036</v>
+      </c>
+      <c r="K7" t="n">
         <v>5</v>
       </c>
     </row>
@@ -40969,34 +40993,37 @@
         <v>19</v>
       </c>
       <c r="C8" t="n">
+        <v>19</v>
+      </c>
+      <c r="D8" t="n">
         <v>9.59</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>125</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>0.59</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Tamed Game</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>205</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>20.54</v>
       </c>
-      <c r="I8" t="n">
-        <v>8932</v>
-      </c>
       <c r="J8" t="n">
+        <v>9026</v>
+      </c>
+      <c r="K8" t="n">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J8"/>
+  <autoFilter ref="A1:K8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/skibi-data.xlsx
+++ b/skibi-data.xlsx
@@ -43,9 +43,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'minigames'!$A$1:$I$80</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'other_towers'!$A$1:$AW$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'ranger'!$A$1:$AV$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'royal_family'!$A$1:$BB$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'royal_family'!$A$1:$BC$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'scarlet_knight'!$A$1:$AV$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'specialist'!$A$1:$AZ$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'specialist'!$A$1:$BA$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'tempest'!$A$1:$BB$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'tower_traits'!$A$1:$I$113</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'wave_modifiers'!$A$1:$D$46</definedName>
@@ -10821,7 +10821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB28"/>
+  <dimension ref="A1:BC23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10878,6 +10878,7 @@
     <col width="22" customWidth="1" min="52" max="52"/>
     <col width="48" customWidth="1" min="53" max="53"/>
     <col width="13" customWidth="1" min="54" max="54"/>
+    <col width="21" customWidth="1" min="55" max="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11151,6 +11152,11 @@
           <t>cost_source</t>
         </is>
       </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>hand_capture_name</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11251,6 +11257,16 @@
       <c r="AJ2" t="inlineStr">
         <is>
           <t>Build Grayson's Fort Buster ( R )</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>observed</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>COSTS 1 FOOD - a THIRD resource beyond gold and tiles, capped at 5 and unlocked partway through the run. So gold is not its real cost: at 175g it is the best gold-efficiency in the kit after Odin's Soul, but you can field at most FIVE food towers all run, and it competes against every other food tower rather than against 175g of anything else. SIEGE, so 13.82 becomes 22.11 on the Fortified waves (3, 8, 13, 18). Wave-20 gated.</t>
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
@@ -11295,6 +11311,11 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>Grayson Fort Buster</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11670,6 +11691,21 @@
           <t>Build Tyr's Spirit ( W )</t>
         </is>
       </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>observed</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Unlock confirmed by the owner 2026-09-05. BOUGHT FOR THE STUN, NOT THE DAMAGE. At very rapid fire a 20% proc lands every ~1.75s and the stun lasts 1.5s, so it holds ~86% STUN UPTIME on non-hero ground units - near-permanent lockdown. Damage is a modest 3.63 range-adjusted. BASH is a named tier trait: the treant Battleship Mackinaw carries a higher one (20%, +235, 2.0s, non-boss) - same 20% chance and same shape, and its "non-boss" is the same exclusion as this one's "non-hero".</t>
+        </is>
+      </c>
       <c r="AQ5" s="2" t="n">
         <v>388</v>
       </c>
@@ -11714,6 +11750,11 @@
       <c r="BB5" t="inlineStr">
         <is>
           <t>map</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>Tyr Spirit</t>
         </is>
       </c>
     </row>
@@ -11974,6 +12015,16 @@
           <t>Build Peppy Bronzebeard ( E )</t>
         </is>
       </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>observed</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>NO CRIT - untyped damage, so its 8.33 applies on EVERY wave rather than on a schedule, unlike most elite towers here. SLOW POISON III is the headline: 260 dps and 65% slow. The 260 dps alone out-damages several whole towers (treant Machination 54 dps, hawk Lasher 74 dps), so at tier III a debuff is worth more than a cheap tower. Completes the Slow Poison curve: 4 -&gt; 36 -&gt; 260 dps, 25% -&gt; 40% -&gt; 65% slow.</t>
+        </is>
+      </c>
       <c r="AQ7" s="2" t="n">
         <v>1485</v>
       </c>
@@ -12016,6 +12067,11 @@
       <c r="BB7" t="inlineStr">
         <is>
           <t>map</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>Peepy Bronzebeard</t>
         </is>
       </c>
     </row>
@@ -12936,6 +12992,16 @@
           <t>Build Petrified Cell ( C )</t>
         </is>
       </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>observed</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>THE K-DIG LINE ENDS IN A TANK. 3.22 range-adjusted is low, but FORTITUDE is durability + splash and eff/g cannot see survivability - the same caveat as the treant Ruby Scorpion, and a tower that dies is worth 0. Note the line's arc: K-Dig (siege utility/heal) -&gt; Xavier (siege damage) -&gt; Bartlebee (stun) -&gt; Delphinus (mana + spells) -&gt; this (tank). FIVE different jobs down one line. TWO NEW TRAITS: FROST I (the treant Sewage Surprise carries an unlabelled "frost", so that is probably the same family) and FORTITUDE. FAST = RAPID confirmed by the owner 2026-09-05, so the five bands stand.</t>
+        </is>
+      </c>
       <c r="AQ13" s="2" t="n">
         <v>600</v>
       </c>
@@ -12978,6 +13044,11 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>Petrified Shell</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -14147,6 +14218,16 @@
           <t>Build Lilianna Mai ( F )</t>
         </is>
       </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>observed</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>CORRECTED 2026-09-05: damage is 1000-1455 (a normal 1.46x roll), not 100-1455. An earlier note here called it the widest spread recorded and read it as a deliberately unreliable autoattack - that was built on the typo and is WITHDRAWN. At 5.12 range-adjusted it is still modest for 850g plus a food slot, so it is still bought for its spells, but by the ordinary reading rather than a variance argument. GRAVITY WELL CORRECTED: 10% of LIFE as damage plus a 5% PERMANENT speed reduction - double the damage I first recorded, and a smaller but PERMANENT slow. "Permanent" implies it may STACK across casts, which would make it a different mechanic class from every other slow here. Worth confirming whether it stacks. DIVINE SHIELD makes the TOWER immune for 10s, the answer to the tower-destroying boss the owner flagged in their first message. Priciest Royal Family tower AND food-capped.</t>
+        </is>
+      </c>
       <c r="AQ21" s="2" t="n">
         <v>4910</v>
       </c>
@@ -14189,6 +14270,11 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>Lilliana May</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -14374,7 +14460,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tyr Spirit</t>
+          <t>Royal Base II</t>
         </is>
       </c>
       <c r="AA23" s="2" t="n"/>
@@ -14383,14 +14469,9 @@
           <t>hand capture only — no extracted counterpart</t>
         </is>
       </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>Unlock confirmed by the owner 2026-09-05. BOUGHT FOR THE STUN, NOT THE DAMAGE. At very rapid fire a 20% proc lands every ~1.75s and the stun lasts 1.5s, so it holds ~86% STUN UPTIME on non-hero ground units - near-permanent lockdown. Damage is a modest 3.63 range-adjusted. BASH is a named tier trait: the treant Battleship Mackinaw carries a higher one (20%, +235, 2.0s, non-boss) - same 20% chance and same shape, and its "non-boss" is the same exclusion as this one's "non-hero".</t>
+          <t>NOT A TOWER and not a "base tower" either - it is an upgrade purchased at the HERO SELECTION BUILDING (owner 2026-09-05). At 50g it is a pure tech gate for Peepy Bronzebeard, Cloud Buster, Lilliana May and Petrified Shell. It has no stat block to collect. The mechanism is per-hero: the Tempest Hawk has no equivalent.</t>
         </is>
       </c>
       <c r="AQ23" s="2" t="n"/>
@@ -14429,273 +14510,8 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Royal Base II</t>
-        </is>
-      </c>
-      <c r="AA24" s="2" t="n"/>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>hand capture only — no extracted counterpart</t>
-        </is>
-      </c>
-      <c r="AP24" t="inlineStr">
-        <is>
-          <t>NOT A TOWER and not a "base tower" either - it is an upgrade purchased at the HERO SELECTION BUILDING (owner 2026-09-05). At 50g it is a pure tech gate for Peepy Bronzebeard, Cloud Buster, Lilliana May and Petrified Shell. It has no stat block to collect. The mechanism is per-hero: the Tempest Hawk has no equivalent.</t>
-        </is>
-      </c>
-      <c r="AQ24" s="2" t="n"/>
-      <c r="AR24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS24" s="2">
-        <f>AQ24*AR24</f>
-        <v/>
-      </c>
-      <c r="AT24" s="3">
-        <f>IF(D24=0,"",AY24/D24)</f>
-        <v/>
-      </c>
-      <c r="AU24" s="3">
-        <f>(N24/725)^2</f>
-        <v/>
-      </c>
-      <c r="AV24" s="3">
-        <f>IF(D24=0,"",AT24*AU24)</f>
-        <v/>
-      </c>
-      <c r="AW24" s="2" t="n"/>
-      <c r="AX24" s="2" t="n"/>
-      <c r="AY24" s="2">
-        <f>AS24+N(AW24)+N(AX24)</f>
-        <v/>
-      </c>
-      <c r="AZ24" s="3">
-        <f>IF(D24=0,"",AT24*(N24/725))</f>
-        <v/>
-      </c>
-      <c r="BA24" t="inlineStr">
-        <is>
-          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Peepy Bronzebeard</t>
-        </is>
-      </c>
-      <c r="AA25" s="2" t="n"/>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>hand capture only — no extracted counterpart</t>
-        </is>
-      </c>
-      <c r="AP25" t="inlineStr">
-        <is>
-          <t>NO CRIT - untyped damage, so its 8.33 applies on EVERY wave rather than on a schedule, unlike most elite towers here. SLOW POISON III is the headline: 260 dps and 65% slow. The 260 dps alone out-damages several whole towers (treant Machination 54 dps, hawk Lasher 74 dps), so at tier III a debuff is worth more than a cheap tower. Completes the Slow Poison curve: 4 -&gt; 36 -&gt; 260 dps, 25% -&gt; 40% -&gt; 65% slow.</t>
-        </is>
-      </c>
-      <c r="AQ25" s="2" t="n"/>
-      <c r="AR25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS25" s="2">
-        <f>AQ25*AR25</f>
-        <v/>
-      </c>
-      <c r="AT25" s="3">
-        <f>IF(D25=0,"",AY25/D25)</f>
-        <v/>
-      </c>
-      <c r="AU25" s="3">
-        <f>(N25/725)^2</f>
-        <v/>
-      </c>
-      <c r="AV25" s="3">
-        <f>IF(D25=0,"",AT25*AU25)</f>
-        <v/>
-      </c>
-      <c r="AW25" s="2" t="n"/>
-      <c r="AX25" s="2" t="n"/>
-      <c r="AY25" s="2">
-        <f>AS25+N(AW25)+N(AX25)</f>
-        <v/>
-      </c>
-      <c r="AZ25" s="3">
-        <f>IF(D25=0,"",AT25*(N25/725))</f>
-        <v/>
-      </c>
-      <c r="BA25" t="inlineStr">
-        <is>
-          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Grayson Fort Buster</t>
-        </is>
-      </c>
-      <c r="AA26" s="2" t="n"/>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>hand capture only — no extracted counterpart</t>
-        </is>
-      </c>
-      <c r="AP26" t="inlineStr">
-        <is>
-          <t>COSTS 1 FOOD - a THIRD resource beyond gold and tiles, capped at 5 and unlocked partway through the run. So gold is not its real cost: at 175g it is the best gold-efficiency in the kit after Odin's Soul, but you can field at most FIVE food towers all run, and it competes against every other food tower rather than against 175g of anything else. SIEGE, so 13.82 becomes 22.11 on the Fortified waves (3, 8, 13, 18). Wave-20 gated.</t>
-        </is>
-      </c>
-      <c r="AQ26" s="2" t="n"/>
-      <c r="AR26" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS26" s="2">
-        <f>AQ26*AR26</f>
-        <v/>
-      </c>
-      <c r="AT26" s="3">
-        <f>IF(D26=0,"",AY26/D26)</f>
-        <v/>
-      </c>
-      <c r="AU26" s="3">
-        <f>(N26/725)^2</f>
-        <v/>
-      </c>
-      <c r="AV26" s="3">
-        <f>IF(D26=0,"",AT26*AU26)</f>
-        <v/>
-      </c>
-      <c r="AW26" s="2" t="n"/>
-      <c r="AX26" s="2" t="n"/>
-      <c r="AY26" s="2">
-        <f>AS26+N(AW26)+N(AX26)</f>
-        <v/>
-      </c>
-      <c r="AZ26" s="3">
-        <f>IF(D26=0,"",AT26*(N26/725))</f>
-        <v/>
-      </c>
-      <c r="BA26" t="inlineStr">
-        <is>
-          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Lilliana May</t>
-        </is>
-      </c>
-      <c r="AA27" s="2" t="n"/>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>hand capture only — no extracted counterpart</t>
-        </is>
-      </c>
-      <c r="AP27" t="inlineStr">
-        <is>
-          <t>CORRECTED 2026-09-05: damage is 1000-1455 (a normal 1.46x roll), not 100-1455. An earlier note here called it the widest spread recorded and read it as a deliberately unreliable autoattack - that was built on the typo and is WITHDRAWN. At 5.12 range-adjusted it is still modest for 850g plus a food slot, so it is still bought for its spells, but by the ordinary reading rather than a variance argument. GRAVITY WELL CORRECTED: 10% of LIFE as damage plus a 5% PERMANENT speed reduction - double the damage I first recorded, and a smaller but PERMANENT slow. "Permanent" implies it may STACK across casts, which would make it a different mechanic class from every other slow here. Worth confirming whether it stacks. DIVINE SHIELD makes the TOWER immune for 10s, the answer to the tower-destroying boss the owner flagged in their first message. Priciest Royal Family tower AND food-capped.</t>
-        </is>
-      </c>
-      <c r="AQ27" s="2" t="n"/>
-      <c r="AR27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS27" s="2">
-        <f>AQ27*AR27</f>
-        <v/>
-      </c>
-      <c r="AT27" s="3">
-        <f>IF(D27=0,"",AY27/D27)</f>
-        <v/>
-      </c>
-      <c r="AU27" s="3">
-        <f>(N27/725)^2</f>
-        <v/>
-      </c>
-      <c r="AV27" s="3">
-        <f>IF(D27=0,"",AT27*AU27)</f>
-        <v/>
-      </c>
-      <c r="AW27" s="2" t="n"/>
-      <c r="AX27" s="2" t="n"/>
-      <c r="AY27" s="2">
-        <f>AS27+N(AW27)+N(AX27)</f>
-        <v/>
-      </c>
-      <c r="AZ27" s="3">
-        <f>IF(D27=0,"",AT27*(N27/725))</f>
-        <v/>
-      </c>
-      <c r="BA27" t="inlineStr">
-        <is>
-          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Petrified Shell</t>
-        </is>
-      </c>
-      <c r="AA28" s="2" t="n"/>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>hand capture only — no extracted counterpart</t>
-        </is>
-      </c>
-      <c r="AP28" t="inlineStr">
-        <is>
-          <t>THE K-DIG LINE ENDS IN A TANK. 3.22 range-adjusted is low, but FORTITUDE is durability + splash and eff/g cannot see survivability - the same caveat as the treant Ruby Scorpion, and a tower that dies is worth 0. Note the line's arc: K-Dig (siege utility/heal) -&gt; Xavier (siege damage) -&gt; Bartlebee (stun) -&gt; Delphinus (mana + spells) -&gt; this (tank). FIVE different jobs down one line. TWO NEW TRAITS: FROST I (the treant Sewage Surprise carries an unlabelled "frost", so that is probably the same family) and FORTITUDE. FAST = RAPID confirmed by the owner 2026-09-05, so the five bands stand.</t>
-        </is>
-      </c>
-      <c r="AQ28" s="2" t="n"/>
-      <c r="AR28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS28" s="2">
-        <f>AQ28*AR28</f>
-        <v/>
-      </c>
-      <c r="AT28" s="3">
-        <f>IF(D28=0,"",AY28/D28)</f>
-        <v/>
-      </c>
-      <c r="AU28" s="3">
-        <f>(N28/725)^2</f>
-        <v/>
-      </c>
-      <c r="AV28" s="3">
-        <f>IF(D28=0,"",AT28*AU28)</f>
-        <v/>
-      </c>
-      <c r="AW28" s="2" t="n"/>
-      <c r="AX28" s="2" t="n"/>
-      <c r="AY28" s="2">
-        <f>AS28+N(AW28)+N(AX28)</f>
-        <v/>
-      </c>
-      <c r="AZ28" s="3">
-        <f>IF(D28=0,"",AT28*(N28/725))</f>
-        <v/>
-      </c>
-      <c r="BA28" t="inlineStr">
-        <is>
-          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BB28"/>
+  <autoFilter ref="A1:BC23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17808,7 +17624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:BA23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -17863,6 +17679,7 @@
     <col width="22" customWidth="1" min="50" max="50"/>
     <col width="48" customWidth="1" min="51" max="51"/>
     <col width="13" customWidth="1" min="52" max="52"/>
+    <col width="19" customWidth="1" min="53" max="53"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18126,6 +17943,11 @@
           <t>cost_source</t>
         </is>
       </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>hand_capture_name</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18704,6 +18526,21 @@
           <t>U pgrade to Gigas Spike</t>
         </is>
       </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>observed</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SIEGE (owner 2026-09-06) - note its BASE Spike Shooter is CHAOS, so this upgrade CHANGES type, the second confirmed case after Sewer Barge -&gt; Sewage Surprise. 4.95 becomes 7.92 on Fortified. RESOLVED 2026-09-05: the trait is named "Boss Assassin" but TARGETS HEROES - the owner read "boss assassin II (50% x8 against heroes)" on a Royal Family tower. So the earlier boss-vs-hero ambiguity was the GAME conflating them, not a transcription slip. Both readings were right. Upgrade of Spike Shooter. Keeps the anti-boss crit - 'same passive against boss', confirmed by the owner checking Giga Spikes directly (2026-09-03). Range jumps 600-&gt;900. </t>
+        </is>
+      </c>
       <c r="AO5" s="2" t="n">
         <v>477.8</v>
       </c>
@@ -18746,6 +18583,11 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>Giga Spikes</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21204,7 +21046,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Giga Spikes</t>
+          <t>Specialist Base</t>
         </is>
       </c>
       <c r="AA23" s="2" t="n"/>
@@ -21213,14 +21055,9 @@
           <t>hand capture only — no extracted counterpart</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>D4</t>
-        </is>
-      </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t xml:space="preserve">SIEGE (owner 2026-09-06) - note its BASE Spike Shooter is CHAOS, so this upgrade CHANGES type, the second confirmed case after Sewer Barge -&gt; Sewage Surprise. 4.95 becomes 7.92 on Fortified. RESOLVED 2026-09-05: the trait is named "Boss Assassin" but TARGETS HEROES - the owner read "boss assassin II (50% x8 against heroes)" on a Royal Family tower. So the earlier boss-vs-hero ambiguity was the GAME conflating them, not a transcription slip. Both readings were right. Upgrade of Spike Shooter. Keeps the anti-boss crit - 'same passive against boss', confirmed by the owner checking Giga Spikes directly (2026-09-03). Range jumps 600-&gt;900. </t>
+          <t>THE TREANT HAS A BASE UPGRADE TOO. Analogous to the Royal Family's Royal Base II, which is bought at the hero-selection building. So base upgrades are present in 2 of 3 captured kits - the Tempest Hawk, which has none, is the exception. Cost and purchase location unread.</t>
         </is>
       </c>
       <c r="AO23" s="2" t="n"/>
@@ -21259,61 +21096,8 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Specialist Base</t>
-        </is>
-      </c>
-      <c r="AA24" s="2" t="n"/>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>hand capture only — no extracted counterpart</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>THE TREANT HAS A BASE UPGRADE TOO. Analogous to the Royal Family's Royal Base II, which is bought at the hero-selection building. So base upgrades are present in 2 of 3 captured kits - the Tempest Hawk, which has none, is the exception. Cost and purchase location unread.</t>
-        </is>
-      </c>
-      <c r="AO24" s="2" t="n"/>
-      <c r="AP24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ24" s="2">
-        <f>AO24*AP24</f>
-        <v/>
-      </c>
-      <c r="AR24" s="3">
-        <f>IF(D24=0,"",AW24/D24)</f>
-        <v/>
-      </c>
-      <c r="AS24" s="3">
-        <f>(N24/725)^2</f>
-        <v/>
-      </c>
-      <c r="AT24" s="3">
-        <f>IF(D24=0,"",AR24*AS24)</f>
-        <v/>
-      </c>
-      <c r="AU24" s="2" t="n"/>
-      <c r="AV24" s="2" t="n"/>
-      <c r="AW24" s="2">
-        <f>AQ24+N(AU24)+N(AV24)</f>
-        <v/>
-      </c>
-      <c r="AX24" s="3">
-        <f>IF(D24=0,"",AR24*(N24/725))</f>
-        <v/>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AZ24"/>
+  <autoFilter ref="A1:BA23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -40798,7 +40582,7 @@
         <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
         <v>5.88</v>
@@ -40954,7 +40738,7 @@
         <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
         <v>4.41</v>

--- a/skibi-data.xlsx
+++ b/skibi-data.xlsx
@@ -41,12 +41,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'minigame_items'!$A$1:$D$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'minigame_readings'!$A$1:$G$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'minigames'!$A$1:$I$80</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'other_towers'!$A$1:$AW$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'other_towers'!$A$1:$AW$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'ranger'!$A$1:$AV$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'royal_family'!$A$1:$BC$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'scarlet_knight'!$A$1:$AV$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'specialist'!$A$1:$BA$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'tempest'!$A$1:$BB$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'specialist'!$A$1:$BA$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'tempest'!$A$1:$BB$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'tower_traits'!$A$1:$I$113</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'wave_modifiers'!$A$1:$D$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'wave_traits'!$A$1:$K$51</definedName>
@@ -5642,11 +5642,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW15"/>
+  <dimension ref="A1:AW11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
@@ -5678,9 +5678,9 @@
     <col width="9" customWidth="1" min="31" max="31"/>
     <col width="26" customWidth="1" min="32" max="32"/>
     <col width="35" customWidth="1" min="33" max="33"/>
-    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="9" customWidth="1" min="34" max="34"/>
     <col width="17" customWidth="1" min="35" max="35"/>
-    <col width="48" customWidth="1" min="36" max="36"/>
+    <col width="11" customWidth="1" min="36" max="36"/>
     <col width="48" customWidth="1" min="37" max="37"/>
     <col width="9" customWidth="1" min="38" max="38"/>
     <col width="17" customWidth="1" min="39" max="39"/>
@@ -5946,60 +5946,55 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>h04H</t>
+          <t>h04I</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Brahma's Fix-it Shop</t>
+          <t>Equipped Peasant 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>175</v>
+        <v>19</v>
       </c>
       <c r="G2" t="n">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="H2" t="n">
-        <v>175</v>
+        <v>20</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J2" t="n">
-        <v>116.7</v>
+        <v>33.3</v>
       </c>
       <c r="K2" t="n">
-        <v>1100</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>siege</t>
-        </is>
+        <v>125</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>missile</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>174</v>
+        <v>18</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>siege</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -6008,31 +6003,26 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="2" t="n">
-        <v>1500</v>
+        <v>1250</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>A03Y,A070,AChv,A028</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>Up g rade to Brahma's Fix-it Shop</t>
+          <t>A03C,A028</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Machine Critical Strike (A03Y); Super Regeneration (A070); Empathic Fix (AChv); Sell Tower (A028)</t>
+          <t>Vindicator II (A03C); Sell Tower (A028)</t>
         </is>
       </c>
       <c r="AL2" s="2" t="n">
-        <v>116.7</v>
+        <v>33.3</v>
       </c>
       <c r="AM2" s="3" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="AN2" s="2">
         <f>AL2*AM2</f>
@@ -6074,12 +6064,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>h04I</t>
+          <t>h03P</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Equipped Peasant 1</t>
+          <t>Equipped Peasant 2</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -6089,19 +6079,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" t="n">
+        <v>22</v>
+      </c>
+      <c r="H3" t="n">
         <v>21</v>
-      </c>
-      <c r="H3" t="n">
-        <v>20</v>
       </c>
       <c r="I3" t="n">
         <v>0.6</v>
       </c>
       <c r="J3" t="n">
-        <v>33.3</v>
+        <v>35</v>
       </c>
       <c r="K3" t="n">
         <v>125</v>
@@ -6112,7 +6102,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -6134,20 +6124,20 @@
         <v>0</v>
       </c>
       <c r="AE3" s="2" t="n">
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>A03C,A028</t>
+          <t>A03C,A004,A028</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Vindicator II (A03C); Sell Tower (A028)</t>
+          <t>Vindicator II (A03C); Versatile Critical Strike I (A004); Sell Tower (A028)</t>
         </is>
       </c>
       <c r="AL3" s="2" t="n">
-        <v>33.3</v>
+        <v>35</v>
       </c>
       <c r="AM3" s="3" t="n">
         <v>3.5</v>
@@ -6192,12 +6182,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>h03P</t>
+          <t>h04O</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Equipped Peasant 2</t>
+          <t>Equipped Peasant 3</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -6207,19 +6197,19 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I4" t="n">
         <v>0.6</v>
       </c>
       <c r="J4" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K4" t="n">
         <v>125</v>
@@ -6230,13 +6220,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -6249,23 +6239,23 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" s="2" t="n">
-        <v>1500</v>
+        <v>1750</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>A03C,A004,A028</t>
+          <t>A03C,A01E,A028</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Vindicator II (A03C); Versatile Critical Strike I (A004); Sell Tower (A028)</t>
+          <t>Vindicator II (A03C); Versatile Critical Strike II (A01E); Sell Tower (A028)</t>
         </is>
       </c>
       <c r="AL4" s="2" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="AM4" s="3" t="n">
         <v>3.5</v>
@@ -6310,12 +6300,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>h04O</t>
+          <t>h04P</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Equipped Peasant 3</t>
+          <t>Equipped Peasant 4</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6325,19 +6315,19 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G5" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H5" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I5" t="n">
         <v>0.6</v>
       </c>
       <c r="J5" t="n">
-        <v>40</v>
+        <v>46.7</v>
       </c>
       <c r="K5" t="n">
         <v>125</v>
@@ -6348,13 +6338,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -6367,26 +6357,26 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE5" s="2" t="n">
-        <v>1750</v>
+        <v>2000</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>A03C,A01E,A028</t>
+          <t>A02Z,A01E,A028</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Vindicator II (A03C); Versatile Critical Strike II (A01E); Sell Tower (A028)</t>
+          <t>Vindicator III (A02Z); Versatile Critical Strike II (A01E); Sell Tower (A028)</t>
         </is>
       </c>
       <c r="AL5" s="2" t="n">
-        <v>40</v>
+        <v>46.7</v>
       </c>
       <c r="AM5" s="3" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="AN5" s="2">
         <f>AL5*AM5</f>
@@ -6428,12 +6418,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>h04P</t>
+          <t>h04Q</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Equipped Peasant 4</t>
+          <t>Equipped Peasant 5</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -6443,19 +6433,19 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="G6" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="H6" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="I6" t="n">
         <v>0.6</v>
       </c>
       <c r="J6" t="n">
-        <v>46.7</v>
+        <v>71.7</v>
       </c>
       <c r="K6" t="n">
         <v>125</v>
@@ -6466,13 +6456,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -6485,23 +6475,23 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>2000</v>
+        <v>2250</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>A02Z,A01E,A028</t>
+          <t>ANbh,A02Z,A01E,A028</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Vindicator III (A02Z); Versatile Critical Strike II (A01E); Sell Tower (A028)</t>
+          <t>Bash I (ANbh); Vindicator III (A02Z); Versatile Critical Strike II (A01E); Sell Tower (A028)</t>
         </is>
       </c>
       <c r="AL6" s="2" t="n">
-        <v>46.7</v>
+        <v>71.7</v>
       </c>
       <c r="AM6" s="3" t="n">
         <v>5.5</v>
@@ -6510,7 +6500,9 @@
         <f>AL6*AM6</f>
         <v/>
       </c>
-      <c r="AO6" s="2" t="n"/>
+      <c r="AO6" s="2" t="n">
+        <v>16.7</v>
+      </c>
       <c r="AP6" s="2" t="n"/>
       <c r="AQ6" s="2">
         <f>AN6+N(AO6)+N(AP6)</f>
@@ -6546,55 +6538,60 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>h04Q</t>
+          <t>h00R</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Equipped Peasant 5</t>
+          <t>Exiled Soul</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="G7" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="H7" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J7" t="n">
-        <v>71.7</v>
+        <v>280</v>
       </c>
       <c r="K7" t="n">
-        <v>125</v>
+        <v>600</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>missile</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>chaos</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -6603,34 +6600,37 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE7" s="2" t="n">
-        <v>2250</v>
+        <v>1500</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>ANbh,A02Z,A01E,A028</t>
+          <t>A03W,A028,Afra</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Up g rade to Exiled Soul</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Bash I (ANbh); Vindicator III (A02Z); Versatile Critical Strike II (A01E); Sell Tower (A028)</t>
+          <t>Regeneration (A03W); Sell Tower (A028); Frost I (Afra)</t>
         </is>
       </c>
       <c r="AL7" s="2" t="n">
-        <v>71.7</v>
+        <v>280</v>
       </c>
       <c r="AM7" s="3" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="AN7" s="2">
         <f>AL7*AM7</f>
         <v/>
       </c>
-      <c r="AO7" s="2" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="AO7" s="2" t="n"/>
       <c r="AP7" s="2" t="n"/>
       <c r="AQ7" s="2">
         <f>AN7+N(AO7)+N(AP7)</f>
@@ -6666,60 +6666,55 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>h00R</t>
+          <t>h00H</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Exiled Soul</t>
+          <t>Footman</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="G8" t="n">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="H8" t="n">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J8" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="K8" t="n">
-        <v>600</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>chaos</t>
-        </is>
+        <v>125</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>missile</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>chaos</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -6728,28 +6723,28 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="2" t="n">
-        <v>1500</v>
+        <v>1250</v>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>A03W,A028,Afra</t>
+          <t>ANbh,A028</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>Up g rade to Exiled Soul</t>
+          <t>U pgrade to Footman</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Regeneration (A03W); Sell Tower (A028); Frost I (Afra)</t>
+          <t>Bash I (ANbh); Sell Tower (A028)</t>
         </is>
       </c>
       <c r="AL8" s="2" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AM8" s="3" t="n">
         <v>1</v>
@@ -6758,7 +6753,9 @@
         <f>AL8*AM8</f>
         <v/>
       </c>
-      <c r="AO8" s="2" t="n"/>
+      <c r="AO8" s="2" t="n">
+        <v>33.3</v>
+      </c>
       <c r="AP8" s="2" t="n"/>
       <c r="AQ8" s="2">
         <f>AN8+N(AO8)+N(AP8)</f>
@@ -6794,60 +6791,60 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>h01J</t>
+          <t>h03O</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Father Dragon</t>
+          <t>Heartseeker</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>298</v>
+        <v>23</v>
       </c>
       <c r="G9" t="n">
-        <v>298</v>
+        <v>28</v>
       </c>
       <c r="H9" t="n">
-        <v>298</v>
+        <v>25.5</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
-        <v>425.7</v>
+        <v>51</v>
       </c>
       <c r="K9" t="n">
-        <v>600</v>
+        <v>1150</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>magic</t>
+          <t>chaos</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>missile</t>
+          <t>instant</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>297</v>
+        <v>22</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>magic</t>
+          <t>chaos</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -6863,48 +6860,31 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>A03D,A028,A006,A008</t>
+          <t>Afbb,Aabr,AIva,A01E,A028</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>U pgrade to Father Dragon</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>tempest</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AIR CRITICAL STRIKE II identified 2026-09-05 (the Royal Family named the tier: 50% x4). RESOLVED 2026-09-05: the trait is named "Boss Assassin" but TARGETS HEROES - the owner read "boss assassin II (50% x8 against heroes)" on a Royal Family tower. So the earlier boss-vs-hero ambiguity was the GAME conflating them, not a transcription slip. Both readings were right. DUAL crit (air AND boss) at 50% x4 each. 16.78 range-adjusted against either. Its 600 range is short for the kit. </t>
+          <t>U pgrade to Heartseeker</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Boss Assassin I (A03D); Sell Tower (A028); Air Critical Strike II (A006); Slow Poison II (A008)</t>
+          <t>Sunder Armor (Afbb); (Dummy Ability - Life Steal) (Aabr); AIva (AIva); Versatile Critical Strike II (A01E); Sell Tower (A028)</t>
         </is>
       </c>
       <c r="AL9" s="2" t="n">
-        <v>425.7</v>
+        <v>51</v>
       </c>
       <c r="AM9" s="3" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AN9" s="2">
         <f>AL9*AM9</f>
         <v/>
       </c>
       <c r="AO9" s="2" t="n"/>
-      <c r="AP9" s="2" t="n">
-        <v>36</v>
-      </c>
+      <c r="AP9" s="2" t="n"/>
       <c r="AQ9" s="2">
         <f>AN9+N(AO9)+N(AP9)</f>
         <v/>
@@ -6939,55 +6919,63 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>h00H</t>
+          <t>h048</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Footman</t>
+          <t>Krotas</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>45</v>
+        <v>1325</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
       <c r="F10" t="n">
-        <v>85</v>
+        <v>851</v>
       </c>
       <c r="G10" t="n">
-        <v>89</v>
+        <v>858</v>
       </c>
       <c r="H10" t="n">
-        <v>87</v>
+        <v>854.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="J10" t="n">
-        <v>290</v>
+        <v>2589.4</v>
       </c>
       <c r="K10" t="n">
-        <v>125</v>
+        <v>1500</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>missile</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>84</v>
+        <v>850</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>chaos</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -6995,40 +6983,35 @@
           <t>hhou</t>
         </is>
       </c>
-      <c r="AD10" t="n">
-        <v>1</v>
-      </c>
       <c r="AE10" s="2" t="n">
-        <v>1250</v>
+        <v>2500</v>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>ANbh,A028</t>
+          <t>ANcl,A004,A02X,A014,A028</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>U pgrade to Footman</t>
+          <t>Up g rade to Krotas - 1325</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Bash I (ANbh); Sell Tower (A028)</t>
+          <t>Activate / Deactivate Mana Detection (ANcl); Versatile Critical Strike I (A004); Gooify (A02X); Combustion (A014); Sell Tower (A028)</t>
         </is>
       </c>
       <c r="AL10" s="2" t="n">
-        <v>290</v>
+        <v>2589.4</v>
       </c>
       <c r="AM10" s="3" t="n">
-        <v>1</v>
+        <v>1.52</v>
       </c>
       <c r="AN10" s="2">
         <f>AL10*AM10</f>
         <v/>
       </c>
-      <c r="AO10" s="2" t="n">
-        <v>33.3</v>
-      </c>
+      <c r="AO10" s="2" t="n"/>
       <c r="AP10" s="2" t="n"/>
       <c r="AQ10" s="2">
         <f>AN10+N(AO10)+N(AP10)</f>
@@ -7064,34 +7047,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>h03O</t>
+          <t>h047</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Heartseeker</t>
+          <t>Von Chillspeak</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>45</v>
+        <v>1225</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
       <c r="F11" t="n">
-        <v>23</v>
+        <v>12000</v>
       </c>
       <c r="G11" t="n">
-        <v>28</v>
+        <v>12000</v>
       </c>
       <c r="H11" t="n">
-        <v>25.5</v>
+        <v>12000</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>51</v>
+        <v>6000</v>
       </c>
       <c r="K11" t="n">
         <v>1150</v>
@@ -7103,17 +7089,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>instant</t>
+          <t>missile</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>22</v>
+        <v>11999</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -7125,39 +7111,38 @@
           <t>hhou</t>
         </is>
       </c>
-      <c r="AD11" t="n">
-        <v>2</v>
-      </c>
       <c r="AE11" s="2" t="n">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>Afbb,Aabr,AIva,A01E,A028</t>
+          <t>ANcl,Afrz,Aap1,AIm2,A028</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>U pgrade to Heartseeker</t>
+          <t>U pgrade to Von Chillspeak - 1225</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Sunder Armor (Afbb); (Dummy Ability - Life Steal) (Aabr); AIva (AIva); Versatile Critical Strike II (A01E); Sell Tower (A028)</t>
+          <t>Activate / Deactivate Mana Detection (ANcl); Stone Cold (Afrz); Grounding Curse (Aap1); Cold Snap (AIm2); Sell Tower (A028)</t>
         </is>
       </c>
       <c r="AL11" s="2" t="n">
-        <v>51</v>
+        <v>6000</v>
       </c>
       <c r="AM11" s="3" t="n">
-        <v>2.05</v>
+        <v>1</v>
       </c>
       <c r="AN11" s="2">
         <f>AL11*AM11</f>
         <v/>
       </c>
       <c r="AO11" s="2" t="n"/>
-      <c r="AP11" s="2" t="n"/>
+      <c r="AP11" s="2" t="n">
+        <v>1000</v>
+      </c>
       <c r="AQ11" s="2">
         <f>AN11+N(AO11)+N(AP11)</f>
         <v/>
@@ -7189,552 +7174,8 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>h048</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Krotas</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>1325</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>851</v>
-      </c>
-      <c r="G12" t="n">
-        <v>858</v>
-      </c>
-      <c r="H12" t="n">
-        <v>854.5</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2589.4</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1500</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>chaos</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>missile</t>
-        </is>
-      </c>
-      <c r="N12" t="n">
-        <v>850</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1</v>
-      </c>
-      <c r="P12" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>chaos</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>hhou</t>
-        </is>
-      </c>
-      <c r="AE12" s="2" t="n">
-        <v>2500</v>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>ANcl,A004,A02X,A014,A028</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>Up g rade to Krotas - 1325</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Activate / Deactivate Mana Detection (ANcl); Versatile Critical Strike I (A004); Gooify (A02X); Combustion (A014); Sell Tower (A028)</t>
-        </is>
-      </c>
-      <c r="AL12" s="2" t="n">
-        <v>2589.4</v>
-      </c>
-      <c r="AM12" s="3" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AN12" s="2">
-        <f>AL12*AM12</f>
-        <v/>
-      </c>
-      <c r="AO12" s="2" t="n"/>
-      <c r="AP12" s="2" t="n"/>
-      <c r="AQ12" s="2">
-        <f>AN12+N(AO12)+N(AP12)</f>
-        <v/>
-      </c>
-      <c r="AR12" s="3">
-        <f>IF(C12=0,"",AQ12/C12)</f>
-        <v/>
-      </c>
-      <c r="AS12" s="3">
-        <f>IF(C12=0,"",AR12*(K12/725))</f>
-        <v/>
-      </c>
-      <c r="AT12" s="3">
-        <f>(K12/725)^2</f>
-        <v/>
-      </c>
-      <c r="AU12" s="3">
-        <f>IF(C12=0,"",AR12*AT12)</f>
-        <v/>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>basic attack</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>h04G</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Reaperspawn</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>50</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>287</v>
-      </c>
-      <c r="G13" t="n">
-        <v>287</v>
-      </c>
-      <c r="H13" t="n">
-        <v>287</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J13" t="n">
-        <v>358.8</v>
-      </c>
-      <c r="K13" t="n">
-        <v>125</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>chaos</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="N13" t="n">
-        <v>286</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>chaos</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>hhou</t>
-        </is>
-      </c>
-      <c r="AD13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE13" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>A006,A028,ACvp</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>Up g rade to Reaperspawn</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>tempest</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>AIR CRITICAL STRIKE II identified 2026-09-05 (the Royal Family named the tier: 50% x4). CHAOS attack type - the kit's ONLY non-magic tower. In stock WC3 chaos deals full damage to every armour type, i.e. it ignores the matrix entirely; UNVERIFIED for this map. Melee, but DOES hit air when the flyer passes directly above it (owner 2026-09-05) - so it is a positional anti-air, not a blind spot. 23.90 raw dps/gold is among the best recorded, but it is unadjustable for range and demands exact placement under the flight path.</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Air Critical Strike II (A006); Sell Tower (A028); Vampiric Aura (ACvp)</t>
-        </is>
-      </c>
-      <c r="AL13" s="2" t="n">
-        <v>358.8</v>
-      </c>
-      <c r="AM13" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AN13" s="2">
-        <f>AL13*AM13</f>
-        <v/>
-      </c>
-      <c r="AO13" s="2" t="n"/>
-      <c r="AP13" s="2" t="n"/>
-      <c r="AQ13" s="2">
-        <f>AN13+N(AO13)+N(AP13)</f>
-        <v/>
-      </c>
-      <c r="AR13" s="3">
-        <f>IF(C13=0,"",AQ13/C13)</f>
-        <v/>
-      </c>
-      <c r="AS13" s="3">
-        <f>IF(C13=0,"",AR13*(K13/725))</f>
-        <v/>
-      </c>
-      <c r="AT13" s="3">
-        <f>(K13/725)^2</f>
-        <v/>
-      </c>
-      <c r="AU13" s="3">
-        <f>IF(C13=0,"",AR13*AT13)</f>
-        <v/>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>basic attack</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>h017</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Sewage Surprise</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>105</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>246</v>
-      </c>
-      <c r="G14" t="n">
-        <v>246</v>
-      </c>
-      <c r="H14" t="n">
-        <v>246</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J14" t="n">
-        <v>289.4</v>
-      </c>
-      <c r="K14" t="n">
-        <v>800</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>magic</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>msplash</t>
-        </is>
-      </c>
-      <c r="N14" t="n">
-        <v>245</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>magic</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>hhou</t>
-        </is>
-      </c>
-      <c r="AD14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE14" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>A03Y,A021,A028,Afra</t>
-        </is>
-      </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>U pgrade to Sewage Surprise</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>specialist</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>MAGIC (owner 2026-09-06), where its BASE Sewer Barge is siege - so attack type is NOT inherited on upgrade. Consequence: the upgrade gains everywhere except FORTIFIED, where siege 160% vs magic 75% leaves the base nearly as strong as its own upgrade (8.10 vs 5.92). Upgrading is a downgrade on 1 wave in 5. THE AIR BRANCH: this is the T2 upgrade that leads to Interceptor and Arcadia. Choosing the other branch (Brahma Fix It Shop) forfeits the treant's only passive air answer on that Sewer Barge. 'crit mecha like base' - the anti-mecha crit carries.</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Machine Critical Strike (A03Y); Splash (A021); Sell Tower (A028); Frost I (Afra)</t>
-        </is>
-      </c>
-      <c r="AL14" s="2" t="n">
-        <v>289.4</v>
-      </c>
-      <c r="AM14" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AN14" s="2">
-        <f>AL14*AM14</f>
-        <v/>
-      </c>
-      <c r="AO14" s="2" t="n"/>
-      <c r="AP14" s="2" t="n"/>
-      <c r="AQ14" s="2">
-        <f>AN14+N(AO14)+N(AP14)</f>
-        <v/>
-      </c>
-      <c r="AR14" s="3">
-        <f>IF(C14=0,"",AQ14/C14)</f>
-        <v/>
-      </c>
-      <c r="AS14" s="3">
-        <f>IF(C14=0,"",AR14*(K14/725))</f>
-        <v/>
-      </c>
-      <c r="AT14" s="3">
-        <f>(K14/725)^2</f>
-        <v/>
-      </c>
-      <c r="AU14" s="3">
-        <f>IF(C14=0,"",AR14*AT14)</f>
-        <v/>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>basic attack</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>h047</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Von Chillspeak</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>1225</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>12000</v>
-      </c>
-      <c r="G15" t="n">
-        <v>12000</v>
-      </c>
-      <c r="H15" t="n">
-        <v>12000</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" t="n">
-        <v>6000</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1150</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>chaos</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>missile</t>
-        </is>
-      </c>
-      <c r="N15" t="n">
-        <v>11999</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>chaos</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>hhou</t>
-        </is>
-      </c>
-      <c r="AE15" s="2" t="n">
-        <v>2500</v>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>ANcl,Afrz,Aap1,AIm2,A028</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>U pgrade to Von Chillspeak - 1225</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Activate / Deactivate Mana Detection (ANcl); Stone Cold (Afrz); Grounding Curse (Aap1); Cold Snap (AIm2); Sell Tower (A028)</t>
-        </is>
-      </c>
-      <c r="AL15" s="2" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AM15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN15" s="2">
-        <f>AL15*AM15</f>
-        <v/>
-      </c>
-      <c r="AO15" s="2" t="n"/>
-      <c r="AP15" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AQ15" s="2">
-        <f>AN15+N(AO15)+N(AP15)</f>
-        <v/>
-      </c>
-      <c r="AR15" s="3">
-        <f>IF(C15=0,"",AQ15/C15)</f>
-        <v/>
-      </c>
-      <c r="AS15" s="3">
-        <f>IF(C15=0,"",AR15*(K15/725))</f>
-        <v/>
-      </c>
-      <c r="AT15" s="3">
-        <f>(K15/725)^2</f>
-        <v/>
-      </c>
-      <c r="AU15" s="3">
-        <f>IF(C15=0,"",AR15*AT15)</f>
-        <v/>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>basic attack</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AW15"/>
+  <autoFilter ref="A1:AW11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17624,10 +17065,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA23"/>
+  <dimension ref="A1:BA22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
@@ -17662,7 +17103,7 @@
     <col width="20" customWidth="1" min="33" max="33"/>
     <col width="11" customWidth="1" min="34" max="34"/>
     <col width="26" customWidth="1" min="35" max="35"/>
-    <col width="33" customWidth="1" min="36" max="36"/>
+    <col width="35" customWidth="1" min="36" max="36"/>
     <col width="11" customWidth="1" min="37" max="37"/>
     <col width="46" customWidth="1" min="38" max="38"/>
     <col width="17" customWidth="1" min="39" max="39"/>
@@ -17679,7 +17120,7 @@
     <col width="22" customWidth="1" min="50" max="50"/>
     <col width="48" customWidth="1" min="51" max="51"/>
     <col width="13" customWidth="1" min="52" max="52"/>
-    <col width="19" customWidth="1" min="53" max="53"/>
+    <col width="20" customWidth="1" min="53" max="53"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20930,7 +20371,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sewage Surprise</t>
+          <t>Specialist Base</t>
         </is>
       </c>
       <c r="AA21" s="2" t="n"/>
@@ -20939,14 +20380,9 @@
           <t>hand capture only — no extracted counterpart</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>MAGIC (owner 2026-09-06), where its BASE Sewer Barge is siege - so attack type is NOT inherited on upgrade. Consequence: the upgrade gains everywhere except FORTIFIED, where siege 160% vs magic 75% leaves the base nearly as strong as its own upgrade (8.10 vs 5.92). Upgrading is a downgrade on 1 wave in 5. THE AIR BRANCH: this is the T2 upgrade that leads to Interceptor and Arcadia. Choosing the other branch (Brahma Fix It Shop) forfeits the treant's only passive air answer on that Sewer Barge. 'crit mecha like base' - the anti-mecha crit carries.</t>
+          <t>THE TREANT HAS A BASE UPGRADE TOO. Analogous to the Royal Family's Royal Base II, which is bought at the hero-selection building. So base upgrades are present in 2 of 3 captured kits - the Tempest Hawk, which has none, is the exception. Cost and purchase location unread.</t>
         </is>
       </c>
       <c r="AO21" s="2" t="n"/>
@@ -20988,13 +20424,91 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Brahma Fix It Shop</t>
-        </is>
-      </c>
-      <c r="AA22" s="2" t="n"/>
+          <t>Brahma's Fix-it Shop</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>h04H</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>95</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Machine Critical Strike (A03Y); Super Regeneration (A070); Empathic Fix (AChv); Sell Tower (A028)</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>175</v>
+      </c>
+      <c r="K22" t="n">
+        <v>175</v>
+      </c>
+      <c r="L22" t="n">
+        <v>175</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1100</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>siege</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA22" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>missile</t>
+        </is>
+      </c>
+      <c r="AD22" t="n">
+        <v>174</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>siege</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>hhou</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>A03Y,A070,AChv,A028</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>Up g rade to Brahma's Fix-it Shop</t>
+        </is>
+      </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>hand capture only — no extracted counterpart</t>
+          <t>relocated</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -21007,9 +20521,11 @@
           <t>SIEGE (owner 2026-09-06) - and that sharpens the T2 fork: the air branch (Sewage Surprise) switches the line to MAGIC, while this branch KEEPS siege. So the fork is siege-stays vs magic-switch, not two arbitrary paths. Its 4.67 becomes 7.47 on Fortified. THE GENERALIST BRANCH: leads to Little Jack and Battleship Mackinaw (22.07 untyped, the kit's best all-purpose tower). The opposite branch leads to the air line. Support branch. Longest range in the captured kit (1100). 'same passive to crit unit' - target type not stated.</t>
         </is>
       </c>
-      <c r="AO22" s="2" t="n"/>
+      <c r="AO22" s="2" t="n">
+        <v>116.7</v>
+      </c>
       <c r="AP22" s="3" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="AQ22" s="2">
         <f>AO22*AP22</f>
@@ -21039,65 +20555,22 @@
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Specialist Base</t>
-        </is>
-      </c>
-      <c r="AA23" s="2" t="n"/>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>hand capture only — no extracted counterpart</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>THE TREANT HAS A BASE UPGRADE TOO. Analogous to the Royal Family's Royal Base II, which is bought at the hero-selection building. So base upgrades are present in 2 of 3 captured kits - the Tempest Hawk, which has none, is the exception. Cost and purchase location unread.</t>
-        </is>
-      </c>
-      <c r="AO23" s="2" t="n"/>
-      <c r="AP23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ23" s="2">
-        <f>AO23*AP23</f>
-        <v/>
-      </c>
-      <c r="AR23" s="3">
-        <f>IF(D23=0,"",AW23/D23)</f>
-        <v/>
-      </c>
-      <c r="AS23" s="3">
-        <f>(N23/725)^2</f>
-        <v/>
-      </c>
-      <c r="AT23" s="3">
-        <f>IF(D23=0,"",AR23*AS23)</f>
-        <v/>
-      </c>
-      <c r="AU23" s="2" t="n"/>
-      <c r="AV23" s="2" t="n"/>
-      <c r="AW23" s="2">
-        <f>AQ23+N(AU23)+N(AV23)</f>
-        <v/>
-      </c>
-      <c r="AX23" s="3">
-        <f>IF(D23=0,"",AR23*(N23/725))</f>
-        <v/>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
+          <t>basic attack</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>Brahma Fix It Shop</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BA23"/>
+  <autoFilter ref="A1:BA22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21108,7 +20581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB22"/>
+  <dimension ref="A1:BB21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -21150,7 +20623,7 @@
     <col width="11" customWidth="1" min="37" max="37"/>
     <col width="11" customWidth="1" min="38" max="38"/>
     <col width="12" customWidth="1" min="39" max="39"/>
-    <col width="46" customWidth="1" min="40" max="40"/>
+    <col width="11" customWidth="1" min="40" max="40"/>
     <col width="17" customWidth="1" min="41" max="41"/>
     <col width="48" customWidth="1" min="42" max="42"/>
     <col width="9" customWidth="1" min="43" max="43"/>
@@ -24418,13 +23891,91 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Father Dragon</t>
-        </is>
-      </c>
-      <c r="AA21" s="2" t="n"/>
+          <t>Reaperspawn</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>h04G</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>50</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Air Critical Strike II (A006); Sell Tower (A028); Vampiric Aura (ACvp)</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>287</v>
+      </c>
+      <c r="K21" t="n">
+        <v>287</v>
+      </c>
+      <c r="L21" t="n">
+        <v>287</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N21" t="n">
+        <v>125</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>358.8</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA21" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="AD21" t="n">
+        <v>286</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>chaos</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>hhou</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>A006,A028,ACvp</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>Up g rade to Reaperspawn</t>
+        </is>
+      </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>hand capture only — no extracted counterpart</t>
+          <t>relocated</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -24434,12 +23985,14 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t xml:space="preserve">AIR CRITICAL STRIKE II identified 2026-09-05 (the Royal Family named the tier: 50% x4). RESOLVED 2026-09-05: the trait is named "Boss Assassin" but TARGETS HEROES - the owner read "boss assassin II (50% x8 against heroes)" on a Royal Family tower. So the earlier boss-vs-hero ambiguity was the GAME conflating them, not a transcription slip. Both readings were right. DUAL crit (air AND boss) at 50% x4 each. 16.78 range-adjusted against either. Its 600 range is short for the kit. </t>
-        </is>
-      </c>
-      <c r="AQ21" s="2" t="n"/>
+          <t>AIR CRITICAL STRIKE II identified 2026-09-05 (the Royal Family named the tier: 50% x4). CHAOS attack type - the kit's ONLY non-magic tower. In stock WC3 chaos deals full damage to every armour type, i.e. it ignores the matrix entirely; UNVERIFIED for this map. Melee, but DOES hit air when the flyer passes directly above it (owner 2026-09-05) - so it is a positional anti-air, not a blind spot. 23.90 raw dps/gold is among the best recorded, but it is unadjustable for range and demands exact placement under the flight path.</t>
+        </is>
+      </c>
+      <c r="AQ21" s="2" t="n">
+        <v>358.8</v>
+      </c>
       <c r="AR21" s="3" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="AS21" s="2">
         <f>AQ21*AR21</f>
@@ -24469,70 +24022,17 @@
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Reaper Spawn</t>
-        </is>
-      </c>
-      <c r="AA22" s="2" t="n"/>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>hand capture only — no extracted counterpart</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>AIR CRITICAL STRIKE II identified 2026-09-05 (the Royal Family named the tier: 50% x4). CHAOS attack type - the kit's ONLY non-magic tower. In stock WC3 chaos deals full damage to every armour type, i.e. it ignores the matrix entirely; UNVERIFIED for this map. Melee, but DOES hit air when the flyer passes directly above it (owner 2026-09-05) - so it is a positional anti-air, not a blind spot. 23.90 raw dps/gold is among the best recorded, but it is unadjustable for range and demands exact placement under the flight path.</t>
-        </is>
-      </c>
-      <c r="AQ22" s="2" t="n"/>
-      <c r="AR22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS22" s="2">
-        <f>AQ22*AR22</f>
-        <v/>
-      </c>
-      <c r="AT22" s="3">
-        <f>IF(D22=0,"",AY22/D22)</f>
-        <v/>
-      </c>
-      <c r="AU22" s="3">
-        <f>(N22/725)^2</f>
-        <v/>
-      </c>
-      <c r="AV22" s="3">
-        <f>IF(D22=0,"",AT22*AU22)</f>
-        <v/>
-      </c>
-      <c r="AW22" s="2" t="n"/>
-      <c r="AX22" s="2" t="n"/>
-      <c r="AY22" s="2">
-        <f>AS22+N(AW22)+N(AX22)</f>
-        <v/>
-      </c>
-      <c r="AZ22" s="3">
-        <f>IF(D22=0,"",AT22*(N22/725))</f>
-        <v/>
-      </c>
-      <c r="BA22" t="inlineStr">
-        <is>
-          <t>no damage figure — support/on-death, or a bonus that needs a basic attack it lacks</t>
+          <t>basic attack</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BB22"/>
+  <autoFilter ref="A1:BB21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -24806,11 +24306,11 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tamed Game; Toxic Assassin; Father Dragon</t>
+          <t>Tamed Game; Toxic Assassin; Frigid Dryad</t>
         </is>
       </c>
     </row>
@@ -24871,11 +24371,11 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Axeman; Ruthless Warlord; Father Dragon</t>
+          <t>Axeman; Ruthless Warlord; Jailing Officer</t>
         </is>
       </c>
     </row>
@@ -25771,11 +25271,11 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Orobos Slave; Sewage Surprise; Frigid Dryad</t>
+          <t>Orobos Slave; Frigid Dryad; Iron Mistress</t>
         </is>
       </c>
     </row>
@@ -25861,11 +25361,11 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Brahma's Fix-it Shop; Equipped Peasant 1; Equipped Peasant 2</t>
+          <t>Equipped Peasant 1; Equipped Peasant 2; Equipped Peasant 3</t>
         </is>
       </c>
     </row>
@@ -26071,11 +25571,11 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Myrkridon Trow; Father Dragon; Hunter</t>
+          <t>Myrkridon Trow; Hunter; Jailing Officer</t>
         </is>
       </c>
     </row>
@@ -26401,11 +25901,11 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Brahma's Fix-it Shop; Sewage Surprise; Xavier</t>
+          <t>Xavier; Sewer Barge; Frankenstone</t>
         </is>
       </c>
     </row>
@@ -27096,7 +26596,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -40653,37 +40153,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tempest</t>
+          <t>arcane</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>4.2</v>
+        <v>2.04</v>
       </c>
       <c r="E5" t="n">
-        <v>850</v>
+        <v>1150</v>
       </c>
       <c r="F5" t="n">
-        <v>5.84</v>
+        <v>5.43</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Jenovaroth</t>
+          <t>Fire Hydra</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>800</v>
+        <v>255</v>
       </c>
       <c r="I5" t="n">
-        <v>101.25</v>
+        <v>6.41</v>
       </c>
       <c r="J5" t="n">
-        <v>21722</v>
+        <v>1357</v>
       </c>
       <c r="K5" t="n">
         <v>5</v>
@@ -40692,37 +40192,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>arcane</t>
+          <t>tempest</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>2.04</v>
+        <v>4.24</v>
       </c>
       <c r="E6" t="n">
-        <v>1150</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>5.43</v>
+        <v>5.22</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fire Hydra</t>
+          <t>Jenovaroth</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>255</v>
+        <v>800</v>
       </c>
       <c r="I6" t="n">
-        <v>6.41</v>
+        <v>101.25</v>
       </c>
       <c r="J6" t="n">
-        <v>1357</v>
+        <v>21722</v>
       </c>
       <c r="K6" t="n">
         <v>5</v>
@@ -40735,16 +40235,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>4.41</v>
+        <v>4.35</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>850</v>
       </c>
       <c r="F7" t="n">
         <v>5.09</v>

--- a/skibi-data.xlsx
+++ b/skibi-data.xlsx
@@ -30,23 +30,23 @@
     <sheet name="waves" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'arcane'!$A$1:$AV$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'arcane'!$A$1:$AZ$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'armour_matrix'!$A$1:$F$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'bosses'!$A$1:$O$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'caster_dps'!$A$1:$L$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'game_modes'!$A$1:$I$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'hero_ranking'!$A$1:$K$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'heroes'!$A$1:$H$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'military'!$A$1:$AY$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'military'!$A$1:$BC$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'minigame_items'!$A$1:$D$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'minigame_readings'!$A$1:$G$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'minigames'!$A$1:$I$80</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'other_towers'!$A$1:$AW$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'ranger'!$A$1:$AV$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'royal_family'!$A$1:$BC$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'scarlet_knight'!$A$1:$AV$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'specialist'!$A$1:$BA$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'tempest'!$A$1:$BB$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'ranger'!$A$1:$AZ$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'royal_family'!$A$1:$BG$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'scarlet_knight'!$A$1:$AZ$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'specialist'!$A$1:$BE$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'tempest'!$A$1:$BF$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'tower_traits'!$A$1:$I$113</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'wave_modifiers'!$A$1:$D$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'wave_traits'!$A$1:$K$51</definedName>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -514,6 +514,10 @@
     <col width="22" customWidth="1" min="46" max="46"/>
     <col width="48" customWidth="1" min="47" max="47"/>
     <col width="13" customWidth="1" min="48" max="48"/>
+    <col width="14" customWidth="1" min="49" max="49"/>
+    <col width="10" customWidth="1" min="50" max="50"/>
+    <col width="13" customWidth="1" min="51" max="51"/>
+    <col width="31" customWidth="1" min="52" max="52"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -757,6 +761,26 @@
           <t>cost_source</t>
         </is>
       </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>attack_count</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>hits_air</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>hits_ground</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>targets_all</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -839,6 +863,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -923,6 +965,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1005,6 +1065,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1089,6 +1167,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1173,6 +1269,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1255,6 +1369,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1411,6 +1543,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1493,6 +1643,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1637,6 +1805,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1781,6 +1967,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1865,6 +2069,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1949,6 +2171,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2228,7 +2468,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AV18"/>
+  <autoFilter ref="A1:AZ18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7186,7 +7426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7237,6 +7477,10 @@
     <col width="22" customWidth="1" min="46" max="46"/>
     <col width="14" customWidth="1" min="47" max="47"/>
     <col width="13" customWidth="1" min="48" max="48"/>
+    <col width="14" customWidth="1" min="49" max="49"/>
+    <col width="10" customWidth="1" min="50" max="50"/>
+    <col width="13" customWidth="1" min="51" max="51"/>
+    <col width="31" customWidth="1" min="52" max="52"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7480,6 +7724,26 @@
           <t>cost_source</t>
         </is>
       </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>attack_count</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>hits_air</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>hits_ground</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>targets_all</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7624,6 +7888,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7768,6 +8050,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7917,6 +8217,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8063,6 +8381,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8209,6 +8545,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8353,6 +8707,24 @@
       <c r="AV7" t="inlineStr">
         <is>
           <t>map</t>
+        </is>
+      </c>
+      <c r="AW7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
     </row>
@@ -8499,6 +8871,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8638,6 +9028,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8787,6 +9195,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8936,6 +9362,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9080,6 +9524,24 @@
       <c r="AV12" t="inlineStr">
         <is>
           <t>map</t>
+        </is>
+      </c>
+      <c r="AW12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
     </row>
@@ -9231,6 +9693,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9375,6 +9855,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9519,6 +10017,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9665,6 +10181,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9811,6 +10345,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9957,6 +10509,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10098,6 +10668,24 @@
       <c r="AV19" t="inlineStr">
         <is>
           <t>map</t>
+        </is>
+      </c>
+      <c r="AW19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
     </row>
@@ -10249,9 +10837,27 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AV20"/>
+  <autoFilter ref="A1:AZ20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10262,7 +10868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC23"/>
+  <dimension ref="A1:BG23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10320,6 +10926,10 @@
     <col width="48" customWidth="1" min="53" max="53"/>
     <col width="13" customWidth="1" min="54" max="54"/>
     <col width="21" customWidth="1" min="55" max="55"/>
+    <col width="14" customWidth="1" min="56" max="56"/>
+    <col width="10" customWidth="1" min="57" max="57"/>
+    <col width="13" customWidth="1" min="58" max="58"/>
+    <col width="31" customWidth="1" min="59" max="59"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10598,6 +11208,26 @@
           <t>hand_capture_name</t>
         </is>
       </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>attack_count</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>hits_air</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>hits_ground</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>targets_all</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10757,6 +11387,24 @@
           <t>Grayson Fort Buster</t>
         </is>
       </c>
+      <c r="BD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10911,6 +11559,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11030,6 +11696,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BD4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11196,6 +11880,24 @@
       <c r="BC5" t="inlineStr">
         <is>
           <t>Tyr Spirit</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
     </row>
@@ -11357,6 +12059,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11513,6 +12233,24 @@
       <c r="BC7" t="inlineStr">
         <is>
           <t>Peepy Bronzebeard</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
     </row>
@@ -11701,6 +12439,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BD8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11855,6 +12611,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BD9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12014,6 +12788,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BD10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12170,6 +12962,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BD11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12324,6 +13134,24 @@
       <c r="BB12" t="inlineStr">
         <is>
           <t>map</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
     </row>
@@ -12490,6 +13318,24 @@
           <t>Petrified Shell</t>
         </is>
       </c>
+      <c r="BD13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12644,6 +13490,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BD14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12803,6 +13667,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BD15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -12962,6 +13844,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BD16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13111,6 +14011,24 @@
       <c r="BB17" t="inlineStr">
         <is>
           <t>map</t>
+        </is>
+      </c>
+      <c r="BD17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
     </row>
@@ -13262,6 +14180,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BD18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -13408,6 +14344,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BD19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -13557,6 +14511,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BD20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -13716,6 +14688,24 @@
           <t>Lilliana May</t>
         </is>
       </c>
+      <c r="BD21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -13897,6 +14887,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BD22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -13952,7 +14960,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BC23"/>
+  <autoFilter ref="A1:BG23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13963,7 +14971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -14014,6 +15022,10 @@
     <col width="22" customWidth="1" min="46" max="46"/>
     <col width="48" customWidth="1" min="47" max="47"/>
     <col width="13" customWidth="1" min="48" max="48"/>
+    <col width="14" customWidth="1" min="49" max="49"/>
+    <col width="10" customWidth="1" min="50" max="50"/>
+    <col width="13" customWidth="1" min="51" max="51"/>
+    <col width="31" customWidth="1" min="52" max="52"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14257,6 +15269,26 @@
           <t>cost_source</t>
         </is>
       </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>attack_count</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>hits_air</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>hits_ground</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>targets_all</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14396,6 +15428,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14535,6 +15585,24 @@
       <c r="AV3" t="inlineStr">
         <is>
           <t>map</t>
+        </is>
+      </c>
+      <c r="AW3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
     </row>
@@ -14686,6 +15754,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14775,6 +15861,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14924,6 +16028,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15073,6 +16195,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15212,6 +16352,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15356,6 +16514,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15505,6 +16681,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15654,6 +16848,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15743,6 +16955,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15887,6 +17117,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16033,6 +17281,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -16179,6 +17445,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -16328,6 +17612,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -16477,6 +17779,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -16621,6 +17941,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -16762,6 +18100,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -16906,6 +18262,24 @@
       <c r="AV20" t="inlineStr">
         <is>
           <t>map</t>
+        </is>
+      </c>
+      <c r="AW20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
     </row>
@@ -17052,9 +18426,27 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AW21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AV21"/>
+  <autoFilter ref="A1:AZ21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17065,7 +18457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA22"/>
+  <dimension ref="A1:BE22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17121,6 +18513,10 @@
     <col width="48" customWidth="1" min="51" max="51"/>
     <col width="13" customWidth="1" min="52" max="52"/>
     <col width="20" customWidth="1" min="53" max="53"/>
+    <col width="14" customWidth="1" min="54" max="54"/>
+    <col width="10" customWidth="1" min="55" max="55"/>
+    <col width="13" customWidth="1" min="56" max="56"/>
+    <col width="31" customWidth="1" min="57" max="57"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17389,6 +18785,26 @@
           <t>hand_capture_name</t>
         </is>
       </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>attack_count</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>hits_air</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>hits_ground</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>targets_all</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17548,6 +18964,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BB2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17707,6 +19141,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17863,6 +19315,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18029,6 +19499,24 @@
           <t>Giga Spikes</t>
         </is>
       </c>
+      <c r="BB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18182,6 +19670,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18333,6 +19839,24 @@
       <c r="AZ7" t="inlineStr">
         <is>
           <t>map</t>
+        </is>
+      </c>
+      <c r="BB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
     </row>
@@ -18481,6 +20005,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18630,6 +20172,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18789,6 +20349,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BB10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -18948,6 +20526,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -19102,6 +20698,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BB12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -19258,6 +20872,24 @@
       <c r="AZ13" t="inlineStr">
         <is>
           <t>map</t>
+        </is>
+      </c>
+      <c r="BB13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
     </row>
@@ -19428,6 +21060,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BB14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -19587,6 +21237,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BB15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -19746,6 +21414,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BB16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -19905,6 +21591,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BB17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -20059,6 +21763,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BB18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -20218,6 +21940,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BB19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -20367,6 +22107,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BB20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -20568,9 +22326,27 @@
           <t>Brahma Fix It Shop</t>
         </is>
       </c>
+      <c r="BB22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BA22"/>
+  <autoFilter ref="A1:BE22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20581,7 +22357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB21"/>
+  <dimension ref="A1:BF21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -20638,6 +22414,10 @@
     <col width="22" customWidth="1" min="52" max="52"/>
     <col width="48" customWidth="1" min="53" max="53"/>
     <col width="13" customWidth="1" min="54" max="54"/>
+    <col width="14" customWidth="1" min="55" max="55"/>
+    <col width="10" customWidth="1" min="56" max="56"/>
+    <col width="13" customWidth="1" min="57" max="57"/>
+    <col width="31" customWidth="1" min="58" max="58"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20911,6 +22691,26 @@
           <t>cost_source</t>
         </is>
       </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>attack_count</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>hits_air</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>hits_ground</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>targets_all</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21070,6 +22870,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21224,6 +23042,24 @@
       <c r="BB3" t="inlineStr">
         <is>
           <t>map</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
     </row>
@@ -21385,6 +23221,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -21544,6 +23398,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21698,6 +23570,24 @@
       <c r="BB6" t="inlineStr">
         <is>
           <t>map</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
     </row>
@@ -21854,6 +23744,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22008,6 +23916,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22162,6 +24088,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22321,6 +24265,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -22506,6 +24468,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BC11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -22662,6 +24642,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -22816,6 +24814,24 @@
       <c r="BB13" t="inlineStr">
         <is>
           <t>map</t>
+        </is>
+      </c>
+      <c r="BC13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
     </row>
@@ -22972,6 +24988,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BC14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -23128,6 +25162,24 @@
       <c r="BB15" t="inlineStr">
         <is>
           <t>map</t>
+        </is>
+      </c>
+      <c r="BC15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
     </row>
@@ -23224,6 +25276,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BC16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -23378,6 +25448,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BC17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -23564,6 +25652,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BC18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -23715,6 +25821,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BC19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -23885,6 +26009,24 @@
       <c r="BB20" t="inlineStr">
         <is>
           <t>map</t>
+        </is>
+      </c>
+      <c r="BC20" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
     </row>
@@ -24030,9 +26172,27 @@
           <t>map</t>
         </is>
       </c>
+      <c r="BC21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BB21"/>
+  <autoFilter ref="A1:BF21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -41715,7 +43875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:BC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -41769,6 +43929,10 @@
     <col width="22" customWidth="1" min="49" max="49"/>
     <col width="14" customWidth="1" min="50" max="50"/>
     <col width="13" customWidth="1" min="51" max="51"/>
+    <col width="14" customWidth="1" min="52" max="52"/>
+    <col width="10" customWidth="1" min="53" max="53"/>
+    <col width="13" customWidth="1" min="54" max="54"/>
+    <col width="31" customWidth="1" min="55" max="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -42027,6 +44191,26 @@
           <t>cost_source</t>
         </is>
       </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>attack_count</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>hits_air</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>hits_ground</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>targets_all</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -42166,6 +44350,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AZ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -42305,6 +44507,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AZ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -42446,6 +44666,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AZ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -42585,6 +44823,24 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>map</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
     </row>
@@ -42731,6 +44987,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AZ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -42880,6 +45154,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AZ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -43014,6 +45306,24 @@
       <c r="AY8" t="inlineStr">
         <is>
           <t>map</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
     </row>
@@ -43150,6 +45460,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AZ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -43294,6 +45622,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AZ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -43438,6 +45784,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AZ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -43577,6 +45941,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AZ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -43713,6 +46095,24 @@
       <c r="AY13" t="inlineStr">
         <is>
           <t>map</t>
+        </is>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
     </row>
@@ -43849,6 +46249,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AZ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -43990,6 +46408,24 @@
       <c r="AY15" t="inlineStr">
         <is>
           <t>map</t>
+        </is>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
     </row>
@@ -44143,6 +46579,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AZ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -44284,6 +46738,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AZ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -44455,6 +46927,24 @@
       <c r="AY18" t="inlineStr">
         <is>
           <t>map</t>
+        </is>
+      </c>
+      <c r="AZ18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
     </row>
@@ -44593,6 +47083,24 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AZ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -44732,9 +47240,27 @@
           <t>map</t>
         </is>
       </c>
+      <c r="AZ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AY20"/>
+  <autoFilter ref="A1:BC20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/skibi-data.xlsx
+++ b/skibi-data.xlsx
@@ -30,23 +30,23 @@
     <sheet name="waves" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'arcane'!$A$1:$AZ$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'arcane'!$A$1:$BD$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'armour_matrix'!$A$1:$F$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'bosses'!$A$1:$O$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'caster_dps'!$A$1:$L$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'game_modes'!$A$1:$I$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'hero_ranking'!$A$1:$K$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'heroes'!$A$1:$H$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'military'!$A$1:$BC$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'military'!$A$1:$BG$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'minigame_items'!$A$1:$D$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'minigame_readings'!$A$1:$G$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'minigames'!$A$1:$I$80</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'other_towers'!$A$1:$AW$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'ranger'!$A$1:$AZ$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'royal_family'!$A$1:$BG$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'scarlet_knight'!$A$1:$AZ$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'specialist'!$A$1:$BE$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'tempest'!$A$1:$BF$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'other_towers'!$A$1:$AY$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'ranger'!$A$1:$BD$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'royal_family'!$A$1:$BK$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'scarlet_knight'!$A$1:$BD$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'specialist'!$A$1:$BI$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'tempest'!$A$1:$BJ$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'tower_traits'!$A$1:$I$113</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'wave_modifiers'!$A$1:$D$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'wave_traits'!$A$1:$K$51</definedName>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ18"/>
+  <dimension ref="A1:BD18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -518,6 +518,10 @@
     <col width="10" customWidth="1" min="50" max="50"/>
     <col width="13" customWidth="1" min="51" max="51"/>
     <col width="31" customWidth="1" min="52" max="52"/>
+    <col width="31" customWidth="1" min="53" max="53"/>
+    <col width="14" customWidth="1" min="54" max="54"/>
+    <col width="15" customWidth="1" min="55" max="55"/>
+    <col width="12" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -781,6 +785,26 @@
           <t>targets_all</t>
         </is>
       </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>atk1_targets</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>atk2_targets</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dps_vs_ground</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dps_vs_air</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -881,6 +905,11 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -983,6 +1012,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>39.8</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1083,6 +1123,11 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1185,6 +1230,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>47.3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1287,6 +1343,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>48.6</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1387,6 +1454,11 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1561,6 +1633,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>58</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1661,6 +1744,11 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1823,6 +1911,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>710</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>710</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1985,6 +2084,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>649.4</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>649.4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2087,6 +2197,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC13" t="n">
+        <v>857.1</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>857.1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2189,6 +2310,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC14" t="n">
+        <v>1356.7</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1356.7</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2468,7 +2600,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AZ18"/>
+  <autoFilter ref="A1:BD18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5882,7 +6014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW11"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5934,6 +6066,8 @@
     <col width="27" customWidth="1" min="47" max="47"/>
     <col width="14" customWidth="1" min="48" max="48"/>
     <col width="13" customWidth="1" min="49" max="49"/>
+    <col width="15" customWidth="1" min="50" max="50"/>
+    <col width="12" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6182,6 +6316,16 @@
           <t>cost_source</t>
         </is>
       </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dps_vs_ground</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dps_vs_air</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7415,7 +7559,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AW11"/>
+  <autoFilter ref="A1:AY11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7426,7 +7570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:BD20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7481,6 +7625,10 @@
     <col width="10" customWidth="1" min="50" max="50"/>
     <col width="13" customWidth="1" min="51" max="51"/>
     <col width="31" customWidth="1" min="52" max="52"/>
+    <col width="31" customWidth="1" min="53" max="53"/>
+    <col width="14" customWidth="1" min="54" max="54"/>
+    <col width="15" customWidth="1" min="55" max="55"/>
+    <col width="12" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7744,6 +7892,26 @@
           <t>targets_all</t>
         </is>
       </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>atk1_targets</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>atk2_targets</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dps_vs_ground</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dps_vs_air</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7906,6 +8074,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>46.8</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8068,6 +8247,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>345</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>345</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8235,6 +8425,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>142.5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8399,6 +8600,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>1252.1</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1252.1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8563,6 +8775,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>274</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>274</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8726,6 +8949,17 @@
         <is>
           <t>air,enemies,ground,nonancient</t>
         </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>1007</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1007</v>
       </c>
     </row>
     <row r="8">
@@ -8889,6 +9123,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>2536.9</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>2536.9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9046,6 +9291,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>113</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9213,6 +9469,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
+        <v>542.5</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>542.5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9380,6 +9647,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>3362.1</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>3362.1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9543,6 +9821,17 @@
         <is>
           <t>air,enemies,ground,nonancient</t>
         </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>322.2</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>322.2</v>
       </c>
     </row>
     <row r="13">
@@ -9711,6 +10000,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC13" t="n">
+        <v>1064.4</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1064.4</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9873,6 +10173,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC14" t="n">
+        <v>975</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>975</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -10035,6 +10346,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC15" t="n">
+        <v>689.3</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>689.3</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10199,6 +10521,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC16" t="n">
+        <v>1883.4</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1883.4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -10363,6 +10696,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC17" t="n">
+        <v>4874.8</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>4874.8</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10527,6 +10871,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC18" t="n">
+        <v>14960.4</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>14960.4</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10687,6 +11042,17 @@
         <is>
           <t>air,enemies,ground,nonancient</t>
         </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC19" t="n">
+        <v>4041.3</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4041.3</v>
       </c>
     </row>
     <row r="20">
@@ -10855,9 +11221,20 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC20" t="n">
+        <v>6926.1</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>6926.1</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AZ20"/>
+  <autoFilter ref="A1:BD20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10868,7 +11245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG23"/>
+  <dimension ref="A1:BK23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10930,6 +11307,10 @@
     <col width="10" customWidth="1" min="57" max="57"/>
     <col width="13" customWidth="1" min="58" max="58"/>
     <col width="31" customWidth="1" min="59" max="59"/>
+    <col width="31" customWidth="1" min="60" max="60"/>
+    <col width="24" customWidth="1" min="61" max="61"/>
+    <col width="15" customWidth="1" min="62" max="62"/>
+    <col width="12" customWidth="1" min="63" max="63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11228,6 +11609,26 @@
           <t>targets_all</t>
         </is>
       </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>atk1_targets</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>atk2_targets</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dps_vs_ground</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dps_vs_air</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11405,6 +11806,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BJ2" t="n">
+        <v>2147.1</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>2147.1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11577,6 +11989,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BJ3" t="n">
+        <v>158.6</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>158.6</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11714,6 +12137,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BJ4" t="n">
+        <v>380.7</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>380.7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11899,6 +12333,17 @@
         <is>
           <t>air,enemies,ground,nonancient</t>
         </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BJ5" t="n">
+        <v>412</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>412</v>
       </c>
     </row>
     <row r="6">
@@ -12077,6 +12522,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1580</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1580</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12252,6 +12708,17 @@
         <is>
           <t>air,enemies,ground,nonancient</t>
         </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1735</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1735</v>
       </c>
     </row>
     <row r="8">
@@ -12457,6 +12924,22 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>air,enemies,nonancient</t>
+        </is>
+      </c>
+      <c r="BJ8" t="n">
+        <v>4322.2</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>4823.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12629,6 +13112,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BJ9" t="n">
+        <v>158.2</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>158.2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12806,6 +13300,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BJ10" t="n">
+        <v>521.9</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>521.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12980,6 +13485,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1733.5</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1733.5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -13153,6 +13669,17 @@
         <is>
           <t>air,enemies,ground,nonancient</t>
         </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BJ12" t="n">
+        <v>7063</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>7063</v>
       </c>
     </row>
     <row r="13">
@@ -13336,6 +13863,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BJ13" t="n">
+        <v>600</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>600</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13508,6 +14046,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BJ14" t="n">
+        <v>2677.3</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>2677.3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13685,6 +14234,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BJ15" t="n">
+        <v>324</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>324</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13862,6 +14422,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BJ16" t="n">
+        <v>1247.9</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>1247.9</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -14030,6 +14601,17 @@
         <is>
           <t>air,enemies,ground,nonancient</t>
         </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1193.5</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>1193.5</v>
       </c>
     </row>
     <row r="18">
@@ -14198,6 +14780,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BJ18" t="n">
+        <v>4068.7</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>4068.7</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -14362,6 +14955,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BJ19" t="n">
+        <v>4268.8</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>4268.8</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -14529,6 +15133,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BJ20" t="n">
+        <v>5005.6</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>5005.6</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -14706,6 +15321,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BJ21" t="n">
+        <v>4910</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>4910</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -14905,6 +15531,22 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>air,enemies,nonancient</t>
+        </is>
+      </c>
+      <c r="BJ22" t="n">
+        <v>3333.3</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>3333.3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -14960,7 +15602,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BG23"/>
+  <autoFilter ref="A1:BK23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14971,7 +15613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ21"/>
+  <dimension ref="A1:BD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -15026,6 +15668,10 @@
     <col width="10" customWidth="1" min="50" max="50"/>
     <col width="13" customWidth="1" min="51" max="51"/>
     <col width="31" customWidth="1" min="52" max="52"/>
+    <col width="31" customWidth="1" min="53" max="53"/>
+    <col width="14" customWidth="1" min="54" max="54"/>
+    <col width="15" customWidth="1" min="55" max="55"/>
+    <col width="12" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15289,6 +15935,26 @@
           <t>targets_all</t>
         </is>
       </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>atk1_targets</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>atk2_targets</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dps_vs_ground</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dps_vs_air</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15446,6 +16112,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>349.8</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>349.8</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15604,6 +16281,17 @@
         <is>
           <t>air,enemies,ground,nonancient</t>
         </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>107.3</v>
       </c>
     </row>
     <row r="4">
@@ -15772,6 +16460,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>715.9</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>715.9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15879,6 +16578,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>217.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>217.5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16046,6 +16756,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>206.6</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>206.6</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16213,6 +16934,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>535.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>535.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16370,6 +17102,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>152.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16532,6 +17275,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>220</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>220</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16699,6 +17453,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
+        <v>300</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -16866,6 +17631,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>800</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>800</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -16973,6 +17749,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -17135,6 +17922,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC13" t="n">
+        <v>469.2</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>469.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17299,6 +18097,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC14" t="n">
+        <v>317.5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>317.5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17463,6 +18272,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC15" t="n">
+        <v>811.2</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>811.2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -17630,6 +18450,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC16" t="n">
+        <v>470</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>470</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -17797,6 +18628,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC17" t="n">
+        <v>429</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>429</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -17959,6 +18801,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC18" t="n">
+        <v>963.5</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>963.5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -18118,6 +18971,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC19" t="n">
+        <v>2418.8</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>2418.8</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -18281,6 +19145,17 @@
         <is>
           <t>air,enemies,ground,nonancient</t>
         </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC20" t="n">
+        <v>7327.7</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>7327.7</v>
       </c>
     </row>
     <row r="21">
@@ -18444,9 +19319,20 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BC21" t="n">
+        <v>13333.3</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>13333.3</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AZ21"/>
+  <autoFilter ref="A1:BD21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18457,7 +19343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE22"/>
+  <dimension ref="A1:BI22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -18517,6 +19403,10 @@
     <col width="10" customWidth="1" min="55" max="55"/>
     <col width="13" customWidth="1" min="56" max="56"/>
     <col width="31" customWidth="1" min="57" max="57"/>
+    <col width="31" customWidth="1" min="58" max="58"/>
+    <col width="24" customWidth="1" min="59" max="59"/>
+    <col width="15" customWidth="1" min="60" max="60"/>
+    <col width="12" customWidth="1" min="61" max="61"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18805,6 +19695,26 @@
           <t>targets_all</t>
         </is>
       </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>atk1_targets</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>atk2_targets</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dps_vs_ground</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dps_vs_air</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18982,6 +19892,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BH2" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>56.9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19159,6 +20080,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BH3" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>105.5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19333,6 +20265,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BH4" t="n">
+        <v>246.7</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>246.7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19517,6 +20460,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BH5" t="n">
+        <v>477.8</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>477.8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19688,6 +20642,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BH6" t="n">
+        <v>781.3</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>781.3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19858,6 +20823,17 @@
         <is>
           <t>air,enemies,ground,nonancient</t>
         </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BH7" t="n">
+        <v>1243.1</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1243.1</v>
       </c>
     </row>
     <row r="8">
@@ -20023,6 +20999,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BH8" t="n">
+        <v>1506.1</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1506.1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20190,6 +21177,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BH9" t="n">
+        <v>176.6</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>176.6</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20367,6 +21365,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BH10" t="n">
+        <v>318.8</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>318.8</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -20544,6 +21553,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BH11" t="n">
+        <v>1925</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1925</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -20716,6 +21736,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BH12" t="n">
+        <v>1417.5</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1417.5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -20891,6 +21922,17 @@
         <is>
           <t>air,enemies,ground,nonancient</t>
         </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BH13" t="n">
+        <v>2230</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2230</v>
       </c>
     </row>
     <row r="14">
@@ -21078,6 +22120,19 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>air,enemies,nonancient</t>
+        </is>
+      </c>
+      <c r="BH14" t="n">
+        <v>1998.7</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -21255,6 +22310,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BH15" t="n">
+        <v>641.9</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>641.9</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -21432,6 +22498,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BH16" t="n">
+        <v>2257</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2257</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -21609,6 +22686,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BH17" t="n">
+        <v>1059.2</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>1059.2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -21781,6 +22869,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BH18" t="n">
+        <v>1802.5</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>1802.5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -21958,6 +23057,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BH19" t="n">
+        <v>3975.8</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>3975.8</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -22125,6 +23235,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BH20" t="n">
+        <v>7035.7</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>7035.7</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -22344,9 +23465,20 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BH22" t="n">
+        <v>210.1</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>210.1</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BE22"/>
+  <autoFilter ref="A1:BI22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22357,7 +23489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF21"/>
+  <dimension ref="A1:BJ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -22418,6 +23550,10 @@
     <col width="10" customWidth="1" min="56" max="56"/>
     <col width="13" customWidth="1" min="57" max="57"/>
     <col width="31" customWidth="1" min="58" max="58"/>
+    <col width="31" customWidth="1" min="59" max="59"/>
+    <col width="27" customWidth="1" min="60" max="60"/>
+    <col width="15" customWidth="1" min="61" max="61"/>
+    <col width="12" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22711,6 +23847,26 @@
           <t>targets_all</t>
         </is>
       </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>atk1_targets</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>atk2_targets</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dps_vs_ground</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dps_vs_air</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22888,6 +24044,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BI2" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>81.2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23061,6 +24228,17 @@
         <is>
           <t>air,enemies,ground,nonancient</t>
         </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BI3" t="n">
+        <v>363.2</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>363.2</v>
       </c>
     </row>
     <row r="4">
@@ -23239,6 +24417,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BI4" t="n">
+        <v>132</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>132</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23416,6 +24605,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BI5" t="n">
+        <v>525</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>525</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23589,6 +24789,17 @@
         <is>
           <t>air,enemies,ground,nonancient</t>
         </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BI6" t="n">
+        <v>309.6</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>309.6</v>
       </c>
     </row>
     <row r="7">
@@ -23762,6 +24973,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BI7" t="n">
+        <v>1562.5</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1562.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23934,6 +25156,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BI8" t="n">
+        <v>813</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>813</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24106,6 +25339,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BI9" t="n">
+        <v>265.5</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>265.5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24283,6 +25527,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BI10" t="n">
+        <v>253.7</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>253.7</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24486,6 +25741,22 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>air,enemies,nonancient</t>
+        </is>
+      </c>
+      <c r="BI11" t="n">
+        <v>6254.3</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>3273.1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24660,6 +25931,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BI12" t="n">
+        <v>986</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>986</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24833,6 +26115,17 @@
         <is>
           <t>air,enemies,ground,nonancient</t>
         </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BI13" t="n">
+        <v>1369.3</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1369.3</v>
       </c>
     </row>
     <row r="14">
@@ -25006,6 +26299,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BI14" t="n">
+        <v>1783</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1783</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -25181,6 +26485,17 @@
         <is>
           <t>air,enemies,ground,nonancient</t>
         </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BI15" t="n">
+        <v>839</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>839</v>
       </c>
     </row>
     <row r="16">
@@ -25294,6 +26609,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BI16" t="n">
+        <v>316.7</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>316.7</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -25466,6 +26792,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BI17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -25670,6 +27007,22 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>air,enemies,nonancient</t>
+        </is>
+      </c>
+      <c r="BI18" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>2000</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -25839,6 +27192,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BI19" t="n">
+        <v>16329.2</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>16329.2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -26028,6 +27392,19 @@
         <is>
           <t>air,enemies,ground,nonancient</t>
         </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>air,enemies,nonancient</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BJ20" t="n">
+        <v>21721.5</v>
       </c>
     </row>
     <row r="21">
@@ -26190,9 +27567,20 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BI21" t="n">
+        <v>897</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>897</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BF21"/>
+  <autoFilter ref="A1:BJ21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -43875,7 +45263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC20"/>
+  <dimension ref="A1:BG20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -43933,6 +45321,10 @@
     <col width="10" customWidth="1" min="53" max="53"/>
     <col width="13" customWidth="1" min="54" max="54"/>
     <col width="31" customWidth="1" min="55" max="55"/>
+    <col width="31" customWidth="1" min="56" max="56"/>
+    <col width="24" customWidth="1" min="57" max="57"/>
+    <col width="15" customWidth="1" min="58" max="58"/>
+    <col width="12" customWidth="1" min="59" max="59"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -44211,6 +45603,26 @@
           <t>targets_all</t>
         </is>
       </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>atk1_targets</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>atk2_targets</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dps_vs_ground</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dps_vs_air</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -44368,6 +45780,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BF2" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>93.5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -44525,6 +45948,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BF3" t="n">
+        <v>779.3</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>779.3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -44684,6 +46118,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BF4" t="n">
+        <v>218.6</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>218.6</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -44842,6 +46287,17 @@
         <is>
           <t>air,enemies,ground,nonancient</t>
         </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BF5" t="n">
+        <v>1825.3</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>1825.3</v>
       </c>
     </row>
     <row r="6">
@@ -45005,6 +46461,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BF6" t="n">
+        <v>175</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>175</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -45172,6 +46639,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BF7" t="n">
+        <v>2062.6</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>2062.6</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -45325,6 +46803,17 @@
         <is>
           <t>air,enemies,ground,nonancient</t>
         </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BF8" t="n">
+        <v>3156</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>3156</v>
       </c>
     </row>
     <row r="9">
@@ -45478,6 +46967,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BF9" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>81.7</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -45640,6 +47140,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BF10" t="n">
+        <v>363</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>363</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -45802,6 +47313,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BF11" t="n">
+        <v>2007.5</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2007.5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -45959,6 +47481,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BF12" t="n">
+        <v>2380</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>2380</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -46114,6 +47647,17 @@
         <is>
           <t>air,enemies,ground,nonancient</t>
         </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BF13" t="n">
+        <v>9026</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>9026</v>
       </c>
     </row>
     <row r="14">
@@ -46267,6 +47811,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BF14" t="n">
+        <v>4925.8</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>4925.8</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -46427,6 +47982,17 @@
         <is>
           <t>air,enemies,ground,nonancient</t>
         </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BF15" t="n">
+        <v>727</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>727</v>
       </c>
     </row>
     <row r="16">
@@ -46597,6 +48163,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BF16" t="n">
+        <v>2118.7</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>2118.7</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -46756,6 +48333,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BF17" t="n">
+        <v>1807.6</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1807.6</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -46946,6 +48534,22 @@
         <is>
           <t>air,enemies,ground,nonancient</t>
         </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>air,enemies,nonancient</t>
+        </is>
+      </c>
+      <c r="BF18" t="n">
+        <v>1630.5</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>2697.5</v>
       </c>
     </row>
     <row r="19">
@@ -47101,6 +48705,17 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BF19" t="n">
+        <v>5275</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>5275</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -47258,9 +48873,20 @@
           <t>air,enemies,ground,nonancient</t>
         </is>
       </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>air,enemies,ground,nonancient</t>
+        </is>
+      </c>
+      <c r="BF20" t="n">
+        <v>8905.6</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>8905.6</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BC20"/>
+  <autoFilter ref="A1:BG20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
